--- a/inputs/fr/demo_national_input.xlsx
+++ b/inputs/fr/demo_national_input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr saveExternalLinkValues="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\Nutrition\inputs\fr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD7EAF46-FE61-4A4C-8646-EE7D7EBA4DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72442774-22DF-4D56-B68C-F88F4C0D9299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3670" windowWidth="19200" windowHeight="6530" tabRatio="961" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="961" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Données pop de l'année de ref" sheetId="1" r:id="rId1"/>
@@ -5669,7 +5669,7 @@
       <c r="A63" s="4"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="RKduuUz7h+gkU2aLbLYIKKMCZB6LzHZx/SFcicVJGRv3gr2nnUJMP7tKBBfOWrTc5A9+cAyhk1Qz7cLB1onr1A==" saltValue="epbmugzd7zCXGWZMRBizHQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="9gizxvDRtYJ2FicmJhOKv83Ey7zWoZtKDQrWclH69SgbPQEEdHLx7ucy78BBxJ1AoOb33Jxc+BKJxuHnAGDETA==" saltValue="I9r4kuTxyWtQt8/VibQSuA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -5694,7 +5694,7 @@
     <col min="8" max="16384" width="14.453125" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A1" s="41" t="s">
         <v>160</v>
       </c>
@@ -6593,7 +6593,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="bxW8vv3C2OZ+AXw4ALsR2rGjRinI7pqS9uEVCYNKgPIUEZ2S66tqKs5tdX1bhsoxkdRNBxlNOjiMPbZNaNWqyQ==" saltValue="HRkyOEyloXPSZVkcbEDyuw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="1cNA82dRDUoGyjy18oPTztDeW5Ltx/q51bJWcJZ2NB7tvRQFGuUJG1aSiSgDC1tZp15Mp7CfWZa8BKw07WHcBg==" saltValue="8aQ6W9DtGs1nfgVusfX+kA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D39">
     <sortCondition ref="A2:A39"/>
   </sortState>
@@ -6752,7 +6752,7 @@
       <c r="C20" s="67"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="f/9N814saij6KNMBE2echQAElmzCOga+ZT7cwx+yQUTGrVJ+GcwLGtbejEK9RauN+ioYw5wMn6/vUgBMqNDpCA==" saltValue="zuCGjagqr9Gt5wnQwlP2Mw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="GkjSDQ98pdAkZnrMUNQ855mzC5h6/ybZ1WqXno0/hQkw0xyqunK19EDh8EmNmaOq/1M+6Q8sh+CziX/Vmbs/Aw==" saltValue="eULBhS42/Cju0tqggeHTRg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -6847,7 +6847,7 @@
       <c r="A19" s="35"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="aEmTqOS5L8DC31QkYcu9BlKmoPANE2YM8AidKdimJ7eXH39Jeken0coEyX5bJUgO2Dbp0ZMA5qMhF0WsiAiQFA==" saltValue="M1elYcr10ADzUNVzjlO+rA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="dEa9AMosXGnfo+xUM1XqTAXVNKimgo5h2k9riNOZ7PlFqCp4hahbb7jsZoukvn+bzDABO/azBrw+tAPr7AENOQ==" saltValue="05WfxP3MQ7mALZnmuXyPeA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -6957,7 +6957,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="wbU1tSF8R49BzGDPU5dN4OabhtQia/TrA90zLHKk7UqUqHUr8RhBhl425d3r9ByvKJndxvZ6B+nfjvvpIotT0Q==" saltValue="sVxDPXROvGKIdhsIsSUPFw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="HWAGg1wLQHjxu69Kqi9QM/Ph69ppaTMBWlKQU0DB7PIqTujOFU0zMcG2cpjIdaUn35jlwVad7lfEtkvtRW3d6w==" saltValue="dqwe27qUkQuvoMc5gPIETg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -8713,7 +8713,7 @@
       <c r="B40" s="9"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Fi2m1Ib7UhE9sUORkm0JYLgDTGVW7L2/IYSseVvXFiWv6fChI1GE4IGZz/I8sAV1NiLzRwH76h71jyD6sN4ktA==" saltValue="qQp4lcq36Fe/gpEhmAdmbQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="OEPP47uYCytcDOyxdHT++Ib3u4UyhaUpe6HLX1BecDyJtxRbDqBkGrskM+LnMAyt1aG37SFwlnMAfsvhSSN4Fw==" saltValue="1Ady6J5HYVYaCOz2OmSC8g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B15:O22">
     <sortCondition ref="B15:B22"/>
   </sortState>
@@ -8748,7 +8748,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="4uj78WsRaJjf4GeaynWwzq7azHESDpuZRjrvx7cSKejZerue+Og0jgvENx5yRQBE0bWDPqrOw5NXzOsngx0moQ==" saltValue="uUkVzROu16mwhfWn+mY1Og==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="6SeBS2Ee+ZxIBL4jIYI/QaRRnf8C1j6ZLnireDVTcrXPrtLwCpSmIm3J/sRNlChyMWTwFOj1Nje4AMf7MwZ/iw==" saltValue="ZzplEobGDr8VgWZCgL99YQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8948,7 +8948,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="C5l98D6VEQOdetf1dYtz9EJgOdLmxvgb9cPFhrwy2ZG3KyNpp8WgC4yOy2xK8atCjyoqCllLbv7GxikV57DXIg==" saltValue="oyJCw0jSG9t2IWlOfSSy+w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="SgYqDVeG71kbEuerYsLQ9+r2iqc7OrpcTtS5SaoTn4+vVimT6T7cw1G7Ji4LkeIs9d3eL5eIN4zrFoHzXs1F3g==" saltValue="qsGbYg+hn/ja+eJpd4mmdg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -10757,7 +10757,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Q8F7IBfBCNEgdH8IDJYuo8AkiXIdVq/Y0hTG3XnptX1Jklz9te9SMvp0f+46wUGT5ofr62Md/sR94Wr7b6EGug==" saltValue="wlSWcqVeNc/fo4dRo0AKmA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="zvRXivAncZzn86RaTlxZ4PBo5XQXFheyWKsW5JQZRV0LPDuaCyM4qxFy8hiA0nQ9NfDC27GHss3TlagtVMqtLw==" saltValue="sTrhfpGVluFuhB0fTCvXIg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -11519,7 +11519,7 @@
       <c r="K39" s="101"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="pNvL0NwtLKkoaLpntDC5CW6q+UNLhbbHo2rrhk17rFEfSh5HkooBp9a9LkFk/G2yFDLfSTMFg62GcJAI4Q6Z/A==" saltValue="Iilf22a40B7Bl50ynvTvFA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="6UipioMbckY2rfKhyhIKuqN/qW126A+QyADgvP/LpNioFod0ztjd4xDP4SalOTiGe6ofOHOSEko2m5/WrzkC9w==" saltValue="K/lMqnC8Gk/1Bmp+qPJHBQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -11888,7 +11888,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Lcruk+eWbyybrs0Ld/p8scQUwTwRscdtbIdm+XEidWdbZ35KIoSUe+9rzyIU6AVJTIR65oEQUIWZaHne5zlDNQ==" saltValue="+bIBcvMeqekF7C4ZJxFL1w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ipkqVGNWmTpZ/jeGR0Kjvi5HtuADpVe4RBpHeq07hmsKZBZ5qsIrgrBkV0R0UbJnHJBL1r24CGKMlIh0KIc0GA==" saltValue="es4h9pfUy7L3yiN3RoD7MA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -12972,7 +12972,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="gPmMmKjNGBxxAQQ5W+ly8PhiOvjJXXfTvdiUjCPpO3jCqSqb9O96gGmZfVjnonjY1mJO4465DUP3aixikW9kmA==" saltValue="ohIp5lUcQALrgR9e7vkXoQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="bmf+EGasAIV7X69KUm5rUC0BSe4T7JS0T/xq1MAActjYVPamBZPzNV63lzQIBASezGjykP2VkLT0SydWmk/z/Q==" saltValue="GgxCBjGDkJz6JopRZnKVRA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <conditionalFormatting sqref="B2:I16 B17:C17 E17:I17 B18:I40">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>$A2=""</formula>
@@ -13101,9 +13101,7 @@
         <v>153</v>
       </c>
       <c r="D5" s="102">
-        <f>IFERROR((MIN(1,1.56*'Dist. l''allaitement maternel'!$C$2)/(1-MIN(1,1.56*'Dist. l''allaitement maternel'!$C$2))) /
-('Dist. l''allaitement maternel'!$C$2/(1-'Dist. l''allaitement maternel'!$C$2)), 1.56)</f>
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="E5" s="102">
         <v>1</v>
@@ -13124,9 +13122,7 @@
         <v>154</v>
       </c>
       <c r="D6" s="102">
-        <f>IFERROR((MIN(1,1.56*'Dist. l''allaitement maternel'!$C$2)/(1-MIN(1,1.56*'Dist. l''allaitement maternel'!$C$2))) /
-('Dist. l''allaitement maternel'!$C$2/(1-'Dist. l''allaitement maternel'!$C$2)), 1.56)</f>
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="E6" s="102">
         <v>1</v>
@@ -13173,9 +13169,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="102">
-        <f>IFERROR((MIN(1,1.56*'Dist. l''allaitement maternel'!$D$2)/(1-MIN(1,1.56*'Dist. l''allaitement maternel'!$D$2))) /
-('Dist. l''allaitement maternel'!$D$2/(1-'Dist. l''allaitement maternel'!$D$2)), 1.56)</f>
-        <v>2.8134491663553263</v>
+        <v>1.73</v>
       </c>
       <c r="F8" s="102">
         <v>1</v>
@@ -13196,9 +13190,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="102">
-        <f>IFERROR((MIN(1,1.56*'Dist. l''allaitement maternel'!$D$2)/(1-MIN(1,1.56*'Dist. l''allaitement maternel'!$D$2))) /
-('Dist. l''allaitement maternel'!$D$2/(1-'Dist. l''allaitement maternel'!$D$2)), 1.56)</f>
-        <v>2.8134491663553263</v>
+        <v>1.73</v>
       </c>
       <c r="F9" s="102">
         <v>1</v>
@@ -14229,9 +14221,7 @@
         <v>153</v>
       </c>
       <c r="D58" s="102">
-        <f>IFERROR((MIN(1,1.37*'Dist. l''allaitement maternel'!$C$2)/(1-MIN(1,1.37*'Dist. l''allaitement maternel'!$C$2))) /
-('Dist. l''allaitement maternel'!$C$2/(1-'Dist. l''allaitement maternel'!$C$2)), 1.37)</f>
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="E58" s="102">
         <f t="shared" si="1"/>
@@ -14256,9 +14246,7 @@
         <v>154</v>
       </c>
       <c r="D59" s="102">
-        <f>IFERROR((MIN(1,1.37*'Dist. l''allaitement maternel'!$C$2)/(1-MIN(1,1.37*'Dist. l''allaitement maternel'!$C$2))) /
-('Dist. l''allaitement maternel'!$C$2/(1-'Dist. l''allaitement maternel'!$C$2)), 1.37)</f>
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="E59" s="102">
         <f t="shared" si="1"/>
@@ -14315,9 +14303,7 @@
         <v>1</v>
       </c>
       <c r="E61" s="102">
-        <f>IFERROR((MIN(1,1.37*'Dist. l''allaitement maternel'!$D$2)/(1-MIN(1,1.37*'Dist. l''allaitement maternel'!$D$2))) /
-('Dist. l''allaitement maternel'!$D$2/(1-'Dist. l''allaitement maternel'!$D$2)), 1.37)</f>
-        <v>1.9415046815127641</v>
+        <v>1.35</v>
       </c>
       <c r="F61" s="102">
         <f t="shared" si="2"/>
@@ -14342,9 +14328,7 @@
         <v>1</v>
       </c>
       <c r="E62" s="102">
-        <f>IFERROR((MIN(1,1.37*'Dist. l''allaitement maternel'!$D$2)/(1-MIN(1,1.37*'Dist. l''allaitement maternel'!$D$2))) /
-('Dist. l''allaitement maternel'!$D$2/(1-'Dist. l''allaitement maternel'!$D$2)), 1.37)</f>
-        <v>1.9415046815127641</v>
+        <v>1.35</v>
       </c>
       <c r="F62" s="102">
         <f t="shared" si="2"/>
@@ -15574,9 +15558,7 @@
         <v>153</v>
       </c>
       <c r="D111" s="102">
-        <f>IFERROR((MIN(1,1.77*'Dist. l''allaitement maternel'!$C$2)/(1-MIN(1,1.77*'Dist. l''allaitement maternel'!$C$2))) /
-('Dist. l''allaitement maternel'!$C$2/(1-'Dist. l''allaitement maternel'!$C$2)), 1.77)</f>
-        <v>1.77</v>
+        <v>2.11</v>
       </c>
       <c r="E111" s="102">
         <f t="shared" si="8"/>
@@ -15601,9 +15583,7 @@
         <v>154</v>
       </c>
       <c r="D112" s="102">
-        <f>IFERROR((MIN(1,1.77*'Dist. l''allaitement maternel'!$C$2)/(1-MIN(1,1.77*'Dist. l''allaitement maternel'!$C$2))) /
-('Dist. l''allaitement maternel'!$C$2/(1-'Dist. l''allaitement maternel'!$C$2)), 1.77)</f>
-        <v>1.77</v>
+        <v>2.11</v>
       </c>
       <c r="E112" s="102">
         <f t="shared" si="8"/>
@@ -15660,9 +15640,7 @@
         <v>1</v>
       </c>
       <c r="E114" s="102">
-        <f>IFERROR((MIN(1,1.77*'Dist. l''allaitement maternel'!$D$2)/(1-MIN(1,1.77*'Dist. l''allaitement maternel'!$D$2))) /
-('Dist. l''allaitement maternel'!$D$2/(1-'Dist. l''allaitement maternel'!$D$2)), 1.77)</f>
-        <v>4.5688105335991329</v>
+        <v>2.11</v>
       </c>
       <c r="F114" s="102">
         <f t="shared" si="9"/>
@@ -15687,9 +15665,7 @@
         <v>1</v>
       </c>
       <c r="E115" s="102">
-        <f>IFERROR((MIN(1,1.77*'Dist. l''allaitement maternel'!$D$2)/(1-MIN(1,1.77*'Dist. l''allaitement maternel'!$D$2))) /
-('Dist. l''allaitement maternel'!$D$2/(1-'Dist. l''allaitement maternel'!$D$2)), 1.77)</f>
-        <v>4.5688105335991329</v>
+        <v>2.11</v>
       </c>
       <c r="F115" s="102">
         <f t="shared" si="9"/>
@@ -16791,14 +16767,38 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Ri7VWV//DDUQaTb8yO9+eskdyslwkZTO6DKeR1Fximp/jqXtzHGn5HAPeynuw+UaMvwkKfk6bWeqYMDBst5xBg==" saltValue="8z8m9WW+gDac86aIaKzrzQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="wdPnGut1gAAo2a6JybfvR0sZX2M3Xgei21FcXUZ7eE3BbYUhSym1B+x/EakUpAbpAhAZ2ElhejwQplGJxtkRNA==" saltValue="AOeZO/yQFwd2MWB2+9YJuw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="45">
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B145:B147"/>
+    <mergeCell ref="B148:B150"/>
+    <mergeCell ref="B151:B153"/>
+    <mergeCell ref="B154:B156"/>
+    <mergeCell ref="B128:B130"/>
+    <mergeCell ref="B131:B133"/>
+    <mergeCell ref="B134:B136"/>
+    <mergeCell ref="B137:B139"/>
+    <mergeCell ref="B142:B144"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="B120:B122"/>
+    <mergeCell ref="B125:B127"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="B98:B100"/>
+    <mergeCell ref="B101:B103"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="B67:B69"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="B45:B47"/>
     <mergeCell ref="B48:B50"/>
@@ -16808,41 +16808,14 @@
     <mergeCell ref="B31:B33"/>
     <mergeCell ref="B36:B38"/>
     <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="B72:B74"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="B81:B83"/>
-    <mergeCell ref="B84:B86"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="B89:B91"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="B98:B100"/>
-    <mergeCell ref="B101:B103"/>
-    <mergeCell ref="B111:B113"/>
-    <mergeCell ref="B114:B116"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="B120:B122"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="B145:B147"/>
-    <mergeCell ref="B148:B150"/>
-    <mergeCell ref="B151:B153"/>
-    <mergeCell ref="B154:B156"/>
-    <mergeCell ref="B128:B130"/>
-    <mergeCell ref="B131:B133"/>
-    <mergeCell ref="B134:B136"/>
-    <mergeCell ref="B137:B139"/>
-    <mergeCell ref="B142:B144"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="D158:H158" unlockedFormula="1"/>
-  </ignoredErrors>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -18055,7 +18028,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="VsNxLy3D1NZbIJhIDRj213mb114uiCAsJxDOnSw85odt4lI0OBKvqzhTV3BELuJuf4NH7qJxnL7fRI4eT4Z5Xw==" saltValue="aiVEljEA5mhqbDnzTdZhcg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="7XD+Bvoc9+9grszYvJ09L3rqKRW6v6g5lK9o2b+d1J/LAirOX3leo5JpZ3LvPpgDyTswRlJ7pXip+J6Ecjo8DA==" saltValue="glsa+xD4bKe+n54m/6hnsw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -19769,7 +19742,7 @@
         <v>129</v>
       </c>
       <c r="D66" s="103">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="E66" s="103">
         <v>1</v>
@@ -19884,7 +19857,7 @@
         <v>129</v>
       </c>
       <c r="D70" s="103">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="E70" s="103">
         <v>1</v>
@@ -19999,7 +19972,7 @@
         <v>129</v>
       </c>
       <c r="D74" s="103">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="E74" s="103">
         <v>1</v>
@@ -21001,24 +20974,24 @@
         <v>9</v>
       </c>
       <c r="D113" s="105">
-        <f>D3*0.8</f>
-        <v>0.8</v>
+        <f>IF(D3=1,1,D3*0.9)</f>
+        <v>1</v>
       </c>
       <c r="E113" s="105">
-        <f t="shared" ref="E113:H113" si="0">E3*0.8</f>
-        <v>0.8</v>
+        <f t="shared" ref="E113:H113" si="0">IF(E3=1,1,E3*0.9)</f>
+        <v>1</v>
       </c>
       <c r="F113" s="105">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G113" s="105">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H113" s="105">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -21026,24 +20999,24 @@
         <v>267</v>
       </c>
       <c r="D114" s="105">
-        <f t="shared" ref="D114:H114" si="1">D4*0.8</f>
-        <v>0.8</v>
+        <f t="shared" ref="D114:H129" si="1">IF(D4=1,1,D4*0.9)</f>
+        <v>1</v>
       </c>
       <c r="E114" s="105">
         <f t="shared" si="1"/>
-        <v>1.3360000000000001</v>
+        <v>1.5029999999999999</v>
       </c>
       <c r="F114" s="105">
         <f t="shared" si="1"/>
-        <v>1.3360000000000001</v>
+        <v>1.5029999999999999</v>
       </c>
       <c r="G114" s="105">
         <f t="shared" si="1"/>
-        <v>1.3360000000000001</v>
+        <v>1.5029999999999999</v>
       </c>
       <c r="H114" s="105">
         <f t="shared" si="1"/>
-        <v>1.3360000000000001</v>
+        <v>1.5029999999999999</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -21051,24 +21024,24 @@
         <v>268</v>
       </c>
       <c r="D115" s="105">
-        <f t="shared" ref="D115:H115" si="2">D5*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E115" s="105">
-        <f t="shared" si="2"/>
-        <v>1.9039999999999999</v>
+        <f t="shared" si="1"/>
+        <v>2.1419999999999999</v>
       </c>
       <c r="F115" s="105">
-        <f t="shared" si="2"/>
-        <v>1.9039999999999999</v>
+        <f t="shared" si="1"/>
+        <v>2.1419999999999999</v>
       </c>
       <c r="G115" s="105">
-        <f t="shared" si="2"/>
-        <v>1.9039999999999999</v>
+        <f t="shared" si="1"/>
+        <v>2.1419999999999999</v>
       </c>
       <c r="H115" s="105">
-        <f t="shared" si="2"/>
-        <v>1.9039999999999999</v>
+        <f t="shared" si="1"/>
+        <v>2.1419999999999999</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
@@ -21076,24 +21049,24 @@
         <v>269</v>
       </c>
       <c r="D116" s="105">
-        <f t="shared" ref="D116:H116" si="3">D6*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E116" s="105">
-        <f t="shared" si="3"/>
-        <v>5.0640000000000001</v>
+        <f t="shared" si="1"/>
+        <v>5.6970000000000001</v>
       </c>
       <c r="F116" s="105">
-        <f t="shared" si="3"/>
-        <v>5.0640000000000001</v>
+        <f t="shared" si="1"/>
+        <v>5.6970000000000001</v>
       </c>
       <c r="G116" s="105">
-        <f t="shared" si="3"/>
-        <v>5.0640000000000001</v>
+        <f t="shared" si="1"/>
+        <v>5.6970000000000001</v>
       </c>
       <c r="H116" s="105">
-        <f t="shared" si="3"/>
-        <v>5.0640000000000001</v>
+        <f t="shared" si="1"/>
+        <v>5.6970000000000001</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -21104,24 +21077,24 @@
         <v>9</v>
       </c>
       <c r="D117" s="105">
-        <f t="shared" ref="D117:H117" si="4">D7*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E117" s="105">
-        <f t="shared" si="4"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="F117" s="105">
-        <f t="shared" si="4"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="G117" s="105">
-        <f t="shared" si="4"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H117" s="105">
-        <f t="shared" si="4"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -21129,24 +21102,24 @@
         <v>267</v>
       </c>
       <c r="D118" s="105">
-        <f t="shared" ref="D118:H118" si="5">D8*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E118" s="105">
-        <f t="shared" si="5"/>
-        <v>1.2400000000000002</v>
+        <f t="shared" si="1"/>
+        <v>1.395</v>
       </c>
       <c r="F118" s="105">
-        <f t="shared" si="5"/>
-        <v>1.2400000000000002</v>
+        <f t="shared" si="1"/>
+        <v>1.395</v>
       </c>
       <c r="G118" s="105">
-        <f t="shared" si="5"/>
-        <v>1.2400000000000002</v>
+        <f t="shared" si="1"/>
+        <v>1.395</v>
       </c>
       <c r="H118" s="105">
-        <f t="shared" si="5"/>
-        <v>1.2400000000000002</v>
+        <f t="shared" si="1"/>
+        <v>1.395</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -21154,24 +21127,24 @@
         <v>268</v>
       </c>
       <c r="D119" s="105">
-        <f t="shared" ref="D119:H119" si="6">D9*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E119" s="105">
-        <f t="shared" si="6"/>
-        <v>1.7440000000000002</v>
+        <f t="shared" si="1"/>
+        <v>1.9620000000000002</v>
       </c>
       <c r="F119" s="105">
-        <f t="shared" si="6"/>
-        <v>1.7440000000000002</v>
+        <f t="shared" si="1"/>
+        <v>1.9620000000000002</v>
       </c>
       <c r="G119" s="105">
-        <f t="shared" si="6"/>
-        <v>1.7440000000000002</v>
+        <f t="shared" si="1"/>
+        <v>1.9620000000000002</v>
       </c>
       <c r="H119" s="105">
-        <f t="shared" si="6"/>
-        <v>1.7440000000000002</v>
+        <f t="shared" si="1"/>
+        <v>1.9620000000000002</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -21179,24 +21152,24 @@
         <v>269</v>
       </c>
       <c r="D120" s="105">
-        <f t="shared" ref="D120:H120" si="7">D10*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E120" s="105">
-        <f t="shared" si="7"/>
-        <v>5.1120000000000001</v>
+        <f t="shared" si="1"/>
+        <v>5.7509999999999994</v>
       </c>
       <c r="F120" s="105">
-        <f t="shared" si="7"/>
-        <v>5.1120000000000001</v>
+        <f t="shared" si="1"/>
+        <v>5.7509999999999994</v>
       </c>
       <c r="G120" s="105">
-        <f t="shared" si="7"/>
-        <v>5.1120000000000001</v>
+        <f t="shared" si="1"/>
+        <v>5.7509999999999994</v>
       </c>
       <c r="H120" s="105">
-        <f t="shared" si="7"/>
-        <v>5.1120000000000001</v>
+        <f t="shared" si="1"/>
+        <v>5.7509999999999994</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
@@ -21207,24 +21180,24 @@
         <v>9</v>
       </c>
       <c r="D121" s="105">
-        <f t="shared" ref="D121:H121" si="8">D11*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E121" s="105">
-        <f t="shared" si="8"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="F121" s="105">
-        <f t="shared" si="8"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="G121" s="105">
-        <f t="shared" si="8"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H121" s="105">
-        <f t="shared" si="8"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -21232,24 +21205,24 @@
         <v>267</v>
       </c>
       <c r="D122" s="105">
-        <f t="shared" ref="D122:H122" si="9">D12*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E122" s="105">
-        <f t="shared" si="9"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="F122" s="105">
-        <f t="shared" si="9"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="G122" s="105">
-        <f t="shared" si="9"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H122" s="105">
-        <f t="shared" si="9"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -21257,24 +21230,24 @@
         <v>268</v>
       </c>
       <c r="D123" s="105">
-        <f t="shared" ref="D123:H123" si="10">D13*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E123" s="105">
-        <f t="shared" si="10"/>
-        <v>2.2320000000000002</v>
+        <f t="shared" si="1"/>
+        <v>2.5110000000000001</v>
       </c>
       <c r="F123" s="105">
-        <f t="shared" si="10"/>
-        <v>2.2320000000000002</v>
+        <f t="shared" si="1"/>
+        <v>2.5110000000000001</v>
       </c>
       <c r="G123" s="105">
-        <f t="shared" si="10"/>
-        <v>2.2320000000000002</v>
+        <f t="shared" si="1"/>
+        <v>2.5110000000000001</v>
       </c>
       <c r="H123" s="105">
-        <f t="shared" si="10"/>
-        <v>2.2320000000000002</v>
+        <f t="shared" si="1"/>
+        <v>2.5110000000000001</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -21282,24 +21255,24 @@
         <v>269</v>
       </c>
       <c r="D124" s="105">
-        <f t="shared" ref="D124:H124" si="11">D14*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E124" s="105">
-        <f t="shared" si="11"/>
-        <v>4.8079999999999998</v>
+        <f t="shared" si="1"/>
+        <v>5.4089999999999998</v>
       </c>
       <c r="F124" s="105">
-        <f t="shared" si="11"/>
-        <v>4.8079999999999998</v>
+        <f t="shared" si="1"/>
+        <v>5.4089999999999998</v>
       </c>
       <c r="G124" s="105">
-        <f t="shared" si="11"/>
-        <v>4.8079999999999998</v>
+        <f t="shared" si="1"/>
+        <v>5.4089999999999998</v>
       </c>
       <c r="H124" s="105">
-        <f t="shared" si="11"/>
-        <v>4.8079999999999998</v>
+        <f t="shared" si="1"/>
+        <v>5.4089999999999998</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -21310,24 +21283,24 @@
         <v>9</v>
       </c>
       <c r="D125" s="105">
-        <f t="shared" ref="D125:H125" si="12">D15*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E125" s="105">
-        <f t="shared" si="12"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="F125" s="105">
-        <f t="shared" si="12"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="G125" s="105">
-        <f t="shared" si="12"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H125" s="105">
-        <f t="shared" si="12"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -21335,24 +21308,24 @@
         <v>267</v>
       </c>
       <c r="D126" s="105">
-        <f t="shared" ref="D126:H126" si="13">D16*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E126" s="105">
-        <f t="shared" si="13"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="F126" s="105">
-        <f t="shared" si="13"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="G126" s="105">
-        <f t="shared" si="13"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H126" s="105">
-        <f t="shared" si="13"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -21360,24 +21333,24 @@
         <v>268</v>
       </c>
       <c r="D127" s="105">
-        <f t="shared" ref="D127:H127" si="14">D17*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E127" s="105">
-        <f t="shared" si="14"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="F127" s="105">
-        <f t="shared" si="14"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="G127" s="105">
-        <f t="shared" si="14"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H127" s="105">
-        <f t="shared" si="14"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -21385,24 +21358,24 @@
         <v>269</v>
       </c>
       <c r="D128" s="105">
-        <f t="shared" ref="D128:H128" si="15">D18*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E128" s="105">
-        <f t="shared" si="15"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="F128" s="105">
-        <f t="shared" si="15"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="G128" s="105">
-        <f t="shared" si="15"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H128" s="105">
-        <f t="shared" si="15"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -21413,24 +21386,24 @@
         <v>9</v>
       </c>
       <c r="D129" s="105">
-        <f t="shared" ref="D129:H129" si="16">D19*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E129" s="105">
-        <f t="shared" si="16"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="F129" s="105">
-        <f t="shared" si="16"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="G129" s="105">
-        <f t="shared" si="16"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H129" s="105">
-        <f t="shared" si="16"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -21438,24 +21411,24 @@
         <v>267</v>
       </c>
       <c r="D130" s="105">
-        <f t="shared" ref="D130:H130" si="17">D20*0.8</f>
-        <v>0.8</v>
+        <f t="shared" ref="D130:H136" si="2">IF(D20=1,1,D20*0.9)</f>
+        <v>1</v>
       </c>
       <c r="E130" s="105">
-        <f t="shared" si="17"/>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="F130" s="105">
-        <f t="shared" si="17"/>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="G130" s="105">
-        <f t="shared" si="17"/>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="H130" s="105">
-        <f t="shared" si="17"/>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -21463,24 +21436,24 @@
         <v>268</v>
       </c>
       <c r="D131" s="105">
-        <f t="shared" ref="D131:H131" si="18">D21*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="E131" s="105">
-        <f t="shared" si="18"/>
-        <v>1.4880000000000002</v>
+        <f t="shared" si="2"/>
+        <v>1.6740000000000002</v>
       </c>
       <c r="F131" s="105">
-        <f t="shared" si="18"/>
-        <v>1.4880000000000002</v>
+        <f t="shared" si="2"/>
+        <v>1.6740000000000002</v>
       </c>
       <c r="G131" s="105">
-        <f t="shared" si="18"/>
-        <v>1.4880000000000002</v>
+        <f t="shared" si="2"/>
+        <v>1.6740000000000002</v>
       </c>
       <c r="H131" s="105">
-        <f t="shared" si="18"/>
-        <v>1.4880000000000002</v>
+        <f t="shared" si="2"/>
+        <v>1.6740000000000002</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -21488,24 +21461,24 @@
         <v>269</v>
       </c>
       <c r="D132" s="105">
-        <f t="shared" ref="D132:H132" si="19">D22*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="E132" s="105">
-        <f t="shared" si="19"/>
-        <v>2.4079999999999999</v>
+        <f t="shared" si="2"/>
+        <v>2.7090000000000001</v>
       </c>
       <c r="F132" s="105">
-        <f t="shared" si="19"/>
-        <v>2.4079999999999999</v>
+        <f t="shared" si="2"/>
+        <v>2.7090000000000001</v>
       </c>
       <c r="G132" s="105">
-        <f t="shared" si="19"/>
-        <v>2.4079999999999999</v>
+        <f t="shared" si="2"/>
+        <v>2.7090000000000001</v>
       </c>
       <c r="H132" s="105">
-        <f t="shared" si="19"/>
-        <v>2.4079999999999999</v>
+        <f t="shared" si="2"/>
+        <v>2.7090000000000001</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -21516,24 +21489,24 @@
         <v>9</v>
       </c>
       <c r="D133" s="105">
-        <f t="shared" ref="D133:H133" si="20">D23*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="E133" s="105">
-        <f t="shared" si="20"/>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="F133" s="105">
-        <f t="shared" si="20"/>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="G133" s="105">
-        <f t="shared" si="20"/>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="H133" s="105">
-        <f t="shared" si="20"/>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
@@ -21541,24 +21514,24 @@
         <v>267</v>
       </c>
       <c r="D134" s="105">
-        <f t="shared" ref="D134:H134" si="21">D24*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="E134" s="105">
-        <f t="shared" si="21"/>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="F134" s="105">
-        <f t="shared" si="21"/>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="G134" s="105">
-        <f t="shared" si="21"/>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="H134" s="105">
-        <f t="shared" si="21"/>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
@@ -21566,24 +21539,24 @@
         <v>268</v>
       </c>
       <c r="D135" s="105">
-        <f t="shared" ref="D135:H135" si="22">D25*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="E135" s="105">
-        <f t="shared" si="22"/>
-        <v>1.4880000000000002</v>
+        <f t="shared" si="2"/>
+        <v>1.6740000000000002</v>
       </c>
       <c r="F135" s="105">
-        <f t="shared" si="22"/>
-        <v>1.4880000000000002</v>
+        <f t="shared" si="2"/>
+        <v>1.6740000000000002</v>
       </c>
       <c r="G135" s="105">
-        <f t="shared" si="22"/>
-        <v>1.4880000000000002</v>
+        <f t="shared" si="2"/>
+        <v>1.6740000000000002</v>
       </c>
       <c r="H135" s="105">
-        <f t="shared" si="22"/>
-        <v>1.4880000000000002</v>
+        <f t="shared" si="2"/>
+        <v>1.6740000000000002</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
@@ -21591,24 +21564,24 @@
         <v>269</v>
       </c>
       <c r="D136" s="105">
-        <f t="shared" ref="D136:H136" si="23">D26*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="E136" s="105">
-        <f t="shared" si="23"/>
-        <v>2.4079999999999999</v>
+        <f t="shared" si="2"/>
+        <v>2.7090000000000001</v>
       </c>
       <c r="F136" s="105">
-        <f t="shared" si="23"/>
-        <v>2.4079999999999999</v>
+        <f t="shared" si="2"/>
+        <v>2.7090000000000001</v>
       </c>
       <c r="G136" s="105">
-        <f t="shared" si="23"/>
-        <v>2.4079999999999999</v>
+        <f t="shared" si="2"/>
+        <v>2.7090000000000001</v>
       </c>
       <c r="H136" s="105">
-        <f t="shared" si="23"/>
-        <v>2.4079999999999999</v>
+        <f t="shared" si="2"/>
+        <v>2.7090000000000001</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="13" x14ac:dyDescent="0.3">
@@ -21658,24 +21631,24 @@
         <v>9</v>
       </c>
       <c r="D140" s="105">
-        <f>D30*0.7</f>
-        <v>0.7</v>
+        <f>IF(D30=1,1,D30*0.9)</f>
+        <v>1</v>
       </c>
       <c r="E140" s="105">
-        <f t="shared" ref="E140:H140" si="24">E30*0.7</f>
-        <v>0.7</v>
+        <f t="shared" ref="E140:H140" si="3">IF(E30=1,1,E30*0.9)</f>
+        <v>1</v>
       </c>
       <c r="F140" s="105">
-        <f t="shared" si="24"/>
-        <v>0.7</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="G140" s="105">
-        <f t="shared" si="24"/>
-        <v>0.7</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="H140" s="105">
-        <f t="shared" si="24"/>
-        <v>0.7</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -21683,24 +21656,24 @@
         <v>267</v>
       </c>
       <c r="D141" s="105">
-        <f t="shared" ref="D141:H141" si="25">D31*0.7</f>
-        <v>0.7</v>
+        <f t="shared" ref="D141:H156" si="4">IF(D31=1,1,D31*0.9)</f>
+        <v>1</v>
       </c>
       <c r="E141" s="105">
-        <f t="shared" si="25"/>
-        <v>1.1199999999999999</v>
+        <f t="shared" si="4"/>
+        <v>1.4400000000000002</v>
       </c>
       <c r="F141" s="105">
-        <f t="shared" si="25"/>
-        <v>1.1199999999999999</v>
+        <f t="shared" si="4"/>
+        <v>1.4400000000000002</v>
       </c>
       <c r="G141" s="105">
-        <f t="shared" si="25"/>
-        <v>1.1199999999999999</v>
+        <f t="shared" si="4"/>
+        <v>1.4400000000000002</v>
       </c>
       <c r="H141" s="105">
-        <f t="shared" si="25"/>
-        <v>1.1199999999999999</v>
+        <f t="shared" si="4"/>
+        <v>1.4400000000000002</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -21708,24 +21681,24 @@
         <v>209</v>
       </c>
       <c r="D142" s="105">
-        <f t="shared" ref="D142:H142" si="26">D32*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E142" s="105">
-        <f t="shared" si="26"/>
-        <v>2.387</v>
+        <f t="shared" si="4"/>
+        <v>3.0690000000000004</v>
       </c>
       <c r="F142" s="105">
-        <f t="shared" si="26"/>
-        <v>2.387</v>
+        <f t="shared" si="4"/>
+        <v>3.0690000000000004</v>
       </c>
       <c r="G142" s="105">
-        <f t="shared" si="26"/>
-        <v>2.387</v>
+        <f t="shared" si="4"/>
+        <v>3.0690000000000004</v>
       </c>
       <c r="H142" s="105">
-        <f t="shared" si="26"/>
-        <v>2.387</v>
+        <f t="shared" si="4"/>
+        <v>3.0690000000000004</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -21733,24 +21706,24 @@
         <v>208</v>
       </c>
       <c r="D143" s="105">
-        <f t="shared" ref="D143:H143" si="27">D33*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E143" s="105">
-        <f t="shared" si="27"/>
-        <v>8.6310000000000002</v>
+        <f t="shared" si="4"/>
+        <v>11.097</v>
       </c>
       <c r="F143" s="105">
-        <f t="shared" si="27"/>
-        <v>8.6310000000000002</v>
+        <f t="shared" si="4"/>
+        <v>11.097</v>
       </c>
       <c r="G143" s="105">
-        <f t="shared" si="27"/>
-        <v>8.6310000000000002</v>
+        <f t="shared" si="4"/>
+        <v>11.097</v>
       </c>
       <c r="H143" s="105">
-        <f t="shared" si="27"/>
-        <v>8.6310000000000002</v>
+        <f t="shared" si="4"/>
+        <v>11.097</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -21761,24 +21734,24 @@
         <v>9</v>
       </c>
       <c r="D144" s="105">
-        <f t="shared" ref="D144:H144" si="28">D34*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E144" s="105">
-        <f t="shared" si="28"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="F144" s="105">
-        <f t="shared" si="28"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="G144" s="105">
-        <f t="shared" si="28"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="H144" s="105">
-        <f t="shared" si="28"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
     </row>
     <row r="145" spans="2:8" x14ac:dyDescent="0.25">
@@ -21786,24 +21759,24 @@
         <v>267</v>
       </c>
       <c r="D145" s="105">
-        <f t="shared" ref="D145:H145" si="29">D35*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E145" s="105">
-        <f t="shared" si="29"/>
-        <v>1.3439999999999999</v>
+        <f t="shared" si="4"/>
+        <v>1.728</v>
       </c>
       <c r="F145" s="105">
-        <f t="shared" si="29"/>
-        <v>1.3439999999999999</v>
+        <f t="shared" si="4"/>
+        <v>1.728</v>
       </c>
       <c r="G145" s="105">
-        <f t="shared" si="29"/>
-        <v>1.3439999999999999</v>
+        <f t="shared" si="4"/>
+        <v>1.728</v>
       </c>
       <c r="H145" s="105">
-        <f t="shared" si="29"/>
-        <v>1.3439999999999999</v>
+        <f t="shared" si="4"/>
+        <v>1.728</v>
       </c>
     </row>
     <row r="146" spans="2:8" x14ac:dyDescent="0.25">
@@ -21811,24 +21784,24 @@
         <v>209</v>
       </c>
       <c r="D146" s="105">
-        <f t="shared" ref="D146:H146" si="30">D36*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E146" s="105">
-        <f t="shared" si="30"/>
-        <v>3.262</v>
+        <f t="shared" si="4"/>
+        <v>4.194</v>
       </c>
       <c r="F146" s="105">
-        <f t="shared" si="30"/>
-        <v>3.262</v>
+        <f t="shared" si="4"/>
+        <v>4.194</v>
       </c>
       <c r="G146" s="105">
-        <f t="shared" si="30"/>
-        <v>3.262</v>
+        <f t="shared" si="4"/>
+        <v>4.194</v>
       </c>
       <c r="H146" s="105">
-        <f t="shared" si="30"/>
-        <v>3.262</v>
+        <f t="shared" si="4"/>
+        <v>4.194</v>
       </c>
     </row>
     <row r="147" spans="2:8" x14ac:dyDescent="0.25">
@@ -21836,24 +21809,24 @@
         <v>208</v>
       </c>
       <c r="D147" s="105">
-        <f t="shared" ref="D147:H147" si="31">D37*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E147" s="105">
-        <f t="shared" si="31"/>
-        <v>6.7759999999999998</v>
+        <f t="shared" si="4"/>
+        <v>8.7119999999999997</v>
       </c>
       <c r="F147" s="105">
-        <f t="shared" si="31"/>
-        <v>6.7759999999999998</v>
+        <f t="shared" si="4"/>
+        <v>8.7119999999999997</v>
       </c>
       <c r="G147" s="105">
-        <f t="shared" si="31"/>
-        <v>6.7759999999999998</v>
+        <f t="shared" si="4"/>
+        <v>8.7119999999999997</v>
       </c>
       <c r="H147" s="105">
-        <f t="shared" si="31"/>
-        <v>6.7759999999999998</v>
+        <f t="shared" si="4"/>
+        <v>8.7119999999999997</v>
       </c>
     </row>
     <row r="148" spans="2:8" x14ac:dyDescent="0.25">
@@ -21864,24 +21837,24 @@
         <v>9</v>
       </c>
       <c r="D148" s="105">
-        <f t="shared" ref="D148:H148" si="32">D38*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E148" s="105">
-        <f t="shared" si="32"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="F148" s="105">
-        <f t="shared" si="32"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="G148" s="105">
-        <f t="shared" si="32"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="H148" s="105">
-        <f t="shared" si="32"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
     </row>
     <row r="149" spans="2:8" x14ac:dyDescent="0.25">
@@ -21889,24 +21862,24 @@
         <v>267</v>
       </c>
       <c r="D149" s="105">
-        <f t="shared" ref="D149:H149" si="33">D39*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E149" s="105">
-        <f t="shared" si="33"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="F149" s="105">
-        <f t="shared" si="33"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="G149" s="105">
-        <f t="shared" si="33"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="H149" s="105">
-        <f t="shared" si="33"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
     </row>
     <row r="150" spans="2:8" x14ac:dyDescent="0.25">
@@ -21914,24 +21887,24 @@
         <v>209</v>
       </c>
       <c r="D150" s="105">
-        <f t="shared" ref="D150:H150" si="34">D40*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E150" s="105">
-        <f t="shared" si="34"/>
-        <v>1.8059999999999998</v>
+        <f t="shared" si="4"/>
+        <v>2.3220000000000001</v>
       </c>
       <c r="F150" s="105">
-        <f t="shared" si="34"/>
-        <v>1.8059999999999998</v>
+        <f t="shared" si="4"/>
+        <v>2.3220000000000001</v>
       </c>
       <c r="G150" s="105">
-        <f t="shared" si="34"/>
-        <v>1.8059999999999998</v>
+        <f t="shared" si="4"/>
+        <v>2.3220000000000001</v>
       </c>
       <c r="H150" s="105">
-        <f t="shared" si="34"/>
-        <v>1.8059999999999998</v>
+        <f t="shared" si="4"/>
+        <v>2.3220000000000001</v>
       </c>
     </row>
     <row r="151" spans="2:8" x14ac:dyDescent="0.25">
@@ -21939,24 +21912,24 @@
         <v>208</v>
       </c>
       <c r="D151" s="105">
-        <f t="shared" ref="D151:H151" si="35">D41*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E151" s="105">
-        <f t="shared" si="35"/>
-        <v>6.7410000000000005</v>
+        <f t="shared" si="4"/>
+        <v>8.6670000000000016</v>
       </c>
       <c r="F151" s="105">
-        <f t="shared" si="35"/>
-        <v>6.7410000000000005</v>
+        <f t="shared" si="4"/>
+        <v>8.6670000000000016</v>
       </c>
       <c r="G151" s="105">
-        <f t="shared" si="35"/>
-        <v>6.7410000000000005</v>
+        <f t="shared" si="4"/>
+        <v>8.6670000000000016</v>
       </c>
       <c r="H151" s="105">
-        <f t="shared" si="35"/>
-        <v>6.7410000000000005</v>
+        <f t="shared" si="4"/>
+        <v>8.6670000000000016</v>
       </c>
     </row>
     <row r="152" spans="2:8" x14ac:dyDescent="0.25">
@@ -21967,24 +21940,24 @@
         <v>9</v>
       </c>
       <c r="D152" s="105">
-        <f t="shared" ref="D152:H152" si="36">D42*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E152" s="105">
-        <f t="shared" si="36"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="F152" s="105">
-        <f t="shared" si="36"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="G152" s="105">
-        <f t="shared" si="36"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="H152" s="105">
-        <f t="shared" si="36"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
     </row>
     <row r="153" spans="2:8" x14ac:dyDescent="0.25">
@@ -21992,24 +21965,24 @@
         <v>267</v>
       </c>
       <c r="D153" s="105">
-        <f t="shared" ref="D153:H153" si="37">D43*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E153" s="105">
-        <f t="shared" si="37"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="F153" s="105">
-        <f t="shared" si="37"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="G153" s="105">
-        <f t="shared" si="37"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="H153" s="105">
-        <f t="shared" si="37"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="2:8" x14ac:dyDescent="0.25">
@@ -22017,24 +21990,24 @@
         <v>209</v>
       </c>
       <c r="D154" s="105">
-        <f t="shared" ref="D154:H154" si="38">D44*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E154" s="105">
-        <f t="shared" si="38"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="F154" s="105">
-        <f t="shared" si="38"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="G154" s="105">
-        <f t="shared" si="38"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="H154" s="105">
-        <f t="shared" si="38"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
     </row>
     <row r="155" spans="2:8" x14ac:dyDescent="0.25">
@@ -22042,24 +22015,24 @@
         <v>208</v>
       </c>
       <c r="D155" s="105">
-        <f t="shared" ref="D155:H155" si="39">D45*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E155" s="105">
-        <f t="shared" si="39"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="F155" s="105">
-        <f t="shared" si="39"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="G155" s="105">
-        <f t="shared" si="39"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="H155" s="105">
-        <f t="shared" si="39"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
     </row>
     <row r="156" spans="2:8" x14ac:dyDescent="0.25">
@@ -22070,24 +22043,24 @@
         <v>9</v>
       </c>
       <c r="D156" s="105">
-        <f t="shared" ref="D156:H156" si="40">D46*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E156" s="105">
-        <f t="shared" si="40"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="F156" s="105">
-        <f t="shared" si="40"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="G156" s="105">
-        <f t="shared" si="40"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="H156" s="105">
-        <f t="shared" si="40"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="2:8" x14ac:dyDescent="0.25">
@@ -22095,24 +22068,24 @@
         <v>267</v>
       </c>
       <c r="D157" s="105">
-        <f t="shared" ref="D157:H157" si="41">D47*0.7</f>
-        <v>0.7</v>
+        <f t="shared" ref="D157:H163" si="5">IF(D47=1,1,D47*0.9)</f>
+        <v>1</v>
       </c>
       <c r="E157" s="105">
-        <f t="shared" si="41"/>
-        <v>1.1549999999999998</v>
+        <f t="shared" si="5"/>
+        <v>1.4849999999999999</v>
       </c>
       <c r="F157" s="105">
-        <f t="shared" si="41"/>
-        <v>1.1549999999999998</v>
+        <f t="shared" si="5"/>
+        <v>1.4849999999999999</v>
       </c>
       <c r="G157" s="105">
-        <f t="shared" si="41"/>
-        <v>1.1549999999999998</v>
+        <f t="shared" si="5"/>
+        <v>1.4849999999999999</v>
       </c>
       <c r="H157" s="105">
-        <f t="shared" si="41"/>
-        <v>1.1549999999999998</v>
+        <f t="shared" si="5"/>
+        <v>1.4849999999999999</v>
       </c>
     </row>
     <row r="158" spans="2:8" x14ac:dyDescent="0.25">
@@ -22120,24 +22093,24 @@
         <v>209</v>
       </c>
       <c r="D158" s="105">
-        <f t="shared" ref="D158:H158" si="42">D48*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="E158" s="105">
-        <f t="shared" si="42"/>
-        <v>1.9109999999999998</v>
+        <f t="shared" si="5"/>
+        <v>2.4569999999999999</v>
       </c>
       <c r="F158" s="105">
-        <f t="shared" si="42"/>
-        <v>1.9109999999999998</v>
+        <f t="shared" si="5"/>
+        <v>2.4569999999999999</v>
       </c>
       <c r="G158" s="105">
-        <f t="shared" si="42"/>
-        <v>1.9109999999999998</v>
+        <f t="shared" si="5"/>
+        <v>2.4569999999999999</v>
       </c>
       <c r="H158" s="105">
-        <f t="shared" si="42"/>
-        <v>1.9109999999999998</v>
+        <f t="shared" si="5"/>
+        <v>2.4569999999999999</v>
       </c>
     </row>
     <row r="159" spans="2:8" x14ac:dyDescent="0.25">
@@ -22145,24 +22118,24 @@
         <v>208</v>
       </c>
       <c r="D159" s="105">
-        <f t="shared" ref="D159:H159" si="43">D49*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="E159" s="105">
-        <f t="shared" si="43"/>
-        <v>7.8470000000000004</v>
+        <f t="shared" si="5"/>
+        <v>10.089</v>
       </c>
       <c r="F159" s="105">
-        <f t="shared" si="43"/>
-        <v>7.8470000000000004</v>
+        <f t="shared" si="5"/>
+        <v>10.089</v>
       </c>
       <c r="G159" s="105">
-        <f t="shared" si="43"/>
-        <v>7.8470000000000004</v>
+        <f t="shared" si="5"/>
+        <v>10.089</v>
       </c>
       <c r="H159" s="105">
-        <f t="shared" si="43"/>
-        <v>7.8470000000000004</v>
+        <f t="shared" si="5"/>
+        <v>10.089</v>
       </c>
     </row>
     <row r="160" spans="2:8" x14ac:dyDescent="0.25">
@@ -22173,24 +22146,24 @@
         <v>9</v>
       </c>
       <c r="D160" s="105">
-        <f t="shared" ref="D160:H160" si="44">D50*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="E160" s="105">
-        <f t="shared" si="44"/>
-        <v>0.7</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="F160" s="105">
-        <f t="shared" si="44"/>
-        <v>0.7</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="G160" s="105">
-        <f t="shared" si="44"/>
-        <v>0.7</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="H160" s="105">
-        <f t="shared" si="44"/>
-        <v>0.7</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
@@ -22198,24 +22171,24 @@
         <v>267</v>
       </c>
       <c r="D161" s="105">
-        <f t="shared" ref="D161:H161" si="45">D51*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="E161" s="105">
-        <f t="shared" si="45"/>
-        <v>1.1549999999999998</v>
+        <f t="shared" si="5"/>
+        <v>1.4849999999999999</v>
       </c>
       <c r="F161" s="105">
-        <f t="shared" si="45"/>
-        <v>1.1549999999999998</v>
+        <f t="shared" si="5"/>
+        <v>1.4849999999999999</v>
       </c>
       <c r="G161" s="105">
-        <f t="shared" si="45"/>
-        <v>1.1549999999999998</v>
+        <f t="shared" si="5"/>
+        <v>1.4849999999999999</v>
       </c>
       <c r="H161" s="105">
-        <f t="shared" si="45"/>
-        <v>1.1549999999999998</v>
+        <f t="shared" si="5"/>
+        <v>1.4849999999999999</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
@@ -22223,24 +22196,24 @@
         <v>209</v>
       </c>
       <c r="D162" s="105">
-        <f t="shared" ref="D162:H162" si="46">D52*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="E162" s="105">
-        <f t="shared" si="46"/>
-        <v>1.9109999999999998</v>
+        <f t="shared" si="5"/>
+        <v>2.4569999999999999</v>
       </c>
       <c r="F162" s="105">
-        <f t="shared" si="46"/>
-        <v>1.9109999999999998</v>
+        <f t="shared" si="5"/>
+        <v>2.4569999999999999</v>
       </c>
       <c r="G162" s="105">
-        <f t="shared" si="46"/>
-        <v>1.9109999999999998</v>
+        <f t="shared" si="5"/>
+        <v>2.4569999999999999</v>
       </c>
       <c r="H162" s="105">
-        <f t="shared" si="46"/>
-        <v>1.9109999999999998</v>
+        <f t="shared" si="5"/>
+        <v>2.4569999999999999</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -22248,24 +22221,24 @@
         <v>208</v>
       </c>
       <c r="D163" s="105">
-        <f t="shared" ref="D163:H163" si="47">D53*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="E163" s="105">
-        <f t="shared" si="47"/>
-        <v>7.8470000000000004</v>
+        <f t="shared" si="5"/>
+        <v>10.089</v>
       </c>
       <c r="F163" s="105">
-        <f t="shared" si="47"/>
-        <v>7.8470000000000004</v>
+        <f t="shared" si="5"/>
+        <v>10.089</v>
       </c>
       <c r="G163" s="105">
-        <f t="shared" si="47"/>
-        <v>7.8470000000000004</v>
+        <f t="shared" si="5"/>
+        <v>10.089</v>
       </c>
       <c r="H163" s="105">
-        <f t="shared" si="47"/>
-        <v>7.8470000000000004</v>
+        <f t="shared" si="5"/>
+        <v>10.089</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -22317,20 +22290,20 @@
         <v>273</v>
       </c>
       <c r="D167" s="105">
-        <f>D57*0.7</f>
-        <v>0.7</v>
+        <f>IF(D57=1,1,D57*0.9)</f>
+        <v>1</v>
       </c>
       <c r="E167" s="105">
-        <f t="shared" ref="E167:G167" si="48">E57*0.7</f>
-        <v>0.7</v>
+        <f t="shared" ref="E167:G167" si="6">IF(E57=1,1,E57*0.9)</f>
+        <v>1</v>
       </c>
       <c r="F167" s="105">
-        <f t="shared" si="48"/>
-        <v>0.7</v>
+        <f t="shared" si="6"/>
+        <v>1</v>
       </c>
       <c r="G167" s="105">
-        <f t="shared" si="48"/>
-        <v>0.7</v>
+        <f t="shared" si="6"/>
+        <v>1</v>
       </c>
       <c r="H167" s="92"/>
     </row>
@@ -22339,20 +22312,20 @@
         <v>274</v>
       </c>
       <c r="D168" s="105">
-        <f t="shared" ref="D168:G168" si="49">D58*0.7</f>
-        <v>7.4725000000000001</v>
+        <f t="shared" ref="D168:G172" si="7">IF(D58=1,1,D58*0.9)</f>
+        <v>9.6075000000000017</v>
       </c>
       <c r="E168" s="105">
-        <f t="shared" si="49"/>
-        <v>7.4725000000000001</v>
+        <f t="shared" si="7"/>
+        <v>9.6075000000000017</v>
       </c>
       <c r="F168" s="105">
-        <f t="shared" si="49"/>
-        <v>7.4725000000000001</v>
+        <f t="shared" si="7"/>
+        <v>9.6075000000000017</v>
       </c>
       <c r="G168" s="105">
-        <f t="shared" si="49"/>
-        <v>7.4725000000000001</v>
+        <f t="shared" si="7"/>
+        <v>9.6075000000000017</v>
       </c>
       <c r="H168" s="92"/>
     </row>
@@ -22364,20 +22337,20 @@
         <v>273</v>
       </c>
       <c r="D169" s="105">
-        <f t="shared" ref="D169:G169" si="50">D59*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="E169" s="105">
-        <f t="shared" si="50"/>
-        <v>0.7</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="F169" s="105">
-        <f t="shared" si="50"/>
-        <v>0.7</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="G169" s="105">
-        <f t="shared" si="50"/>
-        <v>0.7</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="H169" s="92"/>
     </row>
@@ -22386,20 +22359,20 @@
         <v>274</v>
       </c>
       <c r="D170" s="105">
-        <f t="shared" ref="D170:G170" si="51">D60*0.7</f>
-        <v>7.4725000000000001</v>
+        <f t="shared" si="7"/>
+        <v>9.6075000000000017</v>
       </c>
       <c r="E170" s="105">
-        <f t="shared" si="51"/>
-        <v>7.4725000000000001</v>
+        <f t="shared" si="7"/>
+        <v>9.6075000000000017</v>
       </c>
       <c r="F170" s="105">
-        <f t="shared" si="51"/>
-        <v>7.4725000000000001</v>
+        <f t="shared" si="7"/>
+        <v>9.6075000000000017</v>
       </c>
       <c r="G170" s="105">
-        <f t="shared" si="51"/>
-        <v>7.4725000000000001</v>
+        <f t="shared" si="7"/>
+        <v>9.6075000000000017</v>
       </c>
       <c r="H170" s="92"/>
     </row>
@@ -22411,20 +22384,20 @@
         <v>273</v>
       </c>
       <c r="D171" s="105">
-        <f t="shared" ref="D171:G171" si="52">D61*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="E171" s="105">
-        <f t="shared" si="52"/>
-        <v>0.7</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="F171" s="105">
-        <f t="shared" si="52"/>
-        <v>0.7</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="G171" s="105">
-        <f t="shared" si="52"/>
-        <v>0.7</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="H171" s="92"/>
     </row>
@@ -22433,20 +22406,20 @@
         <v>274</v>
       </c>
       <c r="D172" s="105">
-        <f t="shared" ref="D172:G172" si="53">D62*0.7</f>
-        <v>7.4725000000000001</v>
+        <f t="shared" si="7"/>
+        <v>9.6075000000000017</v>
       </c>
       <c r="E172" s="105">
-        <f t="shared" si="53"/>
-        <v>7.4725000000000001</v>
+        <f t="shared" si="7"/>
+        <v>9.6075000000000017</v>
       </c>
       <c r="F172" s="105">
-        <f t="shared" si="53"/>
-        <v>7.4725000000000001</v>
+        <f t="shared" si="7"/>
+        <v>9.6075000000000017</v>
       </c>
       <c r="G172" s="105">
-        <f t="shared" si="53"/>
-        <v>7.4725000000000001</v>
+        <f t="shared" si="7"/>
+        <v>9.6075000000000017</v>
       </c>
       <c r="H172" s="92"/>
     </row>
@@ -22501,20 +22474,20 @@
         <v>129</v>
       </c>
       <c r="D176" s="105">
-        <f>D66*0.7</f>
-        <v>0.7</v>
+        <f>IF(D66=1,1,D66*0.9)</f>
+        <v>1.2150000000000001</v>
       </c>
       <c r="E176" s="105">
-        <f t="shared" ref="E176:G176" si="54">E66*0.7</f>
-        <v>0.7</v>
+        <f t="shared" ref="E176:G176" si="8">IF(E66=1,1,E66*0.9)</f>
+        <v>1</v>
       </c>
       <c r="F176" s="105">
-        <f t="shared" si="54"/>
-        <v>0.7</v>
+        <f t="shared" si="8"/>
+        <v>1</v>
       </c>
       <c r="G176" s="105">
-        <f t="shared" si="54"/>
-        <v>0.7</v>
+        <f t="shared" si="8"/>
+        <v>1</v>
       </c>
       <c r="H176" s="92">
         <v>0.9</v>
@@ -22525,20 +22498,20 @@
         <v>130</v>
       </c>
       <c r="D177" s="105">
-        <f t="shared" ref="D177:G177" si="55">D67*0.7</f>
-        <v>0.94499999999999995</v>
+        <f t="shared" ref="D177:G192" si="9">IF(D67=1,1,D67*0.9)</f>
+        <v>1.2150000000000001</v>
       </c>
       <c r="E177" s="105">
-        <f t="shared" si="55"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F177" s="105">
-        <f t="shared" si="55"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G177" s="105">
-        <f t="shared" si="55"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H177" s="92">
         <v>0.9</v>
@@ -22549,20 +22522,20 @@
         <v>131</v>
       </c>
       <c r="D178" s="105">
-        <f t="shared" ref="D178:G178" si="56">D68*0.7</f>
-        <v>0.94499999999999995</v>
+        <f t="shared" si="9"/>
+        <v>1.2150000000000001</v>
       </c>
       <c r="E178" s="105">
-        <f t="shared" si="56"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F178" s="105">
-        <f t="shared" si="56"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G178" s="105">
-        <f t="shared" si="56"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H178" s="92">
         <v>0.9</v>
@@ -22573,20 +22546,20 @@
         <v>132</v>
       </c>
       <c r="D179" s="105">
-        <f t="shared" ref="D179:G179" si="57">D69*0.7</f>
-        <v>3.78</v>
+        <f t="shared" si="9"/>
+        <v>4.8600000000000003</v>
       </c>
       <c r="E179" s="105">
-        <f t="shared" si="57"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F179" s="105">
-        <f t="shared" si="57"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G179" s="105">
-        <f t="shared" si="57"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H179" s="92">
         <v>0.9</v>
@@ -22600,20 +22573,20 @@
         <v>129</v>
       </c>
       <c r="D180" s="105">
-        <f t="shared" ref="D180:G180" si="58">D70*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1.2150000000000001</v>
       </c>
       <c r="E180" s="105">
-        <f t="shared" si="58"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F180" s="105">
-        <f t="shared" si="58"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G180" s="105">
-        <f t="shared" si="58"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H180" s="92">
         <v>0.9</v>
@@ -22624,20 +22597,20 @@
         <v>130</v>
       </c>
       <c r="D181" s="105">
-        <f t="shared" ref="D181:G181" si="59">D71*0.7</f>
-        <v>0.94499999999999995</v>
+        <f t="shared" si="9"/>
+        <v>1.2150000000000001</v>
       </c>
       <c r="E181" s="105">
-        <f t="shared" si="59"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F181" s="105">
-        <f t="shared" si="59"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G181" s="105">
-        <f t="shared" si="59"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H181" s="92">
         <v>0.9</v>
@@ -22648,20 +22621,20 @@
         <v>131</v>
       </c>
       <c r="D182" s="105">
-        <f t="shared" ref="D182:G182" si="60">D72*0.7</f>
-        <v>0.94499999999999995</v>
+        <f t="shared" si="9"/>
+        <v>1.2150000000000001</v>
       </c>
       <c r="E182" s="105">
-        <f t="shared" si="60"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F182" s="105">
-        <f t="shared" si="60"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G182" s="105">
-        <f t="shared" si="60"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H182" s="92">
         <v>0.9</v>
@@ -22672,20 +22645,20 @@
         <v>132</v>
       </c>
       <c r="D183" s="105">
-        <f t="shared" ref="D183:G183" si="61">D73*0.7</f>
-        <v>3.78</v>
+        <f t="shared" si="9"/>
+        <v>4.8600000000000003</v>
       </c>
       <c r="E183" s="105">
-        <f t="shared" si="61"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F183" s="105">
-        <f t="shared" si="61"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G183" s="105">
-        <f t="shared" si="61"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H183" s="92">
         <v>0.9</v>
@@ -22699,20 +22672,20 @@
         <v>129</v>
       </c>
       <c r="D184" s="105">
-        <f t="shared" ref="D184:G184" si="62">D74*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1.2150000000000001</v>
       </c>
       <c r="E184" s="105">
-        <f t="shared" si="62"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F184" s="105">
-        <f t="shared" si="62"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G184" s="105">
-        <f t="shared" si="62"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H184" s="92">
         <v>0.9</v>
@@ -22723,20 +22696,20 @@
         <v>130</v>
       </c>
       <c r="D185" s="105">
-        <f t="shared" ref="D185:G185" si="63">D75*0.7</f>
-        <v>0.94499999999999995</v>
+        <f t="shared" si="9"/>
+        <v>1.2150000000000001</v>
       </c>
       <c r="E185" s="105">
-        <f t="shared" si="63"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F185" s="105">
-        <f t="shared" si="63"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G185" s="105">
-        <f t="shared" si="63"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H185" s="92">
         <v>0.9</v>
@@ -22747,20 +22720,20 @@
         <v>131</v>
       </c>
       <c r="D186" s="105">
-        <f t="shared" ref="D186:G186" si="64">D76*0.7</f>
-        <v>0.94499999999999995</v>
+        <f t="shared" si="9"/>
+        <v>1.2150000000000001</v>
       </c>
       <c r="E186" s="105">
-        <f t="shared" si="64"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F186" s="105">
-        <f t="shared" si="64"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G186" s="105">
-        <f t="shared" si="64"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H186" s="92">
         <v>0.9</v>
@@ -22771,20 +22744,20 @@
         <v>132</v>
       </c>
       <c r="D187" s="105">
-        <f t="shared" ref="D187:G187" si="65">D77*0.7</f>
-        <v>3.78</v>
+        <f t="shared" si="9"/>
+        <v>4.8600000000000003</v>
       </c>
       <c r="E187" s="105">
-        <f t="shared" si="65"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F187" s="105">
-        <f t="shared" si="65"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G187" s="105">
-        <f t="shared" si="65"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H187" s="92">
         <v>0.9</v>
@@ -22798,20 +22771,20 @@
         <v>129</v>
       </c>
       <c r="D188" s="105">
-        <f t="shared" ref="D188:G188" si="66">D78*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="E188" s="105">
-        <f t="shared" si="66"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F188" s="105">
-        <f t="shared" si="66"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G188" s="105">
-        <f t="shared" si="66"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H188" s="92">
         <v>0.9</v>
@@ -22822,20 +22795,20 @@
         <v>130</v>
       </c>
       <c r="D189" s="105">
-        <f t="shared" ref="D189:G189" si="67">D79*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="E189" s="105">
-        <f t="shared" si="67"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F189" s="105">
-        <f t="shared" si="67"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G189" s="105">
-        <f t="shared" si="67"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H189" s="92">
         <v>0.9</v>
@@ -22846,20 +22819,20 @@
         <v>131</v>
       </c>
       <c r="D190" s="105">
-        <f t="shared" ref="D190:G190" si="68">D80*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="E190" s="105">
-        <f t="shared" si="68"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F190" s="105">
-        <f t="shared" si="68"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G190" s="105">
-        <f t="shared" si="68"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H190" s="92">
         <v>0.9</v>
@@ -22870,20 +22843,20 @@
         <v>132</v>
       </c>
       <c r="D191" s="105">
-        <f t="shared" ref="D191:G191" si="69">D81*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="E191" s="105">
-        <f t="shared" si="69"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F191" s="105">
-        <f t="shared" si="69"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G191" s="105">
-        <f t="shared" si="69"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H191" s="92">
         <v>0.9</v>
@@ -22897,20 +22870,20 @@
         <v>129</v>
       </c>
       <c r="D192" s="105">
-        <f t="shared" ref="D192:G192" si="70">D82*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="E192" s="105">
-        <f t="shared" si="70"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F192" s="105">
-        <f t="shared" si="70"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G192" s="105">
-        <f t="shared" si="70"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H192" s="92">
         <v>0.9</v>
@@ -22921,20 +22894,20 @@
         <v>130</v>
       </c>
       <c r="D193" s="105">
-        <f t="shared" ref="D193:G193" si="71">D83*0.7</f>
-        <v>0.7</v>
+        <f t="shared" ref="D193:G208" si="10">IF(D83=1,1,D83*0.9)</f>
+        <v>1</v>
       </c>
       <c r="E193" s="105">
-        <f t="shared" si="71"/>
-        <v>1.5959999999999999</v>
+        <f t="shared" si="10"/>
+        <v>2.052</v>
       </c>
       <c r="F193" s="105">
-        <f t="shared" si="71"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="G193" s="105">
-        <f t="shared" si="71"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="H193" s="92">
         <v>0.9</v>
@@ -22945,20 +22918,20 @@
         <v>131</v>
       </c>
       <c r="D194" s="105">
-        <f t="shared" ref="D194:G194" si="72">D84*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E194" s="105">
-        <f t="shared" si="72"/>
-        <v>3.234</v>
+        <f t="shared" si="10"/>
+        <v>4.1580000000000004</v>
       </c>
       <c r="F194" s="105">
-        <f t="shared" si="72"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="G194" s="105">
-        <f t="shared" si="72"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="H194" s="92">
         <v>0.9</v>
@@ -22969,20 +22942,20 @@
         <v>132</v>
       </c>
       <c r="D195" s="105">
-        <f t="shared" ref="D195:G195" si="73">D85*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E195" s="105">
-        <f t="shared" si="73"/>
-        <v>7.3709999999999987</v>
+        <f t="shared" si="10"/>
+        <v>9.4770000000000003</v>
       </c>
       <c r="F195" s="105">
-        <f t="shared" si="73"/>
-        <v>1.0289999999999999</v>
+        <f t="shared" si="10"/>
+        <v>1.323</v>
       </c>
       <c r="G195" s="105">
-        <f t="shared" si="73"/>
-        <v>1.7989999999999997</v>
+        <f t="shared" si="10"/>
+        <v>2.3129999999999997</v>
       </c>
       <c r="H195" s="92">
         <v>0.9</v>
@@ -22996,20 +22969,20 @@
         <v>129</v>
       </c>
       <c r="D196" s="105">
-        <f t="shared" ref="D196:G196" si="74">D86*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E196" s="105">
-        <f t="shared" si="74"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="F196" s="105">
-        <f t="shared" si="74"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="G196" s="105">
-        <f t="shared" si="74"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="H196" s="92">
         <v>0.9</v>
@@ -23020,20 +22993,20 @@
         <v>130</v>
       </c>
       <c r="D197" s="105">
-        <f t="shared" ref="D197:G197" si="75">D87*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E197" s="105">
-        <f t="shared" si="75"/>
-        <v>1.1619999999999999</v>
+        <f t="shared" si="10"/>
+        <v>1.494</v>
       </c>
       <c r="F197" s="105">
-        <f t="shared" si="75"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="G197" s="105">
-        <f t="shared" si="75"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="H197" s="92">
         <v>0.9</v>
@@ -23044,20 +23017,20 @@
         <v>131</v>
       </c>
       <c r="D198" s="105">
-        <f t="shared" ref="D198:G198" si="76">D88*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E198" s="105">
-        <f t="shared" si="76"/>
-        <v>1.75</v>
+        <f t="shared" si="10"/>
+        <v>2.25</v>
       </c>
       <c r="F198" s="105">
-        <f t="shared" si="76"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="G198" s="105">
-        <f t="shared" si="76"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="H198" s="92">
         <v>0.9</v>
@@ -23068,20 +23041,20 @@
         <v>132</v>
       </c>
       <c r="D199" s="105">
-        <f t="shared" ref="D199:G199" si="77">D89*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E199" s="105">
-        <f t="shared" si="77"/>
-        <v>10.478999999999999</v>
+        <f t="shared" si="10"/>
+        <v>13.473000000000001</v>
       </c>
       <c r="F199" s="105">
-        <f t="shared" si="77"/>
-        <v>1.3439999999999999</v>
+        <f t="shared" si="10"/>
+        <v>1.728</v>
       </c>
       <c r="G199" s="105">
-        <f t="shared" si="77"/>
-        <v>1.3439999999999999</v>
+        <f t="shared" si="10"/>
+        <v>1.728</v>
       </c>
       <c r="H199" s="92">
         <v>0.9</v>
@@ -23095,20 +23068,20 @@
         <v>129</v>
       </c>
       <c r="D200" s="105">
-        <f t="shared" ref="D200:G200" si="78">D90*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E200" s="105">
-        <f t="shared" si="78"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="F200" s="105">
-        <f t="shared" si="78"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="G200" s="105">
-        <f t="shared" si="78"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="H200" s="92">
         <v>0.9</v>
@@ -23119,20 +23092,20 @@
         <v>130</v>
       </c>
       <c r="D201" s="105">
-        <f t="shared" ref="D201:G201" si="79">D91*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E201" s="105">
-        <f t="shared" si="79"/>
-        <v>1.036</v>
+        <f t="shared" si="10"/>
+        <v>1.3320000000000001</v>
       </c>
       <c r="F201" s="105">
-        <f t="shared" si="79"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="G201" s="105">
-        <f t="shared" si="79"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="H201" s="92">
         <v>0.9</v>
@@ -23143,20 +23116,20 @@
         <v>131</v>
       </c>
       <c r="D202" s="105">
-        <f t="shared" ref="D202:G202" si="80">D92*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E202" s="105">
-        <f t="shared" si="80"/>
-        <v>1.9879999999999998</v>
+        <f t="shared" si="10"/>
+        <v>2.556</v>
       </c>
       <c r="F202" s="105">
-        <f t="shared" si="80"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="G202" s="105">
-        <f t="shared" si="80"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="H202" s="92">
         <v>0.9</v>
@@ -23167,20 +23140,20 @@
         <v>132</v>
       </c>
       <c r="D203" s="105">
-        <f t="shared" ref="D203:G203" si="81">D93*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E203" s="105">
-        <f t="shared" si="81"/>
-        <v>10.08</v>
+        <f t="shared" si="10"/>
+        <v>12.96</v>
       </c>
       <c r="F203" s="105">
-        <f t="shared" si="81"/>
-        <v>2.5829999999999997</v>
+        <f t="shared" si="10"/>
+        <v>3.3210000000000002</v>
       </c>
       <c r="G203" s="105">
-        <f t="shared" si="81"/>
-        <v>2.5829999999999997</v>
+        <f t="shared" si="10"/>
+        <v>3.3210000000000002</v>
       </c>
       <c r="H203" s="92">
         <v>0.9</v>
@@ -23194,20 +23167,20 @@
         <v>129</v>
       </c>
       <c r="D204" s="105">
-        <f t="shared" ref="D204:G204" si="82">D94*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E204" s="105">
-        <f t="shared" si="82"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="F204" s="105">
-        <f t="shared" si="82"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="G204" s="105">
-        <f t="shared" si="82"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="H204" s="92">
         <v>0.9</v>
@@ -23218,20 +23191,20 @@
         <v>130</v>
       </c>
       <c r="D205" s="105">
-        <f t="shared" ref="D205:G205" si="83">D95*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E205" s="105">
-        <f t="shared" si="83"/>
-        <v>1.036</v>
+        <f t="shared" si="10"/>
+        <v>1.3320000000000001</v>
       </c>
       <c r="F205" s="105">
-        <f t="shared" si="83"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="G205" s="105">
-        <f t="shared" si="83"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="H205" s="92">
         <v>0.9</v>
@@ -23242,20 +23215,20 @@
         <v>131</v>
       </c>
       <c r="D206" s="105">
-        <f t="shared" ref="D206:G206" si="84">D96*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E206" s="105">
-        <f t="shared" si="84"/>
-        <v>1.9879999999999998</v>
+        <f t="shared" si="10"/>
+        <v>2.556</v>
       </c>
       <c r="F206" s="105">
-        <f t="shared" si="84"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="G206" s="105">
-        <f t="shared" si="84"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="H206" s="92">
         <v>0.9</v>
@@ -23266,20 +23239,20 @@
         <v>132</v>
       </c>
       <c r="D207" s="105">
-        <f t="shared" ref="D207:G207" si="85">D97*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E207" s="105">
-        <f t="shared" si="85"/>
-        <v>10.08</v>
+        <f t="shared" si="10"/>
+        <v>12.96</v>
       </c>
       <c r="F207" s="105">
-        <f t="shared" si="85"/>
-        <v>2.5829999999999997</v>
+        <f t="shared" si="10"/>
+        <v>3.3210000000000002</v>
       </c>
       <c r="G207" s="105">
-        <f t="shared" si="85"/>
-        <v>2.5829999999999997</v>
+        <f t="shared" si="10"/>
+        <v>3.3210000000000002</v>
       </c>
       <c r="H207" s="92">
         <v>0.9</v>
@@ -23293,20 +23266,20 @@
         <v>129</v>
       </c>
       <c r="D208" s="105">
-        <f t="shared" ref="D208:G208" si="86">D98*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E208" s="105">
-        <f t="shared" si="86"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="F208" s="105">
-        <f t="shared" si="86"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="G208" s="105">
-        <f t="shared" si="86"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="H208" s="92">
         <v>0.9</v>
@@ -23317,20 +23290,20 @@
         <v>130</v>
       </c>
       <c r="D209" s="105">
-        <f t="shared" ref="D209:G209" si="87">D99*0.7</f>
-        <v>0.7</v>
+        <f t="shared" ref="D209:G211" si="11">IF(D99=1,1,D99*0.9)</f>
+        <v>1</v>
       </c>
       <c r="E209" s="105">
-        <f t="shared" si="87"/>
-        <v>1.036</v>
+        <f t="shared" si="11"/>
+        <v>1.3320000000000001</v>
       </c>
       <c r="F209" s="105">
-        <f t="shared" si="87"/>
-        <v>0.7</v>
+        <f t="shared" si="11"/>
+        <v>1</v>
       </c>
       <c r="G209" s="105">
-        <f t="shared" si="87"/>
-        <v>0.7</v>
+        <f t="shared" si="11"/>
+        <v>1</v>
       </c>
       <c r="H209" s="92">
         <v>0.9</v>
@@ -23341,20 +23314,20 @@
         <v>131</v>
       </c>
       <c r="D210" s="105">
-        <f t="shared" ref="D210:G210" si="88">D100*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="11"/>
+        <v>1</v>
       </c>
       <c r="E210" s="105">
-        <f t="shared" si="88"/>
-        <v>1.9879999999999998</v>
+        <f t="shared" si="11"/>
+        <v>2.556</v>
       </c>
       <c r="F210" s="105">
-        <f t="shared" si="88"/>
-        <v>0.7</v>
+        <f t="shared" si="11"/>
+        <v>1</v>
       </c>
       <c r="G210" s="105">
-        <f t="shared" si="88"/>
-        <v>0.7</v>
+        <f t="shared" si="11"/>
+        <v>1</v>
       </c>
       <c r="H210" s="92">
         <v>0.9</v>
@@ -23365,20 +23338,20 @@
         <v>132</v>
       </c>
       <c r="D211" s="105">
-        <f t="shared" ref="D211:G211" si="89">D101*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="11"/>
+        <v>1</v>
       </c>
       <c r="E211" s="105">
-        <f t="shared" si="89"/>
-        <v>10.08</v>
+        <f t="shared" si="11"/>
+        <v>12.96</v>
       </c>
       <c r="F211" s="105">
-        <f t="shared" si="89"/>
-        <v>2.5829999999999997</v>
+        <f t="shared" si="11"/>
+        <v>3.3210000000000002</v>
       </c>
       <c r="G211" s="105">
-        <f t="shared" si="89"/>
-        <v>2.5829999999999997</v>
+        <f t="shared" si="11"/>
+        <v>3.3210000000000002</v>
       </c>
       <c r="H211" s="92">
         <v>0.9</v>
@@ -23428,20 +23401,20 @@
         <v>129</v>
       </c>
       <c r="D215" s="105">
-        <f>D105*0.7</f>
-        <v>0.7</v>
+        <f>IF(D105=1,1,D105*0.9)</f>
+        <v>1</v>
       </c>
       <c r="E215" s="105">
-        <f t="shared" ref="E215:G215" si="90">E105*0.7</f>
-        <v>0.7</v>
+        <f t="shared" ref="E215:G215" si="12">IF(E105=1,1,E105*0.9)</f>
+        <v>1</v>
       </c>
       <c r="F215" s="105">
-        <f t="shared" si="90"/>
-        <v>0.7</v>
+        <f t="shared" si="12"/>
+        <v>1</v>
       </c>
       <c r="G215" s="105">
-        <f t="shared" si="90"/>
-        <v>0.7</v>
+        <f t="shared" si="12"/>
+        <v>1</v>
       </c>
       <c r="H215" s="92">
         <v>0.9</v>
@@ -23452,20 +23425,20 @@
         <v>130</v>
       </c>
       <c r="D216" s="105">
-        <f t="shared" ref="D216:G216" si="91">D106*0.7</f>
-        <v>0.8819999999999999</v>
+        <f t="shared" ref="D216:G218" si="13">IF(D106=1,1,D106*0.9)</f>
+        <v>1.1340000000000001</v>
       </c>
       <c r="E216" s="105">
-        <f t="shared" si="91"/>
-        <v>0.8819999999999999</v>
+        <f t="shared" si="13"/>
+        <v>1.1340000000000001</v>
       </c>
       <c r="F216" s="105">
-        <f t="shared" si="91"/>
-        <v>0.7</v>
+        <f t="shared" si="13"/>
+        <v>1</v>
       </c>
       <c r="G216" s="105">
-        <f t="shared" si="91"/>
-        <v>0.7</v>
+        <f t="shared" si="13"/>
+        <v>1</v>
       </c>
       <c r="H216" s="92">
         <v>0.9</v>
@@ -23476,20 +23449,20 @@
         <v>131</v>
       </c>
       <c r="D217" s="105">
-        <f t="shared" ref="D217:G217" si="92">D107*0.7</f>
-        <v>1.1759999999999999</v>
+        <f t="shared" si="13"/>
+        <v>1.512</v>
       </c>
       <c r="E217" s="105">
-        <f t="shared" si="92"/>
-        <v>1.1759999999999999</v>
+        <f t="shared" si="13"/>
+        <v>1.512</v>
       </c>
       <c r="F217" s="105">
-        <f t="shared" si="92"/>
-        <v>0.7</v>
+        <f t="shared" si="13"/>
+        <v>1</v>
       </c>
       <c r="G217" s="105">
-        <f t="shared" si="92"/>
-        <v>0.7</v>
+        <f t="shared" si="13"/>
+        <v>1</v>
       </c>
       <c r="H217" s="92">
         <v>0.9</v>
@@ -23500,20 +23473,20 @@
         <v>132</v>
       </c>
       <c r="D218" s="105">
-        <f t="shared" ref="D218:G218" si="93">D108*0.7</f>
-        <v>1.8549999999999998</v>
+        <f t="shared" si="13"/>
+        <v>2.3849999999999998</v>
       </c>
       <c r="E218" s="105">
-        <f t="shared" si="93"/>
-        <v>1.8549999999999998</v>
+        <f t="shared" si="13"/>
+        <v>2.3849999999999998</v>
       </c>
       <c r="F218" s="105">
-        <f t="shared" si="93"/>
-        <v>1.4489999999999998</v>
+        <f t="shared" si="13"/>
+        <v>1.863</v>
       </c>
       <c r="G218" s="105">
-        <f t="shared" si="93"/>
-        <v>1.4489999999999998</v>
+        <f t="shared" si="13"/>
+        <v>1.863</v>
       </c>
       <c r="H218" s="92">
         <v>0.9</v>
@@ -23574,24 +23547,24 @@
         <v>9</v>
       </c>
       <c r="D223" s="105">
-        <f>D3*1.2</f>
-        <v>1.2</v>
+        <f>IF(D3=1,1,D3*1.1)</f>
+        <v>1</v>
       </c>
       <c r="E223" s="105">
-        <f t="shared" ref="E223:H223" si="94">E3*1.2</f>
-        <v>1.2</v>
+        <f t="shared" ref="E223:H223" si="14">IF(E3=1,1,E3*1.1)</f>
+        <v>1</v>
       </c>
       <c r="F223" s="105">
-        <f t="shared" si="94"/>
-        <v>1.2</v>
+        <f t="shared" si="14"/>
+        <v>1</v>
       </c>
       <c r="G223" s="105">
-        <f t="shared" si="94"/>
-        <v>1.2</v>
+        <f t="shared" si="14"/>
+        <v>1</v>
       </c>
       <c r="H223" s="105">
-        <f t="shared" si="94"/>
-        <v>1.2</v>
+        <f t="shared" si="14"/>
+        <v>1</v>
       </c>
       <c r="I223" s="92"/>
     </row>
@@ -23600,24 +23573,24 @@
         <v>267</v>
       </c>
       <c r="D224" s="105">
-        <f t="shared" ref="D224:H224" si="95">D4*1.2</f>
-        <v>1.2</v>
+        <f t="shared" ref="D224:H239" si="15">IF(D4=1,1,D4*1.1)</f>
+        <v>1</v>
       </c>
       <c r="E224" s="105">
-        <f t="shared" si="95"/>
-        <v>2.004</v>
+        <f t="shared" si="15"/>
+        <v>1.837</v>
       </c>
       <c r="F224" s="105">
-        <f t="shared" si="95"/>
-        <v>2.004</v>
+        <f t="shared" si="15"/>
+        <v>1.837</v>
       </c>
       <c r="G224" s="105">
-        <f t="shared" si="95"/>
-        <v>2.004</v>
+        <f t="shared" si="15"/>
+        <v>1.837</v>
       </c>
       <c r="H224" s="105">
-        <f t="shared" si="95"/>
-        <v>2.004</v>
+        <f t="shared" si="15"/>
+        <v>1.837</v>
       </c>
       <c r="I224" s="92"/>
     </row>
@@ -23626,24 +23599,24 @@
         <v>268</v>
       </c>
       <c r="D225" s="105">
-        <f t="shared" ref="D225:H225" si="96">D5*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E225" s="105">
-        <f t="shared" si="96"/>
-        <v>2.8559999999999999</v>
+        <f t="shared" si="15"/>
+        <v>2.6179999999999999</v>
       </c>
       <c r="F225" s="105">
-        <f t="shared" si="96"/>
-        <v>2.8559999999999999</v>
+        <f t="shared" si="15"/>
+        <v>2.6179999999999999</v>
       </c>
       <c r="G225" s="105">
-        <f t="shared" si="96"/>
-        <v>2.8559999999999999</v>
+        <f t="shared" si="15"/>
+        <v>2.6179999999999999</v>
       </c>
       <c r="H225" s="105">
-        <f t="shared" si="96"/>
-        <v>2.8559999999999999</v>
+        <f t="shared" si="15"/>
+        <v>2.6179999999999999</v>
       </c>
       <c r="I225" s="92"/>
     </row>
@@ -23652,24 +23625,24 @@
         <v>269</v>
       </c>
       <c r="D226" s="105">
-        <f t="shared" ref="D226:H226" si="97">D6*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E226" s="105">
-        <f t="shared" si="97"/>
-        <v>7.5960000000000001</v>
+        <f t="shared" si="15"/>
+        <v>6.963000000000001</v>
       </c>
       <c r="F226" s="105">
-        <f t="shared" si="97"/>
-        <v>7.5960000000000001</v>
+        <f t="shared" si="15"/>
+        <v>6.963000000000001</v>
       </c>
       <c r="G226" s="105">
-        <f t="shared" si="97"/>
-        <v>7.5960000000000001</v>
+        <f t="shared" si="15"/>
+        <v>6.963000000000001</v>
       </c>
       <c r="H226" s="105">
-        <f t="shared" si="97"/>
-        <v>7.5960000000000001</v>
+        <f t="shared" si="15"/>
+        <v>6.963000000000001</v>
       </c>
       <c r="I226" s="92"/>
     </row>
@@ -23681,24 +23654,24 @@
         <v>9</v>
       </c>
       <c r="D227" s="105">
-        <f t="shared" ref="D227:H227" si="98">D7*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E227" s="105">
-        <f t="shared" si="98"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="F227" s="105">
-        <f t="shared" si="98"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="G227" s="105">
-        <f t="shared" si="98"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="H227" s="105">
-        <f t="shared" si="98"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="I227" s="92"/>
     </row>
@@ -23707,24 +23680,24 @@
         <v>267</v>
       </c>
       <c r="D228" s="105">
-        <f t="shared" ref="D228:H228" si="99">D8*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E228" s="105">
-        <f t="shared" si="99"/>
-        <v>1.8599999999999999</v>
+        <f t="shared" si="15"/>
+        <v>1.7050000000000003</v>
       </c>
       <c r="F228" s="105">
-        <f t="shared" si="99"/>
-        <v>1.8599999999999999</v>
+        <f t="shared" si="15"/>
+        <v>1.7050000000000003</v>
       </c>
       <c r="G228" s="105">
-        <f t="shared" si="99"/>
-        <v>1.8599999999999999</v>
+        <f t="shared" si="15"/>
+        <v>1.7050000000000003</v>
       </c>
       <c r="H228" s="105">
-        <f t="shared" si="99"/>
-        <v>1.8599999999999999</v>
+        <f t="shared" si="15"/>
+        <v>1.7050000000000003</v>
       </c>
       <c r="I228" s="92"/>
     </row>
@@ -23733,24 +23706,24 @@
         <v>268</v>
       </c>
       <c r="D229" s="105">
-        <f t="shared" ref="D229:H229" si="100">D9*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E229" s="105">
-        <f t="shared" si="100"/>
-        <v>2.6160000000000001</v>
+        <f t="shared" si="15"/>
+        <v>2.3980000000000006</v>
       </c>
       <c r="F229" s="105">
-        <f t="shared" si="100"/>
-        <v>2.6160000000000001</v>
+        <f t="shared" si="15"/>
+        <v>2.3980000000000006</v>
       </c>
       <c r="G229" s="105">
-        <f t="shared" si="100"/>
-        <v>2.6160000000000001</v>
+        <f t="shared" si="15"/>
+        <v>2.3980000000000006</v>
       </c>
       <c r="H229" s="105">
-        <f t="shared" si="100"/>
-        <v>2.6160000000000001</v>
+        <f t="shared" si="15"/>
+        <v>2.3980000000000006</v>
       </c>
       <c r="I229" s="92"/>
     </row>
@@ -23759,24 +23732,24 @@
         <v>269</v>
       </c>
       <c r="D230" s="105">
-        <f t="shared" ref="D230:H230" si="101">D10*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E230" s="105">
-        <f t="shared" si="101"/>
-        <v>7.6679999999999993</v>
+        <f t="shared" si="15"/>
+        <v>7.0289999999999999</v>
       </c>
       <c r="F230" s="105">
-        <f t="shared" si="101"/>
-        <v>7.6679999999999993</v>
+        <f t="shared" si="15"/>
+        <v>7.0289999999999999</v>
       </c>
       <c r="G230" s="105">
-        <f t="shared" si="101"/>
-        <v>7.6679999999999993</v>
+        <f t="shared" si="15"/>
+        <v>7.0289999999999999</v>
       </c>
       <c r="H230" s="105">
-        <f t="shared" si="101"/>
-        <v>7.6679999999999993</v>
+        <f t="shared" si="15"/>
+        <v>7.0289999999999999</v>
       </c>
       <c r="I230" s="92"/>
     </row>
@@ -23788,24 +23761,24 @@
         <v>9</v>
       </c>
       <c r="D231" s="105">
-        <f t="shared" ref="D231:H231" si="102">D11*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E231" s="105">
-        <f t="shared" si="102"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="F231" s="105">
-        <f t="shared" si="102"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="G231" s="105">
-        <f t="shared" si="102"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="H231" s="105">
-        <f t="shared" si="102"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="I231" s="92"/>
     </row>
@@ -23814,24 +23787,24 @@
         <v>267</v>
       </c>
       <c r="D232" s="105">
-        <f t="shared" ref="D232:H232" si="103">D12*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E232" s="105">
-        <f t="shared" si="103"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="F232" s="105">
-        <f t="shared" si="103"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="G232" s="105">
-        <f t="shared" si="103"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="H232" s="105">
-        <f t="shared" si="103"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="I232" s="92"/>
     </row>
@@ -23840,24 +23813,24 @@
         <v>268</v>
       </c>
       <c r="D233" s="105">
-        <f t="shared" ref="D233:H233" si="104">D13*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E233" s="105">
-        <f t="shared" si="104"/>
-        <v>3.3479999999999999</v>
+        <f t="shared" si="15"/>
+        <v>3.0690000000000004</v>
       </c>
       <c r="F233" s="105">
-        <f t="shared" si="104"/>
-        <v>3.3479999999999999</v>
+        <f t="shared" si="15"/>
+        <v>3.0690000000000004</v>
       </c>
       <c r="G233" s="105">
-        <f t="shared" si="104"/>
-        <v>3.3479999999999999</v>
+        <f t="shared" si="15"/>
+        <v>3.0690000000000004</v>
       </c>
       <c r="H233" s="105">
-        <f t="shared" si="104"/>
-        <v>3.3479999999999999</v>
+        <f t="shared" si="15"/>
+        <v>3.0690000000000004</v>
       </c>
       <c r="I233" s="92"/>
     </row>
@@ -23866,24 +23839,24 @@
         <v>269</v>
       </c>
       <c r="D234" s="105">
-        <f t="shared" ref="D234:H234" si="105">D14*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E234" s="105">
-        <f t="shared" si="105"/>
-        <v>7.2119999999999997</v>
+        <f t="shared" si="15"/>
+        <v>6.6110000000000007</v>
       </c>
       <c r="F234" s="105">
-        <f t="shared" si="105"/>
-        <v>7.2119999999999997</v>
+        <f t="shared" si="15"/>
+        <v>6.6110000000000007</v>
       </c>
       <c r="G234" s="105">
-        <f t="shared" si="105"/>
-        <v>7.2119999999999997</v>
+        <f t="shared" si="15"/>
+        <v>6.6110000000000007</v>
       </c>
       <c r="H234" s="105">
-        <f t="shared" si="105"/>
-        <v>7.2119999999999997</v>
+        <f t="shared" si="15"/>
+        <v>6.6110000000000007</v>
       </c>
       <c r="I234" s="92"/>
     </row>
@@ -23895,24 +23868,24 @@
         <v>9</v>
       </c>
       <c r="D235" s="105">
-        <f t="shared" ref="D235:H235" si="106">D15*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E235" s="105">
-        <f t="shared" si="106"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="F235" s="105">
-        <f t="shared" si="106"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="G235" s="105">
-        <f t="shared" si="106"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="H235" s="105">
-        <f t="shared" si="106"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="I235" s="92"/>
     </row>
@@ -23921,24 +23894,24 @@
         <v>267</v>
       </c>
       <c r="D236" s="105">
-        <f t="shared" ref="D236:H236" si="107">D16*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E236" s="105">
-        <f t="shared" si="107"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="F236" s="105">
-        <f t="shared" si="107"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="G236" s="105">
-        <f t="shared" si="107"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="H236" s="105">
-        <f t="shared" si="107"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="I236" s="92"/>
     </row>
@@ -23947,24 +23920,24 @@
         <v>268</v>
       </c>
       <c r="D237" s="105">
-        <f t="shared" ref="D237:H237" si="108">D17*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E237" s="105">
-        <f t="shared" si="108"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="F237" s="105">
-        <f t="shared" si="108"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="G237" s="105">
-        <f t="shared" si="108"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="H237" s="105">
-        <f t="shared" si="108"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="I237" s="92"/>
     </row>
@@ -23973,24 +23946,24 @@
         <v>269</v>
       </c>
       <c r="D238" s="105">
-        <f t="shared" ref="D238:H238" si="109">D18*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E238" s="105">
-        <f t="shared" si="109"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="F238" s="105">
-        <f t="shared" si="109"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="G238" s="105">
-        <f t="shared" si="109"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="H238" s="105">
-        <f t="shared" si="109"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="I238" s="92"/>
     </row>
@@ -24002,24 +23975,24 @@
         <v>9</v>
       </c>
       <c r="D239" s="105">
-        <f t="shared" ref="D239:H239" si="110">D19*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E239" s="105">
-        <f t="shared" si="110"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="F239" s="105">
-        <f t="shared" si="110"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="G239" s="105">
-        <f t="shared" si="110"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="H239" s="105">
-        <f t="shared" si="110"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="I239" s="92"/>
     </row>
@@ -24028,24 +24001,24 @@
         <v>267</v>
       </c>
       <c r="D240" s="105">
-        <f t="shared" ref="D240:H240" si="111">D20*1.2</f>
-        <v>1.2</v>
+        <f t="shared" ref="D240:H246" si="16">IF(D20=1,1,D20*1.1)</f>
+        <v>1</v>
       </c>
       <c r="E240" s="105">
-        <f t="shared" si="111"/>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="F240" s="105">
-        <f t="shared" si="111"/>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="G240" s="105">
-        <f t="shared" si="111"/>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="H240" s="105">
-        <f t="shared" si="111"/>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="I240" s="92"/>
     </row>
@@ -24054,24 +24027,24 @@
         <v>268</v>
       </c>
       <c r="D241" s="105">
-        <f t="shared" ref="D241:H241" si="112">D21*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="E241" s="105">
-        <f t="shared" si="112"/>
-        <v>2.2320000000000002</v>
+        <f t="shared" si="16"/>
+        <v>2.0460000000000003</v>
       </c>
       <c r="F241" s="105">
-        <f t="shared" si="112"/>
-        <v>2.2320000000000002</v>
+        <f t="shared" si="16"/>
+        <v>2.0460000000000003</v>
       </c>
       <c r="G241" s="105">
-        <f t="shared" si="112"/>
-        <v>2.2320000000000002</v>
+        <f t="shared" si="16"/>
+        <v>2.0460000000000003</v>
       </c>
       <c r="H241" s="105">
-        <f t="shared" si="112"/>
-        <v>2.2320000000000002</v>
+        <f t="shared" si="16"/>
+        <v>2.0460000000000003</v>
       </c>
       <c r="I241" s="92"/>
     </row>
@@ -24080,24 +24053,24 @@
         <v>269</v>
       </c>
       <c r="D242" s="105">
-        <f t="shared" ref="D242:H242" si="113">D22*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="E242" s="105">
-        <f t="shared" si="113"/>
-        <v>3.6119999999999997</v>
+        <f t="shared" si="16"/>
+        <v>3.3109999999999999</v>
       </c>
       <c r="F242" s="105">
-        <f t="shared" si="113"/>
-        <v>3.6119999999999997</v>
+        <f t="shared" si="16"/>
+        <v>3.3109999999999999</v>
       </c>
       <c r="G242" s="105">
-        <f t="shared" si="113"/>
-        <v>3.6119999999999997</v>
+        <f t="shared" si="16"/>
+        <v>3.3109999999999999</v>
       </c>
       <c r="H242" s="105">
-        <f t="shared" si="113"/>
-        <v>3.6119999999999997</v>
+        <f t="shared" si="16"/>
+        <v>3.3109999999999999</v>
       </c>
       <c r="I242" s="92"/>
     </row>
@@ -24109,24 +24082,24 @@
         <v>9</v>
       </c>
       <c r="D243" s="105">
-        <f t="shared" ref="D243:H243" si="114">D23*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="E243" s="105">
-        <f t="shared" si="114"/>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="F243" s="105">
-        <f t="shared" si="114"/>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="G243" s="105">
-        <f t="shared" si="114"/>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="H243" s="105">
-        <f t="shared" si="114"/>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="I243" s="92"/>
     </row>
@@ -24135,24 +24108,24 @@
         <v>267</v>
       </c>
       <c r="D244" s="105">
-        <f t="shared" ref="D244:H244" si="115">D24*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="E244" s="105">
-        <f t="shared" si="115"/>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="F244" s="105">
-        <f t="shared" si="115"/>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="G244" s="105">
-        <f t="shared" si="115"/>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="H244" s="105">
-        <f t="shared" si="115"/>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="I244" s="92"/>
     </row>
@@ -24161,24 +24134,24 @@
         <v>268</v>
       </c>
       <c r="D245" s="105">
-        <f t="shared" ref="D245:H245" si="116">D25*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="E245" s="105">
-        <f t="shared" si="116"/>
-        <v>2.2320000000000002</v>
+        <f t="shared" si="16"/>
+        <v>2.0460000000000003</v>
       </c>
       <c r="F245" s="105">
-        <f t="shared" si="116"/>
-        <v>2.2320000000000002</v>
+        <f t="shared" si="16"/>
+        <v>2.0460000000000003</v>
       </c>
       <c r="G245" s="105">
-        <f t="shared" si="116"/>
-        <v>2.2320000000000002</v>
+        <f t="shared" si="16"/>
+        <v>2.0460000000000003</v>
       </c>
       <c r="H245" s="105">
-        <f t="shared" si="116"/>
-        <v>2.2320000000000002</v>
+        <f t="shared" si="16"/>
+        <v>2.0460000000000003</v>
       </c>
       <c r="I245" s="92"/>
     </row>
@@ -24187,24 +24160,24 @@
         <v>269</v>
       </c>
       <c r="D246" s="105">
-        <f t="shared" ref="D246:H246" si="117">D26*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="E246" s="105">
-        <f t="shared" si="117"/>
-        <v>3.6119999999999997</v>
+        <f t="shared" si="16"/>
+        <v>3.3109999999999999</v>
       </c>
       <c r="F246" s="105">
-        <f t="shared" si="117"/>
-        <v>3.6119999999999997</v>
+        <f t="shared" si="16"/>
+        <v>3.3109999999999999</v>
       </c>
       <c r="G246" s="105">
-        <f t="shared" si="117"/>
-        <v>3.6119999999999997</v>
+        <f t="shared" si="16"/>
+        <v>3.3109999999999999</v>
       </c>
       <c r="H246" s="105">
-        <f t="shared" si="117"/>
-        <v>3.6119999999999997</v>
+        <f t="shared" si="16"/>
+        <v>3.3109999999999999</v>
       </c>
       <c r="I246" s="92"/>
     </row>
@@ -24257,24 +24230,24 @@
         <v>9</v>
       </c>
       <c r="D250" s="105">
-        <f>D30*1.2</f>
-        <v>1.2</v>
+        <f>IF(D30=1,1,D30*1.1)</f>
+        <v>1</v>
       </c>
       <c r="E250" s="105">
-        <f t="shared" ref="E250:H250" si="118">E30*1.2</f>
-        <v>1.2</v>
+        <f t="shared" ref="E250:H250" si="17">IF(E30=1,1,E30*1.1)</f>
+        <v>1</v>
       </c>
       <c r="F250" s="105">
-        <f t="shared" si="118"/>
-        <v>1.2</v>
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="G250" s="105">
-        <f t="shared" si="118"/>
-        <v>1.2</v>
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="H250" s="105">
-        <f t="shared" si="118"/>
-        <v>1.2</v>
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="I250" s="94"/>
     </row>
@@ -24283,24 +24256,24 @@
         <v>267</v>
       </c>
       <c r="D251" s="105">
-        <f t="shared" ref="D251:H251" si="119">D31*1.2</f>
-        <v>1.2</v>
+        <f t="shared" ref="D251:H266" si="18">IF(D31=1,1,D31*1.1)</f>
+        <v>1</v>
       </c>
       <c r="E251" s="105">
-        <f t="shared" si="119"/>
-        <v>1.92</v>
+        <f t="shared" si="18"/>
+        <v>1.7600000000000002</v>
       </c>
       <c r="F251" s="105">
-        <f t="shared" si="119"/>
-        <v>1.92</v>
+        <f t="shared" si="18"/>
+        <v>1.7600000000000002</v>
       </c>
       <c r="G251" s="105">
-        <f t="shared" si="119"/>
-        <v>1.92</v>
+        <f t="shared" si="18"/>
+        <v>1.7600000000000002</v>
       </c>
       <c r="H251" s="105">
-        <f t="shared" si="119"/>
-        <v>1.92</v>
+        <f t="shared" si="18"/>
+        <v>1.7600000000000002</v>
       </c>
       <c r="I251" s="92"/>
     </row>
@@ -24309,24 +24282,24 @@
         <v>209</v>
       </c>
       <c r="D252" s="105">
-        <f t="shared" ref="D252:H252" si="120">D32*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E252" s="105">
-        <f t="shared" si="120"/>
-        <v>4.0919999999999996</v>
+        <f t="shared" si="18"/>
+        <v>3.7510000000000003</v>
       </c>
       <c r="F252" s="105">
-        <f t="shared" si="120"/>
-        <v>4.0919999999999996</v>
+        <f t="shared" si="18"/>
+        <v>3.7510000000000003</v>
       </c>
       <c r="G252" s="105">
-        <f t="shared" si="120"/>
-        <v>4.0919999999999996</v>
+        <f t="shared" si="18"/>
+        <v>3.7510000000000003</v>
       </c>
       <c r="H252" s="105">
-        <f t="shared" si="120"/>
-        <v>4.0919999999999996</v>
+        <f t="shared" si="18"/>
+        <v>3.7510000000000003</v>
       </c>
       <c r="I252" s="92"/>
     </row>
@@ -24335,24 +24308,24 @@
         <v>208</v>
       </c>
       <c r="D253" s="105">
-        <f t="shared" ref="D253:H253" si="121">D33*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E253" s="105">
-        <f t="shared" si="121"/>
-        <v>14.795999999999999</v>
+        <f t="shared" si="18"/>
+        <v>13.563000000000001</v>
       </c>
       <c r="F253" s="105">
-        <f t="shared" si="121"/>
-        <v>14.795999999999999</v>
+        <f t="shared" si="18"/>
+        <v>13.563000000000001</v>
       </c>
       <c r="G253" s="105">
-        <f t="shared" si="121"/>
-        <v>14.795999999999999</v>
+        <f t="shared" si="18"/>
+        <v>13.563000000000001</v>
       </c>
       <c r="H253" s="105">
-        <f t="shared" si="121"/>
-        <v>14.795999999999999</v>
+        <f t="shared" si="18"/>
+        <v>13.563000000000001</v>
       </c>
       <c r="I253" s="92"/>
     </row>
@@ -24364,24 +24337,24 @@
         <v>9</v>
       </c>
       <c r="D254" s="105">
-        <f t="shared" ref="D254:H254" si="122">D34*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E254" s="105">
-        <f t="shared" si="122"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="F254" s="105">
-        <f t="shared" si="122"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="G254" s="105">
-        <f t="shared" si="122"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="H254" s="105">
-        <f t="shared" si="122"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="I254" s="92"/>
     </row>
@@ -24390,24 +24363,24 @@
         <v>267</v>
       </c>
       <c r="D255" s="105">
-        <f t="shared" ref="D255:H255" si="123">D35*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E255" s="105">
-        <f t="shared" si="123"/>
-        <v>2.3039999999999998</v>
+        <f t="shared" si="18"/>
+        <v>2.1120000000000001</v>
       </c>
       <c r="F255" s="105">
-        <f t="shared" si="123"/>
-        <v>2.3039999999999998</v>
+        <f t="shared" si="18"/>
+        <v>2.1120000000000001</v>
       </c>
       <c r="G255" s="105">
-        <f t="shared" si="123"/>
-        <v>2.3039999999999998</v>
+        <f t="shared" si="18"/>
+        <v>2.1120000000000001</v>
       </c>
       <c r="H255" s="105">
-        <f t="shared" si="123"/>
-        <v>2.3039999999999998</v>
+        <f t="shared" si="18"/>
+        <v>2.1120000000000001</v>
       </c>
       <c r="I255" s="92"/>
     </row>
@@ -24416,24 +24389,24 @@
         <v>209</v>
       </c>
       <c r="D256" s="105">
-        <f t="shared" ref="D256:H256" si="124">D36*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E256" s="105">
-        <f t="shared" si="124"/>
-        <v>5.5919999999999996</v>
+        <f t="shared" si="18"/>
+        <v>5.1260000000000003</v>
       </c>
       <c r="F256" s="105">
-        <f t="shared" si="124"/>
-        <v>5.5919999999999996</v>
+        <f t="shared" si="18"/>
+        <v>5.1260000000000003</v>
       </c>
       <c r="G256" s="105">
-        <f t="shared" si="124"/>
-        <v>5.5919999999999996</v>
+        <f t="shared" si="18"/>
+        <v>5.1260000000000003</v>
       </c>
       <c r="H256" s="105">
-        <f t="shared" si="124"/>
-        <v>5.5919999999999996</v>
+        <f t="shared" si="18"/>
+        <v>5.1260000000000003</v>
       </c>
       <c r="I256" s="92"/>
     </row>
@@ -24442,24 +24415,24 @@
         <v>208</v>
       </c>
       <c r="D257" s="105">
-        <f t="shared" ref="D257:H257" si="125">D37*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E257" s="105">
-        <f t="shared" si="125"/>
-        <v>11.616</v>
+        <f t="shared" si="18"/>
+        <v>10.648</v>
       </c>
       <c r="F257" s="105">
-        <f t="shared" si="125"/>
-        <v>11.616</v>
+        <f t="shared" si="18"/>
+        <v>10.648</v>
       </c>
       <c r="G257" s="105">
-        <f t="shared" si="125"/>
-        <v>11.616</v>
+        <f t="shared" si="18"/>
+        <v>10.648</v>
       </c>
       <c r="H257" s="105">
-        <f t="shared" si="125"/>
-        <v>11.616</v>
+        <f t="shared" si="18"/>
+        <v>10.648</v>
       </c>
       <c r="I257" s="92"/>
     </row>
@@ -24471,24 +24444,24 @@
         <v>9</v>
       </c>
       <c r="D258" s="105">
-        <f t="shared" ref="D258:H258" si="126">D38*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E258" s="105">
-        <f t="shared" si="126"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="F258" s="105">
-        <f t="shared" si="126"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="G258" s="105">
-        <f t="shared" si="126"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="H258" s="105">
-        <f t="shared" si="126"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="I258" s="92"/>
     </row>
@@ -24497,24 +24470,24 @@
         <v>267</v>
       </c>
       <c r="D259" s="105">
-        <f t="shared" ref="D259:H259" si="127">D39*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E259" s="105">
-        <f t="shared" si="127"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="F259" s="105">
-        <f t="shared" si="127"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="G259" s="105">
-        <f t="shared" si="127"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="H259" s="105">
-        <f t="shared" si="127"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="I259" s="92"/>
     </row>
@@ -24523,24 +24496,24 @@
         <v>209</v>
       </c>
       <c r="D260" s="105">
-        <f t="shared" ref="D260:H260" si="128">D40*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E260" s="105">
-        <f t="shared" si="128"/>
-        <v>3.0960000000000001</v>
+        <f t="shared" si="18"/>
+        <v>2.8380000000000005</v>
       </c>
       <c r="F260" s="105">
-        <f t="shared" si="128"/>
-        <v>3.0960000000000001</v>
+        <f t="shared" si="18"/>
+        <v>2.8380000000000005</v>
       </c>
       <c r="G260" s="105">
-        <f t="shared" si="128"/>
-        <v>3.0960000000000001</v>
+        <f t="shared" si="18"/>
+        <v>2.8380000000000005</v>
       </c>
       <c r="H260" s="105">
-        <f t="shared" si="128"/>
-        <v>3.0960000000000001</v>
+        <f t="shared" si="18"/>
+        <v>2.8380000000000005</v>
       </c>
       <c r="I260" s="92"/>
     </row>
@@ -24549,24 +24522,24 @@
         <v>208</v>
       </c>
       <c r="D261" s="105">
-        <f t="shared" ref="D261:H261" si="129">D41*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E261" s="105">
-        <f t="shared" si="129"/>
-        <v>11.556000000000001</v>
+        <f t="shared" si="18"/>
+        <v>10.593000000000002</v>
       </c>
       <c r="F261" s="105">
-        <f t="shared" si="129"/>
-        <v>11.556000000000001</v>
+        <f t="shared" si="18"/>
+        <v>10.593000000000002</v>
       </c>
       <c r="G261" s="105">
-        <f t="shared" si="129"/>
-        <v>11.556000000000001</v>
+        <f t="shared" si="18"/>
+        <v>10.593000000000002</v>
       </c>
       <c r="H261" s="105">
-        <f t="shared" si="129"/>
-        <v>11.556000000000001</v>
+        <f t="shared" si="18"/>
+        <v>10.593000000000002</v>
       </c>
       <c r="I261" s="92"/>
     </row>
@@ -24578,24 +24551,24 @@
         <v>9</v>
       </c>
       <c r="D262" s="105">
-        <f t="shared" ref="D262:H262" si="130">D42*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E262" s="105">
-        <f t="shared" si="130"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="F262" s="105">
-        <f t="shared" si="130"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="G262" s="105">
-        <f t="shared" si="130"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="H262" s="105">
-        <f t="shared" si="130"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="I262" s="92"/>
     </row>
@@ -24604,24 +24577,24 @@
         <v>267</v>
       </c>
       <c r="D263" s="105">
-        <f t="shared" ref="D263:H263" si="131">D43*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E263" s="105">
-        <f t="shared" si="131"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="F263" s="105">
-        <f t="shared" si="131"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="G263" s="105">
-        <f t="shared" si="131"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="H263" s="105">
-        <f t="shared" si="131"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="I263" s="92"/>
     </row>
@@ -24630,24 +24603,24 @@
         <v>209</v>
       </c>
       <c r="D264" s="105">
-        <f t="shared" ref="D264:H264" si="132">D44*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E264" s="105">
-        <f t="shared" si="132"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="F264" s="105">
-        <f t="shared" si="132"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="G264" s="105">
-        <f t="shared" si="132"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="H264" s="105">
-        <f t="shared" si="132"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="I264" s="92"/>
     </row>
@@ -24656,24 +24629,24 @@
         <v>208</v>
       </c>
       <c r="D265" s="105">
-        <f t="shared" ref="D265:H265" si="133">D45*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E265" s="105">
-        <f t="shared" si="133"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="F265" s="105">
-        <f t="shared" si="133"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="G265" s="105">
-        <f t="shared" si="133"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="H265" s="105">
-        <f t="shared" si="133"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="I265" s="92"/>
     </row>
@@ -24685,24 +24658,24 @@
         <v>9</v>
       </c>
       <c r="D266" s="105">
-        <f t="shared" ref="D266:H266" si="134">D46*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E266" s="105">
-        <f t="shared" si="134"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="F266" s="105">
-        <f t="shared" si="134"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="G266" s="105">
-        <f t="shared" si="134"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="H266" s="105">
-        <f t="shared" si="134"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="I266" s="92"/>
     </row>
@@ -24711,24 +24684,24 @@
         <v>267</v>
       </c>
       <c r="D267" s="105">
-        <f t="shared" ref="D267:H267" si="135">D47*1.2</f>
-        <v>1.2</v>
+        <f t="shared" ref="D267:H273" si="19">IF(D47=1,1,D47*1.1)</f>
+        <v>1</v>
       </c>
       <c r="E267" s="105">
-        <f t="shared" si="135"/>
-        <v>1.9799999999999998</v>
+        <f t="shared" si="19"/>
+        <v>1.8149999999999999</v>
       </c>
       <c r="F267" s="105">
-        <f t="shared" si="135"/>
-        <v>1.9799999999999998</v>
+        <f t="shared" si="19"/>
+        <v>1.8149999999999999</v>
       </c>
       <c r="G267" s="105">
-        <f t="shared" si="135"/>
-        <v>1.9799999999999998</v>
+        <f t="shared" si="19"/>
+        <v>1.8149999999999999</v>
       </c>
       <c r="H267" s="105">
-        <f t="shared" si="135"/>
-        <v>1.9799999999999998</v>
+        <f t="shared" si="19"/>
+        <v>1.8149999999999999</v>
       </c>
       <c r="I267" s="92"/>
     </row>
@@ -24737,24 +24710,24 @@
         <v>209</v>
       </c>
       <c r="D268" s="105">
-        <f t="shared" ref="D268:H268" si="136">D48*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="19"/>
+        <v>1</v>
       </c>
       <c r="E268" s="105">
-        <f t="shared" si="136"/>
-        <v>3.2759999999999998</v>
+        <f t="shared" si="19"/>
+        <v>3.0030000000000001</v>
       </c>
       <c r="F268" s="105">
-        <f t="shared" si="136"/>
-        <v>3.2759999999999998</v>
+        <f t="shared" si="19"/>
+        <v>3.0030000000000001</v>
       </c>
       <c r="G268" s="105">
-        <f t="shared" si="136"/>
-        <v>3.2759999999999998</v>
+        <f t="shared" si="19"/>
+        <v>3.0030000000000001</v>
       </c>
       <c r="H268" s="105">
-        <f t="shared" si="136"/>
-        <v>3.2759999999999998</v>
+        <f t="shared" si="19"/>
+        <v>3.0030000000000001</v>
       </c>
       <c r="I268" s="92"/>
     </row>
@@ -24763,24 +24736,24 @@
         <v>208</v>
       </c>
       <c r="D269" s="105">
-        <f t="shared" ref="D269:H269" si="137">D49*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="19"/>
+        <v>1</v>
       </c>
       <c r="E269" s="105">
-        <f t="shared" si="137"/>
-        <v>13.452</v>
+        <f t="shared" si="19"/>
+        <v>12.331000000000001</v>
       </c>
       <c r="F269" s="105">
-        <f t="shared" si="137"/>
-        <v>13.452</v>
+        <f t="shared" si="19"/>
+        <v>12.331000000000001</v>
       </c>
       <c r="G269" s="105">
-        <f t="shared" si="137"/>
-        <v>13.452</v>
+        <f t="shared" si="19"/>
+        <v>12.331000000000001</v>
       </c>
       <c r="H269" s="105">
-        <f t="shared" si="137"/>
-        <v>13.452</v>
+        <f t="shared" si="19"/>
+        <v>12.331000000000001</v>
       </c>
       <c r="I269" s="92"/>
     </row>
@@ -24792,24 +24765,24 @@
         <v>9</v>
       </c>
       <c r="D270" s="105">
-        <f t="shared" ref="D270:H270" si="138">D50*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="19"/>
+        <v>1</v>
       </c>
       <c r="E270" s="105">
-        <f t="shared" si="138"/>
-        <v>1.2</v>
+        <f t="shared" si="19"/>
+        <v>1</v>
       </c>
       <c r="F270" s="105">
-        <f t="shared" si="138"/>
-        <v>1.2</v>
+        <f t="shared" si="19"/>
+        <v>1</v>
       </c>
       <c r="G270" s="105">
-        <f t="shared" si="138"/>
-        <v>1.2</v>
+        <f t="shared" si="19"/>
+        <v>1</v>
       </c>
       <c r="H270" s="105">
-        <f t="shared" si="138"/>
-        <v>1.2</v>
+        <f t="shared" si="19"/>
+        <v>1</v>
       </c>
       <c r="I270" s="92"/>
     </row>
@@ -24818,24 +24791,24 @@
         <v>267</v>
       </c>
       <c r="D271" s="105">
-        <f t="shared" ref="D271:H271" si="139">D51*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="19"/>
+        <v>1</v>
       </c>
       <c r="E271" s="105">
-        <f t="shared" si="139"/>
-        <v>1.9799999999999998</v>
+        <f t="shared" si="19"/>
+        <v>1.8149999999999999</v>
       </c>
       <c r="F271" s="105">
-        <f t="shared" si="139"/>
-        <v>1.9799999999999998</v>
+        <f t="shared" si="19"/>
+        <v>1.8149999999999999</v>
       </c>
       <c r="G271" s="105">
-        <f t="shared" si="139"/>
-        <v>1.9799999999999998</v>
+        <f t="shared" si="19"/>
+        <v>1.8149999999999999</v>
       </c>
       <c r="H271" s="105">
-        <f t="shared" si="139"/>
-        <v>1.9799999999999998</v>
+        <f t="shared" si="19"/>
+        <v>1.8149999999999999</v>
       </c>
       <c r="I271" s="92"/>
     </row>
@@ -24844,24 +24817,24 @@
         <v>209</v>
       </c>
       <c r="D272" s="105">
-        <f t="shared" ref="D272:H272" si="140">D52*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="19"/>
+        <v>1</v>
       </c>
       <c r="E272" s="105">
-        <f t="shared" si="140"/>
-        <v>3.2759999999999998</v>
+        <f t="shared" si="19"/>
+        <v>3.0030000000000001</v>
       </c>
       <c r="F272" s="105">
-        <f t="shared" si="140"/>
-        <v>3.2759999999999998</v>
+        <f t="shared" si="19"/>
+        <v>3.0030000000000001</v>
       </c>
       <c r="G272" s="105">
-        <f t="shared" si="140"/>
-        <v>3.2759999999999998</v>
+        <f t="shared" si="19"/>
+        <v>3.0030000000000001</v>
       </c>
       <c r="H272" s="105">
-        <f t="shared" si="140"/>
-        <v>3.2759999999999998</v>
+        <f t="shared" si="19"/>
+        <v>3.0030000000000001</v>
       </c>
       <c r="I272" s="92"/>
     </row>
@@ -24870,24 +24843,24 @@
         <v>208</v>
       </c>
       <c r="D273" s="105">
-        <f t="shared" ref="D273:H273" si="141">D53*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="19"/>
+        <v>1</v>
       </c>
       <c r="E273" s="105">
-        <f t="shared" si="141"/>
-        <v>13.452</v>
+        <f t="shared" si="19"/>
+        <v>12.331000000000001</v>
       </c>
       <c r="F273" s="105">
-        <f t="shared" si="141"/>
-        <v>13.452</v>
+        <f t="shared" si="19"/>
+        <v>12.331000000000001</v>
       </c>
       <c r="G273" s="105">
-        <f t="shared" si="141"/>
-        <v>13.452</v>
+        <f t="shared" si="19"/>
+        <v>12.331000000000001</v>
       </c>
       <c r="H273" s="105">
-        <f t="shared" si="141"/>
-        <v>13.452</v>
+        <f t="shared" si="19"/>
+        <v>12.331000000000001</v>
       </c>
       <c r="I273" s="92"/>
     </row>
@@ -24941,20 +24914,20 @@
         <v>273</v>
       </c>
       <c r="D277" s="105">
-        <f>D57*1.2</f>
-        <v>1.2</v>
+        <f>IF(D57=1,1,D57*1.1)</f>
+        <v>1</v>
       </c>
       <c r="E277" s="105">
-        <f t="shared" ref="E277:G277" si="142">E57*1.2</f>
-        <v>1.2</v>
+        <f t="shared" ref="E277:G277" si="20">IF(E57=1,1,E57*1.1)</f>
+        <v>1</v>
       </c>
       <c r="F277" s="105">
-        <f t="shared" si="142"/>
-        <v>1.2</v>
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="G277" s="105">
-        <f t="shared" si="142"/>
-        <v>1.2</v>
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="H277" s="92"/>
     </row>
@@ -24963,20 +24936,20 @@
         <v>274</v>
       </c>
       <c r="D278" s="105">
-        <f t="shared" ref="D278:G278" si="143">D58*1.2</f>
-        <v>12.81</v>
+        <f t="shared" ref="D278:G282" si="21">IF(D58=1,1,D58*1.1)</f>
+        <v>11.742500000000001</v>
       </c>
       <c r="E278" s="105">
-        <f t="shared" si="143"/>
-        <v>12.81</v>
+        <f t="shared" si="21"/>
+        <v>11.742500000000001</v>
       </c>
       <c r="F278" s="105">
-        <f t="shared" si="143"/>
-        <v>12.81</v>
+        <f t="shared" si="21"/>
+        <v>11.742500000000001</v>
       </c>
       <c r="G278" s="105">
-        <f t="shared" si="143"/>
-        <v>12.81</v>
+        <f t="shared" si="21"/>
+        <v>11.742500000000001</v>
       </c>
       <c r="H278" s="92"/>
     </row>
@@ -24988,20 +24961,20 @@
         <v>273</v>
       </c>
       <c r="D279" s="105">
-        <f t="shared" ref="D279:G279" si="144">D59*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="E279" s="105">
-        <f t="shared" si="144"/>
-        <v>1.2</v>
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="F279" s="105">
-        <f t="shared" si="144"/>
-        <v>1.2</v>
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="G279" s="105">
-        <f t="shared" si="144"/>
-        <v>1.2</v>
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="H279" s="92"/>
     </row>
@@ -25010,20 +24983,20 @@
         <v>274</v>
       </c>
       <c r="D280" s="105">
-        <f t="shared" ref="D280:G280" si="145">D60*1.2</f>
-        <v>12.81</v>
+        <f t="shared" si="21"/>
+        <v>11.742500000000001</v>
       </c>
       <c r="E280" s="105">
-        <f t="shared" si="145"/>
-        <v>12.81</v>
+        <f t="shared" si="21"/>
+        <v>11.742500000000001</v>
       </c>
       <c r="F280" s="105">
-        <f t="shared" si="145"/>
-        <v>12.81</v>
+        <f t="shared" si="21"/>
+        <v>11.742500000000001</v>
       </c>
       <c r="G280" s="105">
-        <f t="shared" si="145"/>
-        <v>12.81</v>
+        <f t="shared" si="21"/>
+        <v>11.742500000000001</v>
       </c>
       <c r="H280" s="92"/>
     </row>
@@ -25035,20 +25008,20 @@
         <v>273</v>
       </c>
       <c r="D281" s="105">
-        <f t="shared" ref="D281:G281" si="146">D61*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="E281" s="105">
-        <f t="shared" si="146"/>
-        <v>1.2</v>
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="F281" s="105">
-        <f t="shared" si="146"/>
-        <v>1.2</v>
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="G281" s="105">
-        <f t="shared" si="146"/>
-        <v>1.2</v>
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="H281" s="92"/>
     </row>
@@ -25057,20 +25030,20 @@
         <v>274</v>
       </c>
       <c r="D282" s="105">
-        <f t="shared" ref="D282:G282" si="147">D62*1.2</f>
-        <v>12.81</v>
+        <f t="shared" si="21"/>
+        <v>11.742500000000001</v>
       </c>
       <c r="E282" s="105">
-        <f t="shared" si="147"/>
-        <v>12.81</v>
+        <f t="shared" si="21"/>
+        <v>11.742500000000001</v>
       </c>
       <c r="F282" s="105">
-        <f t="shared" si="147"/>
-        <v>12.81</v>
+        <f t="shared" si="21"/>
+        <v>11.742500000000001</v>
       </c>
       <c r="G282" s="105">
-        <f t="shared" si="147"/>
-        <v>12.81</v>
+        <f t="shared" si="21"/>
+        <v>11.742500000000001</v>
       </c>
       <c r="H282" s="92"/>
     </row>
@@ -25127,20 +25100,20 @@
         <v>129</v>
       </c>
       <c r="D286" s="105">
-        <f>D66*1.2</f>
-        <v>1.2</v>
+        <f>IF(D66=1,1,D66*1.1)</f>
+        <v>1.4850000000000003</v>
       </c>
       <c r="E286" s="105">
-        <f t="shared" ref="E286:G286" si="148">E66*1.2</f>
-        <v>1.2</v>
+        <f t="shared" ref="E286:G286" si="22">IF(E66=1,1,E66*1.1)</f>
+        <v>1</v>
       </c>
       <c r="F286" s="105">
-        <f t="shared" si="148"/>
-        <v>1.2</v>
+        <f t="shared" si="22"/>
+        <v>1</v>
       </c>
       <c r="G286" s="105">
-        <f t="shared" si="148"/>
-        <v>1.2</v>
+        <f t="shared" si="22"/>
+        <v>1</v>
       </c>
       <c r="H286" s="92">
         <v>1.05</v>
@@ -25152,20 +25125,20 @@
         <v>130</v>
       </c>
       <c r="D287" s="105">
-        <f t="shared" ref="D287:G287" si="149">D67*1.2</f>
-        <v>1.62</v>
+        <f t="shared" ref="D287:G302" si="23">IF(D67=1,1,D67*1.1)</f>
+        <v>1.4850000000000003</v>
       </c>
       <c r="E287" s="105">
-        <f t="shared" si="149"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F287" s="105">
-        <f t="shared" si="149"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G287" s="105">
-        <f t="shared" si="149"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H287" s="92">
         <v>1.05</v>
@@ -25177,20 +25150,20 @@
         <v>131</v>
       </c>
       <c r="D288" s="105">
-        <f t="shared" ref="D288:G288" si="150">D68*1.2</f>
-        <v>1.62</v>
+        <f t="shared" si="23"/>
+        <v>1.4850000000000003</v>
       </c>
       <c r="E288" s="105">
-        <f t="shared" si="150"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F288" s="105">
-        <f t="shared" si="150"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G288" s="105">
-        <f t="shared" si="150"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H288" s="92">
         <v>1.05</v>
@@ -25202,20 +25175,20 @@
         <v>132</v>
       </c>
       <c r="D289" s="105">
-        <f t="shared" ref="D289:G289" si="151">D69*1.2</f>
-        <v>6.48</v>
+        <f t="shared" si="23"/>
+        <v>5.9400000000000013</v>
       </c>
       <c r="E289" s="105">
-        <f t="shared" si="151"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F289" s="105">
-        <f t="shared" si="151"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G289" s="105">
-        <f t="shared" si="151"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H289" s="92">
         <v>1.05</v>
@@ -25230,20 +25203,20 @@
         <v>129</v>
       </c>
       <c r="D290" s="105">
-        <f t="shared" ref="D290:G290" si="152">D70*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1.4850000000000003</v>
       </c>
       <c r="E290" s="105">
-        <f t="shared" si="152"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F290" s="105">
-        <f t="shared" si="152"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G290" s="105">
-        <f t="shared" si="152"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H290" s="92">
         <v>1.05</v>
@@ -25255,20 +25228,20 @@
         <v>130</v>
       </c>
       <c r="D291" s="105">
-        <f t="shared" ref="D291:G291" si="153">D71*1.2</f>
-        <v>1.62</v>
+        <f t="shared" si="23"/>
+        <v>1.4850000000000003</v>
       </c>
       <c r="E291" s="105">
-        <f t="shared" si="153"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F291" s="105">
-        <f t="shared" si="153"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G291" s="105">
-        <f t="shared" si="153"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H291" s="92">
         <v>1.05</v>
@@ -25280,20 +25253,20 @@
         <v>131</v>
       </c>
       <c r="D292" s="105">
-        <f t="shared" ref="D292:G292" si="154">D72*1.2</f>
-        <v>1.62</v>
+        <f t="shared" si="23"/>
+        <v>1.4850000000000003</v>
       </c>
       <c r="E292" s="105">
-        <f t="shared" si="154"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F292" s="105">
-        <f t="shared" si="154"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G292" s="105">
-        <f t="shared" si="154"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H292" s="92">
         <v>1.05</v>
@@ -25305,20 +25278,20 @@
         <v>132</v>
       </c>
       <c r="D293" s="105">
-        <f t="shared" ref="D293:G293" si="155">D73*1.2</f>
-        <v>6.48</v>
+        <f t="shared" si="23"/>
+        <v>5.9400000000000013</v>
       </c>
       <c r="E293" s="105">
-        <f t="shared" si="155"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F293" s="105">
-        <f t="shared" si="155"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G293" s="105">
-        <f t="shared" si="155"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H293" s="92">
         <v>1.05</v>
@@ -25333,20 +25306,20 @@
         <v>129</v>
       </c>
       <c r="D294" s="105">
-        <f t="shared" ref="D294:G294" si="156">D74*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1.4850000000000003</v>
       </c>
       <c r="E294" s="105">
-        <f t="shared" si="156"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F294" s="105">
-        <f t="shared" si="156"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G294" s="105">
-        <f t="shared" si="156"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H294" s="92">
         <v>1.05</v>
@@ -25358,20 +25331,20 @@
         <v>130</v>
       </c>
       <c r="D295" s="105">
-        <f t="shared" ref="D295:G295" si="157">D75*1.2</f>
-        <v>1.62</v>
+        <f t="shared" si="23"/>
+        <v>1.4850000000000003</v>
       </c>
       <c r="E295" s="105">
-        <f t="shared" si="157"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F295" s="105">
-        <f t="shared" si="157"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G295" s="105">
-        <f t="shared" si="157"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H295" s="92">
         <v>1.05</v>
@@ -25383,20 +25356,20 @@
         <v>131</v>
       </c>
       <c r="D296" s="105">
-        <f t="shared" ref="D296:G296" si="158">D76*1.2</f>
-        <v>1.62</v>
+        <f t="shared" si="23"/>
+        <v>1.4850000000000003</v>
       </c>
       <c r="E296" s="105">
-        <f t="shared" si="158"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F296" s="105">
-        <f t="shared" si="158"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G296" s="105">
-        <f t="shared" si="158"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H296" s="92">
         <v>1.05</v>
@@ -25408,20 +25381,20 @@
         <v>132</v>
       </c>
       <c r="D297" s="105">
-        <f t="shared" ref="D297:G297" si="159">D77*1.2</f>
-        <v>6.48</v>
+        <f t="shared" si="23"/>
+        <v>5.9400000000000013</v>
       </c>
       <c r="E297" s="105">
-        <f t="shared" si="159"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F297" s="105">
-        <f t="shared" si="159"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G297" s="105">
-        <f t="shared" si="159"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H297" s="92">
         <v>1.05</v>
@@ -25436,20 +25409,20 @@
         <v>129</v>
       </c>
       <c r="D298" s="105">
-        <f t="shared" ref="D298:G298" si="160">D78*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="E298" s="105">
-        <f t="shared" si="160"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F298" s="105">
-        <f t="shared" si="160"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G298" s="105">
-        <f t="shared" si="160"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H298" s="92">
         <v>1.05</v>
@@ -25461,20 +25434,20 @@
         <v>130</v>
       </c>
       <c r="D299" s="105">
-        <f t="shared" ref="D299:G299" si="161">D79*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="E299" s="105">
-        <f t="shared" si="161"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F299" s="105">
-        <f t="shared" si="161"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G299" s="105">
-        <f t="shared" si="161"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H299" s="92">
         <v>1.05</v>
@@ -25486,20 +25459,20 @@
         <v>131</v>
       </c>
       <c r="D300" s="105">
-        <f t="shared" ref="D300:G300" si="162">D80*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="E300" s="105">
-        <f t="shared" si="162"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F300" s="105">
-        <f t="shared" si="162"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G300" s="105">
-        <f t="shared" si="162"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H300" s="92">
         <v>1.05</v>
@@ -25511,20 +25484,20 @@
         <v>132</v>
       </c>
       <c r="D301" s="105">
-        <f t="shared" ref="D301:G301" si="163">D81*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="E301" s="105">
-        <f t="shared" si="163"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F301" s="105">
-        <f t="shared" si="163"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G301" s="105">
-        <f t="shared" si="163"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H301" s="92">
         <v>1.05</v>
@@ -25539,20 +25512,20 @@
         <v>129</v>
       </c>
       <c r="D302" s="105">
-        <f t="shared" ref="D302:G302" si="164">D82*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="E302" s="105">
-        <f t="shared" si="164"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F302" s="105">
-        <f t="shared" si="164"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G302" s="105">
-        <f t="shared" si="164"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H302" s="92">
         <v>1.05</v>
@@ -25564,20 +25537,20 @@
         <v>130</v>
       </c>
       <c r="D303" s="105">
-        <f t="shared" ref="D303:G303" si="165">D83*1.2</f>
-        <v>1.2</v>
+        <f t="shared" ref="D303:G318" si="24">IF(D83=1,1,D83*1.1)</f>
+        <v>1</v>
       </c>
       <c r="E303" s="105">
-        <f t="shared" si="165"/>
-        <v>2.7359999999999998</v>
+        <f t="shared" si="24"/>
+        <v>2.508</v>
       </c>
       <c r="F303" s="105">
-        <f t="shared" si="165"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="G303" s="105">
-        <f t="shared" si="165"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="H303" s="92">
         <v>1.05</v>
@@ -25589,20 +25562,20 @@
         <v>131</v>
       </c>
       <c r="D304" s="105">
-        <f t="shared" ref="D304:G304" si="166">D84*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E304" s="105">
-        <f t="shared" si="166"/>
-        <v>5.5439999999999996</v>
+        <f t="shared" si="24"/>
+        <v>5.0820000000000007</v>
       </c>
       <c r="F304" s="105">
-        <f t="shared" si="166"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="G304" s="105">
-        <f t="shared" si="166"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="H304" s="92">
         <v>1.05</v>
@@ -25614,20 +25587,20 @@
         <v>132</v>
       </c>
       <c r="D305" s="105">
-        <f t="shared" ref="D305:G305" si="167">D85*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E305" s="105">
-        <f t="shared" si="167"/>
-        <v>12.635999999999999</v>
+        <f t="shared" si="24"/>
+        <v>11.583</v>
       </c>
       <c r="F305" s="105">
-        <f t="shared" si="167"/>
-        <v>1.764</v>
+        <f t="shared" si="24"/>
+        <v>1.617</v>
       </c>
       <c r="G305" s="105">
-        <f t="shared" si="167"/>
-        <v>3.0839999999999996</v>
+        <f t="shared" si="24"/>
+        <v>2.827</v>
       </c>
       <c r="H305" s="92">
         <v>1.05</v>
@@ -25642,20 +25615,20 @@
         <v>129</v>
       </c>
       <c r="D306" s="105">
-        <f t="shared" ref="D306:G306" si="168">D86*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E306" s="105">
-        <f t="shared" si="168"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="F306" s="105">
-        <f t="shared" si="168"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="G306" s="105">
-        <f t="shared" si="168"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="H306" s="92">
         <v>1.05</v>
@@ -25667,20 +25640,20 @@
         <v>130</v>
       </c>
       <c r="D307" s="105">
-        <f t="shared" ref="D307:G307" si="169">D87*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E307" s="105">
-        <f t="shared" si="169"/>
-        <v>1.9919999999999998</v>
+        <f t="shared" si="24"/>
+        <v>1.8260000000000001</v>
       </c>
       <c r="F307" s="105">
-        <f t="shared" si="169"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="G307" s="105">
-        <f t="shared" si="169"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="H307" s="92">
         <v>1.05</v>
@@ -25692,20 +25665,20 @@
         <v>131</v>
       </c>
       <c r="D308" s="105">
-        <f t="shared" ref="D308:G308" si="170">D88*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E308" s="105">
-        <f t="shared" si="170"/>
-        <v>3</v>
+        <f t="shared" si="24"/>
+        <v>2.75</v>
       </c>
       <c r="F308" s="105">
-        <f t="shared" si="170"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="G308" s="105">
-        <f t="shared" si="170"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="H308" s="92">
         <v>1.05</v>
@@ -25717,20 +25690,20 @@
         <v>132</v>
       </c>
       <c r="D309" s="105">
-        <f t="shared" ref="D309:G309" si="171">D89*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E309" s="105">
-        <f t="shared" si="171"/>
-        <v>17.963999999999999</v>
+        <f t="shared" si="24"/>
+        <v>16.467000000000002</v>
       </c>
       <c r="F309" s="105">
-        <f t="shared" si="171"/>
-        <v>2.3039999999999998</v>
+        <f t="shared" si="24"/>
+        <v>2.1120000000000001</v>
       </c>
       <c r="G309" s="105">
-        <f t="shared" si="171"/>
-        <v>2.3039999999999998</v>
+        <f t="shared" si="24"/>
+        <v>2.1120000000000001</v>
       </c>
       <c r="H309" s="92">
         <v>1.05</v>
@@ -25745,20 +25718,20 @@
         <v>129</v>
       </c>
       <c r="D310" s="105">
-        <f t="shared" ref="D310:G310" si="172">D90*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E310" s="105">
-        <f t="shared" si="172"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="F310" s="105">
-        <f t="shared" si="172"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="G310" s="105">
-        <f t="shared" si="172"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="H310" s="92">
         <v>1.05</v>
@@ -25770,20 +25743,20 @@
         <v>130</v>
       </c>
       <c r="D311" s="105">
-        <f t="shared" ref="D311:G311" si="173">D91*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E311" s="105">
-        <f t="shared" si="173"/>
-        <v>1.776</v>
+        <f t="shared" si="24"/>
+        <v>1.6280000000000001</v>
       </c>
       <c r="F311" s="105">
-        <f t="shared" si="173"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="G311" s="105">
-        <f t="shared" si="173"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="H311" s="92">
         <v>1.05</v>
@@ -25795,20 +25768,20 @@
         <v>131</v>
       </c>
       <c r="D312" s="105">
-        <f t="shared" ref="D312:G312" si="174">D92*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E312" s="105">
-        <f t="shared" si="174"/>
-        <v>3.4079999999999999</v>
+        <f t="shared" si="24"/>
+        <v>3.1240000000000001</v>
       </c>
       <c r="F312" s="105">
-        <f t="shared" si="174"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="G312" s="105">
-        <f t="shared" si="174"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="H312" s="92">
         <v>1.05</v>
@@ -25820,20 +25793,20 @@
         <v>132</v>
       </c>
       <c r="D313" s="105">
-        <f t="shared" ref="D313:G313" si="175">D93*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E313" s="105">
-        <f t="shared" si="175"/>
-        <v>17.28</v>
+        <f t="shared" si="24"/>
+        <v>15.840000000000002</v>
       </c>
       <c r="F313" s="105">
-        <f t="shared" si="175"/>
-        <v>4.4279999999999999</v>
+        <f t="shared" si="24"/>
+        <v>4.0590000000000002</v>
       </c>
       <c r="G313" s="105">
-        <f t="shared" si="175"/>
-        <v>4.4279999999999999</v>
+        <f t="shared" si="24"/>
+        <v>4.0590000000000002</v>
       </c>
       <c r="H313" s="92">
         <v>1.05</v>
@@ -25848,20 +25821,20 @@
         <v>129</v>
       </c>
       <c r="D314" s="105">
-        <f t="shared" ref="D314:G314" si="176">D94*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E314" s="105">
-        <f t="shared" si="176"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="F314" s="105">
-        <f t="shared" si="176"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="G314" s="105">
-        <f t="shared" si="176"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="H314" s="92">
         <v>1.05</v>
@@ -25873,20 +25846,20 @@
         <v>130</v>
       </c>
       <c r="D315" s="105">
-        <f t="shared" ref="D315:G315" si="177">D95*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E315" s="105">
-        <f t="shared" si="177"/>
-        <v>1.776</v>
+        <f t="shared" si="24"/>
+        <v>1.6280000000000001</v>
       </c>
       <c r="F315" s="105">
-        <f t="shared" si="177"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="G315" s="105">
-        <f t="shared" si="177"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="H315" s="92">
         <v>1.05</v>
@@ -25898,20 +25871,20 @@
         <v>131</v>
       </c>
       <c r="D316" s="105">
-        <f t="shared" ref="D316:G316" si="178">D96*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E316" s="105">
-        <f t="shared" si="178"/>
-        <v>3.4079999999999999</v>
+        <f t="shared" si="24"/>
+        <v>3.1240000000000001</v>
       </c>
       <c r="F316" s="105">
-        <f t="shared" si="178"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="G316" s="105">
-        <f t="shared" si="178"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="H316" s="92">
         <v>1.05</v>
@@ -25923,20 +25896,20 @@
         <v>132</v>
       </c>
       <c r="D317" s="105">
-        <f t="shared" ref="D317:G317" si="179">D97*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E317" s="105">
-        <f t="shared" si="179"/>
-        <v>17.28</v>
+        <f t="shared" si="24"/>
+        <v>15.840000000000002</v>
       </c>
       <c r="F317" s="105">
-        <f t="shared" si="179"/>
-        <v>4.4279999999999999</v>
+        <f t="shared" si="24"/>
+        <v>4.0590000000000002</v>
       </c>
       <c r="G317" s="105">
-        <f t="shared" si="179"/>
-        <v>4.4279999999999999</v>
+        <f t="shared" si="24"/>
+        <v>4.0590000000000002</v>
       </c>
       <c r="H317" s="92">
         <v>1.05</v>
@@ -25951,20 +25924,20 @@
         <v>129</v>
       </c>
       <c r="D318" s="105">
-        <f t="shared" ref="D318:G318" si="180">D98*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E318" s="105">
-        <f t="shared" si="180"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="F318" s="105">
-        <f t="shared" si="180"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="G318" s="105">
-        <f t="shared" si="180"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="H318" s="92">
         <v>1.05</v>
@@ -25976,20 +25949,20 @@
         <v>130</v>
       </c>
       <c r="D319" s="105">
-        <f t="shared" ref="D319:G319" si="181">D99*1.2</f>
-        <v>1.2</v>
+        <f t="shared" ref="D319:G321" si="25">IF(D99=1,1,D99*1.1)</f>
+        <v>1</v>
       </c>
       <c r="E319" s="105">
-        <f t="shared" si="181"/>
-        <v>1.776</v>
+        <f t="shared" si="25"/>
+        <v>1.6280000000000001</v>
       </c>
       <c r="F319" s="105">
-        <f t="shared" si="181"/>
-        <v>1.2</v>
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="G319" s="105">
-        <f t="shared" si="181"/>
-        <v>1.2</v>
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="H319" s="92">
         <v>1.05</v>
@@ -26001,20 +25974,20 @@
         <v>131</v>
       </c>
       <c r="D320" s="105">
-        <f t="shared" ref="D320:G320" si="182">D100*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="E320" s="105">
-        <f t="shared" si="182"/>
-        <v>3.4079999999999999</v>
+        <f t="shared" si="25"/>
+        <v>3.1240000000000001</v>
       </c>
       <c r="F320" s="105">
-        <f t="shared" si="182"/>
-        <v>1.2</v>
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="G320" s="105">
-        <f t="shared" si="182"/>
-        <v>1.2</v>
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="H320" s="92">
         <v>1.05</v>
@@ -26026,20 +25999,20 @@
         <v>132</v>
       </c>
       <c r="D321" s="105">
-        <f t="shared" ref="D321:G321" si="183">D101*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="E321" s="105">
-        <f t="shared" si="183"/>
-        <v>17.28</v>
+        <f t="shared" si="25"/>
+        <v>15.840000000000002</v>
       </c>
       <c r="F321" s="105">
-        <f t="shared" si="183"/>
-        <v>4.4279999999999999</v>
+        <f t="shared" si="25"/>
+        <v>4.0590000000000002</v>
       </c>
       <c r="G321" s="105">
-        <f t="shared" si="183"/>
-        <v>4.4279999999999999</v>
+        <f t="shared" si="25"/>
+        <v>4.0590000000000002</v>
       </c>
       <c r="H321" s="92">
         <v>1.05</v>
@@ -26092,20 +26065,20 @@
         <v>129</v>
       </c>
       <c r="D325" s="105">
-        <f>D105*1.2</f>
-        <v>1.2</v>
+        <f>IF(D105=1,1,D105*1.1)</f>
+        <v>1</v>
       </c>
       <c r="E325" s="105">
-        <f t="shared" ref="E325:G325" si="184">E105*1.2</f>
-        <v>1.2</v>
+        <f t="shared" ref="E325:G325" si="26">IF(E105=1,1,E105*1.1)</f>
+        <v>1</v>
       </c>
       <c r="F325" s="105">
-        <f t="shared" si="184"/>
-        <v>1.2</v>
+        <f t="shared" si="26"/>
+        <v>1</v>
       </c>
       <c r="G325" s="105">
-        <f t="shared" si="184"/>
-        <v>1.2</v>
+        <f t="shared" si="26"/>
+        <v>1</v>
       </c>
       <c r="H325" s="92">
         <v>1.05</v>
@@ -26117,20 +26090,20 @@
         <v>130</v>
       </c>
       <c r="D326" s="105">
-        <f t="shared" ref="D326:G326" si="185">D106*1.2</f>
-        <v>1.512</v>
+        <f t="shared" ref="D326:G328" si="27">IF(D106=1,1,D106*1.1)</f>
+        <v>1.3860000000000001</v>
       </c>
       <c r="E326" s="105">
-        <f t="shared" si="185"/>
-        <v>1.512</v>
+        <f t="shared" si="27"/>
+        <v>1.3860000000000001</v>
       </c>
       <c r="F326" s="105">
-        <f t="shared" si="185"/>
-        <v>1.2</v>
+        <f t="shared" si="27"/>
+        <v>1</v>
       </c>
       <c r="G326" s="105">
-        <f t="shared" si="185"/>
-        <v>1.2</v>
+        <f t="shared" si="27"/>
+        <v>1</v>
       </c>
       <c r="H326" s="92">
         <v>1.05</v>
@@ -26142,20 +26115,20 @@
         <v>131</v>
       </c>
       <c r="D327" s="105">
-        <f t="shared" ref="D327:G327" si="186">D107*1.2</f>
-        <v>2.016</v>
+        <f t="shared" si="27"/>
+        <v>1.8480000000000001</v>
       </c>
       <c r="E327" s="105">
-        <f t="shared" si="186"/>
-        <v>2.016</v>
+        <f t="shared" si="27"/>
+        <v>1.8480000000000001</v>
       </c>
       <c r="F327" s="105">
-        <f t="shared" si="186"/>
-        <v>1.2</v>
+        <f t="shared" si="27"/>
+        <v>1</v>
       </c>
       <c r="G327" s="105">
-        <f t="shared" si="186"/>
-        <v>1.2</v>
+        <f t="shared" si="27"/>
+        <v>1</v>
       </c>
       <c r="H327" s="92">
         <v>1.05</v>
@@ -26167,20 +26140,20 @@
         <v>132</v>
       </c>
       <c r="D328" s="105">
-        <f t="shared" ref="D328:G328" si="187">D108*1.2</f>
-        <v>3.1799999999999997</v>
+        <f t="shared" si="27"/>
+        <v>2.915</v>
       </c>
       <c r="E328" s="105">
-        <f t="shared" si="187"/>
-        <v>3.1799999999999997</v>
+        <f t="shared" si="27"/>
+        <v>2.915</v>
       </c>
       <c r="F328" s="105">
-        <f t="shared" si="187"/>
-        <v>2.4839999999999995</v>
+        <f t="shared" si="27"/>
+        <v>2.2770000000000001</v>
       </c>
       <c r="G328" s="105">
-        <f t="shared" si="187"/>
-        <v>2.4839999999999995</v>
+        <f t="shared" si="27"/>
+        <v>2.2770000000000001</v>
       </c>
       <c r="H328" s="92">
         <v>1.05</v>
@@ -26188,12 +26161,9 @@
       <c r="I328" s="92"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="mSgxokYZaDRxL4V93+FMsjV9HhQ0AQiXNX8Gv3a6SWXEXoLuWEgr5cLw0sH5cgVSm06POhtPFy/Upl3WtEPTHQ==" saltValue="iFxgbusl+w5BkRSX/YhUbw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="cmc+3/u/AZSHAcHAxPnckSU/IZnsNSz3BXtPyLlh8FBR0p/OTVdAo/YXqRLpMxYSNl+Dr1qVh32uLAuW3ZoQdQ==" saltValue="bFevFWNvipI48zDzYdNrKA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <ignoredErrors>
-    <ignoredError sqref="D113:H135 D140:H163 D167:G172 D176:G211 D215:G218 D223:H246 D250:H273 D277:G282 D286:G321 D325:G328" unlockedFormula="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -26298,13 +26268,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!$E$4),0.64, (0.64*SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)/(1-0.64*SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)))
-/ (SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)/(1-SUM('Dist. de l''état nutritionnel'!$E$4:$E$5))))</f>
-        <v>0.58983967886464039</v>
+        <v>0.89</v>
       </c>
       <c r="F6" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!$F$4),0.64, (0.64*SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)/(1-0.64*SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)))/ (SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)/(1-SUM('Dist. de l''état nutritionnel'!$F$4:$F$5))))</f>
-        <v>0.52474827695613546</v>
+        <v>0.89</v>
       </c>
       <c r="G6" s="104">
         <v>1</v>
@@ -26321,12 +26288,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!$E$4),0.88, (0.88*SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)/(1-0.88*SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)))/ (SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)/(1-SUM('Dist. de l''état nutritionnel'!$E$4:$E$5))))</f>
-        <v>0.85574238427686589</v>
+        <v>0.88</v>
       </c>
       <c r="F7" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!$F$4),0.88, (0.88*SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)/(1-0.88*SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)))/ (SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)/(1-SUM('Dist. de l''état nutritionnel'!$F$4:$F$5))))</f>
-        <v>0.81996938552863874</v>
+        <v>0.88</v>
       </c>
       <c r="G7" s="104">
         <v>1</v>
@@ -26343,12 +26308,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!$E$4),0.88, (0.88*SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)/(1-0.88*SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)))/ (SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)/(1-SUM('Dist. de l''état nutritionnel'!$E$4:$E$5))))</f>
-        <v>0.85574238427686589</v>
+        <v>0.88</v>
       </c>
       <c r="F8" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!$F$4),0.88, (0.88*SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)/(1-0.88*SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)))/ (SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)/(1-SUM('Dist. de l''état nutritionnel'!$F$4:$F$5))))</f>
-        <v>0.81996938552863874</v>
+        <v>0.88</v>
       </c>
       <c r="G8" s="104">
         <v>1</v>
@@ -26626,12 +26589,12 @@
         <v>1</v>
       </c>
       <c r="E29" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$4),0.44, (0.44*SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-0.44*SUM('Dist. de l''état nutritionnel'!E$4:E$5)))/ (SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-SUM('Dist. de l''état nutritionnel'!E$4:E$5))))</f>
-        <v>0.38859461375301474</v>
+        <f>E6*0.9</f>
+        <v>0.80100000000000005</v>
       </c>
       <c r="F29" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$4),0.44, (0.44*SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-0.44*SUM('Dist. de l''état nutritionnel'!F$4:F$5)))/ (SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-SUM('Dist. de l''état nutritionnel'!F$4:F$5))))</f>
-        <v>0.32795428705435947</v>
+        <f>F6*0.9</f>
+        <v>0.80100000000000005</v>
       </c>
       <c r="G29" s="104">
         <f t="shared" si="2"/>
@@ -26651,12 +26614,10 @@
         <v>1</v>
       </c>
       <c r="E30" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$4),0.85, (0.85*SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-0.85*SUM('Dist. de l''état nutritionnel'!E$4:E$5)))/ (SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-SUM('Dist. de l''état nutritionnel'!E$4:E$5))))</f>
-        <v>0.82091214070727592</v>
+        <v>0.85</v>
       </c>
       <c r="F30" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$4),0.85, (0.85*SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-0.85*SUM('Dist. de l''état nutritionnel'!F$4:F$5)))/ (SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-SUM('Dist. de l''état nutritionnel'!F$4:F$5))))</f>
-        <v>0.77873521514816446</v>
+        <v>0.85</v>
       </c>
       <c r="G30" s="104">
         <f t="shared" si="3"/>
@@ -26676,12 +26637,10 @@
         <v>1</v>
       </c>
       <c r="E31" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$4),0.85, (0.85*SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-0.85*SUM('Dist. de l''état nutritionnel'!E$4:E$5)))/ (SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-SUM('Dist. de l''état nutritionnel'!E$4:E$5))))</f>
-        <v>0.82091214070727592</v>
+        <v>0.85</v>
       </c>
       <c r="F31" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$4),0.85, (0.85*SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-0.85*SUM('Dist. de l''état nutritionnel'!F$4:F$5)))/ (SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-SUM('Dist. de l''état nutritionnel'!F$4:F$5))))</f>
-        <v>0.77873521514816446</v>
+        <v>0.85</v>
       </c>
       <c r="G31" s="104">
         <f t="shared" si="3"/>
@@ -26738,12 +26697,10 @@
         <v>296</v>
       </c>
       <c r="C35" s="104">
-        <f>C12*0.9</f>
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="D35" s="104">
-        <f t="shared" ref="D35" si="4">D12*0.9</f>
-        <v>1.2509999999999999</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="E35" s="104">
         <v>1</v>
@@ -26782,19 +26739,19 @@
         <v>0.92249999999999999</v>
       </c>
       <c r="D38" s="104">
-        <f t="shared" ref="D38:G38" si="5">IF(D15=1,1,D15*0.9)</f>
+        <f t="shared" ref="D38:G38" si="4">IF(D15=1,1,D15*0.9)</f>
         <v>0.92249999999999999</v>
       </c>
       <c r="E38" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.92249999999999999</v>
       </c>
       <c r="F38" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.92249999999999999</v>
       </c>
       <c r="G38" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.92249999999999999</v>
       </c>
     </row>
@@ -26804,23 +26761,23 @@
         <v>298</v>
       </c>
       <c r="C39" s="104">
-        <f t="shared" ref="C39:G40" si="6">IF(C16=1,1,C16*0.9)</f>
+        <f t="shared" ref="C39:G40" si="5">IF(C16=1,1,C16*0.9)</f>
         <v>0.92249999999999999</v>
       </c>
       <c r="D39" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.92249999999999999</v>
       </c>
       <c r="E39" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.92249999999999999</v>
       </c>
       <c r="F39" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.92249999999999999</v>
       </c>
       <c r="G39" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.92249999999999999</v>
       </c>
     </row>
@@ -26832,23 +26789,23 @@
         <v>299</v>
       </c>
       <c r="C40" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D40" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E40" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="F40" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="G40" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -26943,19 +26900,19 @@
         <v>10</v>
       </c>
       <c r="D49" s="104">
-        <f t="shared" ref="D49:G50" si="7">D3*1.05</f>
+        <f t="shared" ref="D49:G50" si="6">D3*1.05</f>
         <v>47.25</v>
       </c>
       <c r="E49" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>379.68000000000006</v>
       </c>
       <c r="F49" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>183.435</v>
       </c>
       <c r="G49" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>183.435</v>
       </c>
     </row>
@@ -26969,19 +26926,19 @@
         <v>1.0762499999999999</v>
       </c>
       <c r="D50" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1.0762499999999999</v>
       </c>
       <c r="E50" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1.0762499999999999</v>
       </c>
       <c r="F50" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1.0762499999999999</v>
       </c>
       <c r="G50" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1.0762499999999999</v>
       </c>
     </row>
@@ -26999,19 +26956,19 @@
         <v>1</v>
       </c>
       <c r="D52" s="104">
-        <f t="shared" ref="D52:G52" si="8">IF(D6=1,1,D6*1.1)</f>
+        <f t="shared" ref="D52:G52" si="7">IF(D6=1,1,D6*1.1)</f>
         <v>1</v>
       </c>
       <c r="E52" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$4),0.92, (0.92*SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-0.92*SUM('Dist. de l''état nutritionnel'!E$4:E$5)))/ (SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-SUM('Dist. de l''état nutritionnel'!E$4:E$5))))</f>
-        <v>0.90293638807901733</v>
+        <f>E6*1.05</f>
+        <v>0.93450000000000011</v>
       </c>
       <c r="F52" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$4),0.92, (0.92*SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-0.92*SUM('Dist. de l''état nutritionnel'!F$4:F$5)))/ (SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-SUM('Dist. de l''état nutritionnel'!F$4:F$5))))</f>
-        <v>0.87718696072640712</v>
+        <f>F6*1.05</f>
+        <v>0.93450000000000011</v>
       </c>
       <c r="G52" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -27020,23 +26977,21 @@
         <v>306</v>
       </c>
       <c r="C53" s="104">
-        <f t="shared" ref="C53:G55" si="9">IF(C7=1,1,C7*1.1)</f>
+        <f t="shared" ref="C53:G55" si="8">IF(C7=1,1,C7*1.1)</f>
         <v>1</v>
       </c>
       <c r="D53" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E53" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$4),0.91, (0.91*SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-0.91*SUM('Dist. de l''état nutritionnel'!E$4:E$5)))/ (SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-SUM('Dist. de l''état nutritionnel'!E$4:E$5))))</f>
-        <v>0.89105601510511334</v>
+        <v>0.91</v>
       </c>
       <c r="F53" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$4),0.91, (0.91*SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-0.91*SUM('Dist. de l''état nutritionnel'!F$4:F$5)))/ (SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-SUM('Dist. de l''état nutritionnel'!F$4:F$5))))</f>
-        <v>0.86263438509246337</v>
+        <v>0.91</v>
       </c>
       <c r="G53" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -27045,23 +27000,21 @@
         <v>316</v>
       </c>
       <c r="C54" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="D54" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E54" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$4),0.91, (0.91*SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-0.91*SUM('Dist. de l''état nutritionnel'!E$4:E$5)))/ (SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-SUM('Dist. de l''état nutritionnel'!E$4:E$5))))</f>
-        <v>0.89105601510511334</v>
+        <v>0.91</v>
       </c>
       <c r="F54" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$4),0.91, (0.91*SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-0.91*SUM('Dist. de l''état nutritionnel'!F$4:F$5)))/ (SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-SUM('Dist. de l''état nutritionnel'!F$4:F$5))))</f>
-        <v>0.86263438509246337</v>
+        <v>0.91</v>
       </c>
       <c r="G54" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -27070,23 +27023,23 @@
         <v>307</v>
       </c>
       <c r="C55" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="D55" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E55" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="F55" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="G55" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -27115,12 +27068,10 @@
         <v>309</v>
       </c>
       <c r="C58" s="104">
-        <f>C12*1.1</f>
-        <v>1.6500000000000001</v>
+        <v>1.78</v>
       </c>
       <c r="D58" s="104">
-        <f t="shared" ref="D58" si="10">D12*1.1</f>
-        <v>1.5289999999999999</v>
+        <v>1.74</v>
       </c>
       <c r="E58" s="104">
         <v>1</v>
@@ -27159,19 +27110,19 @@
         <v>1.1274999999999999</v>
       </c>
       <c r="D61" s="104">
-        <f t="shared" ref="D61:G61" si="11">IF(D15=1,1,D15*1.1)</f>
+        <f t="shared" ref="D61:G61" si="9">IF(D15=1,1,D15*1.1)</f>
         <v>1.1274999999999999</v>
       </c>
       <c r="E61" s="104">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1.1274999999999999</v>
       </c>
       <c r="F61" s="104">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1.1274999999999999</v>
       </c>
       <c r="G61" s="104">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1.1274999999999999</v>
       </c>
     </row>
@@ -27181,23 +27132,23 @@
         <v>311</v>
       </c>
       <c r="C62" s="104">
-        <f t="shared" ref="C62:G63" si="12">IF(C16=1,1,C16*1.1)</f>
+        <f t="shared" ref="C62:G63" si="10">IF(C16=1,1,C16*1.1)</f>
         <v>1.1274999999999999</v>
       </c>
       <c r="D62" s="104">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1.1274999999999999</v>
       </c>
       <c r="E62" s="104">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1.1274999999999999</v>
       </c>
       <c r="F62" s="104">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1.1274999999999999</v>
       </c>
       <c r="G62" s="104">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1.1274999999999999</v>
       </c>
     </row>
@@ -27209,23 +27160,23 @@
         <v>312</v>
       </c>
       <c r="C63" s="104">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D63" s="104">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E63" s="104">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="F63" s="104">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G63" s="104">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -27276,7 +27227,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="/QW8Qf7zN6UfUZM7G4bV/CO3W9bwZZC/QdYAOauRYyLPQsdEgCpaC4Y5NV84qM4SArPKfOkeLXrvK9ENnW1Zog==" saltValue="eIo9rWolgcbCCjQxXYiAMw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="AXClvh8rb/1iMq+PVpyB7L55iIZdT8lGkG4rt/ozX+Q2ZCKxvGGq3tZVznabrJj7TXXS6AE2cDebV+wu1FS6HA==" saltValue="W4IKMD8FIFTcVzoxC+6Prw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -28097,7 +28048,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="vzhqnB8QVDvTzhNCXv3wIVg4TYmu4TrCdc+n7yyUVsVxpDTk5rAwX5ODeq3hFEH+Z1vFPSnFY0emu20cgwm8ng==" saltValue="2g/pHRO0bYAyVwMnP5BHUQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="G+MYlZ+++Ryw+6chJOfuNxtuASHvsxaXQtDIvKjh2OP9Nj1CxAAdvRFrw2F2hNtQS6RITIW/8C3EnFlmK3p+cQ==" saltValue="+4fZBArM1KqFs83Hdvi2ig==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -28170,7 +28121,7 @@
         <v>171</v>
       </c>
       <c r="C3" s="104">
-        <v>0.53</v>
+        <v>0.92</v>
       </c>
       <c r="D3" s="104">
         <v>0.53</v>
@@ -28505,16 +28456,16 @@
         <v>1</v>
       </c>
       <c r="L10" s="104">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="M10" s="104">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="N10" s="104">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="O10" s="104">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -28681,15 +28632,19 @@
         <v>1</v>
       </c>
       <c r="L14" s="104">
+        <f>L8</f>
         <v>0.51</v>
       </c>
       <c r="M14" s="104">
+        <f t="shared" ref="M14:O14" si="0">M8</f>
         <v>0.51</v>
       </c>
       <c r="N14" s="104">
+        <f t="shared" si="0"/>
         <v>0.51</v>
       </c>
       <c r="O14" s="104">
+        <f t="shared" si="0"/>
         <v>0.51</v>
       </c>
     </row>
@@ -28798,59 +28753,37 @@
         <v>1</v>
       </c>
       <c r="E19" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$14),0.72,(0.72*'Dist. de l''état nutritionnel'!E$14/(1-0.72*'Dist. de l''état nutritionnel'!E$14))
-/ ('Dist. de l''état nutritionnel'!E$14/(1-'Dist. de l''état nutritionnel'!E$14)))</f>
-        <v>0.36026320599524769</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F19" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$14),0.72,(0.72*'Dist. de l''état nutritionnel'!F$14/(1-0.72*'Dist. de l''état nutritionnel'!F$14))
-/ ('Dist. de l''état nutritionnel'!F$14/(1-'Dist. de l''état nutritionnel'!F$14)))</f>
-        <v>0.41022832589097646</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G19" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$14),0.72,(0.72*'Dist. de l''état nutritionnel'!G$14/(1-0.72*'Dist. de l''état nutritionnel'!G$14))
-/ ('Dist. de l''état nutritionnel'!G$14/(1-'Dist. de l''état nutritionnel'!G$14)))</f>
-        <v>0.57039401006505464</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H19" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!H$14),0.72,(0.72*'Dist. de l''état nutritionnel'!H$14/(1-0.72*'Dist. de l''état nutritionnel'!H$14))
-/ ('Dist. de l''état nutritionnel'!H$14/(1-'Dist. de l''état nutritionnel'!H$14)))</f>
-        <v>0.57539730680577461</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I19" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!I$14),0.72,(0.72*'Dist. de l''état nutritionnel'!I$14/(1-0.72*'Dist. de l''état nutritionnel'!I$14))
-/ ('Dist. de l''état nutritionnel'!I$14/(1-'Dist. de l''état nutritionnel'!I$14)))</f>
-        <v>0.5871180842279109</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J19" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!J$14),0.72,(0.72*'Dist. de l''état nutritionnel'!J$14/(1-0.72*'Dist. de l''état nutritionnel'!J$14))
-/ ('Dist. de l''état nutritionnel'!J$14/(1-'Dist. de l''état nutritionnel'!J$14)))</f>
-        <v>0.5931651749389748</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K19" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!K$14),0.72,(0.72*'Dist. de l''état nutritionnel'!K$14/(1-0.72*'Dist. de l''état nutritionnel'!K$14))
-/ ('Dist. de l''état nutritionnel'!K$14/(1-'Dist. de l''état nutritionnel'!K$14)))</f>
-        <v>0.58929828678713914</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L19" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!L$14),0.72,(0.72*'Dist. de l''état nutritionnel'!L$14/(1-0.72*'Dist. de l''état nutritionnel'!L$14))
-/ ('Dist. de l''état nutritionnel'!L$14/(1-'Dist. de l''état nutritionnel'!L$14)))</f>
-        <v>0.57539730680577461</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M19" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!M$14),0.72,(0.72*'Dist. de l''état nutritionnel'!M$14/(1-0.72*'Dist. de l''état nutritionnel'!M$14))
-/ ('Dist. de l''état nutritionnel'!M$14/(1-'Dist. de l''état nutritionnel'!M$14)))</f>
-        <v>0.5871180842279109</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N19" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!N$14),0.72,(0.72*'Dist. de l''état nutritionnel'!N$14/(1-0.72*'Dist. de l''état nutritionnel'!N$14))
-/ ('Dist. de l''état nutritionnel'!N$14/(1-'Dist. de l''état nutritionnel'!N$14)))</f>
-        <v>0.5931651749389748</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O19" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!O$14),0.72,(0.72*'Dist. de l''état nutritionnel'!O$14/(1-0.72*'Dist. de l''état nutritionnel'!O$14))
-/ ('Dist. de l''état nutritionnel'!O$14/(1-'Dist. de l''état nutritionnel'!O$14)))</f>
-        <v>0.58929828678713914</v>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -28864,37 +28797,48 @@
         <v>1</v>
       </c>
       <c r="E20" s="104">
-        <v>1</v>
+        <f>E19</f>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F20" s="104">
-        <v>1</v>
+        <f t="shared" ref="F20:O20" si="1">F19</f>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G20" s="104">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H20" s="104">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I20" s="104">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J20" s="104">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K20" s="104">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L20" s="104">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M20" s="104">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N20" s="104">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O20" s="104">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -28908,59 +28852,37 @@
         <v>1</v>
       </c>
       <c r="E21" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$14),0.8,(0.8*'Dist. de l''état nutritionnel'!E$14/(1-0.8*'Dist. de l''état nutritionnel'!E$14))
-/ ('Dist. de l''état nutritionnel'!E$14/(1-'Dist. de l''état nutritionnel'!E$14)))</f>
-        <v>0.46695095948827287</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F21" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$14),0.8,(0.8*'Dist. de l''état nutritionnel'!F$14/(1-0.8*'Dist. de l''état nutritionnel'!F$14))
-/ ('Dist. de l''état nutritionnel'!F$14/(1-'Dist. de l''état nutritionnel'!F$14)))</f>
-        <v>0.51969260326609024</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G21" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$14),0.8,(0.8*'Dist. de l''état nutritionnel'!G$14/(1-0.8*'Dist. de l''état nutritionnel'!G$14))
-/ ('Dist. de l''état nutritionnel'!G$14/(1-'Dist. de l''état nutritionnel'!G$14)))</f>
-        <v>0.67377120487168329</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H21" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!H$14),0.8,(0.8*'Dist. de l''état nutritionnel'!H$14/(1-0.8*'Dist. de l''état nutritionnel'!H$14))
-/ ('Dist. de l''état nutritionnel'!H$14/(1-'Dist. de l''état nutritionnel'!H$14)))</f>
-        <v>0.67824967824967841</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I21" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!I$14),0.8,(0.8*'Dist. de l''état nutritionnel'!I$14/(1-0.8*'Dist. de l''état nutritionnel'!I$14))
-/ ('Dist. de l''état nutritionnel'!I$14/(1-'Dist. de l''état nutritionnel'!I$14)))</f>
-        <v>0.68866749688667506</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J21" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!J$14),0.8,(0.8*'Dist. de l''état nutritionnel'!J$14/(1-0.8*'Dist. de l''état nutritionnel'!J$14))
-/ ('Dist. de l''état nutritionnel'!J$14/(1-'Dist. de l''état nutritionnel'!J$14)))</f>
-        <v>0.69400244798041621</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K21" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!K$14),0.8,(0.8*'Dist. de l''état nutritionnel'!K$14/(1-0.8*'Dist. de l''état nutritionnel'!K$14))
-/ ('Dist. de l''état nutritionnel'!K$14/(1-'Dist. de l''état nutritionnel'!K$14)))</f>
-        <v>0.69059405940594076</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L21" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!L$14),0.8,(0.8*'Dist. de l''état nutritionnel'!L$14/(1-0.8*'Dist. de l''état nutritionnel'!L$14))
-/ ('Dist. de l''état nutritionnel'!L$14/(1-'Dist. de l''état nutritionnel'!L$14)))</f>
-        <v>0.67824967824967841</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M21" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!M$14),0.8,(0.8*'Dist. de l''état nutritionnel'!M$14/(1-0.8*'Dist. de l''état nutritionnel'!M$14))
-/ ('Dist. de l''état nutritionnel'!M$14/(1-'Dist. de l''état nutritionnel'!M$14)))</f>
-        <v>0.68866749688667506</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N21" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!N$14),0.8,(0.8*'Dist. de l''état nutritionnel'!N$14/(1-0.8*'Dist. de l''état nutritionnel'!N$14))
-/ ('Dist. de l''état nutritionnel'!N$14/(1-'Dist. de l''état nutritionnel'!N$14)))</f>
-        <v>0.69400244798041621</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O21" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!O$14),0.8,(0.8*'Dist. de l''état nutritionnel'!O$14/(1-0.8*'Dist. de l''état nutritionnel'!O$14))
-/ ('Dist. de l''état nutritionnel'!O$14/(1-'Dist. de l''état nutritionnel'!O$14)))</f>
-        <v>0.69059405940594076</v>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="23" spans="1:15" s="106" customFormat="1" ht="13" x14ac:dyDescent="0.3">
@@ -29021,53 +28943,53 @@
         <v>171</v>
       </c>
       <c r="C26" s="104">
-        <v>0.4</v>
+        <v>0.87</v>
       </c>
       <c r="D26" s="104">
         <v>0.4</v>
       </c>
       <c r="E26" s="104">
-        <f t="shared" ref="E26:O26" si="0">IF(E3=1,1,E3*0.9)</f>
+        <f t="shared" ref="E26:O26" si="2">IF(E3=1,1,E3*0.9)</f>
         <v>1</v>
       </c>
       <c r="F26" s="104">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G26" s="104">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H26" s="104">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I26" s="104">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J26" s="104">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K26" s="104">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="L26" s="104">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M26" s="104">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N26" s="104">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O26" s="104">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -29076,23 +28998,23 @@
         <v>176</v>
       </c>
       <c r="C27" s="104">
-        <f t="shared" ref="C27:O34" si="1">IF(C4=1,1,C4*0.9)</f>
+        <f t="shared" ref="C27:O34" si="3">IF(C4=1,1,C4*0.9)</f>
         <v>1</v>
       </c>
       <c r="D27" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E27" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F27" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G27" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H27" s="104">
@@ -29108,19 +29030,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L27" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M27" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N27" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O27" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -29129,23 +29051,23 @@
         <v>177</v>
       </c>
       <c r="C28" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D28" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E28" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F28" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G28" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H28" s="104">
@@ -29161,19 +29083,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L28" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M28" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N28" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O28" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -29182,23 +29104,23 @@
         <v>178</v>
       </c>
       <c r="C29" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D29" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E29" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F29" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G29" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H29" s="104">
@@ -29214,19 +29136,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L29" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M29" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N29" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O29" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -29235,23 +29157,23 @@
         <v>179</v>
       </c>
       <c r="C30" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D30" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E30" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F30" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G30" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H30" s="104">
@@ -29267,19 +29189,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L30" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M30" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N30" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O30" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -29288,39 +29210,39 @@
         <v>180</v>
       </c>
       <c r="C31" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D31" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E31" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F31" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G31" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H31" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I31" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J31" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K31" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L31" s="104">
@@ -29341,39 +29263,39 @@
         <v>181</v>
       </c>
       <c r="C32" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D32" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E32" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F32" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G32" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H32" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I32" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J32" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K32" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L32" s="104">
@@ -29394,39 +29316,39 @@
         <v>182</v>
       </c>
       <c r="C33" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D33" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E33" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F33" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G33" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H33" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I33" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J33" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K33" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L33" s="104">
@@ -29447,11 +29369,11 @@
         <v>185</v>
       </c>
       <c r="C34" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D34" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E34" s="104">
@@ -29464,35 +29386,35 @@
         <v>1</v>
       </c>
       <c r="H34" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I34" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J34" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K34" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L34" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M34" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N34" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O34" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -29545,11 +29467,11 @@
         <v>189</v>
       </c>
       <c r="C36" s="104">
-        <f t="shared" ref="C36:O38" si="2">IF(C13=1,1,C13*0.9)</f>
+        <f t="shared" ref="C36:O38" si="4">IF(C13=1,1,C13*0.9)</f>
         <v>1</v>
       </c>
       <c r="D36" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E36" s="104">
@@ -29562,35 +29484,35 @@
         <v>0.62</v>
       </c>
       <c r="H36" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I36" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J36" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K36" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L36" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="M36" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="N36" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="O36" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -29599,56 +29521,52 @@
         <v>190</v>
       </c>
       <c r="C37" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D37" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E37" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="F37" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="G37" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="H37" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I37" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J37" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K37" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L37" s="104">
-        <f>L32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="M37" s="104">
-        <f t="shared" ref="M37:O37" si="3">M32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="N37" s="104">
-        <f t="shared" si="3"/>
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="O37" s="104">
-        <f t="shared" si="3"/>
-        <v>0.38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
@@ -29656,11 +29574,11 @@
         <v>205</v>
       </c>
       <c r="C38" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D38" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E38" s="104">
@@ -29670,39 +29588,39 @@
         <v>0.3</v>
       </c>
       <c r="G38" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="H38" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I38" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J38" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K38" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L38" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="M38" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="N38" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="O38" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -29717,55 +29635,55 @@
         <v>173</v>
       </c>
       <c r="C41" s="104">
-        <f t="shared" ref="C41:O44" si="4">IF(C18=1,1,C18*0.9)</f>
+        <f t="shared" ref="C41:O44" si="5">IF(C18=1,1,C18*0.9)</f>
         <v>1</v>
       </c>
       <c r="D41" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E41" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="F41" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="G41" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="H41" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="I41" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="J41" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="K41" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="L41" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="M41" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="N41" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="O41" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -29774,67 +29692,45 @@
         <v>174</v>
       </c>
       <c r="C42" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D42" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E42" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$14),0.54,(0.54*'Dist. de l''état nutritionnel'!E$14/(1-0.54*'Dist. de l''état nutritionnel'!E$14))
-/ ('Dist. de l''état nutritionnel'!E$14/(1-'Dist. de l''état nutritionnel'!E$14)))</f>
-        <v>0.20451008197004808</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F42" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$14),0.54,(0.54*'Dist. de l''état nutritionnel'!F$14/(1-0.54*'Dist. de l''état nutritionnel'!F$14))
-/ ('Dist. de l''état nutritionnel'!F$14/(1-'Dist. de l''état nutritionnel'!F$14)))</f>
-        <v>0.24101176431765312</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="G42" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$14),0.54,(0.54*'Dist. de l''état nutritionnel'!G$14/(1-0.54*'Dist. de l''état nutritionnel'!G$14))
-/ ('Dist. de l''état nutritionnel'!G$14/(1-'Dist. de l''état nutritionnel'!G$14)))</f>
-        <v>0.37738556075904828</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H42" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!H$14),0.54,(0.54*'Dist. de l''état nutritionnel'!H$14/(1-0.54*'Dist. de l''état nutritionnel'!H$14))
-/ ('Dist. de l''état nutritionnel'!H$14/(1-'Dist. de l''état nutritionnel'!H$14)))</f>
-        <v>0.38220204679147979</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I42" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!I$14),0.54,(0.54*'Dist. de l''état nutritionnel'!I$14/(1-0.54*'Dist. de l''état nutritionnel'!I$14))
-/ ('Dist. de l''état nutritionnel'!I$14/(1-'Dist. de l''état nutritionnel'!I$14)))</f>
-        <v>0.39363581239619311</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J42" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!J$14),0.54,(0.54*'Dist. de l''état nutritionnel'!J$14/(1-0.54*'Dist. de l''état nutritionnel'!J$14))
-/ ('Dist. de l''état nutritionnel'!J$14/(1-'Dist. de l''état nutritionnel'!J$14)))</f>
-        <v>0.39961888851183797</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="K42" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!K$14),0.54,(0.54*'Dist. de l''état nutritionnel'!K$14/(1-0.54*'Dist. de l''état nutritionnel'!K$14))
-/ ('Dist. de l''état nutritionnel'!K$14/(1-'Dist. de l''état nutritionnel'!K$14)))</f>
-        <v>0.3957862659591237</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="L42" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!L$14),0.54,(0.54*'Dist. de l''état nutritionnel'!L$14/(1-0.54*'Dist. de l''état nutritionnel'!L$14))
-/ ('Dist. de l''état nutritionnel'!L$14/(1-'Dist. de l''état nutritionnel'!L$14)))</f>
-        <v>0.38220204679147979</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="M42" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!M$14),0.54,(0.54*'Dist. de l''état nutritionnel'!M$14/(1-0.54*'Dist. de l''état nutritionnel'!M$14))
-/ ('Dist. de l''état nutritionnel'!M$14/(1-'Dist. de l''état nutritionnel'!M$14)))</f>
-        <v>0.39363581239619311</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N42" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!N$14),0.54,(0.54*'Dist. de l''état nutritionnel'!N$14/(1-0.54*'Dist. de l''état nutritionnel'!N$14))
-/ ('Dist. de l''état nutritionnel'!N$14/(1-'Dist. de l''état nutritionnel'!N$14)))</f>
-        <v>0.39961888851183797</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="O42" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!O$14),0.54,(0.54*'Dist. de l''état nutritionnel'!O$14/(1-0.54*'Dist. de l''état nutritionnel'!O$14))
-/ ('Dist. de l''état nutritionnel'!O$14/(1-'Dist. de l''état nutritionnel'!O$14)))</f>
-        <v>0.3957862659591237</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
@@ -29842,56 +29738,56 @@
         <v>175</v>
       </c>
       <c r="C43" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D43" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E43" s="104">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="F43" s="104">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="G43" s="104">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="H43" s="104">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="I43" s="104">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="J43" s="104">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="K43" s="104">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="L43" s="104">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="M43" s="104">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="N43" s="104">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="O43" s="104">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.87839999999999996</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -29899,67 +29795,45 @@
         <v>183</v>
       </c>
       <c r="C44" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D44" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E44" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$14),0.7,(0.7*'Dist. de l''état nutritionnel'!E$14/(1-0.7*'Dist. de l''état nutritionnel'!E$14))
-/ ('Dist. de l''état nutritionnel'!E$14/(1-'Dist. de l''état nutritionnel'!E$14)))</f>
-        <v>0.33818663136995358</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F44" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$14),0.7,(0.7*'Dist. de l''état nutritionnel'!F$14/(1-0.7*'Dist. de l''état nutritionnel'!F$14))
-/ ('Dist. de l''état nutritionnel'!F$14/(1-'Dist. de l''état nutritionnel'!F$14)))</f>
-        <v>0.38694186165321348</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="G44" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$14),0.7,(0.7*'Dist. de l''état nutritionnel'!G$14/(1-0.7*'Dist. de l''état nutritionnel'!G$14))
-/ ('Dist. de l''état nutritionnel'!G$14/(1-'Dist. de l''état nutritionnel'!G$14)))</f>
-        <v>0.54643955047119874</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H44" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!H$14),0.7,(0.7*'Dist. de l''état nutritionnel'!H$14/(1-0.7*'Dist. de l''état nutritionnel'!H$14))
-/ ('Dist. de l''état nutritionnel'!H$14/(1-'Dist. de l''état nutritionnel'!H$14)))</f>
-        <v>0.55150246673643288</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I44" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!I$14),0.7,(0.7*'Dist. de l''état nutritionnel'!I$14/(1-0.7*'Dist. de l''état nutritionnel'!I$14))
-/ ('Dist. de l''état nutritionnel'!I$14/(1-'Dist. de l''état nutritionnel'!I$14)))</f>
-        <v>0.56338233153834949</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J44" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!J$14),0.7,(0.7*'Dist. de l''état nutritionnel'!J$14/(1-0.7*'Dist. de l''état nutritionnel'!J$14))
-/ ('Dist. de l''état nutritionnel'!J$14/(1-'Dist. de l''état nutritionnel'!J$14)))</f>
-        <v>0.56952216960826507</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="K44" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!K$14),0.7,(0.7*'Dist. de l''état nutritionnel'!K$14/(1-0.7*'Dist. de l''état nutritionnel'!K$14))
-/ ('Dist. de l''état nutritionnel'!K$14/(1-'Dist. de l''état nutritionnel'!K$14)))</f>
-        <v>0.56559513466550837</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="L44" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!L$14),0.7,(0.7*'Dist. de l''état nutritionnel'!L$14/(1-0.7*'Dist. de l''état nutritionnel'!L$14))
-/ ('Dist. de l''état nutritionnel'!L$14/(1-'Dist. de l''état nutritionnel'!L$14)))</f>
-        <v>0.55150246673643288</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="M44" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!M$14),0.7,(0.7*'Dist. de l''état nutritionnel'!M$14/(1-0.7*'Dist. de l''état nutritionnel'!M$14))
-/ ('Dist. de l''état nutritionnel'!M$14/(1-'Dist. de l''état nutritionnel'!M$14)))</f>
-        <v>0.56338233153834949</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N44" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!N$14),0.7,(0.7*'Dist. de l''état nutritionnel'!N$14/(1-0.7*'Dist. de l''état nutritionnel'!N$14))
-/ ('Dist. de l''état nutritionnel'!N$14/(1-'Dist. de l''état nutritionnel'!N$14)))</f>
-        <v>0.56952216960826507</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="O44" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!O$14),0.7,(0.7*'Dist. de l''état nutritionnel'!O$14/(1-0.7*'Dist. de l''état nutritionnel'!O$14))
-/ ('Dist. de l''état nutritionnel'!O$14/(1-'Dist. de l''état nutritionnel'!O$14)))</f>
-        <v>0.56559513466550837</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="46" spans="1:15" s="106" customFormat="1" ht="13" x14ac:dyDescent="0.3">
@@ -30020,53 +29894,53 @@
         <v>171</v>
       </c>
       <c r="C49" s="104">
-        <v>0.7</v>
+        <v>0.99</v>
       </c>
       <c r="D49" s="104">
         <v>0.7</v>
       </c>
       <c r="E49" s="104">
-        <f t="shared" ref="E49:O49" si="5">IF(E3=1,1,E3*1.05)</f>
+        <f t="shared" ref="E49:O49" si="6">IF(E3=1,1,E3*1.05)</f>
         <v>1</v>
       </c>
       <c r="F49" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G49" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H49" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I49" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J49" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K49" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="L49" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="M49" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="N49" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O49" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -30075,23 +29949,23 @@
         <v>176</v>
       </c>
       <c r="C50" s="104">
-        <f t="shared" ref="C50:O57" si="6">IF(C4=1,1,C4*1.05)</f>
+        <f t="shared" ref="C50:O57" si="7">IF(C4=1,1,C4*1.05)</f>
         <v>1</v>
       </c>
       <c r="D50" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E50" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F50" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G50" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H50" s="104">
@@ -30107,19 +29981,19 @@
         <v>0.95</v>
       </c>
       <c r="L50" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="M50" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N50" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="O50" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -30128,23 +30002,23 @@
         <v>177</v>
       </c>
       <c r="C51" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="D51" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E51" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F51" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G51" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H51" s="104">
@@ -30160,19 +30034,19 @@
         <v>0.95</v>
       </c>
       <c r="L51" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="M51" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N51" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="O51" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -30181,23 +30055,23 @@
         <v>178</v>
       </c>
       <c r="C52" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="D52" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E52" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F52" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G52" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H52" s="104">
@@ -30213,19 +30087,19 @@
         <v>0.95</v>
       </c>
       <c r="L52" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="M52" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N52" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="O52" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -30234,23 +30108,23 @@
         <v>179</v>
       </c>
       <c r="C53" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="D53" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E53" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F53" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G53" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H53" s="104">
@@ -30266,19 +30140,19 @@
         <v>0.95</v>
       </c>
       <c r="L53" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="M53" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N53" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="O53" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -30287,39 +30161,39 @@
         <v>180</v>
       </c>
       <c r="C54" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="D54" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E54" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F54" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G54" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H54" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I54" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J54" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K54" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L54" s="104">
@@ -30340,39 +30214,39 @@
         <v>181</v>
       </c>
       <c r="C55" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="D55" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E55" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F55" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G55" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H55" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I55" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J55" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K55" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L55" s="104">
@@ -30393,52 +30267,52 @@
         <v>182</v>
       </c>
       <c r="C56" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="D56" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E56" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F56" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G56" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H56" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I56" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J56" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K56" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L56" s="104">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="M56" s="104">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="N56" s="104">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="O56" s="104">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
@@ -30446,11 +30320,11 @@
         <v>185</v>
       </c>
       <c r="C57" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="D57" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E57" s="104">
@@ -30460,39 +30334,39 @@
         <v>0.77</v>
       </c>
       <c r="G57" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H57" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I57" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J57" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K57" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L57" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="M57" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N57" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="O57" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -30545,11 +30419,11 @@
         <v>189</v>
       </c>
       <c r="C59" s="104">
-        <f t="shared" ref="C59:O61" si="7">IF(C13=1,1,C13*1.05)</f>
+        <f t="shared" ref="C59:O61" si="8">IF(C13=1,1,C13*1.05)</f>
         <v>1</v>
       </c>
       <c r="D59" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E59" s="104">
@@ -30562,35 +30436,35 @@
         <v>0.77</v>
       </c>
       <c r="H59" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="I59" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J59" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K59" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="L59" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="M59" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="N59" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="O59" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -30599,56 +30473,52 @@
         <v>190</v>
       </c>
       <c r="C60" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="D60" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E60" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="F60" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="G60" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="H60" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="I60" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J60" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K60" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="L60" s="104">
-        <f>L54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M60" s="104">
-        <f t="shared" ref="M60:O60" si="8">M54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="N60" s="104">
-        <f t="shared" si="8"/>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O60" s="104">
-        <f t="shared" si="8"/>
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
@@ -30656,11 +30526,11 @@
         <v>205</v>
       </c>
       <c r="C61" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="D61" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E61" s="104">
@@ -30670,39 +30540,39 @@
         <v>0.44</v>
       </c>
       <c r="G61" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="H61" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="I61" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J61" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K61" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="L61" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="M61" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="N61" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="O61" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -30782,59 +30652,37 @@
         <v>1</v>
       </c>
       <c r="E65" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$14),0.97,(0.97*'Dist. de l''état nutritionnel'!E$14/(1-0.97*'Dist. de l''état nutritionnel'!E$14))
-/ ('Dist. de l''état nutritionnel'!E$14/(1-'Dist. de l''état nutritionnel'!E$14)))</f>
-        <v>0.87625293899269863</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F65" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$14),0.97,(0.97*'Dist. de l''état nutritionnel'!F$14/(1-0.97*'Dist. de l''état nutritionnel'!F$14))
-/ ('Dist. de l''état nutritionnel'!F$14/(1-'Dist. de l''état nutritionnel'!F$14)))</f>
-        <v>0.89739555722762776</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="G65" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$14),0.97,(0.97*'Dist. de l''état nutritionnel'!G$14/(1-0.97*'Dist. de l''état nutritionnel'!G$14))
-/ ('Dist. de l''état nutritionnel'!G$14/(1-'Dist. de l''état nutritionnel'!G$14)))</f>
-        <v>0.94348615096732857</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H65" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!H$14),0.97,(0.97*'Dist. de l''état nutritionnel'!H$14/(1-0.97*'Dist. de l''état nutritionnel'!H$14))
-/ ('Dist. de l''état nutritionnel'!H$14/(1-'Dist. de l''état nutritionnel'!H$14)))</f>
-        <v>0.94456660322622354</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I65" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!I$14),0.97,(0.97*'Dist. de l''état nutritionnel'!I$14/(1-0.97*'Dist. de l''état nutritionnel'!I$14))
-/ ('Dist. de l''état nutritionnel'!I$14/(1-'Dist. de l''état nutritionnel'!I$14)))</f>
-        <v>0.94703483342455097</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J65" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!J$14),0.97,(0.97*'Dist. de l''état nutritionnel'!J$14/(1-0.97*'Dist. de l''état nutritionnel'!J$14))
-/ ('Dist. de l''état nutritionnel'!J$14/(1-'Dist. de l''état nutritionnel'!J$14)))</f>
-        <v>0.94827497025810792</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="K65" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!K$14),0.97,(0.97*'Dist. de l''état nutritionnel'!K$14/(1-0.97*'Dist. de l''état nutritionnel'!K$14))
-/ ('Dist. de l''état nutritionnel'!K$14/(1-'Dist. de l''état nutritionnel'!K$14)))</f>
-        <v>0.94748450792983951</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="L65" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!L$14),0.97,(0.97*'Dist. de l''état nutritionnel'!L$14/(1-0.97*'Dist. de l''état nutritionnel'!L$14))
-/ ('Dist. de l''état nutritionnel'!L$14/(1-'Dist. de l''état nutritionnel'!L$14)))</f>
-        <v>0.94456660322622354</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="M65" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!M$14),0.97,(0.97*'Dist. de l''état nutritionnel'!M$14/(1-0.97*'Dist. de l''état nutritionnel'!M$14))
-/ ('Dist. de l''état nutritionnel'!M$14/(1-'Dist. de l''état nutritionnel'!M$14)))</f>
-        <v>0.94703483342455097</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="N65" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!N$14),0.97,(0.97*'Dist. de l''état nutritionnel'!N$14/(1-0.97*'Dist. de l''état nutritionnel'!N$14))
-/ ('Dist. de l''état nutritionnel'!N$14/(1-'Dist. de l''état nutritionnel'!N$14)))</f>
-        <v>0.94827497025810792</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="O65" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!O$14),0.97,(0.97*'Dist. de l''état nutritionnel'!O$14/(1-0.97*'Dist. de l''état nutritionnel'!O$14))
-/ ('Dist. de l''état nutritionnel'!O$14/(1-'Dist. de l''état nutritionnel'!O$14)))</f>
-        <v>0.94748450792983951</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
     <row r="66" spans="2:15" x14ac:dyDescent="0.25">
@@ -30851,47 +30699,47 @@
       </c>
       <c r="E66" s="104">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>1.0247999999999999</v>
       </c>
       <c r="F66" s="104">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>1.0247999999999999</v>
       </c>
       <c r="G66" s="104">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>1.0247999999999999</v>
       </c>
       <c r="H66" s="104">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>1.0247999999999999</v>
       </c>
       <c r="I66" s="104">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>1.0247999999999999</v>
       </c>
       <c r="J66" s="104">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>1.0247999999999999</v>
       </c>
       <c r="K66" s="104">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>1.0247999999999999</v>
       </c>
       <c r="L66" s="104">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>1.0247999999999999</v>
       </c>
       <c r="M66" s="104">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>1.0247999999999999</v>
       </c>
       <c r="N66" s="104">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>1.0247999999999999</v>
       </c>
       <c r="O66" s="104">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>1.0247999999999999</v>
       </c>
     </row>
     <row r="67" spans="2:15" x14ac:dyDescent="0.25">
@@ -30907,63 +30755,41 @@
         <v>1</v>
       </c>
       <c r="E67" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$14),0.92,(0.92*'Dist. de l''état nutritionnel'!E$14/(1-0.92*'Dist. de l''état nutritionnel'!E$14))
-/ ('Dist. de l''état nutritionnel'!E$14/(1-'Dist. de l''état nutritionnel'!E$14)))</f>
-        <v>0.71578797783146231</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F67" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$14),0.92,(0.92*'Dist. de l''état nutritionnel'!F$14/(1-0.92*'Dist. de l''état nutritionnel'!F$14))
-/ ('Dist. de l''état nutritionnel'!F$14/(1-'Dist. de l''état nutritionnel'!F$14)))</f>
-        <v>0.75673538891929704</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="G67" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$14),0.92,(0.92*'Dist. de l''état nutritionnel'!G$14/(1-0.92*'Dist. de l''état nutritionnel'!G$14))
-/ ('Dist. de l''état nutritionnel'!G$14/(1-'Dist. de l''état nutritionnel'!G$14)))</f>
-        <v>0.85586278136786231</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H67" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!H$14),0.92,(0.92*'Dist. de l''état nutritionnel'!H$14/(1-0.92*'Dist. de l''état nutritionnel'!H$14))
-/ ('Dist. de l''état nutritionnel'!H$14/(1-'Dist. de l''état nutritionnel'!H$14)))</f>
-        <v>0.85836697117767868</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I67" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!I$14),0.92,(0.92*'Dist. de l''état nutritionnel'!I$14/(1-0.92*'Dist. de l''état nutritionnel'!I$14))
-/ ('Dist. de l''état nutritionnel'!I$14/(1-'Dist. de l''état nutritionnel'!I$14)))</f>
-        <v>0.86412120388613367</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J67" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!J$14),0.92,(0.92*'Dist. de l''état nutritionnel'!J$14/(1-0.92*'Dist. de l''état nutritionnel'!J$14))
-/ ('Dist. de l''état nutritionnel'!J$14/(1-'Dist. de l''état nutritionnel'!J$14)))</f>
-        <v>0.86703011767834581</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="K67" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!K$14),0.92,(0.92*'Dist. de l''état nutritionnel'!K$14/(1-0.92*'Dist. de l''état nutritionnel'!K$14))
-/ ('Dist. de l''état nutritionnel'!K$14/(1-'Dist. de l''état nutritionnel'!K$14)))</f>
-        <v>0.86517459889443182</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="L67" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!L$14),0.92,(0.92*'Dist. de l''état nutritionnel'!L$14/(1-0.92*'Dist. de l''état nutritionnel'!L$14))
-/ ('Dist. de l''état nutritionnel'!L$14/(1-'Dist. de l''état nutritionnel'!L$14)))</f>
-        <v>0.85836697117767868</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="M67" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!M$14),0.92,(0.92*'Dist. de l''état nutritionnel'!M$14/(1-0.92*'Dist. de l''état nutritionnel'!M$14))
-/ ('Dist. de l''état nutritionnel'!M$14/(1-'Dist. de l''état nutritionnel'!M$14)))</f>
-        <v>0.86412120388613367</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="N67" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!N$14),0.92,(0.92*'Dist. de l''état nutritionnel'!N$14/(1-0.92*'Dist. de l''état nutritionnel'!N$14))
-/ ('Dist. de l''état nutritionnel'!N$14/(1-'Dist. de l''état nutritionnel'!N$14)))</f>
-        <v>0.86703011767834581</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="O67" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!O$14),0.92,(0.92*'Dist. de l''état nutritionnel'!O$14/(1-0.92*'Dist. de l''état nutritionnel'!O$14))
-/ ('Dist. de l''état nutritionnel'!O$14/(1-'Dist. de l''état nutritionnel'!O$14)))</f>
-        <v>0.86517459889443182</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="lBfUxqkq4mMD01s+wA2xumrI2N27SSZXpCL3oo6kIZKVbQDVRYzrvhPInlnKh+uz9hPXSr2etdmIgZJGZJTH9A==" saltValue="MXcosmR9FKBR8D14jSytsA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="nhVH3M+msgK+si/XFYs9Nd5+JGTrKwnSVw5sZq1hC5pfeDcV9mhwSBg87URWz+XnuFvASl9WzA+yTHdcfnTHTw==" saltValue="xncZD8I+0WcFyhU/aC1o3Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -31015,24 +30841,20 @@
         <v>1</v>
       </c>
       <c r="D3" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!D$11),(1/1.33),((1/1.33)*'Dist. de l''état nutritionnel'!D$11/(1-(1/1.33)*'Dist. de l''état nutritionnel'!D$11))
-/ ('Dist. de l''état nutritionnel'!D$11/(1-'Dist. de l''état nutritionnel'!D$11)))</f>
-        <v>0.74418604651162779</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="E3" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$11),(1/1.33),((1/1.33)*'Dist. de l''état nutritionnel'!E$11/(1-(1/1.33)*'Dist. de l''état nutritionnel'!E$11))
-/ ('Dist. de l''état nutritionnel'!E$11/(1-'Dist. de l''état nutritionnel'!E$11)))</f>
-        <v>0.74891097206376045</v>
+        <f t="shared" ref="E3:G3" si="0">1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="F3" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$11),(1/1.33),((1/1.33)*'Dist. de l''état nutritionnel'!F$11/(1-(1/1.33)*'Dist. de l''état nutritionnel'!F$11))
-/ ('Dist. de l''état nutritionnel'!F$11/(1-'Dist. de l''état nutritionnel'!F$11)))</f>
-        <v>0.74998192742905989</v>
+        <f t="shared" si="0"/>
+        <v>0.75187969924812026</v>
       </c>
       <c r="G3" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$11),(1/1.33),((1/1.33)*'Dist. de l''état nutritionnel'!G$11/(1-(1/1.33)*'Dist. de l''état nutritionnel'!G$11))
-/ ('Dist. de l''état nutritionnel'!G$11/(1-'Dist. de l''état nutritionnel'!G$11)))</f>
-        <v>0.75050381305965674</v>
+        <f t="shared" si="0"/>
+        <v>0.75187969924812026</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -31054,24 +30876,20 @@
         <v>1</v>
       </c>
       <c r="D5" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!D$10),(1/1.33),((1/1.33)*'Dist. de l''état nutritionnel'!D$10/(1-(1/1.33)*'Dist. de l''état nutritionnel'!D$10))
-/ ('Dist. de l''état nutritionnel'!D$10/(1-'Dist. de l''état nutritionnel'!D$10)))</f>
-        <v>0.74137931034482751</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="E5" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$10),(1/1.33),((1/1.33)*'Dist. de l''état nutritionnel'!E$10/(1-(1/1.33)*'Dist. de l''état nutritionnel'!E$10))
-/ ('Dist. de l''état nutritionnel'!E$10/(1-'Dist. de l''état nutritionnel'!E$10)))</f>
-        <v>0.74137473695379219</v>
+        <f t="shared" ref="E5:G5" si="1">1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="F5" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$10),(1/1.33),((1/1.33)*'Dist. de l''état nutritionnel'!F$10/(1-(1/1.33)*'Dist. de l''état nutritionnel'!F$10))
-/ ('Dist. de l''état nutritionnel'!F$10/(1-'Dist. de l''état nutritionnel'!F$10)))</f>
-        <v>0.74367982247882258</v>
+        <f t="shared" si="1"/>
+        <v>0.75187969924812026</v>
       </c>
       <c r="G5" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$10),(1/1.33),((1/1.33)*'Dist. de l''état nutritionnel'!G$10/(1-(1/1.33)*'Dist. de l''état nutritionnel'!G$10))
-/ ('Dist. de l''état nutritionnel'!G$10/(1-'Dist. de l''état nutritionnel'!G$10)))</f>
-        <v>0.74764262641695323</v>
+        <f t="shared" si="1"/>
+        <v>0.75187969924812026</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="106" customFormat="1" ht="13" x14ac:dyDescent="0.3">
@@ -31111,24 +30929,20 @@
         <v>1</v>
       </c>
       <c r="D10" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!D$11),(1/1.54),((1/1.54)*'Dist. de l''état nutritionnel'!D$11/(1-(1/1.54)*'Dist. de l''état nutritionnel'!D$11))
-/ ('Dist. de l''état nutritionnel'!D$11/(1-'Dist. de l''état nutritionnel'!D$11)))</f>
-        <v>0.64</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="E10" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$11),(1/1.54),((1/1.54)*'Dist. de l''état nutritionnel'!E$11/(1-(1/1.54)*'Dist. de l''état nutritionnel'!E$11))
-/ ('Dist. de l''état nutritionnel'!E$11/(1-'Dist. de l''état nutritionnel'!E$11)))</f>
-        <v>0.64573318763423793</v>
+        <f t="shared" ref="E10:G10" si="2">1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="F10" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$11),(1/1.54),((1/1.54)*'Dist. de l''état nutritionnel'!F$11/(1-(1/1.54)*'Dist. de l''état nutritionnel'!F$11))
-/ ('Dist. de l''état nutritionnel'!F$11/(1-'Dist. de l''état nutritionnel'!F$11)))</f>
-        <v>0.64703681148148418</v>
+        <f t="shared" si="2"/>
+        <v>0.64935064935064934</v>
       </c>
       <c r="G10" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$11),(1/1.54),((1/1.54)*'Dist. de l''état nutritionnel'!G$11/(1-(1/1.54)*'Dist. de l''état nutritionnel'!G$11))
-/ ('Dist. de l''état nutritionnel'!G$11/(1-'Dist. de l''état nutritionnel'!G$11)))</f>
-        <v>0.64767263413148468</v>
+        <f t="shared" si="2"/>
+        <v>0.64935064935064934</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -31150,24 +30964,20 @@
         <v>1</v>
       </c>
       <c r="D12" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!D$10),(1/1.54),((1/1.54)*'Dist. de l''état nutritionnel'!D$10/(1-(1/1.54)*'Dist. de l''état nutritionnel'!D$10))
-/ ('Dist. de l''état nutritionnel'!D$10/(1-'Dist. de l''état nutritionnel'!D$10)))</f>
-        <v>0.63660834454912518</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="E12" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$10),(1/1.54),((1/1.54)*'Dist. de l''état nutritionnel'!E$10/(1-(1/1.54)*'Dist. de l''état nutritionnel'!E$10))
-/ ('Dist. de l''état nutritionnel'!E$10/(1-'Dist. de l''état nutritionnel'!E$10)))</f>
-        <v>0.63660282656050271</v>
+        <f t="shared" ref="E12:G12" si="3">1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="F12" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$10),(1/1.54),((1/1.54)*'Dist. de l''état nutritionnel'!F$10/(1-(1/1.54)*'Dist. de l''état nutritionnel'!F$10))
-/ ('Dist. de l''état nutritionnel'!F$10/(1-'Dist. de l''état nutritionnel'!F$10)))</f>
-        <v>0.6393875097491748</v>
+        <f t="shared" si="3"/>
+        <v>0.64935064935064934</v>
       </c>
       <c r="G12" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$10),(1/1.54),((1/1.54)*'Dist. de l''état nutritionnel'!G$10/(1-(1/1.54)*'Dist. de l''état nutritionnel'!G$10))
-/ ('Dist. de l''état nutritionnel'!G$10/(1-'Dist. de l''état nutritionnel'!G$10)))</f>
-        <v>0.64419127013395971</v>
+        <f t="shared" si="3"/>
+        <v>0.64935064935064934</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="106" customFormat="1" ht="13" x14ac:dyDescent="0.3">
@@ -31207,24 +31017,20 @@
         <v>1</v>
       </c>
       <c r="D17" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!D$11),(1/1.16),((1/1.16)*'Dist. de l''état nutritionnel'!D$11/(1-(1/1.16)*'Dist. de l''état nutritionnel'!D$11))
-/ ('Dist. de l''état nutritionnel'!D$11/(1-'Dist. de l''état nutritionnel'!D$11)))</f>
-        <v>0.85714285714285721</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="E17" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$11),(1/1.16),((1/1.16)*'Dist. de l''état nutritionnel'!E$11/(1-(1/1.16)*'Dist. de l''état nutritionnel'!E$11))
-/ ('Dist. de l''état nutritionnel'!E$11/(1-'Dist. de l''état nutritionnel'!E$11)))</f>
-        <v>0.86017345661971134</v>
+        <f t="shared" ref="E17:G17" si="4">1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="F17" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$11),(1/1.16),((1/1.16)*'Dist. de l''état nutritionnel'!F$11/(1-(1/1.16)*'Dist. de l''état nutritionnel'!F$11))
-/ ('Dist. de l''état nutritionnel'!F$11/(1-'Dist. de l''état nutritionnel'!F$11)))</f>
-        <v>0.86085802051335469</v>
+        <f t="shared" si="4"/>
+        <v>0.86206896551724144</v>
       </c>
       <c r="G17" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$11),(1/1.16),((1/1.16)*'Dist. de l''état nutritionnel'!G$11/(1-(1/1.16)*'Dist. de l''état nutritionnel'!G$11))
-/ ('Dist. de l''état nutritionnel'!G$11/(1-'Dist. de l''état nutritionnel'!G$11)))</f>
-        <v>0.86119130020042822</v>
+        <f t="shared" si="4"/>
+        <v>0.86206896551724144</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -31246,28 +31052,24 @@
         <v>1</v>
       </c>
       <c r="D19" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!D$10),(1/1.16),((1/1.16)*'Dist. de l''état nutritionnel'!D$10/(1-(1/1.16)*'Dist. de l''état nutritionnel'!D$10))
-/ ('Dist. de l''état nutritionnel'!D$10/(1-'Dist. de l''état nutritionnel'!D$10)))</f>
-        <v>0.85533453887884281</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="E19" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$10),(1/1.16),((1/1.16)*'Dist. de l''état nutritionnel'!E$10/(1-(1/1.16)*'Dist. de l''état nutritionnel'!E$10))
-/ ('Dist. de l''état nutritionnel'!E$10/(1-'Dist. de l''état nutritionnel'!E$10)))</f>
-        <v>0.85533158742052517</v>
+        <f t="shared" ref="E19:G19" si="5">1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="F19" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$10),(1/1.16),((1/1.16)*'Dist. de l''état nutritionnel'!F$10/(1-(1/1.16)*'Dist. de l''état nutritionnel'!F$10))
-/ ('Dist. de l''état nutritionnel'!F$10/(1-'Dist. de l''état nutritionnel'!F$10)))</f>
-        <v>0.85681715347913645</v>
+        <f t="shared" si="5"/>
+        <v>0.86206896551724144</v>
       </c>
       <c r="G19" s="104">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$10),(1/1.16),((1/1.16)*'Dist. de l''état nutritionnel'!G$10/(1-(1/1.16)*'Dist. de l''état nutritionnel'!G$10))
-/ ('Dist. de l''état nutritionnel'!G$10/(1-'Dist. de l''état nutritionnel'!G$10)))</f>
-        <v>0.8593615961490525</v>
+        <f t="shared" si="5"/>
+        <v>0.86206896551724144</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Tr8/Qc8J7MVM+3NSYnX4sBnJ79P6pezaaBhsrhSfyojB99vHlOU2ooHb9PtzuUYrN3Kcal9z5q3Mdm0/VklEVQ==" saltValue="BP+jVcv38smSvsRh7xwXRA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="4TVIFyOkYfEEwRNam+tDp3gL01o20oPglM32uLUn4TYy2NEjDvJudY0gFmopsI//UgKWogDJ4KcjhSC8V3x7lQ==" saltValue="+VedqTCsotsl2KPdL5O1qQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -32460,7 +32262,7 @@
         <v>335</v>
       </c>
       <c r="D53" s="104">
-        <v>0.51</v>
+        <v>0.32</v>
       </c>
       <c r="E53" s="104">
         <v>0</v>
@@ -33716,7 +33518,7 @@
         <v>335</v>
       </c>
       <c r="D108" s="104">
-        <v>0.18</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="E108" s="104">
         <v>0</v>
@@ -34977,7 +34779,7 @@
         <v>335</v>
       </c>
       <c r="D163" s="104">
-        <v>0.71</v>
+        <v>0.47</v>
       </c>
       <c r="E163" s="104">
         <v>0</v>
@@ -34993,7 +34795,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="lexfA0GgCAdVT7jB0nYZvbWmGzSb3YsKPiqH7h2HPHtqK4NuuPC399eiIrUJTo3m74SNVQbBBSxw39yISnzcVQ==" saltValue="cvCNnQeSMF9NpXKTcTT6lg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="xE6i9biNdAVCejo+IfRN4ZNuyhuHhsvxAy/4FtmLoPVatA6Wb1VIOCSkv86q8qSDz3wLaVVETg6bRNc9XvSViA==" saltValue="c9PY2uVO9t7fS+Hjutog3w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -35495,7 +35297,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="jTvb0XxU8Y+k3GQBZQQhGJhGLPtUuWsWWgKH1ZwowGDytq6n1xDLZZ4uFNtnEKZNm2XLIPLpocp7Fise/fa24g==" saltValue="6tsFZDgQ/b+pntaUKLM3dA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="YYri0FAUqC8xv0bvlGLkAayTmpDYJLqaRBaXZjelul+rn1ydM1mPCUU5U3RiBXAj/AF+4xZ2fVx9e9zgHrquWA==" saltValue="ItPU8UGHxwxStPTnG+bRNg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -35927,7 +35729,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="VycXmAdTm3bHezgiiXJxPQ/fFd1DDg2ZODiXf6Vtx6mE0jWhvzEzoexAzERuUPrhXw21mH7d2lAR8Er5VrvU2Q==" saltValue="vhyLDJfHNoAJ4wzSaYK33Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="4gP6duPJrWQ+IIZjMIfY174qkXgY63nHKkW67Q/N/wkL0NmTr+0JPA3OkSMPWsiLIhBKA7U7dxFEBvhEnpkgDQ==" saltValue="WyYP0BHuvODzTq3N0RRzZw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="69" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
@@ -36346,7 +36148,7 @@
       <c r="G17" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="I5OWTDnSrbdL6OKZ2grj5sDs7N+pvLECWXGxhbWClDR17D8nORNzCX5O/5xLOdzsBQrp5Hw+rU2zQrdmEXWBAw==" saltValue="NnrLreDzaZuOQeKa8C52Qw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="zyj0D3t0eIeCm531PCwIQSxYMVq76MIKiPDr/dJwKIuxA8tfvxtqzyYFjx/aVDUSkefS4vAJczqiJLVpls8wwQ==" saltValue="5q5cIAY6XLaRlQURJMC8uA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <drawing r:id="rId1"/>
@@ -36478,7 +36280,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="uFHQOE7OwhxWa4afGNfkj51sX0G341fJeSOKuGBHJUIs16fpHsa4tydizs1DrISycoxYX6+WdL/fcGeIFxmKNQ==" saltValue="C41hmGivvl3tCQlVX+AUgg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="AekI9uVR8MUuvG/OLQbJi57T4rtg8MX0B/Kg35SP6WHuS7e2oBLzinEacl/u1HgFzysAWjckxe92/iAPPK5XkQ==" saltValue="By84FQmqqNUTRnyV+KYnCg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -36680,7 +36482,7 @@
       <c r="K14" s="115"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="sMZ7vQCJ77HBJdY75LPdwa32v/iX8mOjFlnaSvh2GHIVeMhuFYVfeUKBJFNDii5CQ2iZRrWIeQxOZ2zOpkWBUQ==" saltValue="jQgtwD2WR6GbB+YGBaqaNA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="5fBqH7iacUWMcAWrTXsnMYvTa61BO+CLHpjq7Wpp9+CMSKGIWC8lTc06LSoO5FOMLIlcSJ7ZzFTpXjEgvC2ITw==" saltValue="UAl494FTP6OAyTADfFR2+g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="193" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -36756,7 +36558,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="xX16wnLvnI7Pk07zg8Uf0Doe11iJMmvFrmp8OhgxkMO7prJ3dvkeeQQlOpldtOLRoKZg3ANkJxeq0yY/07KkSA==" saltValue="vTfqdOWCkM1KhSWn8F8c1w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="jtZtEDpMItoplxECtbr6Zfp2STH+NFWQ705aXCfe06iJKpV3wPpUymEnncw5yUJE4yfO/DpX8arW0Zsiwls0pg==" saltValue="Crubk/8ZeB5JHAd0N2PeJA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -37011,7 +36813,7 @@
       <c r="E21" s="62"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="jkqkoLqJAvm+k/2l54CZ2HJDVtIY1RwlXy8GDENXBVFuCAiwvQkSxmR602xMMBn706TiMju+gZQ+rDcJsTiKOg==" saltValue="DjtBP5FSoHw/qiJsYr4rBQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="+7Hz+8ezMn0PTM0m5Wa01rFcVrd0Luv1++5t9CdejkG34vt/d0cBjLd/iM9tmSDZkpDpQwlaxaT99La0Ptr1/Q==" saltValue="PQy2pwnKY3KIAhAZ6mONgA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -37070,7 +36872,7 @@
       <c r="D3" s="62"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ULy1GeqQfGk45V/NPbqFB2r65ni+0cip/Sq8SvrGPMrd4y6sfkcjvH3FYM0wBdTi3LTlQi9ZkbbEYhmdfqPJ9A==" saltValue="lTx4yJowfawaxXClRRJOcw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="PhE3a6uRxOiZj1J662UO5AtnLE4p5b5jzikPoUj16Qz4w+xGiJkevEHi9jThj3zoRxOy0forcOc7b7BXA7RSmA==" saltValue="pbF7KZea7VezsmsBtttTFA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/inputs/fr/demo_national_input.xlsx
+++ b/inputs/fr/demo_national_input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr saveExternalLinkValues="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\Nutrition\inputs\fr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72442774-22DF-4D56-B68C-F88F4C0D9299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E243309B-4E6A-4A9B-A5B3-D41FD901C9C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="961" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10180" tabRatio="961" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Données pop de l'année de ref" sheetId="1" r:id="rId1"/>
@@ -508,6 +508,304 @@
 </file>
 
 <file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Nick Scott</author>
+  </authors>
+  <commentList>
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{7F5E27CE-1436-4C41-A7F1-63F83A7F0B04}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Olofin I, McDonald CM, Ezzati M, et al. Associations of Suboptimal Growth with All-Cause and Cause-Specific Mortality in Children under Five Years: A Pooled Analysis of Ten Prospective Studies. PLOS One 2013; 8(5): e64636. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D30" authorId="0" shapeId="0" xr:uid="{B41F646A-8FD6-4852-BF16-B5442AB7C7D9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Olofin I, McDonald CM, Ezzati M, et al. Associations of Suboptimal Growth with All-Cause and Cause-Specific Mortality in Children under Five Years: A Pooled Analysis of Ten Prospective Studies. PLOS One 2013; 8(5): e64636</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D57" authorId="0" shapeId="0" xr:uid="{CC986596-2B0F-42A9-9A47-88DAE772D109}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Heidkamp R, Guida R, Phillips E, Clermont A. The Lives Saved Tool (LiST) as a Model for Prevention of Anemia in Women of Reproductive Age. J Nutr. 2017;147(11):2156S-2162S</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D66" authorId="0" shapeId="0" xr:uid="{3F4E7CBA-2B10-4502-8317-5655216D1A3E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+NEOVITA Study Group. Timing of initiation, patterns of breastfeeding, and infant survival: prospective analysis of pooled data from three randomised trials. Lancet Global Health 2016; 4(4): e266-75. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D70" authorId="0" shapeId="0" xr:uid="{70995A78-B3A6-4CBF-84F2-73260F6E3697}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+NEOVITA Study Group. Timing of initiation, patterns of breastfeeding, and infant survival: prospective analysis of pooled data from three randomised trials. Lancet Global Health 2016; 4(4): e266-75. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D74" authorId="0" shapeId="0" xr:uid="{6DD196E0-C02E-4DCD-8399-4DB5DA640B82}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+NEOVITA Study Group. Timing of initiation, patterns of breastfeeding, and infant survival: prospective analysis of pooled data from three randomised trials. Lancet Global Health 2016; 4(4): e266-75. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D82" authorId="0" shapeId="0" xr:uid="{AC599970-9F13-47AA-8593-282B4B25AE84}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D86" authorId="0" shapeId="0" xr:uid="{B90C3FE6-0710-44A3-BA91-58AF31680641}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D90" authorId="0" shapeId="0" xr:uid="{AF883F52-57AF-4371-B93E-04D28670E1E3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D94" authorId="0" shapeId="0" xr:uid="{06FA942C-64E9-47C9-A605-62CF64FBD212}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D98" authorId="0" shapeId="0" xr:uid="{0270CB67-F57B-49D6-8659-A0C53EC25924}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D105" authorId="0" shapeId="0" xr:uid="{F2FA744C-6A87-4925-8C09-A199439E98F3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Nick Scott</author>
@@ -1689,7 +1987,7 @@
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1859,6 +2157,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -5669,7 +5980,7 @@
       <c r="A63" s="4"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="9gizxvDRtYJ2FicmJhOKv83Ey7zWoZtKDQrWclH69SgbPQEEdHLx7ucy78BBxJ1AoOb33Jxc+BKJxuHnAGDETA==" saltValue="I9r4kuTxyWtQt8/VibQSuA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="1ssUKEHHlhM640dXHxuSKtD7+stqNsBczvINE3Jp7/HTdd1ttIHGmEQ56BRJSH1MLdgACDcMWdOzz9sCM6TX7Q==" saltValue="bXkeR0b5BlLoGd4x57sr2Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -5694,7 +6005,7 @@
     <col min="8" max="16384" width="14.453125" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="39" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="41" t="s">
         <v>160</v>
       </c>
@@ -6593,7 +6904,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1cNA82dRDUoGyjy18oPTztDeW5Ltx/q51bJWcJZ2NB7tvRQFGuUJG1aSiSgDC1tZp15Mp7CfWZa8BKw07WHcBg==" saltValue="8aQ6W9DtGs1nfgVusfX+kA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="cAb2BLA3Rf9zkXk6Qy+XWYblC2bpGXoUD//jQnIa+4A9aiJlVhR/wLgK3+cHSjDmEjoODYZlwcGHIc9LGJyAHg==" saltValue="OLU2TaTM74sCz8wEcjtozg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D39">
     <sortCondition ref="A2:A39"/>
   </sortState>
@@ -6752,7 +7063,7 @@
       <c r="C20" s="67"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="GkjSDQ98pdAkZnrMUNQ855mzC5h6/ybZ1WqXno0/hQkw0xyqunK19EDh8EmNmaOq/1M+6Q8sh+CziX/Vmbs/Aw==" saltValue="eULBhS42/Cju0tqggeHTRg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="YCEdJsrzxM92U+0cq2X1FSFSXOEwSXb6DP4N0gvLJ8x+DQFM0uEu+NnUT+qq/X/5Pup/yXhHp0g8rtrUjlb3fw==" saltValue="als1hxLdF1aLz3YPt17nQA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -6847,7 +7158,7 @@
       <c r="A19" s="35"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="dEa9AMosXGnfo+xUM1XqTAXVNKimgo5h2k9riNOZ7PlFqCp4hahbb7jsZoukvn+bzDABO/azBrw+tAPr7AENOQ==" saltValue="05WfxP3MQ7mALZnmuXyPeA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="x40i24ZKEegB4ZvjwvRWSYO0cwkHgiYgsqrz41LadYrcCG97NGZjSuj4Uc+eZqxJekH8add00LhFmWnqcUii/g==" saltValue="ku06dmrMe4cr7b2c8sggvw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -6957,7 +7268,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="HWAGg1wLQHjxu69Kqi9QM/Ph69ppaTMBWlKQU0DB7PIqTujOFU0zMcG2cpjIdaUn35jlwVad7lfEtkvtRW3d6w==" saltValue="dqwe27qUkQuvoMc5gPIETg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="wQTPLWA4sbk2bCZ1ICKjdbeFEH8HGbrsI2bi86ehfOU4mwb2CQnMJCjeIGx1VSXxP1A+VaatxKDI/O+rOWekEA==" saltValue="afAYKdRYcpU8Ih7DwZuY/A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -8713,7 +9024,7 @@
       <c r="B40" s="9"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="OEPP47uYCytcDOyxdHT++Ib3u4UyhaUpe6HLX1BecDyJtxRbDqBkGrskM+LnMAyt1aG37SFwlnMAfsvhSSN4Fw==" saltValue="1Ady6J5HYVYaCOz2OmSC8g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="D0PSK3Q/iMDyfvAOf6rV2ks0Y/NOWoapuU713S2BEqEgg8DAEKF4Vopbt79Bvs/0DE6PbfoVYn30EAY6c2qRVQ==" saltValue="PKkbvk9Yu1lwfwjtfpY1PQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B15:O22">
     <sortCondition ref="B15:B22"/>
   </sortState>
@@ -8748,7 +9059,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="6SeBS2Ee+ZxIBL4jIYI/QaRRnf8C1j6ZLnireDVTcrXPrtLwCpSmIm3J/sRNlChyMWTwFOj1Nje4AMf7MwZ/iw==" saltValue="ZzplEobGDr8VgWZCgL99YQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="yAwNK0XzqA2cZxpXW5RgXBuUNNndrMHgU8PyXL+aqHp39FmXpLmDgQBYrBkwk0yxoL2bJ+vwX/eT/2NKRUsgaw==" saltValue="p1aZw5BhaHeJYHG2S7deCQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8948,7 +9259,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="SgYqDVeG71kbEuerYsLQ9+r2iqc7OrpcTtS5SaoTn4+vVimT6T7cw1G7Ji4LkeIs9d3eL5eIN4zrFoHzXs1F3g==" saltValue="qsGbYg+hn/ja+eJpd4mmdg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="oq8yY5FzW0KlzdDystv4m+Y7XOGZ/D+CoF7yk9KJm853dl+ZLrt04RFCg5Gm1kKJm/Ja5KUR3kM3mf8986I7Ig==" saltValue="lD/Yl5Z96WKreqDzcep8Fg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -10757,7 +11068,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="zvRXivAncZzn86RaTlxZ4PBo5XQXFheyWKsW5JQZRV0LPDuaCyM4qxFy8hiA0nQ9NfDC27GHss3TlagtVMqtLw==" saltValue="sTrhfpGVluFuhB0fTCvXIg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="d2dc5Ttu+8O0c1ObZSzb1DRJsUSft3fVwRxnFfNklZUcMnL8NVRsdAklXZNkwmKdHCCz7RggFQ8p+MgsbVzVWA==" saltValue="MN3eqsY9qywxXFdhDPxvSg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -11519,7 +11830,7 @@
       <c r="K39" s="101"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="6UipioMbckY2rfKhyhIKuqN/qW126A+QyADgvP/LpNioFod0ztjd4xDP4SalOTiGe6ofOHOSEko2m5/WrzkC9w==" saltValue="K/lMqnC8Gk/1Bmp+qPJHBQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="sN79CQMb0pIXafv/1oKd/xV1hgrFON8twz/x+zyfTGYtbgSR/uVCDc8EKgVcPuS+hvTX1ialbR9OZdZMMqfZhw==" saltValue="rIusfrKhD1Os5do3ih5QGA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -11888,7 +12199,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ipkqVGNWmTpZ/jeGR0Kjvi5HtuADpVe4RBpHeq07hmsKZBZ5qsIrgrBkV0R0UbJnHJBL1r24CGKMlIh0KIc0GA==" saltValue="es4h9pfUy7L3yiN3RoD7MA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="JXNSv5CHaWrJwYl/igEU/oJV0f+GLV7XnY3STGouXRIjLH2zaXGiq+nQEJEhCxK1Drg3P1W9uxMgtSm9oOv5Nw==" saltValue="l8js7r/D6t94t3L9suVsfg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -12972,7 +13283,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="bmf+EGasAIV7X69KUm5rUC0BSe4T7JS0T/xq1MAActjYVPamBZPzNV63lzQIBASezGjykP2VkLT0SydWmk/z/Q==" saltValue="GgxCBjGDkJz6JopRZnKVRA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="8mc0Xmr0DI7q/2MLnWA9crEnlD34FVmWCjdGM99uYz0CNnyRqbX1biCjFKFyUkuSU0z1+sg5gVmGq9p1UwBVhw==" saltValue="WLluSsn+eln6XhHVJ3+/Nw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <conditionalFormatting sqref="B2:I16 B17:C17 E17:I17 B18:I40">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>$A2=""</formula>
@@ -13101,7 +13412,7 @@
         <v>153</v>
       </c>
       <c r="D5" s="102">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="E5" s="102">
         <v>1</v>
@@ -13122,7 +13433,7 @@
         <v>154</v>
       </c>
       <c r="D6" s="102">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="E6" s="102">
         <v>1</v>
@@ -13169,7 +13480,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="102">
-        <v>1.73</v>
+        <v>2.48</v>
       </c>
       <c r="F8" s="102">
         <v>1</v>
@@ -13190,7 +13501,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="102">
-        <v>1.73</v>
+        <v>2.48</v>
       </c>
       <c r="F9" s="102">
         <v>1</v>
@@ -13237,7 +13548,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="102">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="G11" s="102">
         <v>1</v>
@@ -13258,7 +13569,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="102">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="G12" s="102">
         <v>1</v>
@@ -13305,7 +13616,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="102">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="H14" s="102">
         <v>1</v>
@@ -13326,7 +13637,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="102">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="H15" s="102">
         <v>1</v>
@@ -14167,7 +14478,7 @@
         <v>154</v>
       </c>
       <c r="D56" s="102">
-        <f t="shared" ref="D56:H59" si="1">IF(D3=1,1,D3*0.9)</f>
+        <f t="shared" ref="D56:H68" si="1">IF(D3=1,1,D3*0.9)</f>
         <v>1</v>
       </c>
       <c r="E56" s="102">
@@ -14221,7 +14532,7 @@
         <v>153</v>
       </c>
       <c r="D58" s="102">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="E58" s="102">
         <f t="shared" si="1"/>
@@ -14246,7 +14557,7 @@
         <v>154</v>
       </c>
       <c r="D59" s="102">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="E59" s="102">
         <f t="shared" si="1"/>
@@ -14287,7 +14598,7 @@
         <v>1</v>
       </c>
       <c r="H60" s="102">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -14303,7 +14614,7 @@
         <v>1</v>
       </c>
       <c r="E61" s="102">
-        <v>1.35</v>
+        <v>1.99</v>
       </c>
       <c r="F61" s="102">
         <f t="shared" si="2"/>
@@ -14314,7 +14625,7 @@
         <v>1</v>
       </c>
       <c r="H61" s="102">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -14328,7 +14639,7 @@
         <v>1</v>
       </c>
       <c r="E62" s="102">
-        <v>1.35</v>
+        <v>1.99</v>
       </c>
       <c r="F62" s="102">
         <f t="shared" si="2"/>
@@ -14339,7 +14650,7 @@
         <v>1</v>
       </c>
       <c r="H62" s="102">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -14365,7 +14676,7 @@
         <v>1</v>
       </c>
       <c r="H63" s="102">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -14385,14 +14696,14 @@
         <v>1</v>
       </c>
       <c r="F64" s="102">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G64" s="102">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H64" s="102">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -14410,14 +14721,14 @@
         <v>1</v>
       </c>
       <c r="F65" s="102">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G65" s="102">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H65" s="102">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -14443,7 +14754,7 @@
         <v>1</v>
       </c>
       <c r="H66" s="102">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -14467,10 +14778,10 @@
         <v>1</v>
       </c>
       <c r="G67" s="102">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H67" s="102">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -14492,10 +14803,10 @@
         <v>1</v>
       </c>
       <c r="G68" s="102">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H68" s="102">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -15504,7 +15815,7 @@
         <v>154</v>
       </c>
       <c r="D109" s="102">
-        <f t="shared" ref="D109:H112" si="8">IF(D3=1,1,D3*1.05)</f>
+        <f t="shared" ref="D109:H121" si="8">IF(D3=1,1,D3*1.05)</f>
         <v>1</v>
       </c>
       <c r="E109" s="102">
@@ -15558,18 +15869,18 @@
         <v>153</v>
       </c>
       <c r="D111" s="102">
-        <v>2.11</v>
+        <v>2.56</v>
       </c>
       <c r="E111" s="102">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="E111:G112" si="9">IF(E58=1,1,E58*0.9)</f>
         <v>1</v>
       </c>
       <c r="F111" s="102">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="G111" s="102">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="H111" s="102">
@@ -15583,18 +15894,18 @@
         <v>154</v>
       </c>
       <c r="D112" s="102">
-        <v>2.11</v>
+        <v>2.56</v>
       </c>
       <c r="E112" s="102">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F112" s="102">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="G112" s="102">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="H112" s="102">
@@ -15608,23 +15919,23 @@
         <v>155</v>
       </c>
       <c r="D113" s="102">
-        <f t="shared" ref="D113:H123" si="9">IF(D7=1,1,D7*1.05)</f>
+        <f t="shared" ref="D113:G121" si="10">IF(D60=1,1,D60*0.9)</f>
         <v>1</v>
       </c>
       <c r="E113" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="F113" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G113" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H113" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -15636,22 +15947,22 @@
         <v>153</v>
       </c>
       <c r="D114" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E114" s="102">
-        <v>2.11</v>
+        <v>3.09</v>
       </c>
       <c r="F114" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G114" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H114" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -15661,22 +15972,22 @@
         <v>154</v>
       </c>
       <c r="D115" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E115" s="102">
-        <v>2.11</v>
+        <v>3.09</v>
       </c>
       <c r="F115" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G115" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H115" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -15686,23 +15997,23 @@
         <v>155</v>
       </c>
       <c r="D116" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E116" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="F116" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G116" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H116" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -15714,22 +16025,22 @@
         <v>153</v>
       </c>
       <c r="D117" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E117" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="F117" s="102">
-        <v>2.11</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="G117" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H117" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -15739,22 +16050,22 @@
         <v>154</v>
       </c>
       <c r="D118" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E118" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="F118" s="102">
-        <v>2.11</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="G118" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H118" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -15764,23 +16075,23 @@
         <v>155</v>
       </c>
       <c r="D119" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E119" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="F119" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G119" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H119" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -15792,22 +16103,22 @@
         <v>153</v>
       </c>
       <c r="D120" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E120" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="F120" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G120" s="102">
-        <v>2.11</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="H120" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -15817,22 +16128,22 @@
         <v>154</v>
       </c>
       <c r="D121" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E121" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="F121" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G121" s="102">
-        <v>2.11</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="H121" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -15842,23 +16153,23 @@
         <v>155</v>
       </c>
       <c r="D122" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="D122:H123" si="11">IF(D16=1,1,D16*1.05)</f>
         <v>1</v>
       </c>
       <c r="E122" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="F122" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="G122" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="H122" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -15870,23 +16181,23 @@
         <v>155</v>
       </c>
       <c r="D123" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1.1025</v>
       </c>
       <c r="E123" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1.1025</v>
       </c>
       <c r="F123" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1.1025</v>
       </c>
       <c r="G123" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1.1025</v>
       </c>
       <c r="H123" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -15912,19 +16223,19 @@
         <v>1</v>
       </c>
       <c r="E125" s="102">
-        <f t="shared" ref="E125:H125" si="10">IF(E19=1,1,E19*1.05)</f>
+        <f t="shared" ref="E125:H125" si="12">IF(E19=1,1,E19*1.05)</f>
         <v>1</v>
       </c>
       <c r="F125" s="102">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="G125" s="102">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="H125" s="102">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -15934,23 +16245,23 @@
         <v>154</v>
       </c>
       <c r="D126" s="102">
-        <f t="shared" ref="D126:H140" si="11">IF(D20=1,1,D20*1.05)</f>
+        <f t="shared" ref="D126:H140" si="13">IF(D20=1,1,D20*1.05)</f>
         <v>1</v>
       </c>
       <c r="E126" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F126" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G126" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H126" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -15960,23 +16271,23 @@
         <v>155</v>
       </c>
       <c r="D127" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E127" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F127" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G127" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H127" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -15988,23 +16299,23 @@
         <v>153</v>
       </c>
       <c r="D128" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E128" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F128" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G128" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H128" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16014,23 +16325,23 @@
         <v>154</v>
       </c>
       <c r="D129" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E129" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F129" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G129" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H129" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16040,23 +16351,23 @@
         <v>155</v>
       </c>
       <c r="D130" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E130" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F130" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G130" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H130" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16068,23 +16379,23 @@
         <v>153</v>
       </c>
       <c r="D131" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E131" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F131" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G131" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H131" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16094,23 +16405,23 @@
         <v>154</v>
       </c>
       <c r="D132" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E132" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F132" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G132" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H132" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16120,23 +16431,23 @@
         <v>155</v>
       </c>
       <c r="D133" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E133" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F133" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G133" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H133" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16148,23 +16459,23 @@
         <v>153</v>
       </c>
       <c r="D134" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E134" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F134" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G134" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H134" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16174,23 +16485,23 @@
         <v>154</v>
       </c>
       <c r="D135" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E135" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F135" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G135" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H135" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16200,23 +16511,23 @@
         <v>155</v>
       </c>
       <c r="D136" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E136" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F136" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G136" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H136" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16228,23 +16539,23 @@
         <v>153</v>
       </c>
       <c r="D137" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E137" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F137" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G137" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H137" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16254,23 +16565,23 @@
         <v>154</v>
       </c>
       <c r="D138" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E138" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F138" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G138" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H138" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16280,23 +16591,23 @@
         <v>155</v>
       </c>
       <c r="D139" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E139" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F139" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G139" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H139" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16308,23 +16619,23 @@
         <v>155</v>
       </c>
       <c r="D140" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E140" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F140" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G140" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H140" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16350,19 +16661,19 @@
         <v>1</v>
       </c>
       <c r="E142" s="102">
-        <f t="shared" ref="E142:H142" si="12">IF(E36=1,1,E36*1.05)</f>
+        <f t="shared" ref="E142:H142" si="14">IF(E36=1,1,E36*1.05)</f>
         <v>1</v>
       </c>
       <c r="F142" s="102">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="G142" s="102">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="H142" s="102">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -16372,23 +16683,23 @@
         <v>154</v>
       </c>
       <c r="D143" s="102">
-        <f t="shared" ref="D143:H157" si="13">IF(D37=1,1,D37*1.05)</f>
+        <f t="shared" ref="D143:H157" si="15">IF(D37=1,1,D37*1.05)</f>
         <v>1</v>
       </c>
       <c r="E143" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F143" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G143" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H143" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16398,23 +16709,23 @@
         <v>155</v>
       </c>
       <c r="D144" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E144" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F144" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G144" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H144" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16426,23 +16737,23 @@
         <v>153</v>
       </c>
       <c r="D145" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E145" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F145" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G145" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H145" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16452,23 +16763,23 @@
         <v>154</v>
       </c>
       <c r="D146" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E146" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F146" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G146" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H146" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16478,23 +16789,23 @@
         <v>155</v>
       </c>
       <c r="D147" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E147" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F147" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G147" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H147" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16506,23 +16817,23 @@
         <v>153</v>
       </c>
       <c r="D148" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E148" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F148" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G148" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H148" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16532,23 +16843,23 @@
         <v>154</v>
       </c>
       <c r="D149" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E149" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F149" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G149" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H149" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16558,23 +16869,23 @@
         <v>155</v>
       </c>
       <c r="D150" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E150" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F150" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G150" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H150" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16586,23 +16897,23 @@
         <v>153</v>
       </c>
       <c r="D151" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E151" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F151" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G151" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H151" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16612,23 +16923,23 @@
         <v>154</v>
       </c>
       <c r="D152" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E152" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F152" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G152" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H152" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16638,23 +16949,23 @@
         <v>155</v>
       </c>
       <c r="D153" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E153" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F153" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G153" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H153" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16666,23 +16977,23 @@
         <v>153</v>
       </c>
       <c r="D154" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E154" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F154" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G154" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H154" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16692,23 +17003,23 @@
         <v>154</v>
       </c>
       <c r="D155" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E155" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F155" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G155" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H155" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16718,23 +17029,23 @@
         <v>155</v>
       </c>
       <c r="D156" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E156" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F156" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G156" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H156" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16746,29 +17057,65 @@
         <v>155</v>
       </c>
       <c r="D157" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E157" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F157" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G157" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H157" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="wdPnGut1gAAo2a6JybfvR0sZX2M3Xgei21FcXUZ7eE3BbYUhSym1B+x/EakUpAbpAhAZ2ElhejwQplGJxtkRNA==" saltValue="AOeZO/yQFwd2MWB2+9YJuw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="uWYAnvDgJ5vIc4Ld1c5SLfilnndhq6nLzoaHloCYk/+7IxlRAZ9gib+OJ2TCjnnWVs0+JHIhw05mE4Pgtx2Wbg==" saltValue="NUI9Xt2O7LiyweWoLDoeJA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="45">
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="B98:B100"/>
+    <mergeCell ref="B101:B103"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="B120:B122"/>
+    <mergeCell ref="B125:B127"/>
     <mergeCell ref="B145:B147"/>
     <mergeCell ref="B148:B150"/>
     <mergeCell ref="B151:B153"/>
@@ -16778,42 +17125,6 @@
     <mergeCell ref="B134:B136"/>
     <mergeCell ref="B137:B139"/>
     <mergeCell ref="B142:B144"/>
-    <mergeCell ref="B111:B113"/>
-    <mergeCell ref="B114:B116"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="B120:B122"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="B89:B91"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="B98:B100"/>
-    <mergeCell ref="B101:B103"/>
-    <mergeCell ref="B72:B74"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="B81:B83"/>
-    <mergeCell ref="B84:B86"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B14:B16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18028,14 +18339,14 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="7XD+Bvoc9+9grszYvJ09L3rqKRW6v6g5lK9o2b+d1J/LAirOX3leo5JpZ3LvPpgDyTswRlJ7pXip+J6Ecjo8DA==" saltValue="glsa+xD4bKe+n54m/6hnsw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="LsRT7ZobiY0D+Bkl4mijYKunHwECWckhbdZarIlZ8h/6GdYBoNX57ev2Gacc+M2JMJy0BVXqiY9paNPShhiVaA==" saltValue="lC74ADeIpxa+X+bJqLjbFA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <sheetPr>
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
@@ -18045,7 +18356,7 @@
     <col min="1" max="1" width="27.26953125" style="27" customWidth="1"/>
     <col min="2" max="2" width="26.81640625" style="27" customWidth="1"/>
     <col min="3" max="3" width="18.26953125" style="27" customWidth="1"/>
-    <col min="4" max="8" width="14.7265625" style="27" customWidth="1"/>
+    <col min="4" max="8" width="14.81640625" style="27" customWidth="1"/>
     <col min="9" max="12" width="15.26953125" style="27" bestFit="1" customWidth="1"/>
     <col min="13" max="16" width="16.81640625" style="27" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="12.7265625" style="27"/>
@@ -19520,7 +19831,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" ht="26" x14ac:dyDescent="0.3">
       <c r="A56" s="92" t="s">
         <v>121</v>
       </c>
@@ -19741,8 +20052,8 @@
       <c r="C66" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="D66" s="103">
-        <v>1.35</v>
+      <c r="D66" s="104">
+        <v>1</v>
       </c>
       <c r="E66" s="103">
         <v>1</v>
@@ -19856,8 +20167,8 @@
       <c r="C70" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="D70" s="103">
-        <v>1.35</v>
+      <c r="D70" s="104">
+        <v>1</v>
       </c>
       <c r="E70" s="103">
         <v>1</v>
@@ -19971,8 +20282,8 @@
       <c r="C74" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="D74" s="103">
-        <v>1.35</v>
+      <c r="D74" s="104">
+        <v>1</v>
       </c>
       <c r="E74" s="103">
         <v>1</v>
@@ -22257,7 +22568,7 @@
       <c r="G165" s="79"/>
       <c r="H165" s="79"/>
     </row>
-    <row r="166" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" ht="26" x14ac:dyDescent="0.3">
       <c r="A166" s="92" t="s">
         <v>121</v>
       </c>
@@ -22475,7 +22786,7 @@
       </c>
       <c r="D176" s="105">
         <f>IF(D66=1,1,D66*0.9)</f>
-        <v>1.2150000000000001</v>
+        <v>1</v>
       </c>
       <c r="E176" s="105">
         <f t="shared" ref="E176:G176" si="8">IF(E66=1,1,E66*0.9)</f>
@@ -22574,7 +22885,7 @@
       </c>
       <c r="D180" s="105">
         <f t="shared" si="9"/>
-        <v>1.2150000000000001</v>
+        <v>1</v>
       </c>
       <c r="E180" s="105">
         <f t="shared" si="9"/>
@@ -22673,7 +22984,7 @@
       </c>
       <c r="D184" s="105">
         <f t="shared" si="9"/>
-        <v>1.2150000000000001</v>
+        <v>1</v>
       </c>
       <c r="E184" s="105">
         <f t="shared" si="9"/>
@@ -24881,7 +25192,7 @@
       <c r="H275" s="79"/>
       <c r="I275" s="79"/>
     </row>
-    <row r="276" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9" ht="26" x14ac:dyDescent="0.3">
       <c r="A276" s="92" t="s">
         <v>121</v>
       </c>
@@ -25101,7 +25412,7 @@
       </c>
       <c r="D286" s="105">
         <f>IF(D66=1,1,D66*1.1)</f>
-        <v>1.4850000000000003</v>
+        <v>1</v>
       </c>
       <c r="E286" s="105">
         <f t="shared" ref="E286:G286" si="22">IF(E66=1,1,E66*1.1)</f>
@@ -25204,7 +25515,7 @@
       </c>
       <c r="D290" s="105">
         <f t="shared" si="23"/>
-        <v>1.4850000000000003</v>
+        <v>1</v>
       </c>
       <c r="E290" s="105">
         <f t="shared" si="23"/>
@@ -25307,7 +25618,7 @@
       </c>
       <c r="D294" s="105">
         <f t="shared" si="23"/>
-        <v>1.4850000000000003</v>
+        <v>1</v>
       </c>
       <c r="E294" s="105">
         <f t="shared" si="23"/>
@@ -26161,9 +26472,10 @@
       <c r="I328" s="92"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="cmc+3/u/AZSHAcHAxPnckSU/IZnsNSz3BXtPyLlh8FBR0p/OTVdAo/YXqRLpMxYSNl+Dr1qVh32uLAuW3ZoQdQ==" saltValue="bFevFWNvipI48zDzYdNrKA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="1g90pY3sX26DL+B1wtkivg9UmN+LuBXadvT4HFjlPARr/X9Aa5aRhzWUrgjoU9q/YEwYU5a0KdVbpHQ1+nkX/g==" saltValue="sh2pDj3js0LtRrAsbTnaAg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -26356,7 +26668,7 @@
         <v>184</v>
       </c>
       <c r="C12" s="104">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D12" s="104">
         <v>1.39</v>
@@ -26388,19 +26700,19 @@
         <v>284</v>
       </c>
       <c r="C15" s="104">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="D15" s="104">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="E15" s="104">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="F15" s="104">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="G15" s="104">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -26409,19 +26721,19 @@
         <v>287</v>
       </c>
       <c r="C16" s="104">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="D16" s="104">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="E16" s="104">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="F16" s="104">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="G16" s="104">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -26551,24 +26863,19 @@
         <v>290</v>
       </c>
       <c r="C27" s="104">
-        <f>IF(C4=1,1,C4*0.9)</f>
-        <v>0.92249999999999999</v>
+        <v>1.014</v>
       </c>
       <c r="D27" s="104">
-        <f t="shared" ref="D27:G27" si="1">IF(D4=1,1,D4*0.9)</f>
-        <v>0.92249999999999999</v>
+        <v>1.014</v>
       </c>
       <c r="E27" s="104">
-        <f t="shared" si="1"/>
-        <v>0.92249999999999999</v>
+        <v>1.014</v>
       </c>
       <c r="F27" s="104">
-        <f t="shared" si="1"/>
-        <v>0.92249999999999999</v>
+        <v>1.014</v>
       </c>
       <c r="G27" s="104">
-        <f t="shared" si="1"/>
-        <v>0.92249999999999999</v>
+        <v>1.014</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -26585,7 +26892,7 @@
         <v>1</v>
       </c>
       <c r="D29" s="104">
-        <f t="shared" ref="D29:G29" si="2">IF(D6=1,1,D6*0.9)</f>
+        <f t="shared" ref="D29:G29" si="1">IF(D6=1,1,D6*0.9)</f>
         <v>1</v>
       </c>
       <c r="E29" s="104">
@@ -26597,7 +26904,7 @@
         <v>0.80100000000000005</v>
       </c>
       <c r="G29" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -26606,11 +26913,11 @@
         <v>293</v>
       </c>
       <c r="C30" s="104">
-        <f t="shared" ref="C30:G32" si="3">IF(C7=1,1,C7*0.9)</f>
+        <f t="shared" ref="C30:G32" si="2">IF(C7=1,1,C7*0.9)</f>
         <v>1</v>
       </c>
       <c r="D30" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E30" s="104">
@@ -26620,7 +26927,7 @@
         <v>0.85</v>
       </c>
       <c r="G30" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -26629,11 +26936,11 @@
         <v>315</v>
       </c>
       <c r="C31" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D31" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E31" s="104">
@@ -26643,7 +26950,7 @@
         <v>0.85</v>
       </c>
       <c r="G31" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -26652,23 +26959,23 @@
         <v>294</v>
       </c>
       <c r="C32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -26697,7 +27004,7 @@
         <v>296</v>
       </c>
       <c r="C35" s="104">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="D35" s="104">
         <v>1.1100000000000001</v>
@@ -26735,24 +27042,19 @@
         <v>297</v>
       </c>
       <c r="C38" s="104">
-        <f>IF(C15=1,1,C15*0.9)</f>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="D38" s="104">
-        <f t="shared" ref="D38:G38" si="4">IF(D15=1,1,D15*0.9)</f>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="E38" s="104">
-        <f t="shared" si="4"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="F38" s="104">
-        <f t="shared" si="4"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="G38" s="104">
-        <f t="shared" si="4"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -26761,24 +27063,19 @@
         <v>298</v>
       </c>
       <c r="C39" s="104">
-        <f t="shared" ref="C39:G40" si="5">IF(C16=1,1,C16*0.9)</f>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="D39" s="104">
-        <f t="shared" si="5"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="E39" s="104">
-        <f t="shared" si="5"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="F39" s="104">
-        <f t="shared" si="5"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="G39" s="104">
-        <f t="shared" si="5"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -26789,23 +27086,23 @@
         <v>299</v>
       </c>
       <c r="C40" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C40:G40" si="3">IF(C17=1,1,C17*0.9)</f>
         <v>1</v>
       </c>
       <c r="D40" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E40" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F40" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G40" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -26900,19 +27197,19 @@
         <v>10</v>
       </c>
       <c r="D49" s="104">
-        <f t="shared" ref="D49:G50" si="6">D3*1.05</f>
+        <f t="shared" ref="D49:G49" si="4">D3*1.05</f>
         <v>47.25</v>
       </c>
       <c r="E49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>379.68000000000006</v>
       </c>
       <c r="F49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>183.435</v>
       </c>
       <c r="G49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>183.435</v>
       </c>
     </row>
@@ -26922,24 +27219,19 @@
         <v>303</v>
       </c>
       <c r="C50" s="104">
-        <f>C4*1.05</f>
-        <v>1.0762499999999999</v>
+        <v>1.0349999999999999</v>
       </c>
       <c r="D50" s="104">
-        <f t="shared" si="6"/>
-        <v>1.0762499999999999</v>
+        <v>1.0349999999999999</v>
       </c>
       <c r="E50" s="104">
-        <f t="shared" si="6"/>
-        <v>1.0762499999999999</v>
+        <v>1.0349999999999999</v>
       </c>
       <c r="F50" s="104">
-        <f t="shared" si="6"/>
-        <v>1.0762499999999999</v>
+        <v>1.0349999999999999</v>
       </c>
       <c r="G50" s="104">
-        <f t="shared" si="6"/>
-        <v>1.0762499999999999</v>
+        <v>1.0349999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -26956,7 +27248,7 @@
         <v>1</v>
       </c>
       <c r="D52" s="104">
-        <f t="shared" ref="D52:G52" si="7">IF(D6=1,1,D6*1.1)</f>
+        <f t="shared" ref="D52:G52" si="5">IF(D6=1,1,D6*1.1)</f>
         <v>1</v>
       </c>
       <c r="E52" s="104">
@@ -26968,7 +27260,7 @@
         <v>0.93450000000000011</v>
       </c>
       <c r="G52" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -26977,11 +27269,11 @@
         <v>306</v>
       </c>
       <c r="C53" s="104">
-        <f t="shared" ref="C53:G55" si="8">IF(C7=1,1,C7*1.1)</f>
+        <f t="shared" ref="C53:G55" si="6">IF(C7=1,1,C7*1.1)</f>
         <v>1</v>
       </c>
       <c r="D53" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E53" s="104">
@@ -26991,7 +27283,7 @@
         <v>0.91</v>
       </c>
       <c r="G53" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -27000,11 +27292,11 @@
         <v>316</v>
       </c>
       <c r="C54" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D54" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E54" s="104">
@@ -27014,7 +27306,7 @@
         <v>0.91</v>
       </c>
       <c r="G54" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -27023,23 +27315,23 @@
         <v>307</v>
       </c>
       <c r="C55" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D55" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E55" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="F55" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G55" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -27068,7 +27360,7 @@
         <v>309</v>
       </c>
       <c r="C58" s="104">
-        <v>1.78</v>
+        <v>1</v>
       </c>
       <c r="D58" s="104">
         <v>1.74</v>
@@ -27106,24 +27398,19 @@
         <v>310</v>
       </c>
       <c r="C61" s="104">
-        <f>IF(C15=1,1,C15*1.1)</f>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="D61" s="104">
-        <f t="shared" ref="D61:G61" si="9">IF(D15=1,1,D15*1.1)</f>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="E61" s="104">
-        <f t="shared" si="9"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="F61" s="104">
-        <f t="shared" si="9"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="G61" s="104">
-        <f t="shared" si="9"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -27132,24 +27419,19 @@
         <v>311</v>
       </c>
       <c r="C62" s="104">
-        <f t="shared" ref="C62:G63" si="10">IF(C16=1,1,C16*1.1)</f>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="D62" s="104">
-        <f t="shared" si="10"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="E62" s="104">
-        <f t="shared" si="10"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="F62" s="104">
-        <f t="shared" si="10"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="G62" s="104">
-        <f t="shared" si="10"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -27160,23 +27442,23 @@
         <v>312</v>
       </c>
       <c r="C63" s="104">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="C63:G63" si="7">IF(C17=1,1,C17*1.1)</f>
         <v>1</v>
       </c>
       <c r="D63" s="104">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E63" s="104">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F63" s="104">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G63" s="104">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -27227,7 +27509,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="AXClvh8rb/1iMq+PVpyB7L55iIZdT8lGkG4rt/ozX+Q2ZCKxvGGq3tZVznabrJj7TXXS6AE2cDebV+wu1FS6HA==" saltValue="W4IKMD8FIFTcVzoxC+6Prw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="HCMYLlJXp4dvbcZoxbrbW/Xa9j+rR4B/oXXY25v6kfx0LvyRTo8qCVVmea/ZLE5/98lmvJ8TawMCftTQLpWivw==" saltValue="JGgkS25mjuKoyv5f0wBqtQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -28048,7 +28330,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="G+MYlZ+++Ryw+6chJOfuNxtuASHvsxaXQtDIvKjh2OP9Nj1CxAAdvRFrw2F2hNtQS6RITIW/8C3EnFlmK3p+cQ==" saltValue="+4fZBArM1KqFs83Hdvi2ig==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="/rKioSXERQIk4hTercQQ7bRRzkWDj7FMLnnsWEdqp8myqe7dSJUu8QvpabnkNEJiE7b9nUO8jOCCuk+xSo0AlA==" saltValue="//bY5EkFLu5JaFMzfz8YEg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -28124,10 +28406,10 @@
         <v>0.92</v>
       </c>
       <c r="D3" s="104">
-        <v>0.53</v>
+        <v>0.92</v>
       </c>
       <c r="E3" s="104">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="F3" s="104">
         <v>1</v>
@@ -28709,37 +28991,37 @@
         <v>1</v>
       </c>
       <c r="E18" s="104">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F18" s="104">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G18" s="104">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H18" s="104">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I18" s="104">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J18" s="104">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K18" s="104">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L18" s="104">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M18" s="104">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N18" s="104">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O18" s="104">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -28797,47 +29079,36 @@
         <v>1</v>
       </c>
       <c r="E20" s="104">
-        <f>E19</f>
         <v>0.97599999999999998</v>
       </c>
       <c r="F20" s="104">
-        <f t="shared" ref="F20:O20" si="1">F19</f>
         <v>0.97599999999999998</v>
       </c>
       <c r="G20" s="104">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="H20" s="104">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="I20" s="104">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="J20" s="104">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="K20" s="104">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="L20" s="104">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="M20" s="104">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="N20" s="104">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="O20" s="104">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
     </row>
@@ -28890,7 +29161,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="26" x14ac:dyDescent="0.3">
       <c r="A24" s="29"/>
       <c r="B24" s="29"/>
       <c r="C24" s="82" t="s">
@@ -28946,50 +29217,49 @@
         <v>0.87</v>
       </c>
       <c r="D26" s="104">
-        <v>0.4</v>
+        <v>0.87</v>
       </c>
       <c r="E26" s="104">
-        <f t="shared" ref="E26:O26" si="2">IF(E3=1,1,E3*0.9)</f>
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="F26" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="F26:O26" si="1">IF(F3=1,1,F3*0.9)</f>
         <v>1</v>
       </c>
       <c r="G26" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H26" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I26" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="J26" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K26" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L26" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="M26" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N26" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="O26" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -28998,23 +29268,23 @@
         <v>176</v>
       </c>
       <c r="C27" s="104">
-        <f t="shared" ref="C27:O34" si="3">IF(C4=1,1,C4*0.9)</f>
+        <f t="shared" ref="C27:O34" si="2">IF(C4=1,1,C4*0.9)</f>
         <v>1</v>
       </c>
       <c r="D27" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E27" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F27" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G27" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H27" s="104">
@@ -29030,19 +29300,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L27" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M27" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N27" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O27" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -29051,23 +29321,23 @@
         <v>177</v>
       </c>
       <c r="C28" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D28" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E28" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F28" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G28" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H28" s="104">
@@ -29083,19 +29353,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L28" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M28" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N28" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O28" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -29104,23 +29374,23 @@
         <v>178</v>
       </c>
       <c r="C29" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D29" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E29" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F29" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G29" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H29" s="104">
@@ -29136,19 +29406,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L29" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M29" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N29" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O29" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -29157,23 +29427,23 @@
         <v>179</v>
       </c>
       <c r="C30" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D30" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E30" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F30" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G30" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H30" s="104">
@@ -29189,19 +29459,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L30" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M30" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N30" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O30" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -29210,39 +29480,39 @@
         <v>180</v>
       </c>
       <c r="C31" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D31" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E31" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F31" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G31" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H31" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I31" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J31" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K31" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="L31" s="104">
@@ -29263,39 +29533,39 @@
         <v>181</v>
       </c>
       <c r="C32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="L32" s="104">
@@ -29316,39 +29586,39 @@
         <v>182</v>
       </c>
       <c r="C33" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D33" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E33" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F33" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G33" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H33" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I33" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J33" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K33" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="L33" s="104">
@@ -29369,11 +29639,11 @@
         <v>185</v>
       </c>
       <c r="C34" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D34" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E34" s="104">
@@ -29386,35 +29656,35 @@
         <v>1</v>
       </c>
       <c r="H34" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I34" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J34" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K34" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="L34" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M34" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N34" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O34" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -29467,11 +29737,11 @@
         <v>189</v>
       </c>
       <c r="C36" s="104">
-        <f t="shared" ref="C36:O38" si="4">IF(C13=1,1,C13*0.9)</f>
+        <f t="shared" ref="C36:O38" si="3">IF(C13=1,1,C13*0.9)</f>
         <v>1</v>
       </c>
       <c r="D36" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E36" s="104">
@@ -29484,35 +29754,35 @@
         <v>0.62</v>
       </c>
       <c r="H36" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I36" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J36" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K36" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L36" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M36" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N36" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O36" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -29521,39 +29791,39 @@
         <v>190</v>
       </c>
       <c r="C37" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D37" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E37" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F37" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G37" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H37" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I37" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J37" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K37" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L37" s="104">
@@ -29574,11 +29844,11 @@
         <v>205</v>
       </c>
       <c r="C38" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D38" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E38" s="104">
@@ -29588,39 +29858,39 @@
         <v>0.3</v>
       </c>
       <c r="G38" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H38" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I38" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J38" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K38" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L38" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M38" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N38" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O38" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -29635,56 +29905,45 @@
         <v>173</v>
       </c>
       <c r="C41" s="104">
-        <f t="shared" ref="C41:O44" si="5">IF(C18=1,1,C18*0.9)</f>
+        <f t="shared" ref="C41:D44" si="4">IF(C18=1,1,C18*0.9)</f>
         <v>1</v>
       </c>
       <c r="D41" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E41" s="104">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F41" s="104">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="G41" s="104">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H41" s="104">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I41" s="104">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J41" s="104">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="K41" s="104">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="L41" s="104">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="M41" s="104">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N41" s="104">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="O41" s="104">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
@@ -29692,11 +29951,11 @@
         <v>174</v>
       </c>
       <c r="C42" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D42" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E42" s="104">
@@ -29738,56 +29997,45 @@
         <v>175</v>
       </c>
       <c r="C43" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D43" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E43" s="104">
-        <f t="shared" si="5"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F43" s="104">
-        <f t="shared" si="5"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="G43" s="104">
-        <f t="shared" si="5"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H43" s="104">
-        <f t="shared" si="5"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I43" s="104">
-        <f t="shared" si="5"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J43" s="104">
-        <f t="shared" si="5"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="K43" s="104">
-        <f t="shared" si="5"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="L43" s="104">
-        <f t="shared" si="5"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="M43" s="104">
-        <f t="shared" si="5"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N43" s="104">
-        <f t="shared" si="5"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="O43" s="104">
-        <f t="shared" si="5"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -29795,11 +30043,11 @@
         <v>183</v>
       </c>
       <c r="C44" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D44" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E44" s="104">
@@ -29897,50 +30145,49 @@
         <v>0.99</v>
       </c>
       <c r="D49" s="104">
-        <v>0.7</v>
+        <v>0.99</v>
       </c>
       <c r="E49" s="104">
-        <f t="shared" ref="E49:O49" si="6">IF(E3=1,1,E3*1.05)</f>
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="F49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="F49:O49" si="5">IF(F3=1,1,F3*1.05)</f>
         <v>1</v>
       </c>
       <c r="G49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="H49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="I49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="J49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="K49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="L49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="M49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="N49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="O49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -29949,23 +30196,23 @@
         <v>176</v>
       </c>
       <c r="C50" s="104">
-        <f t="shared" ref="C50:O57" si="7">IF(C4=1,1,C4*1.05)</f>
+        <f t="shared" ref="C50:O57" si="6">IF(C4=1,1,C4*1.05)</f>
         <v>1</v>
       </c>
       <c r="D50" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E50" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="F50" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G50" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H50" s="104">
@@ -29981,19 +30228,19 @@
         <v>0.95</v>
       </c>
       <c r="L50" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="M50" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="N50" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O50" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -30002,23 +30249,23 @@
         <v>177</v>
       </c>
       <c r="C51" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D51" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E51" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="F51" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G51" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H51" s="104">
@@ -30034,19 +30281,19 @@
         <v>0.95</v>
       </c>
       <c r="L51" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="M51" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="N51" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O51" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -30055,23 +30302,23 @@
         <v>178</v>
       </c>
       <c r="C52" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D52" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E52" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="F52" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G52" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H52" s="104">
@@ -30087,19 +30334,19 @@
         <v>0.95</v>
       </c>
       <c r="L52" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="M52" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="N52" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O52" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -30108,23 +30355,23 @@
         <v>179</v>
       </c>
       <c r="C53" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D53" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E53" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="F53" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G53" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H53" s="104">
@@ -30140,19 +30387,19 @@
         <v>0.95</v>
       </c>
       <c r="L53" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="M53" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="N53" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O53" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -30161,39 +30408,39 @@
         <v>180</v>
       </c>
       <c r="C54" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D54" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E54" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="F54" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G54" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H54" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I54" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J54" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K54" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="L54" s="104">
@@ -30214,39 +30461,39 @@
         <v>181</v>
       </c>
       <c r="C55" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D55" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E55" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="F55" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G55" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H55" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I55" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J55" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K55" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="L55" s="104">
@@ -30267,39 +30514,39 @@
         <v>182</v>
       </c>
       <c r="C56" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D56" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E56" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="F56" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G56" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H56" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I56" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J56" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K56" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="L56" s="104">
@@ -30320,11 +30567,11 @@
         <v>185</v>
       </c>
       <c r="C57" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D57" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E57" s="104">
@@ -30334,39 +30581,39 @@
         <v>0.77</v>
       </c>
       <c r="G57" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H57" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I57" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J57" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K57" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="L57" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="M57" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="N57" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O57" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -30419,11 +30666,11 @@
         <v>189</v>
       </c>
       <c r="C59" s="104">
-        <f t="shared" ref="C59:O61" si="8">IF(C13=1,1,C13*1.05)</f>
+        <f t="shared" ref="C59:O61" si="7">IF(C13=1,1,C13*1.05)</f>
         <v>1</v>
       </c>
       <c r="D59" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E59" s="104">
@@ -30436,35 +30683,35 @@
         <v>0.77</v>
       </c>
       <c r="H59" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I59" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J59" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K59" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L59" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="M59" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N59" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="O59" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -30473,39 +30720,39 @@
         <v>190</v>
       </c>
       <c r="C60" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="D60" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E60" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F60" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G60" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H60" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I60" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J60" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K60" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L60" s="104">
@@ -30526,11 +30773,11 @@
         <v>205</v>
       </c>
       <c r="C61" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="D61" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E61" s="104">
@@ -30540,39 +30787,39 @@
         <v>0.44</v>
       </c>
       <c r="G61" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H61" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I61" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J61" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K61" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L61" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="M61" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N61" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="O61" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -30587,56 +30834,45 @@
         <v>173</v>
       </c>
       <c r="C64" s="104">
-        <f t="shared" ref="C64:O67" si="9">IF(C18=1,1,C18*1.05)</f>
+        <f t="shared" ref="C64:D67" si="8">IF(C18=1,1,C18*1.05)</f>
         <v>1</v>
       </c>
       <c r="D64" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E64" s="104">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F64" s="104">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="G64" s="104">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H64" s="104">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I64" s="104">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J64" s="104">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="K64" s="104">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="L64" s="104">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="M64" s="104">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="N64" s="104">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="O64" s="104">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
     <row r="65" spans="2:15" x14ac:dyDescent="0.25">
@@ -30644,11 +30880,11 @@
         <v>174</v>
       </c>
       <c r="C65" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="D65" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E65" s="104">
@@ -30690,56 +30926,45 @@
         <v>175</v>
       </c>
       <c r="C66" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="D66" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E66" s="104">
-        <f t="shared" si="9"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F66" s="104">
-        <f t="shared" si="9"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="G66" s="104">
-        <f t="shared" si="9"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H66" s="104">
-        <f t="shared" si="9"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I66" s="104">
-        <f t="shared" si="9"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J66" s="104">
-        <f t="shared" si="9"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="K66" s="104">
-        <f t="shared" si="9"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="L66" s="104">
-        <f t="shared" si="9"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="M66" s="104">
-        <f t="shared" si="9"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="N66" s="104">
-        <f t="shared" si="9"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="O66" s="104">
-        <f t="shared" si="9"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
     <row r="67" spans="2:15" x14ac:dyDescent="0.25">
@@ -30747,11 +30972,11 @@
         <v>183</v>
       </c>
       <c r="C67" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="D67" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E67" s="104">
@@ -30789,7 +31014,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="nhVH3M+msgK+si/XFYs9Nd5+JGTrKwnSVw5sZq1hC5pfeDcV9mhwSBg87URWz+XnuFvASl9WzA+yTHdcfnTHTw==" saltValue="xncZD8I+0WcFyhU/aC1o3Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="KuTpi13PXfQLF8zN7148BWs80Bs4evBYZkl2GXdIQLtb0GaXqOUv9SuVMT1REs4LGqe+bY4Up0S92Wm2DuKCOg==" saltValue="utDJ4osX+VKpKn6MfocY+A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -31069,7 +31294,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="4TVIFyOkYfEEwRNam+tDp3gL01o20oPglM32uLUn4TYy2NEjDvJudY0gFmopsI//UgKWogDJ4KcjhSC8V3x7lQ==" saltValue="+VedqTCsotsl2KPdL5O1qQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="PF6SldQtYN0BVQa1dQ3GbaJbClaqyt880P7h6nVqlwFVI/fapopUHQ8mfBd4907MgleT3Mbl5qiGqoDjUbKuog==" saltValue="syjEfwPSh5x9jBooO6Nw4Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -31490,13 +31715,16 @@
         <v>0</v>
       </c>
       <c r="F18" s="104">
-        <v>0.68</v>
+        <f>MIN(MAX(1-0.89/(1-frac_sam_6_11months+(frac_sam_6_11months*0.89)),0),1)</f>
+        <v>0.10845784237982603</v>
       </c>
       <c r="G18" s="104">
-        <v>0.68</v>
+        <f>MIN(MAX(1-0.89/(1-frac_sam_12_23months+(frac_sam_12_23months*0.89)),0),1)</f>
+        <v>0.10901055997751219</v>
       </c>
       <c r="H18" s="104">
-        <v>0.68</v>
+        <f>MIN(MAX(1-0.89/(1-frac_sam_24_59months+(frac_sam_24_59months*0.89)),0),1)</f>
+        <v>0.10928137311800357</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -31533,13 +31761,16 @@
         <v>0</v>
       </c>
       <c r="F20" s="104">
-        <v>0.6</v>
+        <f>MIN(MAX(1-0.89/(1-frac_mam_6_11months+(frac_mam_6_11months*0.89)),0),1)</f>
+        <v>0.1046795744409692</v>
       </c>
       <c r="G20" s="104">
-        <v>0.6</v>
+        <f>MIN(MAX(1-0.89/(1-frac_mam_12_23months+(frac_mam_12_23months*0.89)),0),1)</f>
+        <v>0.10581499250070592</v>
       </c>
       <c r="H20" s="104">
-        <v>0.6</v>
+        <f>MIN(MAX(1-0.89/(1-frac_mam_24_59months+(frac_mam_24_59months*0.89)),0),1)</f>
+        <v>0.10780844504922549</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -31711,19 +31942,19 @@
         <v>335</v>
       </c>
       <c r="D28" s="104">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E28" s="104">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F28" s="104">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G28" s="104">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H28" s="104">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -32707,13 +32938,16 @@
         <v>0</v>
       </c>
       <c r="F73" s="104">
-        <v>0.39</v>
+        <f>MIN(MAX(1-0.99/(1-frac_sam_6_11months+(frac_sam_6_11months*0.99)),0),1)</f>
+        <v>9.8442967462329944E-3</v>
       </c>
       <c r="G73" s="104">
-        <v>0.39</v>
+        <f>MIN(MAX(1-0.99/(1-frac_sam_12_23months+(frac_sam_12_23months*0.99)),0),1)</f>
+        <v>9.9000452880145806E-3</v>
       </c>
       <c r="H73" s="104">
-        <v>0.39</v>
+        <f>MIN(MAX(1-0.99/(1-frac_sam_24_59months+(frac_sam_24_59months*0.99)),0),1)</f>
+        <v>9.9273831696513604E-3</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -32732,15 +32966,12 @@
         <v>0</v>
       </c>
       <c r="F74" s="104">
-        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G74" s="104">
-        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H74" s="104">
-        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -32757,13 +32988,16 @@
         <v>0</v>
       </c>
       <c r="F75" s="104">
-        <v>0.32</v>
+        <f>MIN(MAX(1-0.99/(1-frac_mam_6_11months+(frac_mam_6_11months*0.99)),0),1)</f>
+        <v>9.4648875339096161E-3</v>
       </c>
       <c r="G75" s="104">
-        <v>0.32</v>
+        <f>MIN(MAX(1-0.99/(1-frac_mam_12_23months+(frac_mam_12_23months*0.99)),0),1)</f>
+        <v>9.5785983927034746E-3</v>
       </c>
       <c r="H75" s="104">
-        <v>0.32</v>
+        <f>MIN(MAX(1-0.99/(1-frac_mam_24_59months+(frac_mam_24_59months*0.99)),0),1)</f>
+        <v>9.7788770816137349E-3</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -32962,19 +33196,19 @@
         <v>335</v>
       </c>
       <c r="D83" s="104">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="E83" s="104">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F83" s="104">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G83" s="104">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="H83" s="104">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -33963,13 +34197,16 @@
         <v>0</v>
       </c>
       <c r="F128" s="104">
-        <v>0.84</v>
+        <f>MIN(MAX(1-0.8/(1-frac_sam_6_11months+(frac_sam_6_11months*0.8)),0),1)</f>
+        <v>0.1974760415732103</v>
       </c>
       <c r="G128" s="104">
-        <v>0.84</v>
+        <f>MIN(MAX(1-0.8/(1-frac_sam_12_23months+(frac_sam_12_23months*0.8)),0),1)</f>
+        <v>0.19838146543966784</v>
       </c>
       <c r="H128" s="104">
-        <v>0.84</v>
+        <f>MIN(MAX(1-0.8/(1-frac_sam_24_59months+(frac_sam_24_59months*0.8)),0),1)</f>
+        <v>0.19882475677586242</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -33988,15 +34225,12 @@
         <v>0</v>
       </c>
       <c r="F129" s="104">
-        <f t="shared" ref="F129:H129" si="10">IF($C74="Affected fraction",F74,IF(F74=1,1,F74*0.9))</f>
         <v>1</v>
       </c>
       <c r="G129" s="104">
-        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H129" s="104">
-        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -34013,13 +34247,16 @@
         <v>0</v>
       </c>
       <c r="F130" s="104">
-        <v>0.77</v>
+        <f>MIN(MAX(1-0.8/(1-frac_mam_6_11months+(frac_mam_6_11months*0.8)),0),1)</f>
+        <v>0.19126197969113667</v>
       </c>
       <c r="G130" s="104">
-        <v>0.77</v>
+        <f>MIN(MAX(1-0.8/(1-frac_mam_12_23months+(frac_mam_12_23months*0.8)),0),1)</f>
+        <v>0.19313393967166625</v>
       </c>
       <c r="H130" s="104">
-        <v>0.77</v>
+        <f>MIN(MAX(1-0.8/(1-frac_mam_24_59months+(frac_mam_24_59months*0.8)),0),1)</f>
+        <v>0.19641106564514077</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -34033,7 +34270,7 @@
         <v>334</v>
       </c>
       <c r="D131" s="104">
-        <f t="shared" ref="D131" si="11">IF($C76="Affected fraction",D76,IF(D76=1,1,D76*0.9))</f>
+        <f t="shared" ref="D131" si="10">IF($C76="Affected fraction",D76,IF(D76=1,1,D76*0.9))</f>
         <v>1</v>
       </c>
       <c r="E131" s="104">
@@ -34088,7 +34325,7 @@
         <v>334</v>
       </c>
       <c r="D133" s="104">
-        <f t="shared" ref="D133" si="12">IF($C78="Affected fraction",D78,IF(D78=1,1,D78*0.9))</f>
+        <f t="shared" ref="D133" si="11">IF($C78="Affected fraction",D78,IF(D78=1,1,D78*0.9))</f>
         <v>1</v>
       </c>
       <c r="E133" s="104">
@@ -34143,7 +34380,7 @@
         <v>334</v>
       </c>
       <c r="D135" s="104">
-        <f t="shared" ref="D135" si="13">IF($C80="Affected fraction",D80,IF(D80=1,1,D80*0.9))</f>
+        <f t="shared" ref="D135" si="12">IF($C80="Affected fraction",D80,IF(D80=1,1,D80*0.9))</f>
         <v>1</v>
       </c>
       <c r="E135" s="104">
@@ -34218,19 +34455,19 @@
         <v>335</v>
       </c>
       <c r="D138" s="104">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="E138" s="104">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="F138" s="104">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="G138" s="104">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="H138" s="104">
-        <v>0</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -34528,23 +34765,23 @@
         <v>334</v>
       </c>
       <c r="D152" s="104">
-        <f t="shared" ref="D152:H153" si="14">IF($C97="Affected fraction",D97,IF(D97=1,1,D97*0.9))</f>
+        <f t="shared" ref="D152:H153" si="13">IF($C97="Affected fraction",D97,IF(D97=1,1,D97*0.9))</f>
         <v>0</v>
       </c>
       <c r="E152" s="104">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F152" s="104">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G152" s="104">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H152" s="104">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -34553,23 +34790,23 @@
         <v>335</v>
       </c>
       <c r="D153" s="104">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E153" s="104">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F153" s="104">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G153" s="104">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H153" s="104">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -34795,7 +35032,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="xE6i9biNdAVCejo+IfRN4ZNuyhuHhsvxAy/4FtmLoPVatA6Wb1VIOCSkv86q8qSDz3wLaVVETg6bRNc9XvSViA==" saltValue="c9PY2uVO9t7fS+Hjutog3w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ZobVSkt+NhLVGk8JZKhnaUq9qKg5JdG2zxSf0rTCUcuNA2c5xkPpEGFLlRLX8sFm8Q5B2WfI0t9OXGZxd5K7KQ==" saltValue="QRrEb8ohOFg0BzQOt8sV+A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -34867,16 +35104,16 @@
         <v>335</v>
       </c>
       <c r="D3" s="104">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="E3" s="104">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="F3" s="104">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="G3" s="104">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="H3" s="31"/>
     </row>
@@ -35188,16 +35425,16 @@
         <v>335</v>
       </c>
       <c r="D21" s="104">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="E21" s="104">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="F21" s="104">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="G21" s="104">
-        <v>0.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -35297,7 +35534,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="YYri0FAUqC8xv0bvlGLkAayTmpDYJLqaRBaXZjelul+rn1ydM1mPCUU5U3RiBXAj/AF+4xZ2fVx9e9zgHrquWA==" saltValue="ItPU8UGHxwxStPTnG+bRNg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="mfDb7DpCqqMk0TTsvWIB6j2jVFQrfjik1tKlYsc4WLk/hIB7dxFwZykribkHnyWzRCqB6SyDDDggMeeg+nznkw==" saltValue="i4MHYUK5XiwwOamBxsrZoA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -35729,7 +35966,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="4gP6duPJrWQ+IIZjMIfY174qkXgY63nHKkW67Q/N/wkL0NmTr+0JPA3OkSMPWsiLIhBKA7U7dxFEBvhEnpkgDQ==" saltValue="WyYP0BHuvODzTq3N0RRzZw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="3kZBfhog9wcAXcIaeX/auSosqLyScAU4bKiF3J1R2OhMCHsYtT7X3b4uETnrjv2tW7FyRahyyqaCBhHYkx8YvQ==" saltValue="ND8Dtmbf5kqOKPY1BXuNSg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="69" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
@@ -36148,7 +36385,7 @@
       <c r="G17" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="zyj0D3t0eIeCm531PCwIQSxYMVq76MIKiPDr/dJwKIuxA8tfvxtqzyYFjx/aVDUSkefS4vAJczqiJLVpls8wwQ==" saltValue="5q5cIAY6XLaRlQURJMC8uA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="qKsCq8l+ngycmUtCW0kOPBMhz+5zZYW8VzWFLaT0Plh9/ZETCOc4E2bfeO2yedItxh+ZXBiMa+jJN4ub8J1ElQ==" saltValue="sA8l96n2oKG40QCEoP02LA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <drawing r:id="rId1"/>
@@ -36280,7 +36517,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="AekI9uVR8MUuvG/OLQbJi57T4rtg8MX0B/Kg35SP6WHuS7e2oBLzinEacl/u1HgFzysAWjckxe92/iAPPK5XkQ==" saltValue="By84FQmqqNUTRnyV+KYnCg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="huD76IaftLdtdFenGVyOk0oCfteAe5EF8gX8BeL89dGc/x4B4fWe5kLI5KRKW4H0i0jSkOQGcA0IL+IyHXUIiw==" saltValue="w+7Siy/6HYD2oW7rRC7StQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -36482,7 +36719,7 @@
       <c r="K14" s="115"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="5fBqH7iacUWMcAWrTXsnMYvTa61BO+CLHpjq7Wpp9+CMSKGIWC8lTc06LSoO5FOMLIlcSJ7ZzFTpXjEgvC2ITw==" saltValue="UAl494FTP6OAyTADfFR2+g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="xxUl5dBwuSQ60kqAwWBosWHW6PqyK8TqioHM99jHjbfxefR00/kjw8t6QgSOhC9RVm0NE9EwjJv9c8piRLkNLA==" saltValue="Rl4Q0ib0y03xWRmVc8yDHg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="193" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -36558,7 +36795,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="jtZtEDpMItoplxECtbr6Zfp2STH+NFWQ705aXCfe06iJKpV3wPpUymEnncw5yUJE4yfO/DpX8arW0Zsiwls0pg==" saltValue="Crubk/8ZeB5JHAd0N2PeJA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="3p+OiXSjnkfSgldqT3PfMGP4434cHvoVq8bbWyPgwC/qkfWcCFi7wxisyYM1TGU9di70YH/V4HcJS83baZqh8A==" saltValue="10/4k08kic9fW96yv1bxhA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -36813,7 +37050,7 @@
       <c r="E21" s="62"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="+7Hz+8ezMn0PTM0m5Wa01rFcVrd0Luv1++5t9CdejkG34vt/d0cBjLd/iM9tmSDZkpDpQwlaxaT99La0Ptr1/Q==" saltValue="PQy2pwnKY3KIAhAZ6mONgA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="IBZGngRnl7RBerxWsXFvM9sSzAeYlbpn0K8FSKmfQqQSHwndOcc8RHvRk6ggqkFs6FXsgFMQyPlniicq4bIGAg==" saltValue="rqpFVBTlbwQZ1XDcbNUlbw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -36872,7 +37109,7 @@
       <c r="D3" s="62"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="PhE3a6uRxOiZj1J662UO5AtnLE4p5b5jzikPoUj16Qz4w+xGiJkevEHi9jThj3zoRxOy0forcOc7b7BXA7RSmA==" saltValue="pbF7KZea7VezsmsBtttTFA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="KOTN2qblLZopn/UG4/Vmkv3tyZU/Db28CITqirFh3y396JuDBXOmUa3pYeVvHnNG76+LtUDgQSGgCpR1u6plFQ==" saltValue="UcnSDrfDpWKbfL3SOQtwIg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/inputs/fr/demo_national_input.xlsx
+++ b/inputs/fr/demo_national_input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\2025 studies\Nutrition\inputs\fr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F533225A-FA90-4EEA-84D4-417F6AF15657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E0D0289-6683-49AC-975F-40F6C6C9AF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10180" tabRatio="904" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="904" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Données pop de l'année de ref" sheetId="1" r:id="rId1"/>
@@ -3162,7 +3162,31 @@
         </r>
       </text>
     </comment>
-    <comment ref="F18" authorId="1" shapeId="0" xr:uid="{9311E7C8-6DF9-441C-9F8D-E21702435127}">
+    <comment ref="F18" authorId="0" shapeId="0" xr:uid="{B6371D6E-7D64-4A19-A4DA-D81C3077BCE1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Until clear effect evidence is found, assume no effect</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F20" authorId="1" shapeId="0" xr:uid="{9311E7C8-6DF9-441C-9F8D-E21702435127}">
       <text>
         <r>
           <rPr>
@@ -3176,7 +3200,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F20" authorId="1" shapeId="0" xr:uid="{77FA98D7-61BE-429E-A5AA-428007243040}">
+    <comment ref="F22" authorId="1" shapeId="0" xr:uid="{77FA98D7-61BE-429E-A5AA-428007243040}">
       <text>
         <r>
           <rPr>
@@ -3190,7 +3214,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D22" authorId="0" shapeId="0" xr:uid="{93CC1998-BFB8-4B62-BCB5-E1BBBACE6830}">
+    <comment ref="D24" authorId="0" shapeId="0" xr:uid="{93CC1998-BFB8-4B62-BCB5-E1BBBACE6830}">
       <text>
         <r>
           <rPr>
@@ -3205,7 +3229,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D24" authorId="0" shapeId="0" xr:uid="{EF338D2F-A208-4CE3-B808-8AC74AF8E5EF}">
+    <comment ref="D26" authorId="0" shapeId="0" xr:uid="{EF338D2F-A208-4CE3-B808-8AC74AF8E5EF}">
       <text>
         <r>
           <rPr>
@@ -3220,7 +3244,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D26" authorId="0" shapeId="0" xr:uid="{CAAEA887-57C5-43F3-9495-1DEB3D5679A3}">
+    <comment ref="D28" authorId="0" shapeId="0" xr:uid="{CAAEA887-57C5-43F3-9495-1DEB3D5679A3}">
       <text>
         <r>
           <rPr>
@@ -3235,7 +3259,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D28" authorId="1" shapeId="0" xr:uid="{0135FFD5-224E-44D6-89F4-8E19B3F26984}">
+    <comment ref="D30" authorId="1" shapeId="0" xr:uid="{0135FFD5-224E-44D6-89F4-8E19B3F26984}">
       <text>
         <r>
           <rPr>
@@ -3250,7 +3274,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E28" authorId="1" shapeId="0" xr:uid="{087D42A2-DDA0-4EED-96A0-F816CA261B2B}">
+    <comment ref="E30" authorId="1" shapeId="0" xr:uid="{087D42A2-DDA0-4EED-96A0-F816CA261B2B}">
       <text>
         <r>
           <rPr>
@@ -3265,7 +3289,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F28" authorId="1" shapeId="0" xr:uid="{26E7E445-DC62-4BD8-9BA3-94D1A3A915FA}">
+    <comment ref="F30" authorId="1" shapeId="0" xr:uid="{26E7E445-DC62-4BD8-9BA3-94D1A3A915FA}">
       <text>
         <r>
           <rPr>
@@ -3280,7 +3304,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G28" authorId="1" shapeId="0" xr:uid="{288E52AB-6BF7-4AAB-9108-064316FD5C9A}">
+    <comment ref="G30" authorId="1" shapeId="0" xr:uid="{288E52AB-6BF7-4AAB-9108-064316FD5C9A}">
       <text>
         <r>
           <rPr>
@@ -3295,7 +3319,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H28" authorId="1" shapeId="0" xr:uid="{4799CEDE-3E07-4F5C-A7FD-D476484E84ED}">
+    <comment ref="H30" authorId="1" shapeId="0" xr:uid="{4799CEDE-3E07-4F5C-A7FD-D476484E84ED}">
       <text>
         <r>
           <rPr>
@@ -3310,7 +3334,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D43" authorId="0" shapeId="0" xr:uid="{8393718F-9D1E-4E53-BC37-5F6B053D0601}">
+    <comment ref="D45" authorId="0" shapeId="0" xr:uid="{8393718F-9D1E-4E53-BC37-5F6B053D0601}">
       <text>
         <r>
           <rPr>
@@ -3324,7 +3348,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E43" authorId="0" shapeId="0" xr:uid="{AAB9CB4B-0B96-4D0C-83ED-BB195F323ED5}">
+    <comment ref="E45" authorId="0" shapeId="0" xr:uid="{AAB9CB4B-0B96-4D0C-83ED-BB195F323ED5}">
       <text>
         <r>
           <rPr>
@@ -3338,7 +3362,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F43" authorId="0" shapeId="0" xr:uid="{D95C0DFF-F126-4A4C-9069-F298BF3D5946}">
+    <comment ref="F45" authorId="0" shapeId="0" xr:uid="{D95C0DFF-F126-4A4C-9069-F298BF3D5946}">
       <text>
         <r>
           <rPr>
@@ -3352,7 +3376,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G43" authorId="0" shapeId="0" xr:uid="{B5844301-F8EC-4F3A-9817-196B9209D97A}">
+    <comment ref="G45" authorId="0" shapeId="0" xr:uid="{B5844301-F8EC-4F3A-9817-196B9209D97A}">
       <text>
         <r>
           <rPr>
@@ -3366,7 +3390,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H43" authorId="0" shapeId="0" xr:uid="{8686E6B8-3CF0-48DD-94B5-57FC95305DFC}">
+    <comment ref="H45" authorId="0" shapeId="0" xr:uid="{8686E6B8-3CF0-48DD-94B5-57FC95305DFC}">
       <text>
         <r>
           <rPr>
@@ -3380,7 +3404,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D44" authorId="0" shapeId="0" xr:uid="{C0D7BB50-1552-4541-B85E-2A739302DB38}">
+    <comment ref="D46" authorId="0" shapeId="0" xr:uid="{C0D7BB50-1552-4541-B85E-2A739302DB38}">
       <text>
         <r>
           <rPr>
@@ -3394,7 +3418,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E44" authorId="0" shapeId="0" xr:uid="{22CC649A-F611-4A6F-B169-34E4FCE004EA}">
+    <comment ref="E46" authorId="0" shapeId="0" xr:uid="{22CC649A-F611-4A6F-B169-34E4FCE004EA}">
       <text>
         <r>
           <rPr>
@@ -3408,7 +3432,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F44" authorId="0" shapeId="0" xr:uid="{070F384F-6483-4AC9-B7ED-38B4F2DDA14C}">
+    <comment ref="F46" authorId="0" shapeId="0" xr:uid="{070F384F-6483-4AC9-B7ED-38B4F2DDA14C}">
       <text>
         <r>
           <rPr>
@@ -3422,7 +3446,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G44" authorId="0" shapeId="0" xr:uid="{D9E9C5B2-783C-4AF8-B771-863C5ACC6ACE}">
+    <comment ref="G46" authorId="0" shapeId="0" xr:uid="{D9E9C5B2-783C-4AF8-B771-863C5ACC6ACE}">
       <text>
         <r>
           <rPr>
@@ -3436,7 +3460,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H44" authorId="0" shapeId="0" xr:uid="{5DCCDA08-9FDA-4BEA-A37F-1CAF7C50C05D}">
+    <comment ref="H46" authorId="0" shapeId="0" xr:uid="{5DCCDA08-9FDA-4BEA-A37F-1CAF7C50C05D}">
       <text>
         <r>
           <rPr>
@@ -3450,7 +3474,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D47" authorId="0" shapeId="0" xr:uid="{87CE9237-E7B9-4256-B0F4-6398C8974F6E}">
+    <comment ref="D49" authorId="0" shapeId="0" xr:uid="{87CE9237-E7B9-4256-B0F4-6398C8974F6E}">
       <text>
         <r>
           <rPr>
@@ -3465,7 +3489,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E47" authorId="0" shapeId="0" xr:uid="{EF251290-B9E3-4088-98E7-8E0EE3F64386}">
+    <comment ref="E49" authorId="0" shapeId="0" xr:uid="{EF251290-B9E3-4088-98E7-8E0EE3F64386}">
       <text>
         <r>
           <rPr>
@@ -3480,7 +3504,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F47" authorId="0" shapeId="0" xr:uid="{F831ED86-2646-4AD8-91A7-5E7B52E7541C}">
+    <comment ref="F49" authorId="0" shapeId="0" xr:uid="{F831ED86-2646-4AD8-91A7-5E7B52E7541C}">
       <text>
         <r>
           <rPr>
@@ -3495,7 +3519,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G47" authorId="0" shapeId="0" xr:uid="{7A6102BC-F1AA-426A-9F94-322B5CF717CA}">
+    <comment ref="G49" authorId="0" shapeId="0" xr:uid="{7A6102BC-F1AA-426A-9F94-322B5CF717CA}">
       <text>
         <r>
           <rPr>
@@ -3510,7 +3534,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H47" authorId="0" shapeId="0" xr:uid="{15DD3F71-E83E-420A-A0B2-E33077CAC167}">
+    <comment ref="H49" authorId="0" shapeId="0" xr:uid="{15DD3F71-E83E-420A-A0B2-E33077CAC167}">
       <text>
         <r>
           <rPr>
@@ -3525,7 +3549,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D49" authorId="0" shapeId="0" xr:uid="{86C0A37B-7F6B-4635-AB9E-E73E6F45A238}">
+    <comment ref="D51" authorId="0" shapeId="0" xr:uid="{86C0A37B-7F6B-4635-AB9E-E73E6F45A238}">
       <text>
         <r>
           <rPr>
@@ -3541,7 +3565,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E49" authorId="0" shapeId="0" xr:uid="{D0AA5939-B07B-454D-93E1-5439F3EF05BF}">
+    <comment ref="E51" authorId="0" shapeId="0" xr:uid="{D0AA5939-B07B-454D-93E1-5439F3EF05BF}">
       <text>
         <r>
           <rPr>
@@ -3557,7 +3581,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F49" authorId="0" shapeId="0" xr:uid="{A2526AAA-C8D4-4BC4-B08F-A93419C9A866}">
+    <comment ref="F51" authorId="0" shapeId="0" xr:uid="{A2526AAA-C8D4-4BC4-B08F-A93419C9A866}">
       <text>
         <r>
           <rPr>
@@ -3573,7 +3597,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G49" authorId="0" shapeId="0" xr:uid="{ED88F435-71AC-4D5D-A328-7673C102E0CA}">
+    <comment ref="G51" authorId="0" shapeId="0" xr:uid="{ED88F435-71AC-4D5D-A328-7673C102E0CA}">
       <text>
         <r>
           <rPr>
@@ -3589,7 +3613,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H49" authorId="0" shapeId="0" xr:uid="{A7B2D29D-5B87-412D-8065-663376F457DD}">
+    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{A7B2D29D-5B87-412D-8065-663376F457DD}">
       <text>
         <r>
           <rPr>
@@ -3605,7 +3629,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D51" authorId="0" shapeId="0" xr:uid="{BD15B3BB-7B50-4253-82FE-9DEF1EEBAC5D}">
+    <comment ref="D53" authorId="0" shapeId="0" xr:uid="{BD15B3BB-7B50-4253-82FE-9DEF1EEBAC5D}">
       <text>
         <r>
           <rPr>
@@ -3620,7 +3644,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E51" authorId="0" shapeId="0" xr:uid="{E2E384F1-E5BF-4AF5-B4AB-048D4F77BBDC}">
+    <comment ref="E53" authorId="0" shapeId="0" xr:uid="{E2E384F1-E5BF-4AF5-B4AB-048D4F77BBDC}">
       <text>
         <r>
           <rPr>
@@ -3635,7 +3659,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F51" authorId="0" shapeId="0" xr:uid="{D4213AC5-2500-4F01-B3FC-2F4D8787D30C}">
+    <comment ref="F53" authorId="0" shapeId="0" xr:uid="{D4213AC5-2500-4F01-B3FC-2F4D8787D30C}">
       <text>
         <r>
           <rPr>
@@ -3650,7 +3674,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G51" authorId="0" shapeId="0" xr:uid="{3607F6EA-97FE-48B6-AFFB-F689044AA3C1}">
+    <comment ref="G53" authorId="0" shapeId="0" xr:uid="{3607F6EA-97FE-48B6-AFFB-F689044AA3C1}">
       <text>
         <r>
           <rPr>
@@ -3665,7 +3689,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{5D8A957C-01EA-4249-B9A1-69B9F32F608E}">
+    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{5D8A957C-01EA-4249-B9A1-69B9F32F608E}">
       <text>
         <r>
           <rPr>
@@ -3680,7 +3704,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D53" authorId="1" shapeId="0" xr:uid="{412926CC-5A0B-457A-8988-74ABB8BCE8AD}">
+    <comment ref="D55" authorId="1" shapeId="0" xr:uid="{412926CC-5A0B-457A-8988-74ABB8BCE8AD}">
       <text>
         <r>
           <rPr>
@@ -3694,7 +3718,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F58" authorId="0" shapeId="0" xr:uid="{44BEB1FC-80EA-40A2-A377-0E76FBE8C2D0}">
+    <comment ref="F60" authorId="0" shapeId="0" xr:uid="{44BEB1FC-80EA-40A2-A377-0E76FBE8C2D0}">
       <text>
         <r>
           <rPr>
@@ -3708,7 +3732,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G58" authorId="0" shapeId="0" xr:uid="{6F468163-C302-40D7-9F7C-D271694799E9}">
+    <comment ref="G60" authorId="0" shapeId="0" xr:uid="{6F468163-C302-40D7-9F7C-D271694799E9}">
       <text>
         <r>
           <rPr>
@@ -3722,7 +3746,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H58" authorId="0" shapeId="0" xr:uid="{CED83395-DD57-4867-AD1D-3D938938DD9A}">
+    <comment ref="H60" authorId="0" shapeId="0" xr:uid="{CED83395-DD57-4867-AD1D-3D938938DD9A}">
       <text>
         <r>
           <rPr>
@@ -3736,7 +3760,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F59" authorId="0" shapeId="0" xr:uid="{5642B808-E3E5-41D6-B03D-93D57C960EFD}">
+    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{5642B808-E3E5-41D6-B03D-93D57C960EFD}">
       <text>
         <r>
           <rPr>
@@ -3750,7 +3774,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G59" authorId="0" shapeId="0" xr:uid="{042CAAA7-648F-4928-8B52-16C52C1CB9F8}">
+    <comment ref="G61" authorId="0" shapeId="0" xr:uid="{042CAAA7-648F-4928-8B52-16C52C1CB9F8}">
       <text>
         <r>
           <rPr>
@@ -3764,7 +3788,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H59" authorId="0" shapeId="0" xr:uid="{9BA6A879-065C-4211-B29E-6899A259625C}">
+    <comment ref="H61" authorId="0" shapeId="0" xr:uid="{9BA6A879-065C-4211-B29E-6899A259625C}">
       <text>
         <r>
           <rPr>
@@ -3778,7 +3802,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F61" authorId="1" shapeId="0" xr:uid="{565D6423-01E0-47AE-A062-7832C4E375C5}">
+    <comment ref="F63" authorId="1" shapeId="0" xr:uid="{565D6423-01E0-47AE-A062-7832C4E375C5}">
       <text>
         <r>
           <rPr>
@@ -3792,7 +3816,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G61" authorId="1" shapeId="0" xr:uid="{A2040727-4AFC-4417-8173-7FB0863C5CBD}">
+    <comment ref="G63" authorId="1" shapeId="0" xr:uid="{A2040727-4AFC-4417-8173-7FB0863C5CBD}">
       <text>
         <r>
           <rPr>
@@ -3806,7 +3830,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F63" authorId="1" shapeId="0" xr:uid="{6AA85311-F8C0-49FB-8E21-7376530BDE97}">
+    <comment ref="F65" authorId="1" shapeId="0" xr:uid="{6AA85311-F8C0-49FB-8E21-7376530BDE97}">
       <text>
         <r>
           <rPr>
@@ -3820,7 +3844,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G63" authorId="1" shapeId="0" xr:uid="{3374B95E-CE9A-4D2E-9C9D-BFBA7E40C0B8}">
+    <comment ref="G65" authorId="1" shapeId="0" xr:uid="{3374B95E-CE9A-4D2E-9C9D-BFBA7E40C0B8}">
       <text>
         <r>
           <rPr>
@@ -3834,7 +3858,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F65" authorId="1" shapeId="0" xr:uid="{2F6B7874-ED49-4990-8F59-FA104F498ACF}">
+    <comment ref="F67" authorId="1" shapeId="0" xr:uid="{2F6B7874-ED49-4990-8F59-FA104F498ACF}">
       <text>
         <r>
           <rPr>
@@ -3848,7 +3872,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G65" authorId="1" shapeId="0" xr:uid="{9281230B-7F13-4BF3-A15E-5C91DC580EB9}">
+    <comment ref="G67" authorId="1" shapeId="0" xr:uid="{9281230B-7F13-4BF3-A15E-5C91DC580EB9}">
       <text>
         <r>
           <rPr>
@@ -3862,7 +3886,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F67" authorId="1" shapeId="0" xr:uid="{265BA4C5-B482-4466-9EE5-DE8BF4B05171}">
+    <comment ref="F69" authorId="1" shapeId="0" xr:uid="{265BA4C5-B482-4466-9EE5-DE8BF4B05171}">
       <text>
         <r>
           <rPr>
@@ -3876,7 +3900,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G67" authorId="1" shapeId="0" xr:uid="{31729F40-4AEA-4429-AE4C-44E7C56D5A06}">
+    <comment ref="G69" authorId="1" shapeId="0" xr:uid="{31729F40-4AEA-4429-AE4C-44E7C56D5A06}">
       <text>
         <r>
           <rPr>
@@ -3890,7 +3914,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F69" authorId="0" shapeId="0" xr:uid="{40FCD69E-E273-45F9-AD9C-D85ADC8881D3}">
+    <comment ref="F71" authorId="0" shapeId="0" xr:uid="{40FCD69E-E273-45F9-AD9C-D85ADC8881D3}">
       <text>
         <r>
           <rPr>
@@ -3904,7 +3928,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G69" authorId="0" shapeId="0" xr:uid="{574F8A5E-D331-4E39-AF86-D500131B6BD8}">
+    <comment ref="G71" authorId="0" shapeId="0" xr:uid="{574F8A5E-D331-4E39-AF86-D500131B6BD8}">
       <text>
         <r>
           <rPr>
@@ -3918,7 +3942,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F71" authorId="0" shapeId="0" xr:uid="{D8C1EC10-412B-4103-8C9F-F26240D6EA92}">
+    <comment ref="F73" authorId="0" shapeId="0" xr:uid="{D8C1EC10-412B-4103-8C9F-F26240D6EA92}">
       <text>
         <r>
           <rPr>
@@ -3932,7 +3956,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G71" authorId="0" shapeId="0" xr:uid="{0623E9F4-682F-42D6-BB68-F47E7264F4A0}">
+    <comment ref="G73" authorId="0" shapeId="0" xr:uid="{0623E9F4-682F-42D6-BB68-F47E7264F4A0}">
       <text>
         <r>
           <rPr>
@@ -3946,7 +3970,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F73" authorId="1" shapeId="0" xr:uid="{35D28F66-4ED6-4803-A236-4854CEC56423}">
+    <comment ref="F77" authorId="1" shapeId="0" xr:uid="{35D28F66-4ED6-4803-A236-4854CEC56423}">
       <text>
         <r>
           <rPr>
@@ -3961,7 +3985,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F75" authorId="1" shapeId="0" xr:uid="{1B9AA6C2-E8E3-42A6-8C99-E7CB524687D7}">
+    <comment ref="F79" authorId="1" shapeId="0" xr:uid="{1B9AA6C2-E8E3-42A6-8C99-E7CB524687D7}">
       <text>
         <r>
           <rPr>
@@ -3976,7 +4000,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D77" authorId="0" shapeId="0" xr:uid="{75F6BF46-ED4F-4722-B92B-9CA93DEC07A7}">
+    <comment ref="D81" authorId="0" shapeId="0" xr:uid="{75F6BF46-ED4F-4722-B92B-9CA93DEC07A7}">
       <text>
         <r>
           <rPr>
@@ -3991,7 +4015,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D79" authorId="0" shapeId="0" xr:uid="{23D5BD1C-E21E-484D-B255-C1DFA4048ED1}">
+    <comment ref="D83" authorId="0" shapeId="0" xr:uid="{23D5BD1C-E21E-484D-B255-C1DFA4048ED1}">
       <text>
         <r>
           <rPr>
@@ -4006,7 +4030,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D81" authorId="0" shapeId="0" xr:uid="{1AF8F7AB-5D3C-4F8F-B525-26B903297536}">
+    <comment ref="D85" authorId="0" shapeId="0" xr:uid="{1AF8F7AB-5D3C-4F8F-B525-26B903297536}">
       <text>
         <r>
           <rPr>
@@ -4021,7 +4045,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D83" authorId="1" shapeId="0" xr:uid="{E259BDDF-039F-45BC-9F58-6D46E98C9816}">
+    <comment ref="D87" authorId="1" shapeId="0" xr:uid="{E259BDDF-039F-45BC-9F58-6D46E98C9816}">
       <text>
         <r>
           <rPr>
@@ -4036,7 +4060,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E83" authorId="1" shapeId="0" xr:uid="{3106F71E-119F-491A-8533-0339B6FF1A50}">
+    <comment ref="E87" authorId="1" shapeId="0" xr:uid="{3106F71E-119F-491A-8533-0339B6FF1A50}">
       <text>
         <r>
           <rPr>
@@ -4051,7 +4075,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F83" authorId="1" shapeId="0" xr:uid="{E2C10219-0353-498A-A3D2-FF6CC2144909}">
+    <comment ref="F87" authorId="1" shapeId="0" xr:uid="{E2C10219-0353-498A-A3D2-FF6CC2144909}">
       <text>
         <r>
           <rPr>
@@ -4066,7 +4090,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G83" authorId="1" shapeId="0" xr:uid="{A7D9DA6B-332D-41A5-84EC-DD96731D452A}">
+    <comment ref="G87" authorId="1" shapeId="0" xr:uid="{A7D9DA6B-332D-41A5-84EC-DD96731D452A}">
       <text>
         <r>
           <rPr>
@@ -4081,7 +4105,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H83" authorId="1" shapeId="0" xr:uid="{6B6B8972-68C2-42CC-B8BF-FA49C3091C8A}">
+    <comment ref="H87" authorId="1" shapeId="0" xr:uid="{6B6B8972-68C2-42CC-B8BF-FA49C3091C8A}">
       <text>
         <r>
           <rPr>
@@ -4096,7 +4120,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D99" authorId="0" shapeId="0" xr:uid="{DEBAE134-2B56-4018-A42F-24680B56D64A}">
+    <comment ref="D103" authorId="0" shapeId="0" xr:uid="{DEBAE134-2B56-4018-A42F-24680B56D64A}">
       <text>
         <r>
           <rPr>
@@ -4110,7 +4134,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E99" authorId="0" shapeId="0" xr:uid="{23DD1570-2BBD-4337-B53F-9F651BBDEFF3}">
+    <comment ref="E103" authorId="0" shapeId="0" xr:uid="{23DD1570-2BBD-4337-B53F-9F651BBDEFF3}">
       <text>
         <r>
           <rPr>
@@ -4124,7 +4148,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F99" authorId="0" shapeId="0" xr:uid="{BAD62E7A-3F80-48DF-B0D5-DDED4DF5386C}">
+    <comment ref="F103" authorId="0" shapeId="0" xr:uid="{BAD62E7A-3F80-48DF-B0D5-DDED4DF5386C}">
       <text>
         <r>
           <rPr>
@@ -4138,7 +4162,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G99" authorId="0" shapeId="0" xr:uid="{35FB1CFC-F274-4B88-906F-154D53F8CB00}">
+    <comment ref="G103" authorId="0" shapeId="0" xr:uid="{35FB1CFC-F274-4B88-906F-154D53F8CB00}">
       <text>
         <r>
           <rPr>
@@ -4152,7 +4176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H99" authorId="0" shapeId="0" xr:uid="{7AC31835-F6B4-4D56-B100-048A495E78FC}">
+    <comment ref="H103" authorId="0" shapeId="0" xr:uid="{7AC31835-F6B4-4D56-B100-048A495E78FC}">
       <text>
         <r>
           <rPr>
@@ -4166,7 +4190,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D102" authorId="0" shapeId="0" xr:uid="{48D4A664-87D5-4D1F-B8F7-E15EFB01A5C0}">
+    <comment ref="D106" authorId="0" shapeId="0" xr:uid="{48D4A664-87D5-4D1F-B8F7-E15EFB01A5C0}">
       <text>
         <r>
           <rPr>
@@ -4181,7 +4205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E102" authorId="0" shapeId="0" xr:uid="{8846AEC1-EB5A-4BE7-BCF6-04754BF83056}">
+    <comment ref="E106" authorId="0" shapeId="0" xr:uid="{8846AEC1-EB5A-4BE7-BCF6-04754BF83056}">
       <text>
         <r>
           <rPr>
@@ -4196,7 +4220,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F102" authorId="0" shapeId="0" xr:uid="{2B2BADA3-43AE-4E0C-8AB8-9039C5E80A06}">
+    <comment ref="F106" authorId="0" shapeId="0" xr:uid="{2B2BADA3-43AE-4E0C-8AB8-9039C5E80A06}">
       <text>
         <r>
           <rPr>
@@ -4211,7 +4235,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G102" authorId="0" shapeId="0" xr:uid="{36540EE3-5D09-4E35-B1C8-1ECD214C4750}">
+    <comment ref="G106" authorId="0" shapeId="0" xr:uid="{36540EE3-5D09-4E35-B1C8-1ECD214C4750}">
       <text>
         <r>
           <rPr>
@@ -4226,7 +4250,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H102" authorId="0" shapeId="0" xr:uid="{780B86AF-212A-4888-BB06-B31872654F00}">
+    <comment ref="H106" authorId="0" shapeId="0" xr:uid="{780B86AF-212A-4888-BB06-B31872654F00}">
       <text>
         <r>
           <rPr>
@@ -4241,7 +4265,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D104" authorId="0" shapeId="0" xr:uid="{6A58E3BA-ABDD-4DF7-80BD-49A331A247C1}">
+    <comment ref="D108" authorId="0" shapeId="0" xr:uid="{6A58E3BA-ABDD-4DF7-80BD-49A331A247C1}">
       <text>
         <r>
           <rPr>
@@ -4257,7 +4281,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E104" authorId="0" shapeId="0" xr:uid="{9DD7F15B-9294-49B7-9959-F2D5E8EEFBFD}">
+    <comment ref="E108" authorId="0" shapeId="0" xr:uid="{9DD7F15B-9294-49B7-9959-F2D5E8EEFBFD}">
       <text>
         <r>
           <rPr>
@@ -4273,7 +4297,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F104" authorId="0" shapeId="0" xr:uid="{33668BAB-AEDA-46A5-B6D9-E02930970AB5}">
+    <comment ref="F108" authorId="0" shapeId="0" xr:uid="{33668BAB-AEDA-46A5-B6D9-E02930970AB5}">
       <text>
         <r>
           <rPr>
@@ -4289,7 +4313,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G104" authorId="0" shapeId="0" xr:uid="{DA4B34E5-4F18-4451-8CD9-C426C43A25EC}">
+    <comment ref="G108" authorId="0" shapeId="0" xr:uid="{DA4B34E5-4F18-4451-8CD9-C426C43A25EC}">
       <text>
         <r>
           <rPr>
@@ -4305,7 +4329,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H104" authorId="0" shapeId="0" xr:uid="{3014986A-A482-4CFA-AD26-BF3706F3E892}">
+    <comment ref="H108" authorId="0" shapeId="0" xr:uid="{3014986A-A482-4CFA-AD26-BF3706F3E892}">
       <text>
         <r>
           <rPr>
@@ -4321,7 +4345,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D106" authorId="0" shapeId="0" xr:uid="{75E7F49B-310A-447A-8ADF-EF511931023E}">
+    <comment ref="D110" authorId="0" shapeId="0" xr:uid="{75E7F49B-310A-447A-8ADF-EF511931023E}">
       <text>
         <r>
           <rPr>
@@ -4336,7 +4360,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E106" authorId="0" shapeId="0" xr:uid="{E164CB8D-3C40-4D8A-84A8-3F8A07364EF6}">
+    <comment ref="E110" authorId="0" shapeId="0" xr:uid="{E164CB8D-3C40-4D8A-84A8-3F8A07364EF6}">
       <text>
         <r>
           <rPr>
@@ -4351,7 +4375,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F106" authorId="0" shapeId="0" xr:uid="{BB0B4186-80E5-4EEC-96AB-DB35514465A2}">
+    <comment ref="F110" authorId="0" shapeId="0" xr:uid="{BB0B4186-80E5-4EEC-96AB-DB35514465A2}">
       <text>
         <r>
           <rPr>
@@ -4366,7 +4390,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G106" authorId="0" shapeId="0" xr:uid="{E0C637E4-020C-4C67-AC99-39A5E8CA7CB5}">
+    <comment ref="G110" authorId="0" shapeId="0" xr:uid="{E0C637E4-020C-4C67-AC99-39A5E8CA7CB5}">
       <text>
         <r>
           <rPr>
@@ -4381,7 +4405,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H106" authorId="0" shapeId="0" xr:uid="{D1456B7B-6C16-4BA5-8D14-3EF959BCB090}">
+    <comment ref="H110" authorId="0" shapeId="0" xr:uid="{D1456B7B-6C16-4BA5-8D14-3EF959BCB090}">
       <text>
         <r>
           <rPr>
@@ -4396,7 +4420,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D108" authorId="1" shapeId="0" xr:uid="{70887060-8F15-4389-BEF3-44B3C31D441D}">
+    <comment ref="D112" authorId="1" shapeId="0" xr:uid="{70887060-8F15-4389-BEF3-44B3C31D441D}">
       <text>
         <r>
           <rPr>
@@ -4410,7 +4434,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F113" authorId="0" shapeId="0" xr:uid="{E956E280-885D-43E2-8987-C6EECC5CA377}">
+    <comment ref="F117" authorId="0" shapeId="0" xr:uid="{E956E280-885D-43E2-8987-C6EECC5CA377}">
       <text>
         <r>
           <rPr>
@@ -4424,7 +4448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G113" authorId="0" shapeId="0" xr:uid="{5169C578-9E37-44F7-8D68-EFE6C44320E3}">
+    <comment ref="G117" authorId="0" shapeId="0" xr:uid="{5169C578-9E37-44F7-8D68-EFE6C44320E3}">
       <text>
         <r>
           <rPr>
@@ -4438,7 +4462,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H113" authorId="0" shapeId="0" xr:uid="{88882124-535A-47B0-A04F-4D7A84CA192F}">
+    <comment ref="H117" authorId="0" shapeId="0" xr:uid="{88882124-535A-47B0-A04F-4D7A84CA192F}">
       <text>
         <r>
           <rPr>
@@ -4452,7 +4476,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F114" authorId="0" shapeId="0" xr:uid="{0478BDF9-30D0-45EA-884D-3922C12787E1}">
+    <comment ref="F118" authorId="0" shapeId="0" xr:uid="{0478BDF9-30D0-45EA-884D-3922C12787E1}">
       <text>
         <r>
           <rPr>
@@ -4466,7 +4490,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G114" authorId="0" shapeId="0" xr:uid="{DA315D78-6983-47D7-AE51-1D117C78E1D2}">
+    <comment ref="G118" authorId="0" shapeId="0" xr:uid="{DA315D78-6983-47D7-AE51-1D117C78E1D2}">
       <text>
         <r>
           <rPr>
@@ -4480,7 +4504,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H114" authorId="0" shapeId="0" xr:uid="{F7F565BF-40D4-477B-BA08-889762E1B1E5}">
+    <comment ref="H118" authorId="0" shapeId="0" xr:uid="{F7F565BF-40D4-477B-BA08-889762E1B1E5}">
       <text>
         <r>
           <rPr>
@@ -4494,7 +4518,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F116" authorId="1" shapeId="0" xr:uid="{DB71F7C1-336A-45E3-963D-847FA568D415}">
+    <comment ref="F120" authorId="1" shapeId="0" xr:uid="{DB71F7C1-336A-45E3-963D-847FA568D415}">
       <text>
         <r>
           <rPr>
@@ -4508,7 +4532,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G116" authorId="1" shapeId="0" xr:uid="{522309E7-7A0B-472F-8064-C29F3FB505F1}">
+    <comment ref="G120" authorId="1" shapeId="0" xr:uid="{522309E7-7A0B-472F-8064-C29F3FB505F1}">
       <text>
         <r>
           <rPr>
@@ -4522,7 +4546,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F118" authorId="1" shapeId="0" xr:uid="{B3735AF6-982F-47B2-BE1D-6FBBB633F3F8}">
+    <comment ref="F122" authorId="1" shapeId="0" xr:uid="{B3735AF6-982F-47B2-BE1D-6FBBB633F3F8}">
       <text>
         <r>
           <rPr>
@@ -4536,7 +4560,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G118" authorId="1" shapeId="0" xr:uid="{55CC32A9-C242-413D-95ED-5A78B821B340}">
+    <comment ref="G122" authorId="1" shapeId="0" xr:uid="{55CC32A9-C242-413D-95ED-5A78B821B340}">
       <text>
         <r>
           <rPr>
@@ -4550,7 +4574,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F120" authorId="1" shapeId="0" xr:uid="{AC7BB7EF-7B75-412F-8492-B76564E0C14A}">
+    <comment ref="F124" authorId="1" shapeId="0" xr:uid="{AC7BB7EF-7B75-412F-8492-B76564E0C14A}">
       <text>
         <r>
           <rPr>
@@ -4564,7 +4588,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G120" authorId="1" shapeId="0" xr:uid="{28DD649B-C821-4AD3-A0FD-07992B1C0C35}">
+    <comment ref="G124" authorId="1" shapeId="0" xr:uid="{28DD649B-C821-4AD3-A0FD-07992B1C0C35}">
       <text>
         <r>
           <rPr>
@@ -4578,7 +4602,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F122" authorId="1" shapeId="0" xr:uid="{B37653CB-E528-4EB3-A892-BEED4F971924}">
+    <comment ref="F126" authorId="1" shapeId="0" xr:uid="{B37653CB-E528-4EB3-A892-BEED4F971924}">
       <text>
         <r>
           <rPr>
@@ -4592,7 +4616,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G122" authorId="1" shapeId="0" xr:uid="{D81352B8-E49B-4ED4-9260-068FE9EA87A4}">
+    <comment ref="G126" authorId="1" shapeId="0" xr:uid="{D81352B8-E49B-4ED4-9260-068FE9EA87A4}">
       <text>
         <r>
           <rPr>
@@ -4606,7 +4630,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F124" authorId="0" shapeId="0" xr:uid="{C81B46EA-4AE6-426F-8E29-6687826CD77E}">
+    <comment ref="F128" authorId="0" shapeId="0" xr:uid="{C81B46EA-4AE6-426F-8E29-6687826CD77E}">
       <text>
         <r>
           <rPr>
@@ -4620,7 +4644,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G124" authorId="0" shapeId="0" xr:uid="{2A5DAA9E-044F-4BC1-9CC5-853C778F0A5D}">
+    <comment ref="G128" authorId="0" shapeId="0" xr:uid="{2A5DAA9E-044F-4BC1-9CC5-853C778F0A5D}">
       <text>
         <r>
           <rPr>
@@ -4634,7 +4658,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F126" authorId="0" shapeId="0" xr:uid="{2FDE9FF6-3094-4FF5-9705-AC05C2A21CF1}">
+    <comment ref="F130" authorId="0" shapeId="0" xr:uid="{2FDE9FF6-3094-4FF5-9705-AC05C2A21CF1}">
       <text>
         <r>
           <rPr>
@@ -4648,7 +4672,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G126" authorId="0" shapeId="0" xr:uid="{34C2D730-9539-4A84-8FB9-60449CC1C9F8}">
+    <comment ref="G130" authorId="0" shapeId="0" xr:uid="{34C2D730-9539-4A84-8FB9-60449CC1C9F8}">
       <text>
         <r>
           <rPr>
@@ -4662,7 +4686,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F128" authorId="1" shapeId="0" xr:uid="{1CBE3B8E-0A71-484E-8AB5-2E4A9737E416}">
+    <comment ref="F134" authorId="1" shapeId="0" xr:uid="{1CBE3B8E-0A71-484E-8AB5-2E4A9737E416}">
       <text>
         <r>
           <rPr>
@@ -4677,7 +4701,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F130" authorId="1" shapeId="0" xr:uid="{C9BE8D4E-F1CF-450A-9F7F-FE3A76054555}">
+    <comment ref="F136" authorId="1" shapeId="0" xr:uid="{C9BE8D4E-F1CF-450A-9F7F-FE3A76054555}">
       <text>
         <r>
           <rPr>
@@ -4692,7 +4716,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D132" authorId="0" shapeId="0" xr:uid="{CE13D13D-74D4-4C89-9F75-91B5D8538FEE}">
+    <comment ref="D138" authorId="0" shapeId="0" xr:uid="{CE13D13D-74D4-4C89-9F75-91B5D8538FEE}">
       <text>
         <r>
           <rPr>
@@ -4707,7 +4731,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D134" authorId="0" shapeId="0" xr:uid="{252912B5-BBAA-4AE9-8277-3A1466458B1E}">
+    <comment ref="D140" authorId="0" shapeId="0" xr:uid="{252912B5-BBAA-4AE9-8277-3A1466458B1E}">
       <text>
         <r>
           <rPr>
@@ -4722,7 +4746,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D136" authorId="0" shapeId="0" xr:uid="{3E59560A-0C84-48D7-852B-E82392F25AC9}">
+    <comment ref="D142" authorId="0" shapeId="0" xr:uid="{3E59560A-0C84-48D7-852B-E82392F25AC9}">
       <text>
         <r>
           <rPr>
@@ -4737,7 +4761,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D138" authorId="1" shapeId="0" xr:uid="{DB3A1C43-FFBD-4811-96DB-7411C396D242}">
+    <comment ref="D144" authorId="1" shapeId="0" xr:uid="{DB3A1C43-FFBD-4811-96DB-7411C396D242}">
       <text>
         <r>
           <rPr>
@@ -4752,7 +4776,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E138" authorId="1" shapeId="0" xr:uid="{96EC8E96-7B87-4BE6-B2FB-A3593F869427}">
+    <comment ref="E144" authorId="1" shapeId="0" xr:uid="{96EC8E96-7B87-4BE6-B2FB-A3593F869427}">
       <text>
         <r>
           <rPr>
@@ -4767,7 +4791,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F138" authorId="1" shapeId="0" xr:uid="{DD5F88FD-E3D2-4EFC-8913-98A6325A2F9D}">
+    <comment ref="F144" authorId="1" shapeId="0" xr:uid="{DD5F88FD-E3D2-4EFC-8913-98A6325A2F9D}">
       <text>
         <r>
           <rPr>
@@ -4782,7 +4806,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G138" authorId="1" shapeId="0" xr:uid="{5BB9A2A7-6CE4-4189-BE50-9DCBB089C592}">
+    <comment ref="G144" authorId="1" shapeId="0" xr:uid="{5BB9A2A7-6CE4-4189-BE50-9DCBB089C592}">
       <text>
         <r>
           <rPr>
@@ -4797,7 +4821,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H138" authorId="1" shapeId="0" xr:uid="{157AB19B-CD3A-4FD7-B3E7-DAD07F11858B}">
+    <comment ref="H144" authorId="1" shapeId="0" xr:uid="{157AB19B-CD3A-4FD7-B3E7-DAD07F11858B}">
       <text>
         <r>
           <rPr>
@@ -4812,7 +4836,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D154" authorId="0" shapeId="0" xr:uid="{018E70A7-45A0-46D3-B6EA-DEF79DD16FBC}">
+    <comment ref="D160" authorId="0" shapeId="0" xr:uid="{018E70A7-45A0-46D3-B6EA-DEF79DD16FBC}">
       <text>
         <r>
           <rPr>
@@ -4826,7 +4850,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E154" authorId="0" shapeId="0" xr:uid="{BE34538E-8418-421B-95F3-555ADE6D22A4}">
+    <comment ref="E160" authorId="0" shapeId="0" xr:uid="{BE34538E-8418-421B-95F3-555ADE6D22A4}">
       <text>
         <r>
           <rPr>
@@ -4840,7 +4864,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F154" authorId="0" shapeId="0" xr:uid="{A119FDE3-73FC-49AA-961D-75632DF59D6A}">
+    <comment ref="F160" authorId="0" shapeId="0" xr:uid="{A119FDE3-73FC-49AA-961D-75632DF59D6A}">
       <text>
         <r>
           <rPr>
@@ -4854,7 +4878,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G154" authorId="0" shapeId="0" xr:uid="{A49858A8-A08E-4899-AB2B-CDA800BD9C7F}">
+    <comment ref="G160" authorId="0" shapeId="0" xr:uid="{A49858A8-A08E-4899-AB2B-CDA800BD9C7F}">
       <text>
         <r>
           <rPr>
@@ -4868,7 +4892,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H154" authorId="0" shapeId="0" xr:uid="{3E200C1B-B72C-4241-BAA2-2E363086D185}">
+    <comment ref="H160" authorId="0" shapeId="0" xr:uid="{3E200C1B-B72C-4241-BAA2-2E363086D185}">
       <text>
         <r>
           <rPr>
@@ -4882,7 +4906,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D157" authorId="0" shapeId="0" xr:uid="{4A1C8AC9-D54D-429B-ADAB-B3734C83BE23}">
+    <comment ref="D163" authorId="0" shapeId="0" xr:uid="{4A1C8AC9-D54D-429B-ADAB-B3734C83BE23}">
       <text>
         <r>
           <rPr>
@@ -4897,7 +4921,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E157" authorId="0" shapeId="0" xr:uid="{3BB8C26D-459A-4072-9E89-696F518731B1}">
+    <comment ref="E163" authorId="0" shapeId="0" xr:uid="{3BB8C26D-459A-4072-9E89-696F518731B1}">
       <text>
         <r>
           <rPr>
@@ -4912,7 +4936,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F157" authorId="0" shapeId="0" xr:uid="{1C6E857F-6C5D-4FD4-9EE4-2F09705C761A}">
+    <comment ref="F163" authorId="0" shapeId="0" xr:uid="{1C6E857F-6C5D-4FD4-9EE4-2F09705C761A}">
       <text>
         <r>
           <rPr>
@@ -4927,7 +4951,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G157" authorId="0" shapeId="0" xr:uid="{8287F70E-A738-4D8A-881F-7D338A40EC3B}">
+    <comment ref="G163" authorId="0" shapeId="0" xr:uid="{8287F70E-A738-4D8A-881F-7D338A40EC3B}">
       <text>
         <r>
           <rPr>
@@ -4942,7 +4966,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H157" authorId="0" shapeId="0" xr:uid="{014C8729-0CF6-41A9-8D99-FF6BB2C4394C}">
+    <comment ref="H163" authorId="0" shapeId="0" xr:uid="{014C8729-0CF6-41A9-8D99-FF6BB2C4394C}">
       <text>
         <r>
           <rPr>
@@ -4957,7 +4981,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D159" authorId="0" shapeId="0" xr:uid="{D354A556-8714-4D21-80ED-1573194C767A}">
+    <comment ref="D165" authorId="0" shapeId="0" xr:uid="{D354A556-8714-4D21-80ED-1573194C767A}">
       <text>
         <r>
           <rPr>
@@ -4973,7 +4997,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E159" authorId="0" shapeId="0" xr:uid="{485A1108-54DB-42E3-A6F2-C5940A4806C2}">
+    <comment ref="E165" authorId="0" shapeId="0" xr:uid="{485A1108-54DB-42E3-A6F2-C5940A4806C2}">
       <text>
         <r>
           <rPr>
@@ -4989,7 +5013,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F159" authorId="0" shapeId="0" xr:uid="{3EB095CD-A559-42E4-98B4-7A881E399DE6}">
+    <comment ref="F165" authorId="0" shapeId="0" xr:uid="{3EB095CD-A559-42E4-98B4-7A881E399DE6}">
       <text>
         <r>
           <rPr>
@@ -5005,7 +5029,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G159" authorId="0" shapeId="0" xr:uid="{B93A0BBF-6FEC-42F4-8430-29B5F3F939E7}">
+    <comment ref="G165" authorId="0" shapeId="0" xr:uid="{B93A0BBF-6FEC-42F4-8430-29B5F3F939E7}">
       <text>
         <r>
           <rPr>
@@ -5021,7 +5045,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H159" authorId="0" shapeId="0" xr:uid="{8E450807-067F-4B57-B220-14D51887F290}">
+    <comment ref="H165" authorId="0" shapeId="0" xr:uid="{8E450807-067F-4B57-B220-14D51887F290}">
       <text>
         <r>
           <rPr>
@@ -5037,7 +5061,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D161" authorId="0" shapeId="0" xr:uid="{AD46B5B9-39B8-4156-847F-4FF3309E3C00}">
+    <comment ref="D167" authorId="0" shapeId="0" xr:uid="{AD46B5B9-39B8-4156-847F-4FF3309E3C00}">
       <text>
         <r>
           <rPr>
@@ -5052,7 +5076,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E161" authorId="0" shapeId="0" xr:uid="{E43BA91C-6EAB-4A12-AFB0-A40BD4601DDD}">
+    <comment ref="E167" authorId="0" shapeId="0" xr:uid="{E43BA91C-6EAB-4A12-AFB0-A40BD4601DDD}">
       <text>
         <r>
           <rPr>
@@ -5067,7 +5091,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F161" authorId="0" shapeId="0" xr:uid="{D3FC5AB3-B8D4-487D-B89B-06521004E67B}">
+    <comment ref="F167" authorId="0" shapeId="0" xr:uid="{D3FC5AB3-B8D4-487D-B89B-06521004E67B}">
       <text>
         <r>
           <rPr>
@@ -5082,7 +5106,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G161" authorId="0" shapeId="0" xr:uid="{51C19B28-3606-4A3C-AE28-9BB4EA3F06E4}">
+    <comment ref="G167" authorId="0" shapeId="0" xr:uid="{51C19B28-3606-4A3C-AE28-9BB4EA3F06E4}">
       <text>
         <r>
           <rPr>
@@ -5097,7 +5121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H161" authorId="0" shapeId="0" xr:uid="{C9E9A396-CD69-464D-9C3D-544305C89BCD}">
+    <comment ref="H167" authorId="0" shapeId="0" xr:uid="{C9E9A396-CD69-464D-9C3D-544305C89BCD}">
       <text>
         <r>
           <rPr>
@@ -5112,7 +5136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D163" authorId="1" shapeId="0" xr:uid="{992C4CD7-8C10-4363-A95D-2D8B15120731}">
+    <comment ref="D169" authorId="1" shapeId="0" xr:uid="{992C4CD7-8C10-4363-A95D-2D8B15120731}">
       <text>
         <r>
           <rPr>
@@ -6509,7 +6533,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2153" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2167" uniqueCount="369">
   <si>
     <t>Condition</t>
   </si>
@@ -7613,6 +7637,9 @@
   </si>
   <si>
     <t>Efficacité à prévenir un cas</t>
+  </si>
+  <si>
+    <t>Toutes les causes</t>
   </si>
 </sst>
 </file>
@@ -11649,7 +11676,7 @@
       <c r="A63" s="4"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="DC7ci2cw9pUStfz/P3/3wJyRdfmVUP3VTf92ZBF8KPJrwNx75Jwqbly5XFwFEXlvPH6g4Z3mNSoZUWBob6f0Uw==" saltValue="3bZe/YB0Uvsqt9BsHTIT/g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="H19323VJpR294Mf9pMShcYSVsHwpnyvnvun6RxZfEK9wQeaLVi9xhD9iTqCBZI+H1bOSpz5HbfpXH3e1KzdtSQ==" saltValue="1E9+R9pU6MxzQaphuRbTXA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -12573,7 +12600,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="a+jrFaCCMAGveO5gjT/2o8vWw5qWXzyhuT1zJdCCXylW2ZTKVsVTP2hcLElEa6Yg/9KfWNZukzcHLiUla0dEKQ==" saltValue="Bo8a2sKM83G0LtXeYHyFPA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="PfXjQFAwT2j68inwY5COxXGUFlvIkt0RrvFZf9sm8AighH9GZYWLonv+T1LjJHEecMtPwDxNdZXaJZlM5Y1DRw==" saltValue="DA71IZEun9mQsGS6MLEPQA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D39">
     <sortCondition ref="A2:A39"/>
   </sortState>
@@ -12649,21 +12676,29 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="66" t="s">
+        <v>221</v>
+      </c>
+      <c r="B5" s="62" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="62"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="66" t="s">
         <v>218</v>
       </c>
-      <c r="B5" s="62" t="s">
-        <v>214</v>
-      </c>
-      <c r="C5" s="62"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="66"/>
-      <c r="B6" s="67"/>
+      <c r="B6" s="67" t="s">
+        <v>234</v>
+      </c>
       <c r="C6" s="67"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="66"/>
-      <c r="B7" s="67"/>
+      <c r="A7" s="66" t="s">
+        <v>229</v>
+      </c>
+      <c r="B7" s="67" t="s">
+        <v>234</v>
+      </c>
       <c r="C7" s="67"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -12732,7 +12767,7 @@
       <c r="C20" s="67"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="vqp8hta/uz2L5JGlAj198OOrDCpj5KUck6hQ54SYkOWr1G5rfxkDibBt1DOBDD4vFkZht8UMkXbSliII3XM5fA==" saltValue="W+AfjnDm7ONdArndJDBsWw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="PpItXjYvmBe/1PtWnJy2M6fV/UDqVRTrFMe8+a6tC64ax0ZTi979nJNH5Pw+Ak+BhMTf0qsMYcpXDYDXn4LBQg==" saltValue="XsiqtAzrMynWlG65cV+ucQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -12827,7 +12862,7 @@
       <c r="A19" s="35"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ZsnxGecEiTw0EFQcgmmlUAe0ZwEHfVgt71QQ4PKtNn8foVSa6s2rXMog7pFMBZDB0umyvzFelOto4ZTLxUdVDA==" saltValue="sBxV5lMP6R0+WXS8HnBzMQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="OGd94b5K6KrTAlGU8MS6wX1ldqtO6bX/OZ5BHmX1cQWlF3Gu/dcvhO2JpNJNLBGaL4jiWChRUkXcYl/jfZYZkA==" saltValue="LLvmDdC6b5lMTON7595TwQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -12937,7 +12972,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="xQf28hmRHPeHuQeZMgIgQ0nEdHsq+K7eoIMdZcMSTPnxlfMdj8KL8byfiGgtedqxCn1rnXpNnnO5q7fH7smA+A==" saltValue="f27QNJ9G6BxSudf9wOb7Hw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="VRExqdJk2V5qbxeGvi2J/U8HK4aAndcadBnLjGxwhgZzOSoTkoBkoXjGYyZh997cz13ekjvxWIzFwT5VHFyztQ==" saltValue="Eb870y4DVmSTdahpo0cECw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -14695,7 +14730,7 @@
       <c r="B40" s="9"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="JCIwtEigS4u7Ws06t7LGvcP7cyQG2WbCClnqpeIKzaiDdLj9gLkrqionkrw1ZJUsGVQMn7MlUg1f6Z7GxsrI/g==" saltValue="9RXFox+F83ricRGOOnAj6g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="TsYBt5grrE/Z53+XJPwrrLh9RObNGnYXE2wcnbI1WNduBHGN+oLeBuf4lVYY+6vncduHEU5/VKK9IE3iclw4pA==" saltValue="oVVrfHUHfz6pdGoCg2+t1A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B15:O22">
     <sortCondition ref="B15:B22"/>
   </sortState>
@@ -14730,7 +14765,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="PJRPm4wdgQ4H//TAX4WPPD51IKDg89qzhXD5kv4xVOoXUbu7ivBz6n05r/imLfpPh4ndKSZ+3nifieqTRNvRFA==" saltValue="iDZ0uoQ8joMgrYleDBqLww==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="dUTdbzI3pfnE5VIeYrRiEcr/wqy82wibF2mH2qyqp4uqH3jjVxgoAHn/dRo6qwN+D1UEtO8Q4tH0nUJbdPwDZA==" saltValue="x3UFXHjhlQjgLgzFmtD7Jg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14930,7 +14965,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="7tFFDOMQnq7iRrbZn2H5dRTWjZasnaPptvwIUet/2qB3Y9+QRTfbNGYETH1c/XR5nfyJs8QShXXvzW6tlzviig==" saltValue="bfQsVvIwJHLKqOx4iO6D2A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ZYXuBo64Eb9twulANpaOUlcZ9691EaL2RzN7taC0Oa0SJSP99gVzPHmN8AeF67yr6WpNpcsUyit7dyscrovKyQ==" saltValue="HBxTvrxRrZEqaVsmoMGaMg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -16739,7 +16774,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="b/Bfg2i9/OTemRufCPAjhaueVvGF/jCBVxMaje2TngnDHq5ysnkt7bcSb8HH8zdVjH59AvBYVdAsg19yYjwBAw==" saltValue="jM6RKdzv9DKPZWDb3fvHlg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="L13TRjgYMEE6dPIiKMY0sfIKsFWpCOQL3DKpwu9knkM9oO8mKNBVCHusvtlt6xYNuOVoKXUT8x+2CngPAbdQXw==" saltValue="hDRQUcr4bRS36GL0eFeFdw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -17363,7 +17398,9 @@
       <c r="E30" s="100"/>
       <c r="F30" s="100"/>
       <c r="G30" s="100"/>
-      <c r="H30" s="100"/>
+      <c r="H30" s="100" t="s">
+        <v>7</v>
+      </c>
       <c r="I30" s="100"/>
       <c r="J30" s="100"/>
       <c r="K30" s="100"/>
@@ -17548,7 +17585,7 @@
       <c r="L39" s="100"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="oeRDNGWg/c73B99PLcaPV14gYABg0eCi6SRoGFa2AVf7MWPUB6mLSUkFbUPVigyGBTfu/ZBBOzqVnv0tewHE1g==" saltValue="MqWQKHEVbKn/NhNsC+nsWg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="6OMJjrPsk7Ikl/gFZWFNJppmPQn4mFfWl30DLTU5n1VDK2Sb3lfZE5kX7LD0KWPA0TXWu4CTcdC2NZU1uuIYew==" saltValue="9XrEtUmknDHp+R9G7aJ8YQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -17941,7 +17978,7 @@
       <c r="L14" s="100"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Jz4E984v0RX+MYXAzd4jtWJidvbi5GpcvE9Sgjh43mWglxQ0VFfCTry3OPMyLFstpywp7p4G0LpNRCnegR721w==" saltValue="WXD0k1bQY2z7sBpjragB9w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="LwrIVExY5MXkYvixLjcDPw+CN6jcti71CfqgoAZVBh20invSCjiWec7B5dFgd5dan721hcQPiDsoKlwCvykJWg==" saltValue="1daP56fs+4x7NW4nvb1tYA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -19025,7 +19062,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="+GtMIqUd3BQj7al8vGqgl9bDKivLry4wZtTbVM+3hFhxHuWIvkjIz1Ps/rOzugAj0Lvf/sgqRdLO1NtmZ/4+qQ==" saltValue="bl570iKBYxgRudRTqZX/Yg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="OKVCOjRTv4EoPhWdRCz15GEaZ+7PWWwSh24ZO+sF7bIodzfzGu8P+PQdZN7kKX6To+JEWA/zuNkoEu9YqfuvnQ==" saltValue="yK9AgF+yZnG+1v7kENy/fw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <conditionalFormatting sqref="B2:I16 B17:C17 E17:I17 B18:I40">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>$A2=""</formula>
@@ -22820,8 +22857,44 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="lEdMURciM2nBmcPgnMooUocxaqfMGm6n7nM6R4aNt+13gwHDBLeQ/NILiD/PPszVU5H9qDU6u8jedkdP+P9vTQ==" saltValue="1dLiUPUgT24tWQ3Vgh9Vzg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Wqujlo7njSYldG0Hr9eDtk+0FTgpgV2AsAsTMyaEJlBnADMvNZG1QFoaE1Srhm8q/v45eaXFof6xLgEwIxJWVQ==" saltValue="4tgu4jN6HjmJbKTrqExvEw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="45">
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="B98:B100"/>
+    <mergeCell ref="B101:B103"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="B120:B122"/>
+    <mergeCell ref="B125:B127"/>
     <mergeCell ref="B145:B147"/>
     <mergeCell ref="B148:B150"/>
     <mergeCell ref="B151:B153"/>
@@ -22831,42 +22904,6 @@
     <mergeCell ref="B134:B136"/>
     <mergeCell ref="B137:B139"/>
     <mergeCell ref="B142:B144"/>
-    <mergeCell ref="B111:B113"/>
-    <mergeCell ref="B114:B116"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="B120:B122"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="B89:B91"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="B98:B100"/>
-    <mergeCell ref="B101:B103"/>
-    <mergeCell ref="B72:B74"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="B81:B83"/>
-    <mergeCell ref="B84:B86"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B14:B16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -24081,7 +24118,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="uTddhOJlxX80z3BAl6J1wOJ0NazAUVO4ZoLWy9AtiUSIes01jYAyM6oTvboi0E1BUm5btwqqI+N/50Uw0Tm7qA==" saltValue="UY2hfWQbWnIp2wufVgJklg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="mJU+B7YAyorK6h79z6nG1VIDy+cMnlqfNnSpZzxhr+nTwr5Mq4oC1b8cMSoGQSE9VWup7v7P5wLBO0s658ATOQ==" saltValue="aZvO0LzL+h67WHCwNmmy4A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -32214,7 +32251,7 @@
       <c r="I328" s="92"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="IqYldILLTCnDAfY4B+fi0/NUhW6i0fY3ZWj6oM9ll1ETri8SPO82PbViEPw92UdZxCk7YmZPgAzqEUeqG9RozA==" saltValue="+TQhS3f7phGAJfzCwNQwgQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="iC6hZlgTO7qDeg+i2nPI52P3xOYDcHSGyLmu86heseLE+Q1WuwryH+T8XZfQPT1SExzreO/y7ABqNEKnlwSRYg==" saltValue="h8TahLiP4jfaK3bvymg6sA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -33315,7 +33352,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="T2CYRbO1m29H9qPXhTwomjadUMDzzhO1KQTwuc9nSruuOU6QbOJ+duvKbHXY+MqpVaRKLmmvGmwZAb7BaNjgiQ==" saltValue="HGDYgX1cCzup68tLeIBoaQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="FPOv2fA8BGunkz6CuhtJvCWmwu3VvX//eeXCDdMYhVDb7YiOlxEr8m5HMMjp/qC7RLiEuemTFYYGt8CTdkpk2g==" saltValue="ha1hytHWP2mGYg+oYIfixA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -34256,7 +34293,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="VSzN4MTosQ4MnjM6lMnFLM/Fh5fk5cYUEKder2U7LS8SL9SaXzH40DRBSAxdP2lojf1bNVEOEN+DutL6oOBIpg==" saltValue="6z/dZIK5X9WS6X9NRO0Hcg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="9Fkq+LIzBPjH9YzdJQmq3FdlpxSPCovCJ9pKFArypE1O4KbZOPQnlVEX1yJsge4nteDyD2E1KrfOr/AvHdu5hQ==" saltValue="rkeNfy9Oa/li4tKQHdGgJA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -36971,7 +37008,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="e1e52Wbm/gLOFHGc3rxT6U0SivaJLUjDXoyL2sxZ9I4LkDgDQThR3O5MUiOsCMaSvIBgplvqiJzLkNZ99GqBcQ==" saltValue="HP2xg2sR0b7+zNNuHRl8+Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="BIuEQ8aWlCMeLAK8vmZBtwQ3bKri3xZdQFKIPdB7h0MwVs05LjHhubTQCtrE8zgWXaY4NS45XKaS+K4LzLI0Uw==" saltValue="fErcDirD/Dc99ut3lxvAnA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -37262,7 +37299,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="iHJZgwiVNmEOiHe33QXxGk3jfuuUgTtmVtY7tLivmMvRb+SO9h8PzR48vcS5u1BGB8lhrxnbXkGbwdaaFyokzA==" saltValue="lEk/j/v2mJbimlk1UITgtw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ynHJZiciF1URJ9OEcskFHaks7iFbKuQKAYb78z7ljsEwnkh5tPflLpbiIELV1Bb1ua3ZmxpasioneV/GdXL9YA==" saltValue="FRDtz2cPnD8voy5os2HuUQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -37274,7 +37311,7 @@
   <sheetPr>
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:H163"/>
+  <dimension ref="A1:H169"/>
   <sheetFormatPr defaultColWidth="12.7265625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53" style="39" customWidth="1"/>
@@ -37648,11 +37685,8 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="39" t="s">
-        <v>199</v>
-      </c>
       <c r="B17" s="39" t="s">
-        <v>237</v>
+        <v>368</v>
       </c>
       <c r="C17" s="39" t="s">
         <v>365</v>
@@ -37670,12 +37704,12 @@
         <v>1</v>
       </c>
       <c r="H17" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C18" s="39" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D18" s="120">
         <v>0</v>
@@ -37694,8 +37728,11 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="39" t="s">
+        <v>199</v>
+      </c>
       <c r="B19" s="39" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C19" s="39" t="s">
         <v>365</v>
@@ -37737,37 +37774,34 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="39" t="s">
-        <v>204</v>
-      </c>
       <c r="B21" s="39" t="s">
-        <v>102</v>
+        <v>238</v>
       </c>
       <c r="C21" s="39" t="s">
         <v>365</v>
       </c>
       <c r="D21" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="120">
         <v>0</v>
       </c>
       <c r="F21" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C22" s="39" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D22" s="120">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="E22" s="120">
         <v>0</v>
@@ -37784,7 +37818,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="39" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B23" s="39" t="s">
         <v>102</v>
@@ -37830,7 +37864,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="39" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B25" s="39" t="s">
         <v>102</v>
@@ -37876,10 +37910,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="39" t="s">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C27" s="39" t="s">
         <v>365</v>
@@ -37888,16 +37922,16 @@
         <v>1</v>
       </c>
       <c r="E27" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -37905,483 +37939,483 @@
         <v>366</v>
       </c>
       <c r="D28" s="120">
+        <v>0.13</v>
+      </c>
+      <c r="E28" s="120">
+        <v>0</v>
+      </c>
+      <c r="F28" s="120">
+        <v>0</v>
+      </c>
+      <c r="G28" s="120">
+        <v>0</v>
+      </c>
+      <c r="H28" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="39" t="s">
+        <v>226</v>
+      </c>
+      <c r="B29" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="D29" s="120">
+        <v>1</v>
+      </c>
+      <c r="E29" s="120">
+        <v>1</v>
+      </c>
+      <c r="F29" s="120">
+        <v>1</v>
+      </c>
+      <c r="G29" s="120">
+        <v>1</v>
+      </c>
+      <c r="H29" s="120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C30" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="D30" s="120">
         <v>0.3</v>
       </c>
-      <c r="E28" s="120">
+      <c r="E30" s="120">
         <v>0.3</v>
       </c>
-      <c r="F28" s="120">
+      <c r="F30" s="120">
         <v>0.3</v>
       </c>
-      <c r="G28" s="120">
+      <c r="G30" s="120">
         <v>0.3</v>
       </c>
-      <c r="H28" s="120">
+      <c r="H30" s="120">
         <v>0.3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C29" s="39" t="s">
-        <v>367</v>
-      </c>
-      <c r="D29" s="120">
-        <v>0</v>
-      </c>
-      <c r="E29" s="120">
-        <v>0</v>
-      </c>
-      <c r="F29" s="120">
-        <v>0</v>
-      </c>
-      <c r="G29" s="120">
-        <v>0</v>
-      </c>
-      <c r="H29" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="39" t="s">
-        <v>227</v>
-      </c>
-      <c r="B30" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="C30" s="39" t="s">
-        <v>365</v>
-      </c>
-      <c r="D30" s="120">
-        <v>1</v>
-      </c>
-      <c r="E30" s="120">
-        <v>1</v>
-      </c>
-      <c r="F30" s="120">
-        <v>1</v>
-      </c>
-      <c r="G30" s="120">
-        <v>1</v>
-      </c>
-      <c r="H30" s="120">
-        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C31" s="39" t="s">
+        <v>367</v>
+      </c>
+      <c r="D31" s="120">
+        <v>0</v>
+      </c>
+      <c r="E31" s="120">
+        <v>0</v>
+      </c>
+      <c r="F31" s="120">
+        <v>0</v>
+      </c>
+      <c r="G31" s="120">
+        <v>0</v>
+      </c>
+      <c r="H31" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="39" t="s">
+        <v>227</v>
+      </c>
+      <c r="B32" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="D32" s="120">
+        <v>1</v>
+      </c>
+      <c r="E32" s="120">
+        <v>1</v>
+      </c>
+      <c r="F32" s="120">
+        <v>1</v>
+      </c>
+      <c r="G32" s="120">
+        <v>1</v>
+      </c>
+      <c r="H32" s="120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C33" s="39" t="s">
         <v>366</v>
       </c>
-      <c r="D31" s="120">
-        <v>0</v>
-      </c>
-      <c r="E31" s="120">
-        <v>0</v>
-      </c>
-      <c r="F31" s="120">
-        <v>0</v>
-      </c>
-      <c r="G31" s="120">
-        <v>0</v>
-      </c>
-      <c r="H31" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C32" s="39" t="s">
-        <v>367</v>
-      </c>
-      <c r="D32" s="120">
-        <v>0</v>
-      </c>
-      <c r="E32" s="120">
-        <v>0</v>
-      </c>
-      <c r="F32" s="120">
-        <v>0</v>
-      </c>
-      <c r="G32" s="120">
-        <v>0</v>
-      </c>
-      <c r="H32" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="39" t="s">
-        <v>225</v>
-      </c>
-      <c r="B33" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="C33" s="39" t="s">
-        <v>365</v>
-      </c>
       <c r="D33" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C34" s="39" t="s">
+        <v>367</v>
+      </c>
+      <c r="D34" s="120">
+        <v>0</v>
+      </c>
+      <c r="E34" s="120">
+        <v>0</v>
+      </c>
+      <c r="F34" s="120">
+        <v>0</v>
+      </c>
+      <c r="G34" s="120">
+        <v>0</v>
+      </c>
+      <c r="H34" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="39" t="s">
+        <v>225</v>
+      </c>
+      <c r="B35" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="D35" s="120">
+        <v>1</v>
+      </c>
+      <c r="E35" s="120">
+        <v>1</v>
+      </c>
+      <c r="F35" s="120">
+        <v>1</v>
+      </c>
+      <c r="G35" s="120">
+        <v>1</v>
+      </c>
+      <c r="H35" s="120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C36" s="39" t="s">
         <v>366</v>
       </c>
-      <c r="D34" s="120">
-        <v>0</v>
-      </c>
-      <c r="E34" s="120">
-        <v>0</v>
-      </c>
-      <c r="F34" s="120">
-        <v>0</v>
-      </c>
-      <c r="G34" s="120">
-        <v>0</v>
-      </c>
-      <c r="H34" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C35" s="39" t="s">
-        <v>367</v>
-      </c>
-      <c r="D35" s="120">
-        <v>0</v>
-      </c>
-      <c r="E35" s="120">
-        <v>0</v>
-      </c>
-      <c r="F35" s="120">
-        <v>0</v>
-      </c>
-      <c r="G35" s="120">
-        <v>0</v>
-      </c>
-      <c r="H35" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="39" t="s">
-        <v>224</v>
-      </c>
-      <c r="B36" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="C36" s="39" t="s">
-        <v>365</v>
-      </c>
       <c r="D36" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C37" s="39" t="s">
+        <v>367</v>
+      </c>
+      <c r="D37" s="120">
+        <v>0</v>
+      </c>
+      <c r="E37" s="120">
+        <v>0</v>
+      </c>
+      <c r="F37" s="120">
+        <v>0</v>
+      </c>
+      <c r="G37" s="120">
+        <v>0</v>
+      </c>
+      <c r="H37" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="39" t="s">
+        <v>224</v>
+      </c>
+      <c r="B38" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="C38" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="D38" s="120">
+        <v>1</v>
+      </c>
+      <c r="E38" s="120">
+        <v>1</v>
+      </c>
+      <c r="F38" s="120">
+        <v>1</v>
+      </c>
+      <c r="G38" s="120">
+        <v>1</v>
+      </c>
+      <c r="H38" s="120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C39" s="39" t="s">
         <v>366</v>
       </c>
-      <c r="D37" s="120">
-        <v>0</v>
-      </c>
-      <c r="E37" s="120">
-        <v>0</v>
-      </c>
-      <c r="F37" s="120">
-        <v>0</v>
-      </c>
-      <c r="G37" s="120">
-        <v>0</v>
-      </c>
-      <c r="H37" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C38" s="39" t="s">
-        <v>367</v>
-      </c>
-      <c r="D38" s="120">
-        <v>0</v>
-      </c>
-      <c r="E38" s="120">
-        <v>0</v>
-      </c>
-      <c r="F38" s="120">
-        <v>0</v>
-      </c>
-      <c r="G38" s="120">
-        <v>0</v>
-      </c>
-      <c r="H38" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="39" t="s">
-        <v>223</v>
-      </c>
-      <c r="B39" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="C39" s="39" t="s">
-        <v>365</v>
-      </c>
       <c r="D39" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C40" s="39" t="s">
+        <v>367</v>
+      </c>
+      <c r="D40" s="120">
+        <v>0</v>
+      </c>
+      <c r="E40" s="120">
+        <v>0</v>
+      </c>
+      <c r="F40" s="120">
+        <v>0</v>
+      </c>
+      <c r="G40" s="120">
+        <v>0</v>
+      </c>
+      <c r="H40" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="39" t="s">
+        <v>223</v>
+      </c>
+      <c r="B41" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="C41" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="D41" s="120">
+        <v>1</v>
+      </c>
+      <c r="E41" s="120">
+        <v>1</v>
+      </c>
+      <c r="F41" s="120">
+        <v>1</v>
+      </c>
+      <c r="G41" s="120">
+        <v>1</v>
+      </c>
+      <c r="H41" s="120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C42" s="39" t="s">
         <v>366</v>
       </c>
-      <c r="D40" s="120">
-        <v>0</v>
-      </c>
-      <c r="E40" s="120">
-        <v>0</v>
-      </c>
-      <c r="F40" s="120">
-        <v>0</v>
-      </c>
-      <c r="G40" s="120">
-        <v>0</v>
-      </c>
-      <c r="H40" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C41" s="39" t="s">
-        <v>367</v>
-      </c>
-      <c r="D41" s="120">
-        <v>0</v>
-      </c>
-      <c r="E41" s="120">
-        <v>0</v>
-      </c>
-      <c r="F41" s="120">
-        <v>0</v>
-      </c>
-      <c r="G41" s="120">
-        <v>0</v>
-      </c>
-      <c r="H41" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="39" t="s">
-        <v>229</v>
-      </c>
-      <c r="B42" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="C42" s="39" t="s">
-        <v>365</v>
-      </c>
       <c r="D42" s="120">
         <v>0</v>
       </c>
       <c r="E42" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C43" s="39" t="s">
+        <v>367</v>
+      </c>
+      <c r="D43" s="120">
+        <v>0</v>
+      </c>
+      <c r="E43" s="120">
+        <v>0</v>
+      </c>
+      <c r="F43" s="120">
+        <v>0</v>
+      </c>
+      <c r="G43" s="120">
+        <v>0</v>
+      </c>
+      <c r="H43" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="B44" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="C44" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="D44" s="120">
+        <v>0</v>
+      </c>
+      <c r="E44" s="120">
+        <v>1</v>
+      </c>
+      <c r="F44" s="120">
+        <v>1</v>
+      </c>
+      <c r="G44" s="120">
+        <v>1</v>
+      </c>
+      <c r="H44" s="120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C45" s="39" t="s">
         <v>366</v>
       </c>
-      <c r="D43" s="120">
-        <v>0</v>
-      </c>
-      <c r="E43" s="120">
-        <v>0</v>
-      </c>
-      <c r="F43" s="120">
-        <v>0</v>
-      </c>
-      <c r="G43" s="120">
-        <v>0</v>
-      </c>
-      <c r="H43" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C44" s="39" t="s">
-        <v>367</v>
-      </c>
-      <c r="D44" s="120">
-        <v>0.09</v>
-      </c>
-      <c r="E44" s="120">
-        <v>0.09</v>
-      </c>
-      <c r="F44" s="120">
-        <v>0.09</v>
-      </c>
-      <c r="G44" s="120">
-        <v>0.09</v>
-      </c>
-      <c r="H44" s="120">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B45" s="39" t="s">
-        <v>106</v>
-      </c>
-      <c r="C45" s="39" t="s">
-        <v>365</v>
-      </c>
       <c r="D45" s="120">
         <v>0</v>
       </c>
       <c r="E45" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C46" s="39" t="s">
+        <v>367</v>
+      </c>
+      <c r="D46" s="120">
+        <v>0.09</v>
+      </c>
+      <c r="E46" s="120">
+        <v>0.09</v>
+      </c>
+      <c r="F46" s="120">
+        <v>0.09</v>
+      </c>
+      <c r="G46" s="120">
+        <v>0.09</v>
+      </c>
+      <c r="H46" s="120">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B47" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="C47" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="D47" s="120">
+        <v>0</v>
+      </c>
+      <c r="E47" s="120">
+        <v>1</v>
+      </c>
+      <c r="F47" s="120">
+        <v>1</v>
+      </c>
+      <c r="G47" s="120">
+        <v>1</v>
+      </c>
+      <c r="H47" s="120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C48" s="39" t="s">
         <v>366</v>
       </c>
-      <c r="D46" s="120">
-        <v>0</v>
-      </c>
-      <c r="E46" s="120">
-        <v>0</v>
-      </c>
-      <c r="F46" s="120">
-        <v>0</v>
-      </c>
-      <c r="G46" s="120">
-        <v>0</v>
-      </c>
-      <c r="H46" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C47" s="39" t="s">
-        <v>367</v>
-      </c>
-      <c r="D47" s="120">
-        <v>0</v>
-      </c>
-      <c r="E47" s="120">
-        <v>0</v>
-      </c>
-      <c r="F47" s="120">
-        <v>0</v>
-      </c>
-      <c r="G47" s="120">
-        <v>0</v>
-      </c>
-      <c r="H47" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="39" t="s">
-        <v>220</v>
-      </c>
-      <c r="B48" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="C48" s="39" t="s">
-        <v>365</v>
-      </c>
       <c r="D48" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C49" s="39" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D49" s="120">
-        <v>0.69</v>
+        <v>0</v>
       </c>
       <c r="E49" s="120">
-        <v>0.69</v>
+        <v>0</v>
       </c>
       <c r="F49" s="120">
-        <v>0.69</v>
+        <v>0</v>
       </c>
       <c r="G49" s="120">
-        <v>0.69</v>
+        <v>0</v>
       </c>
       <c r="H49" s="120">
-        <v>0.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="39" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B50" s="39" t="s">
         <v>105</v>
@@ -38410,27 +38444,27 @@
         <v>366</v>
       </c>
       <c r="D51" s="120">
-        <v>0.76</v>
+        <v>0.69</v>
       </c>
       <c r="E51" s="120">
-        <v>0.76</v>
+        <v>0.69</v>
       </c>
       <c r="F51" s="120">
-        <v>0.76</v>
+        <v>0.69</v>
       </c>
       <c r="G51" s="120">
-        <v>0.76</v>
+        <v>0.69</v>
       </c>
       <c r="H51" s="120">
-        <v>0.76</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="39" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="B52" s="39" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C52" s="39" t="s">
         <v>365</v>
@@ -38439,16 +38473,16 @@
         <v>1</v>
       </c>
       <c r="E52" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -38456,158 +38490,156 @@
         <v>366</v>
       </c>
       <c r="D53" s="120">
+        <v>0.76</v>
+      </c>
+      <c r="E53" s="120">
+        <v>0.76</v>
+      </c>
+      <c r="F53" s="120">
+        <v>0.76</v>
+      </c>
+      <c r="G53" s="120">
+        <v>0.76</v>
+      </c>
+      <c r="H53" s="120">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="39" t="s">
+        <v>213</v>
+      </c>
+      <c r="B54" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="C54" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="D54" s="120">
+        <v>1</v>
+      </c>
+      <c r="E54" s="120">
+        <v>0</v>
+      </c>
+      <c r="F54" s="120">
+        <v>0</v>
+      </c>
+      <c r="G54" s="120">
+        <v>0</v>
+      </c>
+      <c r="H54" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C55" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="D55" s="120">
         <v>0.32</v>
       </c>
-      <c r="E53" s="120">
-        <v>0</v>
-      </c>
-      <c r="F53" s="120">
-        <v>0</v>
-      </c>
-      <c r="G53" s="120">
-        <v>0</v>
-      </c>
-      <c r="H53" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" s="106" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A55" s="109" t="s">
+      <c r="E55" s="120">
+        <v>0</v>
+      </c>
+      <c r="F55" s="120">
+        <v>0</v>
+      </c>
+      <c r="G55" s="120">
+        <v>0</v>
+      </c>
+      <c r="H55" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" s="106" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A57" s="109" t="s">
         <v>362</v>
       </c>
-      <c r="B55" s="110"/>
-      <c r="C55" s="110"/>
-      <c r="D55" s="124"/>
-      <c r="E55" s="124"/>
-      <c r="F55" s="124"/>
-      <c r="G55" s="124"/>
-      <c r="H55" s="124"/>
-    </row>
-    <row r="56" spans="1:8" ht="13" x14ac:dyDescent="0.3">
-      <c r="A56" s="29" t="s">
+      <c r="B57" s="110"/>
+      <c r="C57" s="110"/>
+      <c r="D57" s="124"/>
+      <c r="E57" s="124"/>
+      <c r="F57" s="124"/>
+      <c r="G57" s="124"/>
+      <c r="H57" s="124"/>
+    </row>
+    <row r="58" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+      <c r="A58" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="B56" s="29" t="s">
+      <c r="B58" s="29" t="s">
         <v>364</v>
       </c>
-      <c r="C56" s="96" t="s">
+      <c r="C58" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="D58" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E56" s="4" t="s">
+      <c r="E58" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="F56" s="4" t="s">
+      <c r="F58" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="G56" s="4" t="s">
+      <c r="G58" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="H56" s="4" t="s">
+      <c r="H58" s="4" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="39" t="s">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="39" t="s">
         <v>222</v>
       </c>
-      <c r="B57" s="39" t="s">
+      <c r="B59" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="C57" s="39" t="s">
+      <c r="C59" s="39" t="s">
         <v>365</v>
       </c>
-      <c r="D57" s="120">
+      <c r="D59" s="120">
         <f>IF($C2="Affected fraction",D2,IF(D2=1,1,D2*0.9))</f>
         <v>0</v>
       </c>
-      <c r="E57" s="120">
+      <c r="E59" s="120">
         <f>IF($C2="Affected fraction",E2,IF(E2=1,1,E2*0.9))</f>
         <v>0</v>
       </c>
-      <c r="F57" s="120">
+      <c r="F59" s="120">
         <f>IF($C2="Affected fraction",F2,IF(F2=1,1,F2*0.9))</f>
         <v>1</v>
       </c>
-      <c r="G57" s="120">
+      <c r="G59" s="120">
         <f>IF($C2="Affected fraction",G2,IF(G2=1,1,G2*0.9))</f>
         <v>1</v>
       </c>
-      <c r="H57" s="120">
+      <c r="H59" s="120">
         <f>IF($C2="Affected fraction",H2,IF(H2=1,1,H2*0.9))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C58" s="39" t="s">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C60" s="39" t="s">
         <v>366</v>
       </c>
-      <c r="D58" s="120">
+      <c r="D60" s="120">
         <f>IF($C3="Affected fraction",D3,IF(D3=1,1,D3*0.9))</f>
         <v>0</v>
       </c>
-      <c r="E58" s="120">
+      <c r="E60" s="120">
         <f>IF($C3="Affected fraction",E3,IF(E3=1,1,E3*0.9))</f>
         <v>0</v>
       </c>
-      <c r="F58" s="120">
+      <c r="F60" s="120">
         <v>0.02</v>
       </c>
-      <c r="G58" s="120">
+      <c r="G60" s="120">
         <v>0.02</v>
       </c>
-      <c r="H58" s="120">
+      <c r="H60" s="120">
         <v>0.02</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C59" s="39" t="s">
-        <v>367</v>
-      </c>
-      <c r="D59" s="120">
-        <f>IF($C4="Affected fraction",D4,IF(D4=1,1,D4*0.9))</f>
-        <v>0</v>
-      </c>
-      <c r="E59" s="120">
-        <f>IF($C4="Affected fraction",E4,IF(E4=1,1,E4*0.9))</f>
-        <v>0</v>
-      </c>
-      <c r="F59" s="120">
-        <v>0.13</v>
-      </c>
-      <c r="G59" s="120">
-        <v>0.13</v>
-      </c>
-      <c r="H59" s="120">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="39" t="s">
-        <v>221</v>
-      </c>
-      <c r="B60" s="39" t="s">
-        <v>237</v>
-      </c>
-      <c r="C60" s="39" t="s">
-        <v>365</v>
-      </c>
-      <c r="D60" s="120">
-        <v>0</v>
-      </c>
-      <c r="E60" s="120">
-        <v>0</v>
-      </c>
-      <c r="F60" s="120">
-        <v>1</v>
-      </c>
-      <c r="G60" s="120">
-        <v>1</v>
-      </c>
-      <c r="H60" s="120">
-        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -38615,24 +38647,29 @@
         <v>367</v>
       </c>
       <c r="D61" s="120">
+        <f>IF($C4="Affected fraction",D4,IF(D4=1,1,D4*0.9))</f>
         <v>0</v>
       </c>
       <c r="E61" s="120">
+        <f>IF($C4="Affected fraction",E4,IF(E4=1,1,E4*0.9))</f>
         <v>0</v>
       </c>
       <c r="F61" s="120">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="G61" s="120">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="H61" s="120">
-        <v>0</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="39" t="s">
+        <v>221</v>
+      </c>
       <c r="B62" s="39" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C62" s="39" t="s">
         <v>365</v>
@@ -38674,11 +38711,8 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="39" t="s">
-        <v>214</v>
-      </c>
       <c r="B64" s="39" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C64" s="39" t="s">
         <v>365</v>
@@ -38720,8 +38754,11 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="39" t="s">
+        <v>214</v>
+      </c>
       <c r="B66" s="39" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C66" s="39" t="s">
         <v>365</v>
@@ -38763,11 +38800,8 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="39" t="s">
-        <v>234</v>
-      </c>
       <c r="B68" s="39" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C68" s="39" t="s">
         <v>365</v>
@@ -38793,49 +38827,44 @@
         <v>367</v>
       </c>
       <c r="D69" s="120">
-        <f t="shared" ref="D69:H81" si="0">IF($C14="Affected fraction",D14,IF(D14=1,1,D14*0.9))</f>
         <v>0</v>
       </c>
       <c r="E69" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F69" s="120">
-        <v>0.14000000000000001</v>
+        <v>0</v>
       </c>
       <c r="G69" s="120">
-        <v>0.14000000000000001</v>
+        <v>0</v>
       </c>
       <c r="H69" s="120">
-        <f>IF($C14="Affected fraction",H14,IF(H14=1,1,H14*0.9))</f>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="39" t="s">
+        <v>234</v>
+      </c>
       <c r="B70" s="39" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C70" s="39" t="s">
         <v>365</v>
       </c>
       <c r="D70" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E70" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F70" s="120">
-        <f>IF($C15="Affected fraction",F15,IF(F15=1,1,F15*0.9))</f>
         <v>1</v>
       </c>
       <c r="G70" s="120">
-        <f>IF($C15="Affected fraction",G15,IF(G15=1,1,G15*0.9))</f>
         <v>1</v>
       </c>
       <c r="H70" s="120">
-        <f>IF($C15="Affected fraction",H15,IF(H15=1,1,H15*0.9))</f>
         <v>0</v>
       </c>
     </row>
@@ -38844,7 +38873,7 @@
         <v>367</v>
       </c>
       <c r="D71" s="120">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D71:E73" si="0">IF($C14="Affected fraction",D14,IF(D14=1,1,D14*0.9))</f>
         <v>0</v>
       </c>
       <c r="E71" s="120">
@@ -38852,22 +38881,19 @@
         <v>0</v>
       </c>
       <c r="F71" s="120">
-        <v>0</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G71" s="120">
-        <v>0</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H71" s="120">
-        <f>IF($C16="Affected fraction",H16,IF(H16=1,1,H16*0.9))</f>
+        <f>IF($C14="Affected fraction",H14,IF(H14=1,1,H14*0.9))</f>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="39" t="s">
-        <v>199</v>
-      </c>
       <c r="B72" s="39" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C72" s="39" t="s">
         <v>365</v>
@@ -38881,16 +38907,16 @@
         <v>0</v>
       </c>
       <c r="F72" s="120">
-        <f>IF($C17="Affected fraction",F17,IF(F17=1,1,F17*0.9))</f>
+        <f>IF($C15="Affected fraction",F15,IF(F15=1,1,F15*0.9))</f>
         <v>1</v>
       </c>
       <c r="G72" s="120">
-        <f>IF($C17="Affected fraction",G17,IF(G17=1,1,G17*0.9))</f>
+        <f>IF($C15="Affected fraction",G15,IF(G15=1,1,G15*0.9))</f>
         <v>1</v>
       </c>
       <c r="H72" s="120">
-        <f>IF($C17="Affected fraction",H17,IF(H17=1,1,H17*0.9))</f>
-        <v>1</v>
+        <f>IF($C15="Affected fraction",H15,IF(H15=1,1,H15*0.9))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -38912,22 +38938,21 @@
         <v>0</v>
       </c>
       <c r="H73" s="120">
+        <f>IF($C16="Affected fraction",H16,IF(H16=1,1,H16*0.9))</f>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B74" s="39" t="s">
-        <v>238</v>
+        <v>368</v>
       </c>
       <c r="C74" s="39" t="s">
         <v>365</v>
       </c>
       <c r="D74" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E74" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F74" s="120">
@@ -38937,19 +38962,17 @@
         <v>1</v>
       </c>
       <c r="H74" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C75" s="39" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D75" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E75" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F75" s="120">
@@ -38964,117 +38987,107 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="39" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B76" s="39" t="s">
-        <v>102</v>
+        <v>237</v>
       </c>
       <c r="C76" s="39" t="s">
         <v>365</v>
       </c>
       <c r="D76" s="120">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>IF($C19="Affected fraction",D19,IF(D19=1,1,D19*0.9))</f>
+        <v>0</v>
       </c>
       <c r="E76" s="120">
-        <f t="shared" si="0"/>
+        <f>IF($C19="Affected fraction",E19,IF(E19=1,1,E19*0.9))</f>
         <v>0</v>
       </c>
       <c r="F76" s="120">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>IF($C19="Affected fraction",F19,IF(F19=1,1,F19*0.9))</f>
+        <v>1</v>
       </c>
       <c r="G76" s="120">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>IF($C19="Affected fraction",G19,IF(G19=1,1,G19*0.9))</f>
+        <v>1</v>
       </c>
       <c r="H76" s="120">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>IF($C19="Affected fraction",H19,IF(H19=1,1,H19*0.9))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C77" s="39" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D77" s="120">
-        <v>0.11</v>
+        <f t="shared" ref="D77:E80" si="1">IF($C20="Affected fraction",D20,IF(D20=1,1,D20*0.9))</f>
+        <v>0</v>
       </c>
       <c r="E77" s="120">
-        <f>IF($C22="Affected fraction",E22,IF(E22=1,1,E22*0.9))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F77" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G77" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H77" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="39" t="s">
-        <v>202</v>
-      </c>
       <c r="B78" s="39" t="s">
-        <v>102</v>
+        <v>238</v>
       </c>
       <c r="C78" s="39" t="s">
         <v>365</v>
       </c>
       <c r="D78" s="120">
-        <f>IF($C23="Affected fraction",D23,IF(D23=1,1,D23*0.9))</f>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="E78" s="120">
-        <f>IF($C23="Affected fraction",E23,IF(E23=1,1,E23*0.9))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F78" s="120">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" s="120">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" s="120">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C79" s="39" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D79" s="120">
-        <v>0.11</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="E79" s="120">
-        <f>IF($C24="Affected fraction",E24,IF(E24=1,1,E24*0.9))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F79" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G79" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H79" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="39" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B80" s="39" t="s">
         <v>102</v>
@@ -39083,23 +39096,23 @@
         <v>365</v>
       </c>
       <c r="D80" s="120">
-        <f>IF($C25="Affected fraction",D25,IF(D25=1,1,D25*0.9))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E80" s="120">
-        <f>IF($C25="Affected fraction",E25,IF(E25=1,1,E25*0.9))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F80" s="120">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F80:H85" si="2">IF($C23="Affected fraction",F23,IF(F23=1,1,F23*0.9))</f>
         <v>0</v>
       </c>
       <c r="G80" s="120">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H80" s="120">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39111,46 +39124,51 @@
         <v>0.11</v>
       </c>
       <c r="E81" s="120">
-        <f>IF($C26="Affected fraction",E26,IF(E26=1,1,E26*0.9))</f>
+        <f>IF($C24="Affected fraction",E24,IF(E24=1,1,E24*0.9))</f>
         <v>0</v>
       </c>
       <c r="F81" s="120">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G81" s="120">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H81" s="120">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="39" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="B82" s="39" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C82" s="39" t="s">
         <v>365</v>
       </c>
       <c r="D82" s="120">
+        <f>IF($C25="Affected fraction",D25,IF(D25=1,1,D25*0.9))</f>
         <v>1</v>
       </c>
       <c r="E82" s="120">
-        <v>1</v>
+        <f>IF($C25="Affected fraction",E25,IF(E25=1,1,E25*0.9))</f>
+        <v>0</v>
       </c>
       <c r="F82" s="120">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="G82" s="120">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="H82" s="120">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -39158,537 +39176,550 @@
         <v>366</v>
       </c>
       <c r="D83" s="120">
-        <v>7.0000000000000007E-2</v>
+        <v>0.11</v>
       </c>
       <c r="E83" s="120">
-        <v>7.0000000000000007E-2</v>
+        <f>IF($C26="Affected fraction",E26,IF(E26=1,1,E26*0.9))</f>
+        <v>0</v>
       </c>
       <c r="F83" s="120">
-        <v>7.0000000000000007E-2</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="G83" s="120">
-        <v>7.0000000000000007E-2</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="H83" s="120">
-        <v>7.0000000000000007E-2</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="B84" s="39" t="s">
+        <v>102</v>
+      </c>
       <c r="C84" s="39" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D84" s="120">
-        <v>0</v>
+        <f>IF($C27="Affected fraction",D27,IF(D27=1,1,D27*0.9))</f>
+        <v>1</v>
       </c>
       <c r="E84" s="120">
+        <f>IF($C27="Affected fraction",E27,IF(E27=1,1,E27*0.9))</f>
         <v>0</v>
       </c>
       <c r="F84" s="120">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G84" s="120">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H84" s="120">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="39" t="s">
-        <v>227</v>
-      </c>
-      <c r="B85" s="39" t="s">
+      <c r="C85" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="D85" s="120">
+        <v>0.11</v>
+      </c>
+      <c r="E85" s="120">
+        <f>IF($C28="Affected fraction",E28,IF(E28=1,1,E28*0.9))</f>
+        <v>0</v>
+      </c>
+      <c r="F85" s="120">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G85" s="120">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H85" s="120">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="39" t="s">
+        <v>226</v>
+      </c>
+      <c r="B86" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="C85" s="39" t="s">
+      <c r="C86" s="39" t="s">
         <v>365</v>
       </c>
-      <c r="D85" s="120">
-        <v>1</v>
-      </c>
-      <c r="E85" s="120">
-        <v>1</v>
-      </c>
-      <c r="F85" s="120">
-        <v>1</v>
-      </c>
-      <c r="G85" s="120">
-        <v>1</v>
-      </c>
-      <c r="H85" s="120">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C86" s="39" t="s">
-        <v>366</v>
-      </c>
       <c r="D86" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C87" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="D87" s="120">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E87" s="120">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F87" s="120">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G87" s="120">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H87" s="120">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C88" s="39" t="s">
         <v>367</v>
       </c>
-      <c r="D87" s="120">
-        <v>0</v>
-      </c>
-      <c r="E87" s="120">
-        <v>0</v>
-      </c>
-      <c r="F87" s="120">
-        <v>0</v>
-      </c>
-      <c r="G87" s="120">
-        <v>0</v>
-      </c>
-      <c r="H87" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="39" t="s">
-        <v>225</v>
-      </c>
-      <c r="B88" s="39" t="s">
+      <c r="D88" s="120">
+        <v>0</v>
+      </c>
+      <c r="E88" s="120">
+        <v>0</v>
+      </c>
+      <c r="F88" s="120">
+        <v>0</v>
+      </c>
+      <c r="G88" s="120">
+        <v>0</v>
+      </c>
+      <c r="H88" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="39" t="s">
+        <v>227</v>
+      </c>
+      <c r="B89" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="C88" s="39" t="s">
+      <c r="C89" s="39" t="s">
         <v>365</v>
       </c>
-      <c r="D88" s="120">
-        <v>1</v>
-      </c>
-      <c r="E88" s="120">
-        <v>1</v>
-      </c>
-      <c r="F88" s="120">
-        <v>1</v>
-      </c>
-      <c r="G88" s="120">
-        <v>1</v>
-      </c>
-      <c r="H88" s="120">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C89" s="39" t="s">
-        <v>366</v>
-      </c>
       <c r="D89" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E89" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C90" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="D90" s="120">
+        <v>0</v>
+      </c>
+      <c r="E90" s="120">
+        <v>0</v>
+      </c>
+      <c r="F90" s="120">
+        <v>0</v>
+      </c>
+      <c r="G90" s="120">
+        <v>0</v>
+      </c>
+      <c r="H90" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C91" s="39" t="s">
         <v>367</v>
       </c>
-      <c r="D90" s="120">
-        <v>0</v>
-      </c>
-      <c r="E90" s="120">
-        <v>0</v>
-      </c>
-      <c r="F90" s="120">
-        <v>0</v>
-      </c>
-      <c r="G90" s="120">
-        <v>0</v>
-      </c>
-      <c r="H90" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="39" t="s">
-        <v>224</v>
-      </c>
-      <c r="B91" s="39" t="s">
+      <c r="D91" s="120">
+        <v>0</v>
+      </c>
+      <c r="E91" s="120">
+        <v>0</v>
+      </c>
+      <c r="F91" s="120">
+        <v>0</v>
+      </c>
+      <c r="G91" s="120">
+        <v>0</v>
+      </c>
+      <c r="H91" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="39" t="s">
+        <v>225</v>
+      </c>
+      <c r="B92" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="C91" s="39" t="s">
+      <c r="C92" s="39" t="s">
         <v>365</v>
       </c>
-      <c r="D91" s="120">
-        <v>1</v>
-      </c>
-      <c r="E91" s="120">
-        <v>1</v>
-      </c>
-      <c r="F91" s="120">
-        <v>1</v>
-      </c>
-      <c r="G91" s="120">
-        <v>1</v>
-      </c>
-      <c r="H91" s="120">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C92" s="39" t="s">
-        <v>366</v>
-      </c>
       <c r="D92" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C93" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="D93" s="120">
+        <v>0</v>
+      </c>
+      <c r="E93" s="120">
+        <v>0</v>
+      </c>
+      <c r="F93" s="120">
+        <v>0</v>
+      </c>
+      <c r="G93" s="120">
+        <v>0</v>
+      </c>
+      <c r="H93" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C94" s="39" t="s">
         <v>367</v>
       </c>
-      <c r="D93" s="120">
-        <v>0</v>
-      </c>
-      <c r="E93" s="120">
-        <v>0</v>
-      </c>
-      <c r="F93" s="120">
-        <v>0</v>
-      </c>
-      <c r="G93" s="120">
-        <v>0</v>
-      </c>
-      <c r="H93" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="39" t="s">
-        <v>223</v>
-      </c>
-      <c r="B94" s="39" t="s">
+      <c r="D94" s="120">
+        <v>0</v>
+      </c>
+      <c r="E94" s="120">
+        <v>0</v>
+      </c>
+      <c r="F94" s="120">
+        <v>0</v>
+      </c>
+      <c r="G94" s="120">
+        <v>0</v>
+      </c>
+      <c r="H94" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="39" t="s">
+        <v>224</v>
+      </c>
+      <c r="B95" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="C94" s="39" t="s">
+      <c r="C95" s="39" t="s">
         <v>365</v>
       </c>
-      <c r="D94" s="120">
-        <v>1</v>
-      </c>
-      <c r="E94" s="120">
-        <v>1</v>
-      </c>
-      <c r="F94" s="120">
-        <v>1</v>
-      </c>
-      <c r="G94" s="120">
-        <v>1</v>
-      </c>
-      <c r="H94" s="120">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C95" s="39" t="s">
-        <v>366</v>
-      </c>
       <c r="D95" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C96" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="D96" s="120">
+        <v>0</v>
+      </c>
+      <c r="E96" s="120">
+        <v>0</v>
+      </c>
+      <c r="F96" s="120">
+        <v>0</v>
+      </c>
+      <c r="G96" s="120">
+        <v>0</v>
+      </c>
+      <c r="H96" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C97" s="39" t="s">
         <v>367</v>
       </c>
-      <c r="D96" s="120">
-        <v>0</v>
-      </c>
-      <c r="E96" s="120">
-        <v>0</v>
-      </c>
-      <c r="F96" s="120">
-        <v>0</v>
-      </c>
-      <c r="G96" s="120">
-        <v>0</v>
-      </c>
-      <c r="H96" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="39" t="s">
-        <v>229</v>
-      </c>
-      <c r="B97" s="39" t="s">
+      <c r="D97" s="120">
+        <v>0</v>
+      </c>
+      <c r="E97" s="120">
+        <v>0</v>
+      </c>
+      <c r="F97" s="120">
+        <v>0</v>
+      </c>
+      <c r="G97" s="120">
+        <v>0</v>
+      </c>
+      <c r="H97" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="39" t="s">
+        <v>223</v>
+      </c>
+      <c r="B98" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="C97" s="39" t="s">
+      <c r="C98" s="39" t="s">
         <v>365</v>
       </c>
-      <c r="D97" s="120">
-        <f>IF($C42="Affected fraction",D42,IF(D42=1,1,D42*0.9))</f>
-        <v>0</v>
-      </c>
-      <c r="E97" s="120">
-        <f>IF($C42="Affected fraction",E42,IF(E42=1,1,E42*0.9))</f>
-        <v>1</v>
-      </c>
-      <c r="F97" s="120">
-        <f>IF($C42="Affected fraction",F42,IF(F42=1,1,F42*0.9))</f>
-        <v>1</v>
-      </c>
-      <c r="G97" s="120">
-        <f>IF($C42="Affected fraction",G42,IF(G42=1,1,G42*0.9))</f>
-        <v>1</v>
-      </c>
-      <c r="H97" s="120">
-        <f>IF($C42="Affected fraction",H42,IF(H42=1,1,H42*0.9))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C98" s="39" t="s">
-        <v>366</v>
-      </c>
       <c r="D98" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C99" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="D99" s="120">
+        <v>0</v>
+      </c>
+      <c r="E99" s="120">
+        <v>0</v>
+      </c>
+      <c r="F99" s="120">
+        <v>0</v>
+      </c>
+      <c r="G99" s="120">
+        <v>0</v>
+      </c>
+      <c r="H99" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C100" s="39" t="s">
         <v>367</v>
       </c>
-      <c r="D99" s="120">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="E99" s="120">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="F99" s="120">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G99" s="120">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="H99" s="120">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B100" s="39" t="s">
-        <v>106</v>
-      </c>
-      <c r="C100" s="39" t="s">
+      <c r="D100" s="120">
+        <v>0</v>
+      </c>
+      <c r="E100" s="120">
+        <v>0</v>
+      </c>
+      <c r="F100" s="120">
+        <v>0</v>
+      </c>
+      <c r="G100" s="120">
+        <v>0</v>
+      </c>
+      <c r="H100" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="B101" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="C101" s="39" t="s">
         <v>365</v>
       </c>
-      <c r="D100" s="120">
-        <v>0</v>
-      </c>
-      <c r="E100" s="120">
-        <v>1</v>
-      </c>
-      <c r="F100" s="120">
-        <v>1</v>
-      </c>
-      <c r="G100" s="120">
-        <v>1</v>
-      </c>
-      <c r="H100" s="120">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C101" s="39" t="s">
-        <v>366</v>
-      </c>
       <c r="D101" s="120">
+        <f>IF($C44="Affected fraction",D44,IF(D44=1,1,D44*0.9))</f>
         <v>0</v>
       </c>
       <c r="E101" s="120">
-        <v>0</v>
+        <f>IF($C44="Affected fraction",E44,IF(E44=1,1,E44*0.9))</f>
+        <v>1</v>
       </c>
       <c r="F101" s="120">
-        <v>0</v>
+        <f>IF($C44="Affected fraction",F44,IF(F44=1,1,F44*0.9))</f>
+        <v>1</v>
       </c>
       <c r="G101" s="120">
-        <v>0</v>
+        <f>IF($C44="Affected fraction",G44,IF(G44=1,1,G44*0.9))</f>
+        <v>1</v>
       </c>
       <c r="H101" s="120">
-        <v>0</v>
+        <f>IF($C44="Affected fraction",H44,IF(H44=1,1,H44*0.9))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C102" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="D102" s="120">
+        <v>0</v>
+      </c>
+      <c r="E102" s="120">
+        <v>0</v>
+      </c>
+      <c r="F102" s="120">
+        <v>0</v>
+      </c>
+      <c r="G102" s="120">
+        <v>0</v>
+      </c>
+      <c r="H102" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C103" s="39" t="s">
         <v>367</v>
       </c>
-      <c r="D102" s="120">
-        <v>0</v>
-      </c>
-      <c r="E102" s="120">
-        <v>0</v>
-      </c>
-      <c r="F102" s="120">
-        <v>0</v>
-      </c>
-      <c r="G102" s="120">
-        <v>0</v>
-      </c>
-      <c r="H102" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="39" t="s">
-        <v>220</v>
-      </c>
-      <c r="B103" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="C103" s="39" t="s">
+      <c r="D103" s="120">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E103" s="120">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F103" s="120">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G103" s="120">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H103" s="120">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B104" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="C104" s="39" t="s">
         <v>365</v>
       </c>
-      <c r="D103" s="120">
-        <v>1</v>
-      </c>
-      <c r="E103" s="120">
-        <v>1</v>
-      </c>
-      <c r="F103" s="120">
-        <v>1</v>
-      </c>
-      <c r="G103" s="120">
-        <v>1</v>
-      </c>
-      <c r="H103" s="120">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C104" s="39" t="s">
+      <c r="D104" s="120">
+        <v>0</v>
+      </c>
+      <c r="E104" s="120">
+        <v>1</v>
+      </c>
+      <c r="F104" s="120">
+        <v>1</v>
+      </c>
+      <c r="G104" s="120">
+        <v>1</v>
+      </c>
+      <c r="H104" s="120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C105" s="39" t="s">
         <v>366</v>
       </c>
-      <c r="D104" s="120">
-        <v>0.51</v>
-      </c>
-      <c r="E104" s="120">
-        <v>0.51</v>
-      </c>
-      <c r="F104" s="120">
-        <v>0.51</v>
-      </c>
-      <c r="G104" s="120">
-        <v>0.51</v>
-      </c>
-      <c r="H104" s="120">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="39" t="s">
-        <v>228</v>
-      </c>
-      <c r="B105" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="C105" s="39" t="s">
-        <v>365</v>
-      </c>
       <c r="D105" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F105" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G105" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H105" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C106" s="39" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D106" s="120">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="E106" s="120">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="F106" s="120">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="G106" s="120">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="H106" s="120">
-        <v>0.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="39" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B107" s="39" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C107" s="39" t="s">
         <v>365</v>
@@ -39697,16 +39728,16 @@
         <v>1</v>
       </c>
       <c r="E107" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G107" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -39714,201 +39745,202 @@
         <v>366</v>
       </c>
       <c r="D108" s="120">
+        <v>0.51</v>
+      </c>
+      <c r="E108" s="120">
+        <v>0.51</v>
+      </c>
+      <c r="F108" s="120">
+        <v>0.51</v>
+      </c>
+      <c r="G108" s="120">
+        <v>0.51</v>
+      </c>
+      <c r="H108" s="120">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="B109" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="C109" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="D109" s="120">
+        <v>1</v>
+      </c>
+      <c r="E109" s="120">
+        <v>1</v>
+      </c>
+      <c r="F109" s="120">
+        <v>1</v>
+      </c>
+      <c r="G109" s="120">
+        <v>1</v>
+      </c>
+      <c r="H109" s="120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C110" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="D110" s="120">
+        <v>0.62</v>
+      </c>
+      <c r="E110" s="120">
+        <v>0.62</v>
+      </c>
+      <c r="F110" s="120">
+        <v>0.62</v>
+      </c>
+      <c r="G110" s="120">
+        <v>0.62</v>
+      </c>
+      <c r="H110" s="120">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="39" t="s">
+        <v>213</v>
+      </c>
+      <c r="B111" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="C111" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="D111" s="120">
+        <v>1</v>
+      </c>
+      <c r="E111" s="120">
+        <v>0</v>
+      </c>
+      <c r="F111" s="120">
+        <v>0</v>
+      </c>
+      <c r="G111" s="120">
+        <v>0</v>
+      </c>
+      <c r="H111" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C112" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="D112" s="120">
         <v>0.14000000000000001</v>
       </c>
-      <c r="E108" s="120">
-        <v>0</v>
-      </c>
-      <c r="F108" s="120">
-        <v>0</v>
-      </c>
-      <c r="G108" s="120">
-        <v>0</v>
-      </c>
-      <c r="H108" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" s="106" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A110" s="109" t="s">
+      <c r="E112" s="120">
+        <v>0</v>
+      </c>
+      <c r="F112" s="120">
+        <v>0</v>
+      </c>
+      <c r="G112" s="120">
+        <v>0</v>
+      </c>
+      <c r="H112" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" s="106" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A114" s="109" t="s">
         <v>363</v>
       </c>
-      <c r="B110" s="110"/>
-      <c r="C110" s="110"/>
-      <c r="D110" s="124"/>
-      <c r="E110" s="124"/>
-      <c r="F110" s="124"/>
-      <c r="G110" s="124"/>
-      <c r="H110" s="124"/>
-    </row>
-    <row r="111" spans="1:8" ht="13" x14ac:dyDescent="0.3">
-      <c r="A111" s="29" t="s">
+      <c r="B114" s="110"/>
+      <c r="C114" s="110"/>
+      <c r="D114" s="124"/>
+      <c r="E114" s="124"/>
+      <c r="F114" s="124"/>
+      <c r="G114" s="124"/>
+      <c r="H114" s="124"/>
+    </row>
+    <row r="115" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+      <c r="A115" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="B111" s="29" t="s">
+      <c r="B115" s="29" t="s">
         <v>364</v>
       </c>
-      <c r="C111" s="96" t="s">
+      <c r="C115" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="D111" s="4" t="s">
+      <c r="D115" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E111" s="4" t="s">
+      <c r="E115" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="F111" s="4" t="s">
+      <c r="F115" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="G111" s="4" t="s">
+      <c r="G115" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="H111" s="4" t="s">
+      <c r="H115" s="4" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="39" t="s">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="39" t="s">
         <v>222</v>
       </c>
-      <c r="B112" s="39" t="s">
+      <c r="B116" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="C112" s="39" t="s">
+      <c r="C116" s="39" t="s">
         <v>365</v>
       </c>
-      <c r="D112" s="120">
-        <f t="shared" ref="D112:E114" si="1">IF($C2="Affected fraction",D2,IF(D2=1,1,D2*1.05))</f>
-        <v>0</v>
-      </c>
-      <c r="E112" s="120">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F112" s="120">
-        <f>IF($C57="Affected fraction",F57,IF(F57=1,1,F57*0.9))</f>
-        <v>1</v>
-      </c>
-      <c r="G112" s="120">
-        <f>IF($C57="Affected fraction",G57,IF(G57=1,1,G57*0.9))</f>
-        <v>1</v>
-      </c>
-      <c r="H112" s="120">
-        <f>IF($C57="Affected fraction",H57,IF(H57=1,1,H57*0.9))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C113" s="39" t="s">
+      <c r="D116" s="120">
+        <f t="shared" ref="D116:E118" si="3">IF($C2="Affected fraction",D2,IF(D2=1,1,D2*1.05))</f>
+        <v>0</v>
+      </c>
+      <c r="E116" s="120">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F116" s="120">
+        <f>IF($C59="Affected fraction",F59,IF(F59=1,1,F59*0.9))</f>
+        <v>1</v>
+      </c>
+      <c r="G116" s="120">
+        <f>IF($C59="Affected fraction",G59,IF(G59=1,1,G59*0.9))</f>
+        <v>1</v>
+      </c>
+      <c r="H116" s="120">
+        <f>IF($C59="Affected fraction",H59,IF(H59=1,1,H59*0.9))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C117" s="39" t="s">
         <v>366</v>
       </c>
-      <c r="D113" s="120">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E113" s="120">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F113" s="120">
+      <c r="D117" s="120">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E117" s="120">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F117" s="120">
         <v>0.21</v>
       </c>
-      <c r="G113" s="120">
+      <c r="G117" s="120">
         <v>0.21</v>
       </c>
-      <c r="H113" s="120">
+      <c r="H117" s="120">
         <v>0.21</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C114" s="39" t="s">
-        <v>367</v>
-      </c>
-      <c r="D114" s="120">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E114" s="120">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F114" s="120">
-        <v>0.18</v>
-      </c>
-      <c r="G114" s="120">
-        <v>0.18</v>
-      </c>
-      <c r="H114" s="120">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" s="39" t="s">
-        <v>221</v>
-      </c>
-      <c r="B115" s="39" t="s">
-        <v>237</v>
-      </c>
-      <c r="C115" s="39" t="s">
-        <v>365</v>
-      </c>
-      <c r="D115" s="120">
-        <v>0</v>
-      </c>
-      <c r="E115" s="120">
-        <v>0</v>
-      </c>
-      <c r="F115" s="120">
-        <v>1</v>
-      </c>
-      <c r="G115" s="120">
-        <v>1</v>
-      </c>
-      <c r="H115" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C116" s="39" t="s">
-        <v>367</v>
-      </c>
-      <c r="D116" s="120">
-        <v>0</v>
-      </c>
-      <c r="E116" s="120">
-        <v>0</v>
-      </c>
-      <c r="F116" s="120">
-        <v>0</v>
-      </c>
-      <c r="G116" s="120">
-        <v>0</v>
-      </c>
-      <c r="H116" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B117" s="39" t="s">
-        <v>238</v>
-      </c>
-      <c r="C117" s="39" t="s">
-        <v>365</v>
-      </c>
-      <c r="D117" s="120">
-        <v>0</v>
-      </c>
-      <c r="E117" s="120">
-        <v>0</v>
-      </c>
-      <c r="F117" s="120">
-        <v>1</v>
-      </c>
-      <c r="G117" s="120">
-        <v>1</v>
-      </c>
-      <c r="H117" s="120">
-        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -39916,24 +39948,26 @@
         <v>367</v>
       </c>
       <c r="D118" s="120">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E118" s="120">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F118" s="120">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="G118" s="120">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="H118" s="120">
-        <v>0</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="39" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B119" s="39" t="s">
         <v>237</v>
@@ -40022,7 +40056,7 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="39" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="B123" s="39" t="s">
         <v>237</v>
@@ -40051,21 +40085,18 @@
         <v>367</v>
       </c>
       <c r="D124" s="120">
-        <f t="shared" ref="D124:H136" si="2">IF($C14="Affected fraction",D14,IF(D14=1,1,D14*1.05))</f>
         <v>0</v>
       </c>
       <c r="E124" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F124" s="120">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="G124" s="120">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="H124" s="120">
-        <f>IF($C14="Affected fraction",H14,IF(H14=1,1,H14*1.05))</f>
         <v>0</v>
       </c>
     </row>
@@ -40077,23 +40108,18 @@
         <v>365</v>
       </c>
       <c r="D125" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E125" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F125" s="120">
-        <f>IF($C15="Affected fraction",F15,IF(F15=1,1,F15*1.05))</f>
         <v>1</v>
       </c>
       <c r="G125" s="120">
-        <f>IF($C15="Affected fraction",G15,IF(G15=1,1,G15*1.05))</f>
         <v>1</v>
       </c>
       <c r="H125" s="120">
-        <f>IF($C15="Affected fraction",H15,IF(H15=1,1,H15*1.05))</f>
         <v>0</v>
       </c>
     </row>
@@ -40102,27 +40128,24 @@
         <v>367</v>
       </c>
       <c r="D126" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E126" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F126" s="120">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G126" s="120">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H126" s="120">
-        <f>IF($C16="Affected fraction",H16,IF(H16=1,1,H16*1.05))</f>
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="39" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="B127" s="39" t="s">
         <v>237</v>
@@ -40131,24 +40154,19 @@
         <v>365</v>
       </c>
       <c r="D127" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E127" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F127" s="120">
-        <f>IF($C17="Affected fraction",F17,IF(F17=1,1,F17*1.05))</f>
         <v>1</v>
       </c>
       <c r="G127" s="120">
-        <f>IF($C17="Affected fraction",G17,IF(G17=1,1,G17*1.05))</f>
         <v>1</v>
       </c>
       <c r="H127" s="120">
-        <f>IF($C17="Affected fraction",H17,IF(H17=1,1,H17*1.05))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -40156,20 +40174,21 @@
         <v>367</v>
       </c>
       <c r="D128" s="120">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="D128:E130" si="4">IF($C14="Affected fraction",D14,IF(D14=1,1,D14*1.05))</f>
         <v>0</v>
       </c>
       <c r="E128" s="120">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F128" s="120">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="G128" s="120">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="H128" s="120">
+        <f>IF($C14="Affected fraction",H14,IF(H14=1,1,H14*1.05))</f>
         <v>0</v>
       </c>
     </row>
@@ -40181,21 +40200,24 @@
         <v>365</v>
       </c>
       <c r="D129" s="120">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E129" s="120">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F129" s="120">
+        <f>IF($C15="Affected fraction",F15,IF(F15=1,1,F15*1.05))</f>
         <v>1</v>
       </c>
       <c r="G129" s="120">
+        <f>IF($C15="Affected fraction",G15,IF(G15=1,1,G15*1.05))</f>
         <v>1</v>
       </c>
       <c r="H129" s="120">
-        <v>1</v>
+        <f>IF($C15="Affected fraction",H15,IF(H15=1,1,H15*1.05))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -40203,51 +40225,44 @@
         <v>367</v>
       </c>
       <c r="D130" s="120">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E130" s="120">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F130" s="120">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G130" s="120">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H130" s="120">
+        <f>IF($C16="Affected fraction",H16,IF(H16=1,1,H16*1.05))</f>
         <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A131" s="39" t="s">
-        <v>204</v>
-      </c>
       <c r="B131" s="39" t="s">
-        <v>102</v>
+        <v>368</v>
       </c>
       <c r="C131" s="39" t="s">
         <v>365</v>
       </c>
       <c r="D131" s="120">
-        <f>IF($C76="Affected fraction",D76,IF(D76=1,1,D76*0.9))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E131" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F131" s="120">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G131" s="120">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H131" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -40256,159 +40271,150 @@
         <v>366</v>
       </c>
       <c r="D132" s="120">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="E132" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F132" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G132" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H132" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="39" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B133" s="39" t="s">
-        <v>102</v>
+        <v>237</v>
       </c>
       <c r="C133" s="39" t="s">
         <v>365</v>
       </c>
       <c r="D133" s="120">
-        <f>IF($C78="Affected fraction",D78,IF(D78=1,1,D78*0.9))</f>
-        <v>1</v>
+        <f>IF($C19="Affected fraction",D19,IF(D19=1,1,D19*1.05))</f>
+        <v>0</v>
       </c>
       <c r="E133" s="120">
-        <f t="shared" si="2"/>
+        <f>IF($C19="Affected fraction",E19,IF(E19=1,1,E19*1.05))</f>
         <v>0</v>
       </c>
       <c r="F133" s="120">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>IF($C19="Affected fraction",F19,IF(F19=1,1,F19*1.05))</f>
+        <v>1</v>
       </c>
       <c r="G133" s="120">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>IF($C19="Affected fraction",G19,IF(G19=1,1,G19*1.05))</f>
+        <v>1</v>
       </c>
       <c r="H133" s="120">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>IF($C19="Affected fraction",H19,IF(H19=1,1,H19*1.05))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C134" s="39" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D134" s="120">
-        <v>0.16</v>
+        <f t="shared" ref="D134:E136" si="5">IF($C20="Affected fraction",D20,IF(D20=1,1,D20*1.05))</f>
+        <v>0</v>
       </c>
       <c r="E134" s="120">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F134" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G134" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H134" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A135" s="39" t="s">
-        <v>203</v>
-      </c>
       <c r="B135" s="39" t="s">
-        <v>102</v>
+        <v>238</v>
       </c>
       <c r="C135" s="39" t="s">
         <v>365</v>
       </c>
       <c r="D135" s="120">
-        <f>IF($C80="Affected fraction",D80,IF(D80=1,1,D80*0.9))</f>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="E135" s="120">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F135" s="120">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G135" s="120">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H135" s="120">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C136" s="39" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D136" s="120">
-        <v>0.16</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="E136" s="120">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F136" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G136" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H136" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="39" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="B137" s="39" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C137" s="39" t="s">
         <v>365</v>
       </c>
       <c r="D137" s="120">
+        <f>IF($C80="Affected fraction",D80,IF(D80=1,1,D80*0.9))</f>
         <v>1</v>
       </c>
       <c r="E137" s="120">
-        <v>1</v>
+        <f t="shared" ref="E137:H142" si="6">IF($C23="Affected fraction",E23,IF(E23=1,1,E23*1.05))</f>
+        <v>0</v>
       </c>
       <c r="F137" s="120">
-        <v>1</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="G137" s="120">
-        <v>1</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="H137" s="120">
-        <v>1</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -40416,110 +40422,138 @@
         <v>366</v>
       </c>
       <c r="D138" s="120">
-        <v>0.51</v>
+        <v>0.16</v>
       </c>
       <c r="E138" s="120">
-        <v>0.51</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="F138" s="120">
-        <v>0.51</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="G138" s="120">
-        <v>0.51</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="H138" s="120">
-        <v>0.51</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="B139" s="39" t="s">
+        <v>102</v>
+      </c>
       <c r="C139" s="39" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D139" s="120">
-        <v>0</v>
+        <f>IF($C82="Affected fraction",D82,IF(D82=1,1,D82*0.9))</f>
+        <v>1</v>
       </c>
       <c r="E139" s="120">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F139" s="120">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G139" s="120">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H139" s="120">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A140" s="39" t="s">
-        <v>227</v>
-      </c>
-      <c r="B140" s="39" t="s">
-        <v>105</v>
-      </c>
       <c r="C140" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="D140" s="120">
+        <v>0.16</v>
+      </c>
+      <c r="E140" s="120">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F140" s="120">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G140" s="120">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H140" s="120">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="B141" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="C141" s="39" t="s">
         <v>365</v>
       </c>
-      <c r="D140" s="120">
-        <v>1</v>
-      </c>
-      <c r="E140" s="120">
-        <v>1</v>
-      </c>
-      <c r="F140" s="120">
-        <v>1</v>
-      </c>
-      <c r="G140" s="120">
-        <v>1</v>
-      </c>
-      <c r="H140" s="120">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C141" s="39" t="s">
-        <v>366</v>
-      </c>
       <c r="D141" s="120">
-        <v>0</v>
+        <f>IF($C84="Affected fraction",D84,IF(D84=1,1,D84*0.9))</f>
+        <v>1</v>
       </c>
       <c r="E141" s="120">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F141" s="120">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G141" s="120">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H141" s="120">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C142" s="39" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D142" s="120">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="E142" s="120">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F142" s="120">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G142" s="120">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H142" s="120">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="39" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B143" s="39" t="s">
         <v>105</v>
@@ -40548,19 +40582,19 @@
         <v>366</v>
       </c>
       <c r="D144" s="120">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="E144" s="120">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="F144" s="120">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="G144" s="120">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="H144" s="120">
-        <v>0</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
@@ -40585,7 +40619,7 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="39" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B146" s="39" t="s">
         <v>105</v>
@@ -40651,7 +40685,7 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="39" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B149" s="39" t="s">
         <v>105</v>
@@ -40717,7 +40751,7 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="39" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B152" s="39" t="s">
         <v>105</v>
@@ -40726,23 +40760,18 @@
         <v>365</v>
       </c>
       <c r="D152" s="120">
-        <f t="shared" ref="D152:H153" si="3">IF($C97="Affected fraction",D97,IF(D97=1,1,D97*0.9))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E152" s="120">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F152" s="120">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G152" s="120">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H152" s="120">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -40751,23 +40780,18 @@
         <v>366</v>
       </c>
       <c r="D153" s="120">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E153" s="120">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F153" s="120">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G153" s="120">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H153" s="120">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40776,30 +40800,33 @@
         <v>367</v>
       </c>
       <c r="D154" s="120">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E154" s="120">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F154" s="120">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G154" s="120">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H154" s="120">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" s="39" t="s">
+        <v>223</v>
+      </c>
       <c r="B155" s="39" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C155" s="39" t="s">
         <v>365</v>
       </c>
       <c r="D155" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E155" s="120">
         <v>1</v>
@@ -40856,7 +40883,7 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="39" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B158" s="39" t="s">
         <v>105</v>
@@ -40865,18 +40892,23 @@
         <v>365</v>
       </c>
       <c r="D158" s="120">
-        <v>1</v>
+        <f t="shared" ref="D158:H159" si="7">IF($C101="Affected fraction",D101,IF(D101=1,1,D101*0.9))</f>
+        <v>0</v>
       </c>
       <c r="E158" s="120">
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F158" s="120">
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G158" s="120">
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H158" s="120">
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -40885,79 +40917,75 @@
         <v>366</v>
       </c>
       <c r="D159" s="120">
-        <v>0.8</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="E159" s="120">
-        <v>0.8</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="F159" s="120">
-        <v>0.8</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="G159" s="120">
-        <v>0.8</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="H159" s="120">
-        <v>0.8</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A160" s="39" t="s">
-        <v>228</v>
-      </c>
-      <c r="B160" s="39" t="s">
-        <v>105</v>
-      </c>
       <c r="C160" s="39" t="s">
+        <v>367</v>
+      </c>
+      <c r="D160" s="120">
+        <v>0.1</v>
+      </c>
+      <c r="E160" s="120">
+        <v>0.1</v>
+      </c>
+      <c r="F160" s="120">
+        <v>0.1</v>
+      </c>
+      <c r="G160" s="120">
+        <v>0.1</v>
+      </c>
+      <c r="H160" s="120">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B161" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="C161" s="39" t="s">
         <v>365</v>
       </c>
-      <c r="D160" s="120">
-        <v>1</v>
-      </c>
-      <c r="E160" s="120">
-        <v>1</v>
-      </c>
-      <c r="F160" s="120">
-        <v>1</v>
-      </c>
-      <c r="G160" s="120">
-        <v>1</v>
-      </c>
-      <c r="H160" s="120">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C161" s="39" t="s">
+      <c r="D161" s="120">
+        <v>0</v>
+      </c>
+      <c r="E161" s="120">
+        <v>1</v>
+      </c>
+      <c r="F161" s="120">
+        <v>1</v>
+      </c>
+      <c r="G161" s="120">
+        <v>1</v>
+      </c>
+      <c r="H161" s="120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C162" s="39" t="s">
         <v>366</v>
       </c>
-      <c r="D161" s="120">
-        <v>0.85</v>
-      </c>
-      <c r="E161" s="120">
-        <v>0.85</v>
-      </c>
-      <c r="F161" s="120">
-        <v>0.85</v>
-      </c>
-      <c r="G161" s="120">
-        <v>0.85</v>
-      </c>
-      <c r="H161" s="120">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A162" s="39" t="s">
-        <v>213</v>
-      </c>
-      <c r="B162" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="C162" s="39" t="s">
-        <v>365</v>
-      </c>
       <c r="D162" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E162" s="120">
         <v>0</v>
@@ -40974,26 +41002,164 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C163" s="39" t="s">
+        <v>367</v>
+      </c>
+      <c r="D163" s="120">
+        <v>0</v>
+      </c>
+      <c r="E163" s="120">
+        <v>0</v>
+      </c>
+      <c r="F163" s="120">
+        <v>0</v>
+      </c>
+      <c r="G163" s="120">
+        <v>0</v>
+      </c>
+      <c r="H163" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" s="39" t="s">
+        <v>220</v>
+      </c>
+      <c r="B164" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="C164" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="D164" s="120">
+        <v>1</v>
+      </c>
+      <c r="E164" s="120">
+        <v>1</v>
+      </c>
+      <c r="F164" s="120">
+        <v>1</v>
+      </c>
+      <c r="G164" s="120">
+        <v>1</v>
+      </c>
+      <c r="H164" s="120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C165" s="39" t="s">
         <v>366</v>
       </c>
-      <c r="D163" s="120">
+      <c r="D165" s="120">
+        <v>0.8</v>
+      </c>
+      <c r="E165" s="120">
+        <v>0.8</v>
+      </c>
+      <c r="F165" s="120">
+        <v>0.8</v>
+      </c>
+      <c r="G165" s="120">
+        <v>0.8</v>
+      </c>
+      <c r="H165" s="120">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="B166" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="C166" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="D166" s="120">
+        <v>1</v>
+      </c>
+      <c r="E166" s="120">
+        <v>1</v>
+      </c>
+      <c r="F166" s="120">
+        <v>1</v>
+      </c>
+      <c r="G166" s="120">
+        <v>1</v>
+      </c>
+      <c r="H166" s="120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C167" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="D167" s="120">
+        <v>0.85</v>
+      </c>
+      <c r="E167" s="120">
+        <v>0.85</v>
+      </c>
+      <c r="F167" s="120">
+        <v>0.85</v>
+      </c>
+      <c r="G167" s="120">
+        <v>0.85</v>
+      </c>
+      <c r="H167" s="120">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" s="39" t="s">
+        <v>213</v>
+      </c>
+      <c r="B168" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="C168" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="D168" s="120">
+        <v>1</v>
+      </c>
+      <c r="E168" s="120">
+        <v>0</v>
+      </c>
+      <c r="F168" s="120">
+        <v>0</v>
+      </c>
+      <c r="G168" s="120">
+        <v>0</v>
+      </c>
+      <c r="H168" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C169" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="D169" s="120">
         <v>0.47</v>
       </c>
-      <c r="E163" s="120">
-        <v>0</v>
-      </c>
-      <c r="F163" s="120">
-        <v>0</v>
-      </c>
-      <c r="G163" s="120">
-        <v>0</v>
-      </c>
-      <c r="H163" s="120">
+      <c r="E169" s="120">
+        <v>0</v>
+      </c>
+      <c r="F169" s="120">
+        <v>0</v>
+      </c>
+      <c r="G169" s="120">
+        <v>0</v>
+      </c>
+      <c r="H169" s="120">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="9DiCLuXjDs5rPJ3tPSHMDNjM5zep/2LkORzEGEepfa9jO3vnpmMHw2nD96P8yKqvcDw23XGK2mHNTNlFyBDppw==" saltValue="3Bn8zzvUDIr7+6cuqih1Sw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="zOkiB1OmAzQuXPtpkcOA7TwcqhDwW9DcMY0wUhOePk1WKjnCO7cT7nbYbNt2eKvusaANDpux9PC+HpGEJfEg8g==" saltValue="nDEDdTkkF3/19yeQzMQ9Ag==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -41634,7 +41800,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="pKkYeBOWcwRftF7kNJNvHBWAsxEyOe1vsMQN6SbtOjeApKAN8z2e7+lqcn3iLZM3k/HK9uDikO+iVeUGHtVm8Q==" saltValue="zIQo6VwZBujt99ZGJRGdbA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="xYo42p3sTptkGB65EsRaZaHhsqzRq0obOurTg1ZjNDmo6EhU3k+HhegO0FDuK9FkDrZ9bmdI3F0VQTYUEDAzjw==" saltValue="bHB82szahGSRo42fd1JvFA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -42067,7 +42233,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="r/PmrWGf2c7crry7ki2tXRkVsaXcfzcj9wKouysw4UVivzZZhkZho9LJ06hc8WDGfPIJknKYI4wRNF3SoUEyOA==" saltValue="lF//wjYCe9Nh/pN1a5wJlg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="CTjgU9tBGPnoUG0vyEvqAecwFw8Tm+MH02x1Zj0Qb/kfC2m/FW0ZJRWGa1HIXxv/Wh90C0o4Vp1nH2H5WQD13g==" saltValue="DSokCl97bjZx4drO9L+aEg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="69" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
@@ -42486,7 +42652,7 @@
       <c r="G17" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="f3C7UcFh4oCb+qYiYBuFSEDYS8+oYAaEbq9kHu8g45ZRrP949m/YHBA/A9Gi+Qi8JJFO3Pqh22iVeW1HQO1ubg==" saltValue="by/1ySE5H9kwzNcvZ1jvhA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="6BjUsVJ+EOC+9NYw54f+/6BZnA4Mv9THgyeFBQy2aSM1BZaN3gfuB+aXeeVULlGrPvIVatciCwrW4uIjvQknyQ==" saltValue="cG7TienrZyQ4khB0vd/thA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <drawing r:id="rId1"/>
@@ -42618,7 +42784,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="gvJKF3wk8uYCz3RKbvbVaJLm04qngqDY+k/8yxU0fyXkFkJHPDCxykHR/ddSRRLPf4LharI+heIAlHHbnfwbMg==" saltValue="/S4cjHc9kQwDcZK/RPnSoA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="fE6jsW/grMGNWUN8xgIEeDSXCctvcachJlxjKQIYPuo4ml3moQtDuH1UmaXYoieuMTure7yeH4JOYHOhXMBmhw==" saltValue="dgtyLaHujITIhkQyQKbfXg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -42820,7 +42986,7 @@
       <c r="K14" s="114"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="8QjHth+obrfGt5eAyNv7vIH5iRZUgLpyi0CcAP1tTc8fFNQof9cdt1S4mgFtoNMOsk++I3UZNKOyYbCgc32CIA==" saltValue="jFLbYnS6BCNcCPPELLUN5g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="p0+nGqI9vXUTL0+JDiAVSRp6g3UH0Uk/A2V2ukC7UsISNJLKH+4eSk4AFajXmWid1uOuaSQSwwITwzUHpo5csg==" saltValue="WaNhhhuTmpWbLLwe0pzm/Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="193" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -43082,7 +43248,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="s6xzES2f8axhf/yrGubRxoEISafmQDHQxNBhjqt2oqUGlRNG/5WgHwb0BhiE3Nis3w43eB1sl/j+jEmfaTRkkA==" saltValue="5iayaOf+IMQE+Ldndh1cZA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="5z+8hbNB2Kl3+9TAWeUBp90YnIJKZnckbOld2JYTzeZDl/W0FdInGdElHIp9s5zuyDCASC5F+0Vczu6e3LFL3g==" saltValue="uhoKwFSm2YHDkkUxeWX1lQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <phoneticPr fontId="29" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -43342,7 +43508,7 @@
       <c r="E21" s="62"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="BO/OmSUtdMOMFPwNik3LBHDSeW5+dyLKx57nMp/NBqJ1HFFzqAUnWakkxaa44B3acT7qeHSG2qiAdgboWapKiw==" saltValue="3MUqdrgOpRc29TekFiUMDQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Q6ST3K6mUnthLZuGRBKBrsMwKjChLeChU14XV6ZzW6k0n/EIOKvXjbRPU6w9Ky0chOT1NBGBiLZrb1LJOYgcMw==" saltValue="kGRdoOJLYvH5IODh94/ROw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -43401,7 +43567,7 @@
       <c r="D3" s="62"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="hIvP9p2x1EiGYTg9kWmxWC7X2jrOaWyuLFf/dBoqG5rtGP7GlkCdtrzijMSF87SpOhu9Sj8FLsBh2drGG7Mamw==" saltValue="uaE5lqOtG71QJupwPNib0g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ABW6KZsbrQkxT0NLTPw4s0yaCT5Dlbj4V0+473eBvJ2GquHGsodZj2syA+YQajq0VwzbxY8EwUIpT3pn5Nw+BQ==" saltValue="CbeEaBTbOQn3B/WZMl5mag==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/inputs/fr/demo_national_input.xlsx
+++ b/inputs/fr/demo_national_input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr saveExternalLinkValues="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\2025 studies\Nutrition\inputs\fr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modelling projects\Nutrition\inputs\fr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E0D0289-6683-49AC-975F-40F6C6C9AF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B5A8AC4-E494-4138-A916-D1BE9F270C55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="904" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="904" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Données pop de l'année de ref" sheetId="1" r:id="rId1"/>
@@ -3170,7 +3170,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:</t>
         </r>
@@ -3179,7 +3179,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Until clear effect evidence is found, assume no effect</t>
@@ -5532,7 +5532,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:</t>
         </r>
@@ -5541,7 +5541,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Average number of individuals surviving in 5-9 years age group starting with 100,000 births</t>
@@ -5855,7 +5855,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Nick Scott:</t>
         </r>
@@ -5864,7 +5864,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Olofin I, McDonald CM, Ezzati M, et al. Associations of Suboptimal Growth with All-Cause and Cause-Specific Mortality in Children under Five Years: A Pooled Analysis of Ten Prospective Studies. PLOS One 2013; 8(5): e64636. </t>
@@ -5879,7 +5879,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Nick Scott:</t>
         </r>
@@ -5888,7 +5888,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Olofin I, McDonald CM, Ezzati M, et al. Associations of Suboptimal Growth with All-Cause and Cause-Specific Mortality in Children under Five Years: A Pooled Analysis of Ten Prospective Studies. PLOS One 2013; 8(5): e64636</t>
@@ -5903,7 +5903,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Nick Scott:</t>
         </r>
@@ -5912,7 +5912,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Heidkamp R, Guida R, Phillips E, Clermont A. The Lives Saved Tool (LiST) as a Model for Prevention of Anemia in Women of Reproductive Age. J Nutr. 2017;147(11):2156S-2162S</t>
@@ -5927,7 +5927,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Nick Scott:</t>
         </r>
@@ -5936,7 +5936,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 NEOVITA Study Group. Timing of initiation, patterns of breastfeeding, and infant survival: prospective analysis of pooled data from three randomised trials. Lancet Global Health 2016; 4(4): e266-75. </t>
@@ -5951,7 +5951,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Nick Scott:</t>
         </r>
@@ -5960,7 +5960,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 NEOVITA Study Group. Timing of initiation, patterns of breastfeeding, and infant survival: prospective analysis of pooled data from three randomised trials. Lancet Global Health 2016; 4(4): e266-75. </t>
@@ -5975,7 +5975,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Nick Scott:</t>
         </r>
@@ -5984,7 +5984,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 NEOVITA Study Group. Timing of initiation, patterns of breastfeeding, and infant survival: prospective analysis of pooled data from three randomised trials. Lancet Global Health 2016; 4(4): e266-75. </t>
@@ -5999,7 +5999,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Nick Scott:</t>
         </r>
@@ -6008,7 +6008,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011. </t>
@@ -6023,7 +6023,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Nick Scott:</t>
         </r>
@@ -6032,7 +6032,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011. </t>
@@ -6047,7 +6047,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Nick Scott:</t>
         </r>
@@ -6056,7 +6056,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011. </t>
@@ -6071,7 +6071,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Nick Scott:</t>
         </r>
@@ -6080,7 +6080,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011. </t>
@@ -6095,7 +6095,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Nick Scott:</t>
         </r>
@@ -6104,7 +6104,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011. </t>
@@ -6119,7 +6119,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Nick Scott:</t>
         </r>
@@ -6128,7 +6128,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011</t>
@@ -7654,7 +7654,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -7826,21 +7826,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -10853,6 +10841,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Baseline year population inputs"/>
       <sheetName val="Demographic projections"/>
@@ -11676,7 +11667,7 @@
       <c r="A63" s="4"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="H19323VJpR294Mf9pMShcYSVsHwpnyvnvun6RxZfEK9wQeaLVi9xhD9iTqCBZI+H1bOSpz5HbfpXH3e1KzdtSQ==" saltValue="1E9+R9pU6MxzQaphuRbTXA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="bemx8kcV+BCiy04Lwq908cNwFodKA1BLok5k7G+VgfNx/hLCLUZWCjKOtVliiwu+L3YmuAodFVerjdRF2its1Q==" saltValue="KTLTNCashYo9JNKjGmacgA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -12600,7 +12591,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="PfXjQFAwT2j68inwY5COxXGUFlvIkt0RrvFZf9sm8AighH9GZYWLonv+T1LjJHEecMtPwDxNdZXaJZlM5Y1DRw==" saltValue="DA71IZEun9mQsGS6MLEPQA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="DyMxIbUTk59YKdjONNFv8xzpXWklRmt09qLcck//NA1zl2xsXAxR2IMwtXD1maO2IB5axO6iQTAapqyLOXcFhw==" saltValue="j5gX0knrIEStFbNjMJ9HZg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D39">
     <sortCondition ref="A2:A39"/>
   </sortState>
@@ -12767,7 +12758,7 @@
       <c r="C20" s="67"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="PpItXjYvmBe/1PtWnJy2M6fV/UDqVRTrFMe8+a6tC64ax0ZTi979nJNH5Pw+Ak+BhMTf0qsMYcpXDYDXn4LBQg==" saltValue="XsiqtAzrMynWlG65cV+ucQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="EsXwHB+gVa0AbiQU397t2JxDCqnyNHexvipDlnAoIYhRPIUg0PIaLsEs/wvvv30YYG4glRoZt4PPX/gDWb7XZQ==" saltValue="fXU+1SYodvBGg7jrXo30XQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -12862,7 +12853,7 @@
       <c r="A19" s="35"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="OGd94b5K6KrTAlGU8MS6wX1ldqtO6bX/OZ5BHmX1cQWlF3Gu/dcvhO2JpNJNLBGaL4jiWChRUkXcYl/jfZYZkA==" saltValue="LLvmDdC6b5lMTON7595TwQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="z6dYab+7uuMW8CeaYqvwX3SL975x3TJ0lfHsiuklMl1oKpcnrKpujYryqJRKkIrRR2pgare1CpGDT+sempvfXQ==" saltValue="Lha/n+s9x0wgEJLq++UWKg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -12972,7 +12963,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="VRExqdJk2V5qbxeGvi2J/U8HK4aAndcadBnLjGxwhgZzOSoTkoBkoXjGYyZh997cz13ekjvxWIzFwT5VHFyztQ==" saltValue="Eb870y4DVmSTdahpo0cECw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="2UjolHaeUgoVQ1kEEQR0f0Y5nd71RFNMQZ9RLZ92n7aVhgcPhd8VaVDo3BPJkm7Niu5tfm38qZmUWrE1koeB8A==" saltValue="dTMXLu/BJ67a/dwhD/3LDA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -14730,7 +14721,7 @@
       <c r="B40" s="9"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="TsYBt5grrE/Z53+XJPwrrLh9RObNGnYXE2wcnbI1WNduBHGN+oLeBuf4lVYY+6vncduHEU5/VKK9IE3iclw4pA==" saltValue="oVVrfHUHfz6pdGoCg2+t1A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="DMZXiMJyx6eRzBaj7DtXwL/dqNIZi7G59MrKekdQQR/Wx3OUida4eDLfReZuq8fPiJdKq9/MyTUyzNHI3UQT1Q==" saltValue="oZk4uhWEAWi6aiHzlptJcQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B15:O22">
     <sortCondition ref="B15:B22"/>
   </sortState>
@@ -14765,7 +14756,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="dUTdbzI3pfnE5VIeYrRiEcr/wqy82wibF2mH2qyqp4uqH3jjVxgoAHn/dRo6qwN+D1UEtO8Q4tH0nUJbdPwDZA==" saltValue="x3UFXHjhlQjgLgzFmtD7Jg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="vbd/ou1cNTorg+8fUZ+nacPCXWDdB0jIreQHWqhHQMSG2wWSsqxhgFmNiqPd2OpI50AWAHkDlgqDNmV/7dPozA==" saltValue="gxIo6+4sJkytAetjmOuiCA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14965,7 +14956,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ZYXuBo64Eb9twulANpaOUlcZ9691EaL2RzN7taC0Oa0SJSP99gVzPHmN8AeF67yr6WpNpcsUyit7dyscrovKyQ==" saltValue="HBxTvrxRrZEqaVsmoMGaMg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="5NKKv+68I3TYxMe2qAa8ZP6CD+b9HWDju09EGnm4zx+hWCmAc/J9JpAtaO6h9zOsd0QDAuL9mzMNllNq5FRBpA==" saltValue="S2YLj9PNB4RA/iArCE8Cbw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -16774,7 +16765,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="L13TRjgYMEE6dPIiKMY0sfIKsFWpCOQL3DKpwu9knkM9oO8mKNBVCHusvtlt6xYNuOVoKXUT8x+2CngPAbdQXw==" saltValue="hDRQUcr4bRS36GL0eFeFdw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="/zKD2i9+kEpbUZfJSeftZgkP59Z8maBYeIZbpPZ1xlhy5ZPR9g8kZpqZx3NqCE61ltvje3q9ytxbNW+/bvVyaw==" saltValue="yC6TWbcXZE4smSEiviJwrA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -17585,7 +17576,7 @@
       <c r="L39" s="100"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="6OMJjrPsk7Ikl/gFZWFNJppmPQn4mFfWl30DLTU5n1VDK2Sb3lfZE5kX7LD0KWPA0TXWu4CTcdC2NZU1uuIYew==" saltValue="9XrEtUmknDHp+R9G7aJ8YQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="eogy8/tMWXf4AX67zZd2qjjDYUPZ6jtdmnu/SULnZnrZHxTS2eZ0/sgN2Y0L+ARHk8sg97rgjdfPzI5sWaHVbw==" saltValue="la5CrRvTc6KxR203cNXjMA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -17978,7 +17969,7 @@
       <c r="L14" s="100"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="LwrIVExY5MXkYvixLjcDPw+CN6jcti71CfqgoAZVBh20invSCjiWec7B5dFgd5dan721hcQPiDsoKlwCvykJWg==" saltValue="1daP56fs+4x7NW4nvb1tYA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="U0nwtCFMIBbDRH2TRmfJRllKNkStd2bAZDPsFiJCdUAeprdo3fjG5uUfekY/o+CpHzewMTz1BLolpt7BHBr6xQ==" saltValue="2anHVAqt3wORXfQ+morCEg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -19062,7 +19053,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="OKVCOjRTv4EoPhWdRCz15GEaZ+7PWWwSh24ZO+sF7bIodzfzGu8P+PQdZN7kKX6To+JEWA/zuNkoEu9YqfuvnQ==" saltValue="yK9AgF+yZnG+1v7kENy/fw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Yeb9YkHq62q2h4Aao/klBqP3yjfsN1lk7TTXCh4Pu4NXLXtfd9lzwamutaQ5PSOZGHegSUHxjKezviK/l12Wxg==" saltValue="FImp7ygAL9tG5yMuUrRrSQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <conditionalFormatting sqref="B2:I16 B17:C17 E17:I17 B18:I40">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>$A2=""</formula>
@@ -22857,7 +22848,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Wqujlo7njSYldG0Hr9eDtk+0FTgpgV2AsAsTMyaEJlBnADMvNZG1QFoaE1Srhm8q/v45eaXFof6xLgEwIxJWVQ==" saltValue="4tgu4jN6HjmJbKTrqExvEw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="h4TJ09Wr2V8XppjKSvxWpd1h8n08cW2TYCa05V79vE24Vf+tNe6/BY8bjps1Q0G3RQWRXXAtogpTKzZt6sotfg==" saltValue="v0SYcDj6SgGUiEsGdijE9A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="45">
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="B2:B4"/>
@@ -24118,7 +24109,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="mJU+B7YAyorK6h79z6nG1VIDy+cMnlqfNnSpZzxhr+nTwr5Mq4oC1b8cMSoGQSE9VWup7v7P5wLBO0s658ATOQ==" saltValue="aZvO0LzL+h67WHCwNmmy4A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="STay0tbQhpqEW9RTic9KCf5Xikq4AUjrjgjcaf4SDNh6xc2FpcPoBvdyhPVvrJAXJGzM9TwJUsSrfwAavpgafA==" saltValue="9eG2yv8N5haQOcJqRNjs3A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -32251,7 +32242,7 @@
       <c r="I328" s="92"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="iC6hZlgTO7qDeg+i2nPI52P3xOYDcHSGyLmu86heseLE+Q1WuwryH+T8XZfQPT1SExzreO/y7ABqNEKnlwSRYg==" saltValue="h8TahLiP4jfaK3bvymg6sA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="MUFOiRflxELkb9MCVxWUs1Q2GliSjOSlZqmgmtQlDiH+WFEKQjKFNG6MYo0YQAO1Tlp0Pkaq/+yAgweabSD1Uw==" saltValue="8zBk3UfvzIEtVbEt7l+Ppw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -33352,7 +33343,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="FPOv2fA8BGunkz6CuhtJvCWmwu3VvX//eeXCDdMYhVDb7YiOlxEr8m5HMMjp/qC7RLiEuemTFYYGt8CTdkpk2g==" saltValue="ha1hytHWP2mGYg+oYIfixA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="PEohdj4ebJ6ZFLmjVEQeoOpYnpGS7W39uZ78SzlPlCojVvZxGrkm244Izt0zFHRxGDglDEwx32pcx5ky3VEZ0Q==" saltValue="Fe/OwrrrqdRGUK953yOzHQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -34293,7 +34284,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="9Fkq+LIzBPjH9YzdJQmq3FdlpxSPCovCJ9pKFArypE1O4KbZOPQnlVEX1yJsge4nteDyD2E1KrfOr/AvHdu5hQ==" saltValue="rkeNfy9Oa/li4tKQHdGgJA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="GEhesZbxVuCEmdUCseZoUJbfd9oe1c7InbQvFk7J7QhDXIy6vlyGA+oL9K3oX8XjVWCh9d6s/BMNQk/pjelgYA==" saltValue="GgxbhyR/MUOxBbQoxKr/ug==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -37008,7 +36999,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="BIuEQ8aWlCMeLAK8vmZBtwQ3bKri3xZdQFKIPdB7h0MwVs05LjHhubTQCtrE8zgWXaY4NS45XKaS+K4LzLI0Uw==" saltValue="fErcDirD/Dc99ut3lxvAnA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="qCr2z6GaEgn3Y/MIwFdG3hI8rfVY2sUAie04LdkLyIMCiUehPSPdXfUCBjyzNkcp1oWe9DxIIJLRKPAj/CuW6g==" saltValue="hoHDkacnzPxyXr+MTNh+8A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -37299,7 +37290,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ynHJZiciF1URJ9OEcskFHaks7iFbKuQKAYb78z7ljsEwnkh5tPflLpbiIELV1Bb1ua3ZmxpasioneV/GdXL9YA==" saltValue="FRDtz2cPnD8voy5os2HuUQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="5Pbd4mpddAmtBaIDtszrTUUcA4YMhKHJtFSkGE0PeCCBzHWz/h6sipV/Xl6eSHE0jvGHM/j1niXPHvZZqTryjg==" saltValue="Q8roLrRiBrLiFur3xXfIcA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -41159,7 +41150,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="zOkiB1OmAzQuXPtpkcOA7TwcqhDwW9DcMY0wUhOePk1WKjnCO7cT7nbYbNt2eKvusaANDpux9PC+HpGEJfEg8g==" saltValue="nDEDdTkkF3/19yeQzMQ9Ag==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="gG3jizObfIhl4l5heZK/Wt1+Ymn7/0GjHx0eF3jEBp9QgACMwQT0CbawlHByoIdkqw4Fv6IbsSGAETsTSxxmsQ==" saltValue="wKNo8OvDCX+0sCABO/OouQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -41800,7 +41791,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="xYo42p3sTptkGB65EsRaZaHhsqzRq0obOurTg1ZjNDmo6EhU3k+HhegO0FDuK9FkDrZ9bmdI3F0VQTYUEDAzjw==" saltValue="bHB82szahGSRo42fd1JvFA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Ch+MRcvdhme7m2wX2Dd0vXvQS5Tnf7XLYACqxM6PoXzaEs9+Y10Oojh9Fb80A06W6ZgvlEpKhyyvELeKsWwpHA==" saltValue="3RRjK7rQbzFTc//jGPCWZA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -42233,7 +42224,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="CTjgU9tBGPnoUG0vyEvqAecwFw8Tm+MH02x1Zj0Qb/kfC2m/FW0ZJRWGa1HIXxv/Wh90C0o4Vp1nH2H5WQD13g==" saltValue="DSokCl97bjZx4drO9L+aEg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="sgaKwOaanyUrjKRv/Hmc9d3NNJiLtnP9V8uNHtwPJVwje+IvrSj9StBNr6eB+olLH4EYVAgZExoaqXMwJW0mmQ==" saltValue="sKnRwgUg2oC3XCmSD6ocYw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="69" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
@@ -42652,7 +42643,7 @@
       <c r="G17" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="6BjUsVJ+EOC+9NYw54f+/6BZnA4Mv9THgyeFBQy2aSM1BZaN3gfuB+aXeeVULlGrPvIVatciCwrW4uIjvQknyQ==" saltValue="cG7TienrZyQ4khB0vd/thA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Y9I8a+O0gqpoeNcKy8UBC+D6YpYWT7GWkuGqIBeMQfCHeTlraSw9+Os4YLFoa58M2DRruZl0RbRcqzl5z+ftUw==" saltValue="WV4g0x0G4ZWmIFdeMI8yAw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <drawing r:id="rId1"/>
@@ -42784,7 +42775,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="fE6jsW/grMGNWUN8xgIEeDSXCctvcachJlxjKQIYPuo4ml3moQtDuH1UmaXYoieuMTure7yeH4JOYHOhXMBmhw==" saltValue="dgtyLaHujITIhkQyQKbfXg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="EpNhnREECot7OiyJCCBWnBJDgH18ajE29w6z6RHZMTe1/zigf+8TqcMTZ619FrcCY8Yk3489l+yLa6Y2rVz0sw==" saltValue="yn8wfh86Dv1W6uqtTrwtGA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -42986,7 +42977,7 @@
       <c r="K14" s="114"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="p0+nGqI9vXUTL0+JDiAVSRp6g3UH0Uk/A2V2ukC7UsISNJLKH+4eSk4AFajXmWid1uOuaSQSwwITwzUHpo5csg==" saltValue="WaNhhhuTmpWbLLwe0pzm/Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="qFP7cnPO12WazEWQo4Qvgon5rhmyxTEhRGSl9hkWWaEbMODPBQHhofh5wHDQjh4e3ZGHcRdferWwZHcnqwRfIg==" saltValue="4UVn1D6sYbv06m23apVlnw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="193" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -43248,8 +43239,8 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="5z+8hbNB2Kl3+9TAWeUBp90YnIJKZnckbOld2JYTzeZDl/W0FdInGdElHIp9s5zuyDCASC5F+0Vczu6e3LFL3g==" saltValue="uhoKwFSm2YHDkkUxeWX1lQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
-  <phoneticPr fontId="29" type="noConversion"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="TWsN8NyfpnvvqF7p67U7STN0YWnEo2HVIMXoCxFZtMnxizcRjBK6EOK1BY4zpFieO8R/nfckMgHP28WVS4ZInw==" saltValue="r27rGyHR9jE9vy2veVtagA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <phoneticPr fontId="27" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="B12:B13" unlockedFormula="1"/>
@@ -43508,7 +43499,7 @@
       <c r="E21" s="62"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Q6ST3K6mUnthLZuGRBKBrsMwKjChLeChU14XV6ZzW6k0n/EIOKvXjbRPU6w9Ky0chOT1NBGBiLZrb1LJOYgcMw==" saltValue="kGRdoOJLYvH5IODh94/ROw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="TcqnPifnZOyc3T1Jp51RK8zsMCWlZTZcs6C3k4QQPvjbhXET9dz6Uu3Gy0P/kxDOkOgGut2rYaAI/sEf8evuWA==" saltValue="0xmxsO/Hf3dKGXRHpdlaRg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -43567,7 +43558,7 @@
       <c r="D3" s="62"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ABW6KZsbrQkxT0NLTPw4s0yaCT5Dlbj4V0+473eBvJ2GquHGsodZj2syA+YQajq0VwzbxY8EwUIpT3pn5Nw+BQ==" saltValue="CbeEaBTbOQn3B/WZMl5mag==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="nfG3EyDhlh75LpuCSyXgCFmMmT1SVbfIZZxh5yL7lrMmvsXZ5sjjyIKeYVVNn1B3f/Q4nstShKUD/Qa491XRng==" saltValue="g9/fjnr2P6if5gfiTplNzg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>